--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4458814A-B891-48ED-A27A-789434F7ACF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74213E5C-B3D6-8040-B304-78B372E9E821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -196,9 +196,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -216,7 +216,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2761,6 +2761,9 @@
                 <c:pt idx="831">
                   <c:v>46199</c:v>
                 </c:pt>
+                <c:pt idx="832">
+                  <c:v>46206</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4634,6 +4637,9 @@
                   <c:v>2326.67</c:v>
                 </c:pt>
                 <c:pt idx="831">
+                  <c:v>2326.67</c:v>
+                </c:pt>
+                <c:pt idx="832">
                   <c:v>2326.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -5448,9 +5454,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5488,7 +5494,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5594,7 +5600,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5736,7 +5742,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5744,18 +5750,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P833"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P834"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -5803,7 +5809,7 @@
       </c>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>40383</v>
       </c>
@@ -5828,7 +5834,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>40390</v>
       </c>
@@ -5853,7 +5859,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>40397</v>
       </c>
@@ -5871,7 +5877,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>40404</v>
       </c>
@@ -5889,7 +5895,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>40411</v>
       </c>
@@ -5907,7 +5913,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>40418</v>
       </c>
@@ -5925,7 +5931,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>40425</v>
       </c>
@@ -5943,7 +5949,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>40432</v>
       </c>
@@ -5961,7 +5967,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>40439</v>
       </c>
@@ -5979,7 +5985,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>40446</v>
       </c>
@@ -5997,7 +6003,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>40453</v>
       </c>
@@ -6015,7 +6021,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>40460</v>
       </c>
@@ -6033,7 +6039,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>40467</v>
       </c>
@@ -6051,7 +6057,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>40474</v>
       </c>
@@ -6069,7 +6075,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>40481</v>
       </c>
@@ -6087,7 +6093,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>40488</v>
       </c>
@@ -6105,7 +6111,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>40495</v>
       </c>
@@ -6123,7 +6129,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>40502</v>
       </c>
@@ -6141,7 +6147,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>40509</v>
       </c>
@@ -6159,7 +6165,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>40516</v>
       </c>
@@ -6177,7 +6183,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>40523</v>
       </c>
@@ -6195,7 +6201,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>40530</v>
       </c>
@@ -6213,7 +6219,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>40537</v>
       </c>
@@ -6231,7 +6237,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>40544</v>
       </c>
@@ -6249,7 +6255,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>40551</v>
       </c>
@@ -6267,7 +6273,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>40558</v>
       </c>
@@ -6285,7 +6291,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>40565</v>
       </c>
@@ -6303,7 +6309,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>40572</v>
       </c>
@@ -6321,7 +6327,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>40579</v>
       </c>
@@ -6339,7 +6345,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>40586</v>
       </c>
@@ -6357,7 +6363,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>40593</v>
       </c>
@@ -6375,7 +6381,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>40600</v>
       </c>
@@ -6393,7 +6399,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>40607</v>
       </c>
@@ -6411,7 +6417,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>40614</v>
       </c>
@@ -6429,7 +6435,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>40621</v>
       </c>
@@ -6447,7 +6453,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>40628</v>
       </c>
@@ -6465,7 +6471,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>40635</v>
       </c>
@@ -6483,7 +6489,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>40642</v>
       </c>
@@ -6501,7 +6507,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>40649</v>
       </c>
@@ -6519,7 +6525,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40656</v>
       </c>
@@ -6537,7 +6543,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40663</v>
       </c>
@@ -6555,7 +6561,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>40670</v>
       </c>
@@ -6573,7 +6579,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40677</v>
       </c>
@@ -6591,7 +6597,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>40684</v>
       </c>
@@ -6609,7 +6615,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>40691</v>
       </c>
@@ -6627,7 +6633,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>40698</v>
       </c>
@@ -6645,7 +6651,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>40705</v>
       </c>
@@ -6663,7 +6669,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>40712</v>
       </c>
@@ -6681,7 +6687,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>40719</v>
       </c>
@@ -6699,7 +6705,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>40726</v>
       </c>
@@ -6717,7 +6723,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>40733</v>
       </c>
@@ -6735,7 +6741,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>40740</v>
       </c>
@@ -6753,7 +6759,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>40747</v>
       </c>
@@ -6771,7 +6777,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>40754</v>
       </c>
@@ -6789,7 +6795,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>40761</v>
       </c>
@@ -6807,7 +6813,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>40768</v>
       </c>
@@ -6825,7 +6831,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>40775</v>
       </c>
@@ -6843,7 +6849,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>40782</v>
       </c>
@@ -6861,7 +6867,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>40789</v>
       </c>
@@ -6879,7 +6885,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>40796</v>
       </c>
@@ -6897,7 +6903,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>40803</v>
       </c>
@@ -6915,7 +6921,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>40810</v>
       </c>
@@ -6933,7 +6939,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>40817</v>
       </c>
@@ -6951,7 +6957,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>40824</v>
       </c>
@@ -6969,7 +6975,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>40831</v>
       </c>
@@ -6987,7 +6993,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>40838</v>
       </c>
@@ -7012,7 +7018,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>40845</v>
       </c>
@@ -7030,7 +7036,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>40852</v>
       </c>
@@ -7048,7 +7054,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>40859</v>
       </c>
@@ -7066,7 +7072,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>40866</v>
       </c>
@@ -7084,7 +7090,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>40873</v>
       </c>
@@ -7102,7 +7108,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>40880</v>
       </c>
@@ -7120,7 +7126,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>40887</v>
       </c>
@@ -7138,7 +7144,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>40894</v>
       </c>
@@ -7156,7 +7162,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>40901</v>
       </c>
@@ -7174,7 +7180,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>40908</v>
       </c>
@@ -7192,7 +7198,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>40915</v>
       </c>
@@ -7210,7 +7216,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>40922</v>
       </c>
@@ -7228,7 +7234,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>40929</v>
       </c>
@@ -7246,7 +7252,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>40936</v>
       </c>
@@ -7264,7 +7270,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>40942</v>
       </c>
@@ -7282,7 +7288,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>40943</v>
       </c>
@@ -7300,7 +7306,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>40950</v>
       </c>
@@ -7318,7 +7324,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>40957</v>
       </c>
@@ -7336,7 +7342,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>40964</v>
       </c>
@@ -7354,7 +7360,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>40978</v>
       </c>
@@ -7372,7 +7378,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>40985</v>
       </c>
@@ -7390,7 +7396,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>40992</v>
       </c>
@@ -7408,7 +7414,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>40999</v>
       </c>
@@ -7426,7 +7432,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>41006</v>
       </c>
@@ -7444,7 +7450,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>41013</v>
       </c>
@@ -7462,7 +7468,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>41020</v>
       </c>
@@ -7480,7 +7486,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>41027</v>
       </c>
@@ -7498,7 +7504,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>41034</v>
       </c>
@@ -7516,7 +7522,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>41041</v>
       </c>
@@ -7534,7 +7540,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>41048</v>
       </c>
@@ -7552,7 +7558,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>41055</v>
       </c>
@@ -7570,7 +7576,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>41062</v>
       </c>
@@ -7588,7 +7594,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>41069</v>
       </c>
@@ -7606,7 +7612,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>41076</v>
       </c>
@@ -7624,7 +7630,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>41083</v>
       </c>
@@ -7642,7 +7648,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>41090</v>
       </c>
@@ -7660,7 +7666,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>41097</v>
       </c>
@@ -7678,7 +7684,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>41104</v>
       </c>
@@ -7696,7 +7702,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>41111</v>
       </c>
@@ -7714,7 +7720,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>41118</v>
       </c>
@@ -7732,7 +7738,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>41125</v>
       </c>
@@ -7750,7 +7756,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>41132</v>
       </c>
@@ -7768,7 +7774,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>41139</v>
       </c>
@@ -7786,7 +7792,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>41146</v>
       </c>
@@ -7804,7 +7810,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>41153</v>
       </c>
@@ -7822,7 +7828,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>41160</v>
       </c>
@@ -7840,7 +7846,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>41167</v>
       </c>
@@ -7858,7 +7864,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>41174</v>
       </c>
@@ -7876,7 +7882,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>41181</v>
       </c>
@@ -7894,7 +7900,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>41188</v>
       </c>
@@ -7912,7 +7918,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>41195</v>
       </c>
@@ -7930,7 +7936,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>41202</v>
       </c>
@@ -7948,7 +7954,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>41209</v>
       </c>
@@ -7966,7 +7972,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>41216</v>
       </c>
@@ -7984,7 +7990,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>41223</v>
       </c>
@@ -8002,7 +8008,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>41230</v>
       </c>
@@ -8020,7 +8026,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>41237</v>
       </c>
@@ -8038,7 +8044,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>41244</v>
       </c>
@@ -8056,7 +8062,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>41251</v>
       </c>
@@ -8074,7 +8080,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>41258</v>
       </c>
@@ -8092,7 +8098,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>41265</v>
       </c>
@@ -8110,7 +8116,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>41272</v>
       </c>
@@ -8128,7 +8134,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>41279</v>
       </c>
@@ -8146,7 +8152,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>41286</v>
       </c>
@@ -8171,7 +8177,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>41293</v>
       </c>
@@ -8189,7 +8195,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>41300</v>
       </c>
@@ -8207,7 +8213,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>41307</v>
       </c>
@@ -8225,7 +8231,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>41314</v>
       </c>
@@ -8243,7 +8249,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>41321</v>
       </c>
@@ -8261,7 +8267,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>41328</v>
       </c>
@@ -8279,7 +8285,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>41335</v>
       </c>
@@ -8297,7 +8303,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>41342</v>
       </c>
@@ -8315,7 +8321,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>41349</v>
       </c>
@@ -8333,7 +8339,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>41356</v>
       </c>
@@ -8351,7 +8357,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>41363</v>
       </c>
@@ -8369,7 +8375,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>41370</v>
       </c>
@@ -8387,7 +8393,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>41377</v>
       </c>
@@ -8405,7 +8411,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>41384</v>
       </c>
@@ -8423,7 +8429,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>41391</v>
       </c>
@@ -8441,7 +8447,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>41398</v>
       </c>
@@ -8459,7 +8465,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41405</v>
       </c>
@@ -8477,7 +8483,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>41412</v>
       </c>
@@ -8495,7 +8501,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>41419</v>
       </c>
@@ -8513,7 +8519,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>41426</v>
       </c>
@@ -8531,7 +8537,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>41433</v>
       </c>
@@ -8549,7 +8555,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>41440</v>
       </c>
@@ -8567,7 +8573,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>41447</v>
       </c>
@@ -8585,7 +8591,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>41454</v>
       </c>
@@ -8603,7 +8609,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>41461</v>
       </c>
@@ -8621,7 +8627,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>41468</v>
       </c>
@@ -8639,7 +8645,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>41475</v>
       </c>
@@ -8657,7 +8663,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>41482</v>
       </c>
@@ -8675,7 +8681,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>41489</v>
       </c>
@@ -8693,7 +8699,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>41496</v>
       </c>
@@ -8711,7 +8717,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>41503</v>
       </c>
@@ -8729,7 +8735,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>41510</v>
       </c>
@@ -8747,7 +8753,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>41517</v>
       </c>
@@ -8765,7 +8771,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>41524</v>
       </c>
@@ -8783,7 +8789,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>41531</v>
       </c>
@@ -8801,7 +8807,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>41538</v>
       </c>
@@ -8819,7 +8825,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>41545</v>
       </c>
@@ -8837,7 +8843,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>41552</v>
       </c>
@@ -8855,7 +8861,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>41559</v>
       </c>
@@ -8873,7 +8879,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>41566</v>
       </c>
@@ -8891,7 +8897,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>41573</v>
       </c>
@@ -8909,7 +8915,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>41580</v>
       </c>
@@ -8927,7 +8933,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>41587</v>
       </c>
@@ -8945,7 +8951,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>41594</v>
       </c>
@@ -8963,7 +8969,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>41601</v>
       </c>
@@ -8981,7 +8987,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>41608</v>
       </c>
@@ -8999,7 +9005,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>41615</v>
       </c>
@@ -9017,7 +9023,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>41622</v>
       </c>
@@ -9035,7 +9041,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>41629</v>
       </c>
@@ -9053,7 +9059,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>41636</v>
       </c>
@@ -9071,7 +9077,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>41643</v>
       </c>
@@ -9089,7 +9095,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>41650</v>
       </c>
@@ -9107,7 +9113,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>41657</v>
       </c>
@@ -9125,7 +9131,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>41664</v>
       </c>
@@ -9143,7 +9149,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>41671</v>
       </c>
@@ -9161,7 +9167,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>41678</v>
       </c>
@@ -9179,7 +9185,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>41685</v>
       </c>
@@ -9197,7 +9203,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>41692</v>
       </c>
@@ -9215,7 +9221,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>41699</v>
       </c>
@@ -9233,7 +9239,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>41706</v>
       </c>
@@ -9251,7 +9257,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>41713</v>
       </c>
@@ -9269,7 +9275,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>41720</v>
       </c>
@@ -9287,7 +9293,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>41727</v>
       </c>
@@ -9305,7 +9311,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>41734</v>
       </c>
@@ -9330,7 +9336,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>41741</v>
       </c>
@@ -9348,7 +9354,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>41748</v>
       </c>
@@ -9366,7 +9372,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>41755</v>
       </c>
@@ -9384,7 +9390,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>41762</v>
       </c>
@@ -9402,7 +9408,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>41769</v>
       </c>
@@ -9420,7 +9426,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>41776</v>
       </c>
@@ -9438,7 +9444,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>41783</v>
       </c>
@@ -9456,7 +9462,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>41790</v>
       </c>
@@ -9474,7 +9480,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>41797</v>
       </c>
@@ -9492,7 +9498,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>41804</v>
       </c>
@@ -9510,7 +9516,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>41811</v>
       </c>
@@ -9528,7 +9534,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>41818</v>
       </c>
@@ -9546,7 +9552,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>41825</v>
       </c>
@@ -9564,7 +9570,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>41832</v>
       </c>
@@ -9582,7 +9588,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>41839</v>
       </c>
@@ -9600,7 +9606,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>41846</v>
       </c>
@@ -9618,7 +9624,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>41853</v>
       </c>
@@ -9636,7 +9642,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>41860</v>
       </c>
@@ -9654,7 +9660,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>41867</v>
       </c>
@@ -9672,7 +9678,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>41874</v>
       </c>
@@ -9690,7 +9696,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>41881</v>
       </c>
@@ -9708,7 +9714,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>41888</v>
       </c>
@@ -9726,7 +9732,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>41895</v>
       </c>
@@ -9744,7 +9750,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>41902</v>
       </c>
@@ -9762,7 +9768,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>41909</v>
       </c>
@@ -9780,7 +9786,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>41916</v>
       </c>
@@ -9798,7 +9804,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>41923</v>
       </c>
@@ -9816,7 +9822,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>41930</v>
       </c>
@@ -9834,7 +9840,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>41937</v>
       </c>
@@ -9852,7 +9858,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>41944</v>
       </c>
@@ -9870,7 +9876,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>41951</v>
       </c>
@@ -9888,7 +9894,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>41958</v>
       </c>
@@ -9906,7 +9912,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>41965</v>
       </c>
@@ -9924,7 +9930,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>41972</v>
       </c>
@@ -9942,7 +9948,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>41979</v>
       </c>
@@ -9960,7 +9966,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>41986</v>
       </c>
@@ -9978,7 +9984,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>41993</v>
       </c>
@@ -9996,7 +10002,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>42000</v>
       </c>
@@ -10014,7 +10020,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>42007</v>
       </c>
@@ -10032,7 +10038,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>42014</v>
       </c>
@@ -10050,7 +10056,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>42021</v>
       </c>
@@ -10068,7 +10074,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>42028</v>
       </c>
@@ -10086,7 +10092,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>42035</v>
       </c>
@@ -10104,7 +10110,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>42042</v>
       </c>
@@ -10122,7 +10128,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>42049</v>
       </c>
@@ -10140,7 +10146,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>42056</v>
       </c>
@@ -10158,7 +10164,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>42063</v>
       </c>
@@ -10176,7 +10182,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>42070</v>
       </c>
@@ -10194,7 +10200,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>42077</v>
       </c>
@@ -10212,7 +10218,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>42084</v>
       </c>
@@ -10230,7 +10236,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>42091</v>
       </c>
@@ -10248,7 +10254,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>42098</v>
       </c>
@@ -10266,7 +10272,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>42105</v>
       </c>
@@ -10284,7 +10290,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>42112</v>
       </c>
@@ -10302,7 +10308,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>42119</v>
       </c>
@@ -10320,7 +10326,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>42126</v>
       </c>
@@ -10338,7 +10344,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>42133</v>
       </c>
@@ -10356,7 +10362,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42140</v>
       </c>
@@ -10374,7 +10380,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>42147</v>
       </c>
@@ -10392,7 +10398,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>42154</v>
       </c>
@@ -10410,7 +10416,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>42161</v>
       </c>
@@ -10428,7 +10434,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>42168</v>
       </c>
@@ -10446,7 +10452,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>42175</v>
       </c>
@@ -10464,7 +10470,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>42182</v>
       </c>
@@ -10489,7 +10495,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>42189</v>
       </c>
@@ -10507,7 +10513,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>42196</v>
       </c>
@@ -10525,7 +10531,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>42203</v>
       </c>
@@ -10543,7 +10549,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>42210</v>
       </c>
@@ -10561,7 +10567,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>42217</v>
       </c>
@@ -10579,7 +10585,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>42224</v>
       </c>
@@ -10597,7 +10603,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>42231</v>
       </c>
@@ -10615,7 +10621,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>42238</v>
       </c>
@@ -10633,7 +10639,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>42245</v>
       </c>
@@ -10651,7 +10657,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>42252</v>
       </c>
@@ -10669,7 +10675,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>42259</v>
       </c>
@@ -10687,7 +10693,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>42266</v>
       </c>
@@ -10705,7 +10711,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>42273</v>
       </c>
@@ -10723,7 +10729,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>42280</v>
       </c>
@@ -10741,7 +10747,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>42287</v>
       </c>
@@ -10759,7 +10765,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>42294</v>
       </c>
@@ -10777,7 +10783,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>42301</v>
       </c>
@@ -10795,7 +10801,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>42308</v>
       </c>
@@ -10813,7 +10819,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>42315</v>
       </c>
@@ -10831,7 +10837,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>42322</v>
       </c>
@@ -10849,7 +10855,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>42329</v>
       </c>
@@ -10867,7 +10873,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>42336</v>
       </c>
@@ -10885,7 +10891,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>42343</v>
       </c>
@@ -10903,7 +10909,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>42350</v>
       </c>
@@ -10921,7 +10927,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>42357</v>
       </c>
@@ -10939,7 +10945,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>42364</v>
       </c>
@@ -10957,7 +10963,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>42371</v>
       </c>
@@ -10975,7 +10981,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>42378</v>
       </c>
@@ -10993,7 +10999,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>42385</v>
       </c>
@@ -11011,7 +11017,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>42392</v>
       </c>
@@ -11029,7 +11035,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>42399</v>
       </c>
@@ -11047,7 +11053,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>42406</v>
       </c>
@@ -11065,7 +11071,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>42413</v>
       </c>
@@ -11083,7 +11089,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>42420</v>
       </c>
@@ -11101,7 +11107,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>42427</v>
       </c>
@@ -11119,7 +11125,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>42434</v>
       </c>
@@ -11137,7 +11143,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>42441</v>
       </c>
@@ -11155,7 +11161,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>42448</v>
       </c>
@@ -11173,7 +11179,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>42455</v>
       </c>
@@ -11191,7 +11197,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>42462</v>
       </c>
@@ -11209,7 +11215,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>42469</v>
       </c>
@@ -11227,7 +11233,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>42476</v>
       </c>
@@ -11245,7 +11251,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>42483</v>
       </c>
@@ -11263,7 +11269,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>42490</v>
       </c>
@@ -11281,7 +11287,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>42497</v>
       </c>
@@ -11299,7 +11305,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>42504</v>
       </c>
@@ -11317,7 +11323,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>42511</v>
       </c>
@@ -11335,7 +11341,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>42518</v>
       </c>
@@ -11353,7 +11359,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>42525</v>
       </c>
@@ -11371,7 +11377,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>42532</v>
       </c>
@@ -11389,7 +11395,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>42539</v>
       </c>
@@ -11407,7 +11413,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>42546</v>
       </c>
@@ -11425,7 +11431,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>42553</v>
       </c>
@@ -11443,7 +11449,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>42560</v>
       </c>
@@ -11461,7 +11467,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>42567</v>
       </c>
@@ -11479,7 +11485,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>42574</v>
       </c>
@@ -11497,7 +11503,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>42581</v>
       </c>
@@ -11515,7 +11521,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>42588</v>
       </c>
@@ -11533,7 +11539,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>42595</v>
       </c>
@@ -11551,7 +11557,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>42602</v>
       </c>
@@ -11569,7 +11575,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>42609</v>
       </c>
@@ -11587,7 +11593,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>42616</v>
       </c>
@@ -11605,7 +11611,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>42623</v>
       </c>
@@ -11623,7 +11629,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>42630</v>
       </c>
@@ -11648,7 +11654,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>42637</v>
       </c>
@@ -11666,7 +11672,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>42644</v>
       </c>
@@ -11684,7 +11690,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>42651</v>
       </c>
@@ -11702,7 +11708,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>42658</v>
       </c>
@@ -11720,7 +11726,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>42665</v>
       </c>
@@ -11738,7 +11744,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>42672</v>
       </c>
@@ -11756,7 +11762,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>42679</v>
       </c>
@@ -11774,7 +11780,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>42686</v>
       </c>
@@ -11792,7 +11798,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>42693</v>
       </c>
@@ -11810,7 +11816,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>42700</v>
       </c>
@@ -11828,7 +11834,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>42707</v>
       </c>
@@ -11846,7 +11852,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>42714</v>
       </c>
@@ -11864,7 +11870,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>42721</v>
       </c>
@@ -11882,7 +11888,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>42728</v>
       </c>
@@ -11900,7 +11906,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>42735</v>
       </c>
@@ -11918,7 +11924,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>42742</v>
       </c>
@@ -11936,7 +11942,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>42749</v>
       </c>
@@ -11954,7 +11960,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>42756</v>
       </c>
@@ -11972,7 +11978,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>42763</v>
       </c>
@@ -11990,7 +11996,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>42770</v>
       </c>
@@ -12008,7 +12014,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>42777</v>
       </c>
@@ -12026,7 +12032,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>42784</v>
       </c>
@@ -12044,7 +12050,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>42791</v>
       </c>
@@ -12062,7 +12068,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>42798</v>
       </c>
@@ -12080,7 +12086,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>42805</v>
       </c>
@@ -12098,7 +12104,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>42812</v>
       </c>
@@ -12116,7 +12122,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>42819</v>
       </c>
@@ -12134,7 +12140,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>42826</v>
       </c>
@@ -12152,7 +12158,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>42833</v>
       </c>
@@ -12170,7 +12176,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>42840</v>
       </c>
@@ -12188,7 +12194,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>42847</v>
       </c>
@@ -12206,7 +12212,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>42854</v>
       </c>
@@ -12224,7 +12230,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>42861</v>
       </c>
@@ -12242,7 +12248,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42868</v>
       </c>
@@ -12260,7 +12266,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>42875</v>
       </c>
@@ -12278,7 +12284,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>42882</v>
       </c>
@@ -12296,7 +12302,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>42889</v>
       </c>
@@ -12314,7 +12320,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>42896</v>
       </c>
@@ -12332,7 +12338,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>42903</v>
       </c>
@@ -12350,7 +12356,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>42910</v>
       </c>
@@ -12368,7 +12374,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>42917</v>
       </c>
@@ -12386,7 +12392,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>42924</v>
       </c>
@@ -12404,7 +12410,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>42931</v>
       </c>
@@ -12422,7 +12428,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>42938</v>
       </c>
@@ -12440,7 +12446,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>42945</v>
       </c>
@@ -12458,7 +12464,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>42952</v>
       </c>
@@ -12476,7 +12482,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>42959</v>
       </c>
@@ -12494,7 +12500,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>42966</v>
       </c>
@@ -12512,7 +12518,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>42973</v>
       </c>
@@ -12530,7 +12536,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>42980</v>
       </c>
@@ -12548,7 +12554,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>42987</v>
       </c>
@@ -12566,7 +12572,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>42994</v>
       </c>
@@ -12584,7 +12590,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>43001</v>
       </c>
@@ -12602,7 +12608,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>43008</v>
       </c>
@@ -12620,7 +12626,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>43015</v>
       </c>
@@ -12638,7 +12644,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>43022</v>
       </c>
@@ -12656,7 +12662,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>43029</v>
       </c>
@@ -12674,7 +12680,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>43036</v>
       </c>
@@ -12692,7 +12698,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>43043</v>
       </c>
@@ -12710,7 +12716,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>43050</v>
       </c>
@@ -12728,7 +12734,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>43057</v>
       </c>
@@ -12746,7 +12752,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>43064</v>
       </c>
@@ -12764,7 +12770,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>43071</v>
       </c>
@@ -12782,7 +12788,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>43078</v>
       </c>
@@ -12807,7 +12813,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>43085</v>
       </c>
@@ -12825,7 +12831,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>43092</v>
       </c>
@@ -12843,7 +12849,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>43099</v>
       </c>
@@ -12861,7 +12867,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>43106</v>
       </c>
@@ -12879,7 +12885,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>43113</v>
       </c>
@@ -12897,7 +12903,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>43120</v>
       </c>
@@ -12915,7 +12921,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>43127</v>
       </c>
@@ -12933,7 +12939,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>43134</v>
       </c>
@@ -12951,7 +12957,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>43141</v>
       </c>
@@ -12969,7 +12975,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>43148</v>
       </c>
@@ -12987,7 +12993,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>43155</v>
       </c>
@@ -13005,7 +13011,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>43162</v>
       </c>
@@ -13023,7 +13029,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>43169</v>
       </c>
@@ -13041,7 +13047,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>43176</v>
       </c>
@@ -13059,7 +13065,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>43183</v>
       </c>
@@ -13077,7 +13083,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>43190</v>
       </c>
@@ -13095,7 +13101,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>43197</v>
       </c>
@@ -13113,7 +13119,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>43204</v>
       </c>
@@ -13131,7 +13137,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>43211</v>
       </c>
@@ -13149,7 +13155,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>43218</v>
       </c>
@@ -13167,7 +13173,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>43225</v>
       </c>
@@ -13185,7 +13191,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>43232</v>
       </c>
@@ -13203,7 +13209,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>43239</v>
       </c>
@@ -13221,7 +13227,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>43245</v>
       </c>
@@ -13239,7 +13245,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>43252</v>
       </c>
@@ -13257,7 +13263,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>43259</v>
       </c>
@@ -13275,7 +13281,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>43266</v>
       </c>
@@ -13293,7 +13299,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>43273</v>
       </c>
@@ -13311,7 +13317,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>43280</v>
       </c>
@@ -13329,7 +13335,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>43287</v>
       </c>
@@ -13347,7 +13353,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>43294</v>
       </c>
@@ -13365,7 +13371,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>43301</v>
       </c>
@@ -13383,7 +13389,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>43308</v>
       </c>
@@ -13401,7 +13407,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>43315</v>
       </c>
@@ -13419,7 +13425,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>43322</v>
       </c>
@@ -13437,7 +13443,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>43329</v>
       </c>
@@ -13455,7 +13461,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>43336</v>
       </c>
@@ -13473,7 +13479,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>43343</v>
       </c>
@@ -13491,7 +13497,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>43350</v>
       </c>
@@ -13509,7 +13515,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>43357</v>
       </c>
@@ -13527,7 +13533,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>43364</v>
       </c>
@@ -13545,7 +13551,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>43371</v>
       </c>
@@ -13563,7 +13569,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>43378</v>
       </c>
@@ -13581,7 +13587,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
         <v>43385</v>
       </c>
@@ -13599,7 +13605,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
         <v>43392</v>
       </c>
@@ -13617,7 +13623,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>43399</v>
       </c>
@@ -13635,7 +13641,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
         <v>43406</v>
       </c>
@@ -13653,7 +13659,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
         <v>43413</v>
       </c>
@@ -13671,7 +13677,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
         <v>43420</v>
       </c>
@@ -13689,7 +13695,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
         <v>43427</v>
       </c>
@@ -13707,7 +13713,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
         <v>43434</v>
       </c>
@@ -13725,7 +13731,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
         <v>43441</v>
       </c>
@@ -13743,7 +13749,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>43448</v>
       </c>
@@ -13761,7 +13767,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>43455</v>
       </c>
@@ -13779,7 +13785,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>43462</v>
       </c>
@@ -13797,7 +13803,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>43469</v>
       </c>
@@ -13815,7 +13821,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>43476</v>
       </c>
@@ -13833,7 +13839,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>43483</v>
       </c>
@@ -13851,7 +13857,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>43490</v>
       </c>
@@ -13869,7 +13875,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>43497</v>
       </c>
@@ -13887,7 +13893,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
         <v>43504</v>
       </c>
@@ -13905,7 +13911,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>43511</v>
       </c>
@@ -13923,7 +13929,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>43518</v>
       </c>
@@ -13941,7 +13947,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>43525</v>
       </c>
@@ -13966,7 +13972,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>43532</v>
       </c>
@@ -13984,7 +13990,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>43539</v>
       </c>
@@ -14002,7 +14008,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>43546</v>
       </c>
@@ -14020,7 +14026,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>43553</v>
       </c>
@@ -14038,7 +14044,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>43560</v>
       </c>
@@ -14056,7 +14062,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
         <v>43567</v>
       </c>
@@ -14074,7 +14080,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
         <v>43574</v>
       </c>
@@ -14092,7 +14098,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
         <v>43581</v>
       </c>
@@ -14110,7 +14116,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>43588</v>
       </c>
@@ -14128,7 +14134,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>43595</v>
       </c>
@@ -14146,7 +14152,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>43602</v>
       </c>
@@ -14164,7 +14170,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>43609</v>
       </c>
@@ -14182,7 +14188,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
         <v>43616</v>
       </c>
@@ -14200,7 +14206,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
         <v>43623</v>
       </c>
@@ -14218,7 +14224,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
         <v>43630</v>
       </c>
@@ -14236,7 +14242,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
         <v>43637</v>
       </c>
@@ -14254,7 +14260,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
         <v>43644</v>
       </c>
@@ -14272,7 +14278,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
         <v>43651</v>
       </c>
@@ -14290,7 +14296,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
         <v>43658</v>
       </c>
@@ -14308,7 +14314,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A471" s="1">
         <v>43665</v>
       </c>
@@ -14326,7 +14332,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A472" s="1">
         <v>43672</v>
       </c>
@@ -14344,7 +14350,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A473" s="1">
         <v>43679</v>
       </c>
@@ -14362,7 +14368,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A474" s="1">
         <v>43686</v>
       </c>
@@ -14380,7 +14386,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A475" s="1">
         <v>43693</v>
       </c>
@@ -14398,7 +14404,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A476" s="1">
         <v>43700</v>
       </c>
@@ -14416,7 +14422,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
         <v>43707</v>
       </c>
@@ -14434,7 +14440,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
         <v>43714</v>
       </c>
@@ -14452,7 +14458,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>43721</v>
       </c>
@@ -14470,7 +14476,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>43728</v>
       </c>
@@ -14488,7 +14494,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>43735</v>
       </c>
@@ -14506,7 +14512,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>43742</v>
       </c>
@@ -14524,7 +14530,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>43749</v>
       </c>
@@ -14542,7 +14548,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>43756</v>
       </c>
@@ -14560,7 +14566,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
         <v>43763</v>
       </c>
@@ -14578,7 +14584,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
         <v>43770</v>
       </c>
@@ -14596,7 +14602,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
         <v>43777</v>
       </c>
@@ -14614,7 +14620,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
         <v>43784</v>
       </c>
@@ -14632,7 +14638,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
         <v>43791</v>
       </c>
@@ -14650,7 +14656,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
         <v>43798</v>
       </c>
@@ -14668,7 +14674,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
         <v>43805</v>
       </c>
@@ -14686,7 +14692,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
         <v>43812</v>
       </c>
@@ -14704,7 +14710,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
         <v>43819</v>
       </c>
@@ -14722,7 +14728,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
         <v>43826</v>
       </c>
@@ -14740,7 +14746,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
         <v>43833</v>
       </c>
@@ -14758,7 +14764,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
         <v>43840</v>
       </c>
@@ -14776,7 +14782,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
         <v>43847</v>
       </c>
@@ -14794,7 +14800,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
         <v>43854</v>
       </c>
@@ -14812,7 +14818,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
         <v>43861</v>
       </c>
@@ -14830,7 +14836,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
         <v>43868</v>
       </c>
@@ -14848,7 +14854,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
         <v>43875</v>
       </c>
@@ -14866,7 +14872,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
         <v>43882</v>
       </c>
@@ -14884,7 +14890,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>43889</v>
       </c>
@@ -14902,7 +14908,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>43896</v>
       </c>
@@ -14920,7 +14926,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>43903</v>
       </c>
@@ -14938,7 +14944,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>43910</v>
       </c>
@@ -14956,7 +14962,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>43917</v>
       </c>
@@ -14974,7 +14980,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>43924</v>
       </c>
@@ -14992,7 +14998,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>43931</v>
       </c>
@@ -15010,7 +15016,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>43938</v>
       </c>
@@ -15028,7 +15034,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>43945</v>
       </c>
@@ -15046,7 +15052,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
         <v>43952</v>
       </c>
@@ -15064,7 +15070,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
         <v>43959</v>
       </c>
@@ -15082,7 +15088,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
         <v>43966</v>
       </c>
@@ -15100,7 +15106,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
         <v>43973</v>
       </c>
@@ -15125,7 +15131,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
         <v>43980</v>
       </c>
@@ -15143,7 +15149,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
         <v>43987</v>
       </c>
@@ -15161,7 +15167,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
         <v>43994</v>
       </c>
@@ -15179,7 +15185,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
         <v>44001</v>
       </c>
@@ -15197,7 +15203,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
         <v>44008</v>
       </c>
@@ -15215,7 +15221,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
         <v>44015</v>
       </c>
@@ -15233,7 +15239,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
         <v>44022</v>
       </c>
@@ -15251,7 +15257,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
         <v>44029</v>
       </c>
@@ -15269,7 +15275,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
         <v>44036</v>
       </c>
@@ -15287,7 +15293,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
         <v>44043</v>
       </c>
@@ -15305,7 +15311,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
         <v>44050</v>
       </c>
@@ -15323,7 +15329,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
         <v>44057</v>
       </c>
@@ -15341,7 +15347,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
         <v>44064</v>
       </c>
@@ -15359,7 +15365,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
         <v>44071</v>
       </c>
@@ -15377,7 +15383,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
         <v>44078</v>
       </c>
@@ -15395,7 +15401,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
         <v>44085</v>
       </c>
@@ -15413,7 +15419,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
         <v>44092</v>
       </c>
@@ -15431,7 +15437,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
         <v>44099</v>
       </c>
@@ -15449,7 +15455,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
         <v>44106</v>
       </c>
@@ -15467,7 +15473,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
         <v>44113</v>
       </c>
@@ -15485,7 +15491,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
         <v>44120</v>
       </c>
@@ -15503,7 +15509,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
         <v>44127</v>
       </c>
@@ -15521,7 +15527,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
         <v>44134</v>
       </c>
@@ -15539,7 +15545,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
         <v>44141</v>
       </c>
@@ -15557,7 +15563,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
         <v>44148</v>
       </c>
@@ -15575,7 +15581,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
         <v>44155</v>
       </c>
@@ -15593,7 +15599,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
         <v>44162</v>
       </c>
@@ -15611,7 +15617,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
         <v>44169</v>
       </c>
@@ -15629,7 +15635,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
         <v>44176</v>
       </c>
@@ -15647,7 +15653,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>44183</v>
       </c>
@@ -15665,7 +15671,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>44190</v>
       </c>
@@ -15683,7 +15689,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>44197</v>
       </c>
@@ -15701,7 +15707,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>44204</v>
       </c>
@@ -15719,7 +15725,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>44211</v>
       </c>
@@ -15737,7 +15743,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>44218</v>
       </c>
@@ -15755,7 +15761,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>44225</v>
       </c>
@@ -15773,7 +15779,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>44232</v>
       </c>
@@ -15791,7 +15797,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
         <v>44239</v>
       </c>
@@ -15809,7 +15815,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
         <v>44246</v>
       </c>
@@ -15827,7 +15833,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
         <v>44253</v>
       </c>
@@ -15845,7 +15851,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
         <v>44260</v>
       </c>
@@ -15863,7 +15869,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
         <v>44267</v>
       </c>
@@ -15881,7 +15887,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
         <v>44274</v>
       </c>
@@ -15899,7 +15905,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
         <v>44281</v>
       </c>
@@ -15917,7 +15923,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
         <v>44288</v>
       </c>
@@ -15935,7 +15941,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
         <v>44295</v>
       </c>
@@ -15953,7 +15959,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
         <v>44302</v>
       </c>
@@ -15971,7 +15977,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
         <v>44309</v>
       </c>
@@ -15989,7 +15995,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
         <v>44316</v>
       </c>
@@ -16007,7 +16013,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
         <v>44323</v>
       </c>
@@ -16025,7 +16031,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
         <v>44330</v>
       </c>
@@ -16043,7 +16049,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
         <v>44337</v>
       </c>
@@ -16061,7 +16067,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
         <v>44344</v>
       </c>
@@ -16079,7 +16085,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
         <v>44351</v>
       </c>
@@ -16097,7 +16103,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
         <v>44358</v>
       </c>
@@ -16115,7 +16121,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
         <v>44365</v>
       </c>
@@ -16133,7 +16139,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
         <v>44372</v>
       </c>
@@ -16151,7 +16157,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
         <v>44379</v>
       </c>
@@ -16169,7 +16175,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
         <v>44386</v>
       </c>
@@ -16187,7 +16193,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
         <v>44393</v>
       </c>
@@ -16205,7 +16211,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
         <v>44400</v>
       </c>
@@ -16223,7 +16229,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
         <v>44407</v>
       </c>
@@ -16241,7 +16247,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
         <v>44414</v>
       </c>
@@ -16259,7 +16265,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
         <v>44421</v>
       </c>
@@ -16284,7 +16290,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
         <v>44428</v>
       </c>
@@ -16302,7 +16308,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
         <v>44435</v>
       </c>
@@ -16320,7 +16326,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
         <v>44442</v>
       </c>
@@ -16338,7 +16344,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
         <v>44449</v>
       </c>
@@ -16356,7 +16362,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A584" s="1">
         <v>44456</v>
       </c>
@@ -16374,7 +16380,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A585" s="1">
         <v>44463</v>
       </c>
@@ -16392,7 +16398,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A586" s="1">
         <v>44470</v>
       </c>
@@ -16410,7 +16416,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A587" s="1">
         <v>44477</v>
       </c>
@@ -16428,7 +16434,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A588" s="1">
         <v>44484</v>
       </c>
@@ -16446,7 +16452,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A589" s="1">
         <v>44491</v>
       </c>
@@ -16464,7 +16470,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A590" s="1">
         <v>44498</v>
       </c>
@@ -16482,7 +16488,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A591" s="1">
         <v>44505</v>
       </c>
@@ -16500,7 +16506,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A592" s="1">
         <v>44512</v>
       </c>
@@ -16518,7 +16524,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A593" s="1">
         <v>44519</v>
       </c>
@@ -16533,7 +16539,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A594" s="1">
         <v>44526</v>
       </c>
@@ -16548,7 +16554,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A595" s="1">
         <v>44533</v>
       </c>
@@ -16563,7 +16569,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A596" s="1">
         <v>44540</v>
       </c>
@@ -16578,7 +16584,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A597" s="1">
         <v>44547</v>
       </c>
@@ -16593,7 +16599,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A598" s="1">
         <v>44554</v>
       </c>
@@ -16608,7 +16614,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A599" s="1">
         <v>44561</v>
       </c>
@@ -16623,7 +16629,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A600" s="1">
         <v>44568</v>
       </c>
@@ -16638,7 +16644,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A601" s="1">
         <v>44575</v>
       </c>
@@ -16653,7 +16659,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A602" s="1">
         <v>44582</v>
       </c>
@@ -16668,7 +16674,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A603" s="1">
         <v>44589</v>
       </c>
@@ -16683,7 +16689,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A604" s="1">
         <v>44596</v>
       </c>
@@ -16698,7 +16704,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A605" s="1">
         <v>44603</v>
       </c>
@@ -16713,7 +16719,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A606" s="1">
         <v>44610</v>
       </c>
@@ -16728,7 +16734,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A607" s="1">
         <v>44617</v>
       </c>
@@ -16743,7 +16749,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A608" s="1">
         <v>44624</v>
       </c>
@@ -16758,7 +16764,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A609" s="1">
         <v>44631</v>
       </c>
@@ -16773,7 +16779,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A610" s="1">
         <v>44638</v>
       </c>
@@ -16788,7 +16794,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A611" s="1">
         <v>44645</v>
       </c>
@@ -16803,7 +16809,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A612" s="1">
         <v>44652</v>
       </c>
@@ -16818,7 +16824,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A613" s="1">
         <v>44659</v>
       </c>
@@ -16833,7 +16839,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A614" s="1">
         <v>44666</v>
       </c>
@@ -16848,7 +16854,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A615" s="1">
         <v>44673</v>
       </c>
@@ -16863,7 +16869,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A616" s="1">
         <v>44680</v>
       </c>
@@ -16878,7 +16884,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A617" s="1">
         <v>44687</v>
       </c>
@@ -16893,7 +16899,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A618" s="1">
         <v>44694</v>
       </c>
@@ -16908,7 +16914,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A619" s="1">
         <v>44701</v>
       </c>
@@ -16923,7 +16929,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A620" s="1">
         <v>44708</v>
       </c>
@@ -16938,7 +16944,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A621" s="1">
         <v>44715</v>
       </c>
@@ -16953,7 +16959,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A622" s="1">
         <v>44722</v>
       </c>
@@ -16968,7 +16974,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A623" s="1">
         <v>44729</v>
       </c>
@@ -16983,7 +16989,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A624" s="1">
         <v>44736</v>
       </c>
@@ -16998,7 +17004,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A625" s="1">
         <v>44743</v>
       </c>
@@ -17013,7 +17019,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A626" s="1">
         <v>44750</v>
       </c>
@@ -17028,7 +17034,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A627" s="1">
         <v>44757</v>
       </c>
@@ -17043,7 +17049,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A628" s="1">
         <v>44764</v>
       </c>
@@ -17058,7 +17064,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A629" s="1">
         <v>44771</v>
       </c>
@@ -17073,7 +17079,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A630" s="1">
         <v>44778</v>
       </c>
@@ -17088,7 +17094,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A631" s="1">
         <v>44785</v>
       </c>
@@ -17103,7 +17109,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A632" s="1">
         <v>44792</v>
       </c>
@@ -17118,7 +17124,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A633" s="1">
         <v>44799</v>
       </c>
@@ -17133,7 +17139,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A634" s="1">
         <v>44806</v>
       </c>
@@ -17148,7 +17154,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A635" s="1">
         <v>44813</v>
       </c>
@@ -17163,7 +17169,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A636" s="1">
         <v>44820</v>
       </c>
@@ -17178,7 +17184,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A637" s="1">
         <v>44827</v>
       </c>
@@ -17193,7 +17199,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A638" s="1">
         <v>44834</v>
       </c>
@@ -17208,7 +17214,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A639" s="1">
         <v>44841</v>
       </c>
@@ -17223,7 +17229,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A640" s="1">
         <v>44848</v>
       </c>
@@ -17238,7 +17244,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A641" s="1">
         <v>44855</v>
       </c>
@@ -17253,7 +17259,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A642" s="1">
         <v>44862</v>
       </c>
@@ -17268,7 +17274,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A643" s="1">
         <v>44869</v>
       </c>
@@ -17290,7 +17296,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A644" s="1">
         <v>44876</v>
       </c>
@@ -17305,7 +17311,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A645" s="1">
         <v>44883</v>
       </c>
@@ -17320,7 +17326,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A646" s="1">
         <v>44890</v>
       </c>
@@ -17335,7 +17341,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A647" s="1">
         <v>44897</v>
       </c>
@@ -17350,7 +17356,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A648" s="1">
         <v>44904</v>
       </c>
@@ -17365,7 +17371,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A649" s="1">
         <v>44911</v>
       </c>
@@ -17380,7 +17386,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A650" s="1">
         <v>44918</v>
       </c>
@@ -17395,7 +17401,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A651" s="1">
         <v>44925</v>
       </c>
@@ -17410,7 +17416,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A652" s="1">
         <v>44932</v>
       </c>
@@ -17425,7 +17431,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A653" s="1">
         <v>44939</v>
       </c>
@@ -17440,7 +17446,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A654" s="1">
         <v>44946</v>
       </c>
@@ -17455,7 +17461,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A655" s="1">
         <v>44953</v>
       </c>
@@ -17470,7 +17476,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A656" s="1">
         <v>44960</v>
       </c>
@@ -17485,7 +17491,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A657" s="1">
         <v>44967</v>
       </c>
@@ -17500,7 +17506,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A658" s="1">
         <v>44974</v>
       </c>
@@ -17515,7 +17521,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A659" s="1">
         <v>44981</v>
       </c>
@@ -17530,7 +17536,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A660" s="1">
         <v>44988</v>
       </c>
@@ -17545,7 +17551,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A661" s="1">
         <v>44995</v>
       </c>
@@ -17560,7 +17566,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A662" s="1">
         <v>45002</v>
       </c>
@@ -17575,7 +17581,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A663" s="1">
         <v>45009</v>
       </c>
@@ -17590,7 +17596,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A664" s="1">
         <v>45016</v>
       </c>
@@ -17605,7 +17611,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A665" s="1">
         <v>45023</v>
       </c>
@@ -17620,7 +17626,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A666" s="1">
         <v>45030</v>
       </c>
@@ -17635,7 +17641,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A667" s="1">
         <v>45037</v>
       </c>
@@ -17650,7 +17656,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A668" s="1">
         <v>45044</v>
       </c>
@@ -17665,7 +17671,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A669" s="1">
         <v>45051</v>
       </c>
@@ -17680,7 +17686,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A670" s="1">
         <v>45058</v>
       </c>
@@ -17695,7 +17701,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A671" s="1">
         <v>45065</v>
       </c>
@@ -17710,7 +17716,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A672" s="1">
         <v>45072</v>
       </c>
@@ -17725,7 +17731,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A673" s="1">
         <v>45079</v>
       </c>
@@ -17740,7 +17746,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A674" s="1">
         <v>45086</v>
       </c>
@@ -17755,7 +17761,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A675" s="1">
         <v>45093</v>
       </c>
@@ -17770,7 +17776,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A676" s="1">
         <v>45100</v>
       </c>
@@ -17785,7 +17791,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A677" s="1">
         <v>45107</v>
       </c>
@@ -17800,7 +17806,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A678" s="1">
         <v>45114</v>
       </c>
@@ -17815,7 +17821,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A679" s="1">
         <v>45121</v>
       </c>
@@ -17830,7 +17836,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A680" s="1">
         <v>45128</v>
       </c>
@@ -17845,7 +17851,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A681" s="1">
         <v>45135</v>
       </c>
@@ -17860,7 +17866,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A682" s="1">
         <v>45142</v>
       </c>
@@ -17875,7 +17881,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A683" s="1">
         <v>45149</v>
       </c>
@@ -17890,7 +17896,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A684" s="1">
         <v>45156</v>
       </c>
@@ -17905,7 +17911,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A685" s="1">
         <v>45163</v>
       </c>
@@ -17920,7 +17926,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A686" s="1">
         <v>45170</v>
       </c>
@@ -17935,7 +17941,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A687" s="1">
         <v>45177</v>
       </c>
@@ -17950,7 +17956,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A688" s="1">
         <v>45184</v>
       </c>
@@ -17965,7 +17971,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A689" s="1">
         <v>45191</v>
       </c>
@@ -17980,7 +17986,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A690" s="1">
         <v>45198</v>
       </c>
@@ -17995,7 +18001,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A691" s="1">
         <v>45205</v>
       </c>
@@ -18010,7 +18016,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A692" s="1">
         <v>45212</v>
       </c>
@@ -18025,7 +18031,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A693" s="1">
         <v>45219</v>
       </c>
@@ -18040,7 +18046,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A694" s="1">
         <v>45226</v>
       </c>
@@ -18055,7 +18061,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A695" s="1">
         <v>45233</v>
       </c>
@@ -18070,7 +18076,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A696" s="1">
         <v>45240</v>
       </c>
@@ -18085,7 +18091,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A697" s="1">
         <v>45247</v>
       </c>
@@ -18100,7 +18106,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A698" s="1">
         <v>45254</v>
       </c>
@@ -18115,7 +18121,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A699" s="1">
         <v>45261</v>
       </c>
@@ -18130,7 +18136,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A700" s="1">
         <v>45268</v>
       </c>
@@ -18145,7 +18151,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A701" s="1">
         <v>45275</v>
       </c>
@@ -18160,7 +18166,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A702" s="1">
         <v>45282</v>
       </c>
@@ -18175,7 +18181,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A703" s="1">
         <v>45289</v>
       </c>
@@ -18190,7 +18196,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A704" s="1">
         <v>45296</v>
       </c>
@@ -18205,7 +18211,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A705" s="1">
         <v>45303</v>
       </c>
@@ -18220,7 +18226,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A706" s="1">
         <v>45310</v>
       </c>
@@ -18235,7 +18241,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A707" s="1">
         <v>45317</v>
       </c>
@@ -18257,7 +18263,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A708" s="1">
         <v>45324</v>
       </c>
@@ -18272,7 +18278,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A709" s="1">
         <v>45331</v>
       </c>
@@ -18287,7 +18293,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A710" s="1">
         <v>45338</v>
       </c>
@@ -18302,7 +18308,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A711" s="1">
         <v>45345</v>
       </c>
@@ -18317,7 +18323,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A712" s="1">
         <v>45352</v>
       </c>
@@ -18332,7 +18338,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A713" s="1">
         <v>45359</v>
       </c>
@@ -18347,7 +18353,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A714" s="1">
         <v>45366</v>
       </c>
@@ -18362,7 +18368,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A715" s="1">
         <v>45373</v>
       </c>
@@ -18377,7 +18383,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A716" s="1">
         <v>45380</v>
       </c>
@@ -18392,7 +18398,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A717" s="1">
         <v>45387</v>
       </c>
@@ -18407,7 +18413,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A718" s="1">
         <v>45394</v>
       </c>
@@ -18422,7 +18428,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A719" s="1">
         <v>45401</v>
       </c>
@@ -18437,7 +18443,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A720" s="1">
         <v>45408</v>
       </c>
@@ -18452,7 +18458,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A721" s="1">
         <v>45415</v>
       </c>
@@ -18467,7 +18473,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A722" s="1">
         <v>45422</v>
       </c>
@@ -18482,7 +18488,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A723" s="1">
         <v>45429</v>
       </c>
@@ -18497,7 +18503,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A724" s="1">
         <v>45436</v>
       </c>
@@ -18512,7 +18518,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A725" s="1">
         <v>45443</v>
       </c>
@@ -18527,7 +18533,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A726" s="1">
         <v>45450</v>
       </c>
@@ -18542,7 +18548,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A727" s="1">
         <v>45457</v>
       </c>
@@ -18557,7 +18563,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A728" s="1">
         <v>45464</v>
       </c>
@@ -18575,7 +18581,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A729" s="1">
         <v>45471</v>
       </c>
@@ -18593,7 +18599,7 @@
         <v>1712.39</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A730" s="1">
         <v>45478</v>
       </c>
@@ -18608,7 +18614,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A731" s="1">
         <v>45485</v>
       </c>
@@ -18623,7 +18629,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A732" s="1">
         <v>45492</v>
       </c>
@@ -18638,7 +18644,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A733" s="1">
         <v>45499</v>
       </c>
@@ -18653,7 +18659,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A734" s="1">
         <v>45506</v>
       </c>
@@ -18668,7 +18674,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A735" s="1">
         <v>45513</v>
       </c>
@@ -18683,7 +18689,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A736" s="1">
         <v>45520</v>
       </c>
@@ -18698,7 +18704,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A737" s="1">
         <v>45527</v>
       </c>
@@ -18713,7 +18719,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A738" s="1">
         <v>45534</v>
       </c>
@@ -18728,7 +18734,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A739" s="1">
         <v>45541</v>
       </c>
@@ -18743,7 +18749,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A740" s="1">
         <v>45548</v>
       </c>
@@ -18758,7 +18764,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A741" s="1">
         <v>45555</v>
       </c>
@@ -18773,7 +18779,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A742" s="1">
         <v>45562</v>
       </c>
@@ -18788,7 +18794,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A743" s="1">
         <v>45569</v>
       </c>
@@ -18803,7 +18809,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A744" s="1">
         <v>45576</v>
       </c>
@@ -18818,7 +18824,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A745" s="1">
         <v>45583</v>
       </c>
@@ -18833,7 +18839,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A746" s="1">
         <v>45590</v>
       </c>
@@ -18848,7 +18854,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A747" s="1">
         <v>45597</v>
       </c>
@@ -18863,7 +18869,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A748" s="1">
         <v>45604</v>
       </c>
@@ -18878,7 +18884,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A749" s="1">
         <v>45611</v>
       </c>
@@ -18893,7 +18899,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A750" s="1">
         <v>45618</v>
       </c>
@@ -18908,7 +18914,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A751" s="1">
         <v>45625</v>
       </c>
@@ -18923,7 +18929,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A752" s="1">
         <v>45632</v>
       </c>
@@ -18938,7 +18944,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A753" s="1">
         <v>45639</v>
       </c>
@@ -18953,7 +18959,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A754" s="1">
         <v>45646</v>
       </c>
@@ -18968,7 +18974,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A755" s="1">
         <v>45653</v>
       </c>
@@ -18983,7 +18989,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A756" s="1">
         <v>45660</v>
       </c>
@@ -18998,7 +19004,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A757" s="1">
         <v>45667</v>
       </c>
@@ -19013,7 +19019,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A758" s="1">
         <v>45674</v>
       </c>
@@ -19028,7 +19034,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A759" s="1">
         <v>45681</v>
       </c>
@@ -19043,7 +19049,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A760" s="1">
         <v>45688</v>
       </c>
@@ -19058,7 +19064,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A761" s="1">
         <v>45695</v>
       </c>
@@ -19073,7 +19079,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A762" s="1">
         <v>45702</v>
       </c>
@@ -19088,7 +19094,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A763" s="1">
         <v>45709</v>
       </c>
@@ -19103,7 +19109,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A764" s="1">
         <v>45716</v>
       </c>
@@ -19118,7 +19124,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A765" s="1">
         <v>45723</v>
       </c>
@@ -19133,7 +19139,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A766" s="1">
         <v>45730</v>
       </c>
@@ -19148,7 +19154,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A767" s="1">
         <v>45737</v>
       </c>
@@ -19163,7 +19169,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A768" s="1">
         <v>45744</v>
       </c>
@@ -19178,7 +19184,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A769" s="1">
         <v>45751</v>
       </c>
@@ -19193,7 +19199,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A770" s="1">
         <v>45758</v>
       </c>
@@ -19208,7 +19214,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A771" s="1">
         <v>45765</v>
       </c>
@@ -19230,7 +19236,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A772" s="1">
         <v>45772</v>
       </c>
@@ -19245,7 +19251,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A773" s="1">
         <v>45779</v>
       </c>
@@ -19260,7 +19266,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A774" s="1">
         <v>45786</v>
       </c>
@@ -19275,7 +19281,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A775" s="1">
         <v>45793</v>
       </c>
@@ -19290,7 +19296,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A776" s="1">
         <v>45800</v>
       </c>
@@ -19305,7 +19311,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A777" s="1">
         <v>45807</v>
       </c>
@@ -19320,7 +19326,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A778" s="1">
         <v>45814</v>
       </c>
@@ -19335,7 +19341,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A779" s="1">
         <v>45821</v>
       </c>
@@ -19350,7 +19356,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A780" s="1">
         <v>45828</v>
       </c>
@@ -19368,7 +19374,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A781" s="1">
         <v>45835</v>
       </c>
@@ -19386,7 +19392,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A782" s="1">
         <v>45842</v>
       </c>
@@ -19401,7 +19407,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A783" s="1">
         <v>45849</v>
       </c>
@@ -19416,7 +19422,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A784" s="1">
         <v>45856</v>
       </c>
@@ -19431,7 +19437,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A785" s="1">
         <v>45863</v>
       </c>
@@ -19446,7 +19452,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A786" s="1">
         <v>45870</v>
       </c>
@@ -19461,7 +19467,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A787" s="1">
         <v>45877</v>
       </c>
@@ -19476,7 +19482,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A788" s="1">
         <v>45884</v>
       </c>
@@ -19491,7 +19497,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A789" s="1">
         <v>45891</v>
       </c>
@@ -19506,7 +19512,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A790" s="1">
         <v>45898</v>
       </c>
@@ -19521,7 +19527,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A791" s="1">
         <v>45905</v>
       </c>
@@ -19536,7 +19542,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A792" s="1">
         <v>45912</v>
       </c>
@@ -19551,7 +19557,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A793" s="1">
         <v>45919</v>
       </c>
@@ -19566,7 +19572,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A794" s="1">
         <v>45926</v>
       </c>
@@ -19581,7 +19587,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="795" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A795" s="1">
         <v>45933</v>
       </c>
@@ -19596,7 +19602,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="796" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A796" s="1">
         <v>45940</v>
       </c>
@@ -19611,7 +19617,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="797" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A797" s="1">
         <v>45947</v>
       </c>
@@ -19626,7 +19632,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="798" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A798" s="1">
         <v>45954</v>
       </c>
@@ -19641,7 +19647,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A799" s="1">
         <v>45961</v>
       </c>
@@ -19656,7 +19662,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A800" s="1">
         <v>45968</v>
       </c>
@@ -19671,7 +19677,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A801" s="1">
         <v>45975</v>
       </c>
@@ -19686,7 +19692,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A802" s="1">
         <v>45982</v>
       </c>
@@ -19701,7 +19707,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A803" s="1">
         <v>45989</v>
       </c>
@@ -19716,7 +19722,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A804" s="1">
         <v>45996</v>
       </c>
@@ -19731,7 +19737,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A805" s="1">
         <v>46003</v>
       </c>
@@ -19746,7 +19752,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A806" s="1">
         <v>46010</v>
       </c>
@@ -19761,7 +19767,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A807" s="1">
         <v>46017</v>
       </c>
@@ -19789,7 +19795,7 @@
       <c r="N807" s="9"/>
       <c r="O807" s="9"/>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A808" s="1">
         <v>46024</v>
       </c>
@@ -19837,7 +19843,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A809" s="1">
         <v>46031</v>
       </c>
@@ -19885,7 +19891,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A810" s="1">
         <v>46038</v>
       </c>
@@ -19933,7 +19939,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A811" s="1">
         <v>46045</v>
       </c>
@@ -19981,7 +19987,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A812" s="1">
         <v>46052</v>
       </c>
@@ -20029,7 +20035,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A813" s="1">
         <v>46059</v>
       </c>
@@ -20077,7 +20083,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A814" s="1">
         <v>46066</v>
       </c>
@@ -20125,7 +20131,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A815" s="1">
         <v>46073</v>
       </c>
@@ -20173,7 +20179,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A816" s="1">
         <v>46080</v>
       </c>
@@ -20221,7 +20227,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A817" s="1">
         <v>46087</v>
       </c>
@@ -20269,7 +20275,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A818" s="1">
         <v>46094</v>
       </c>
@@ -20317,7 +20323,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A819" s="1">
         <v>46101</v>
       </c>
@@ -20365,7 +20371,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A820" s="1">
         <v>46108</v>
       </c>
@@ -20413,7 +20419,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A821" s="1">
         <v>46115</v>
       </c>
@@ -20461,7 +20467,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A822" s="1">
         <v>46122</v>
       </c>
@@ -20489,7 +20495,7 @@
       <c r="N822" s="2"/>
       <c r="O822" s="2"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A823" s="1">
         <v>46129</v>
       </c>
@@ -20517,7 +20523,7 @@
       <c r="N823" s="2"/>
       <c r="O823" s="2"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A824" s="1">
         <v>46136</v>
       </c>
@@ -20545,7 +20551,7 @@
       <c r="N824" s="2"/>
       <c r="O824" s="2"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A825" s="1">
         <v>46143</v>
       </c>
@@ -20593,7 +20599,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A826" s="1">
         <v>46150</v>
       </c>
@@ -20641,7 +20647,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A827" s="1">
         <v>46157</v>
       </c>
@@ -20689,7 +20695,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A828" s="1">
         <v>46164</v>
       </c>
@@ -20737,7 +20743,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A829" s="1">
         <v>46171</v>
       </c>
@@ -20785,7 +20791,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A830" s="1">
         <v>46178</v>
       </c>
@@ -20833,7 +20839,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A831" s="1">
         <v>46185</v>
       </c>
@@ -20881,7 +20887,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A832" s="1">
         <v>46192</v>
       </c>
@@ -20929,7 +20935,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A833" s="1">
         <v>46199</v>
       </c>
@@ -20974,6 +20980,61 @@
         <v>71000</v>
       </c>
       <c r="O833" s="3">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="834" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A834" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B834" s="1">
+        <v>46206</v>
+      </c>
+      <c r="C834" s="15">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="D834" s="1" t="str">
+        <f t="shared" ref="D834" si="13">"UTC+"&amp;IF(
+    AND(
+        B834&gt;=EOMONTH(DATE(YEAR(B834),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B834),3,1),0),2),7),
+        B834&lt;EOMONTH(DATE(YEAR(B834),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B834),10,1),0),2),7)
+    ),
+    2,
+    1
+)</f>
+        <v>UTC+2</v>
+      </c>
+      <c r="E834" s="12">
+        <v>2326.67</v>
+      </c>
+      <c r="F834" s="3">
+        <v>11250</v>
+      </c>
+      <c r="G834" s="3">
+        <v>17750</v>
+      </c>
+      <c r="H834" s="3">
+        <v>30000</v>
+      </c>
+      <c r="I834" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J834" s="3">
+        <v>38000</v>
+      </c>
+      <c r="K834" s="3">
+        <v>40000</v>
+      </c>
+      <c r="L834" s="3">
+        <v>46000</v>
+      </c>
+      <c r="M834" s="3">
+        <v>57000</v>
+      </c>
+      <c r="N834" s="3">
+        <v>71000</v>
+      </c>
+      <c r="O834" s="3">
         <v>78000</v>
       </c>
     </row>
@@ -20985,7 +21046,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -20995,12 +21056,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
@@ -21008,7 +21069,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="7" t="s">
         <v>17</v>
       </c>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A46079-52FE-42E0-A46D-471C44F4EB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEC491E-8564-6649-8B68-7491737A29B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -100,12 +100,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,9 +171,9 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -181,43 +181,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -235,7 +235,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2786,6 +2786,9 @@
                 <c:pt idx="833">
                   <c:v>46213</c:v>
                 </c:pt>
+                <c:pt idx="834">
+                  <c:v>46220</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4586,6 +4589,9 @@
                 <c:pt idx="780">
                   <c:v>2164.15</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>2164.9</c:v>
+                </c:pt>
                 <c:pt idx="805">
                   <c:v>2180.56</c:v>
                 </c:pt>
@@ -4672,6 +4678,9 @@
                 </c:pt>
                 <c:pt idx="833">
                   <c:v>2337.11</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>2340.09</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5485,9 +5494,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5525,7 +5534,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5631,7 +5640,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5773,7 +5782,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5781,19 +5790,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P835"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P836"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.77734375" style="11"/>
+    <col min="5" max="5" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="7" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5841,7 +5850,7 @@
       </c>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16">
       <c r="A2" s="8">
         <v>40383</v>
       </c>
@@ -5866,7 +5875,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16">
       <c r="A3" s="8">
         <v>40390</v>
       </c>
@@ -5891,7 +5900,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16">
       <c r="A4" s="8">
         <v>40397</v>
       </c>
@@ -5909,7 +5918,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="A5" s="8">
         <v>40404</v>
       </c>
@@ -5927,7 +5936,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16">
       <c r="A6" s="8">
         <v>40411</v>
       </c>
@@ -5945,7 +5954,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16">
       <c r="A7" s="8">
         <v>40418</v>
       </c>
@@ -5963,7 +5972,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16">
       <c r="A8" s="8">
         <v>40425</v>
       </c>
@@ -5981,7 +5990,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16">
       <c r="A9" s="8">
         <v>40432</v>
       </c>
@@ -5999,7 +6008,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16">
       <c r="A10" s="8">
         <v>40439</v>
       </c>
@@ -6017,7 +6026,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16">
       <c r="A11" s="8">
         <v>40446</v>
       </c>
@@ -6035,7 +6044,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16">
       <c r="A12" s="8">
         <v>40453</v>
       </c>
@@ -6053,7 +6062,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16">
       <c r="A13" s="8">
         <v>40460</v>
       </c>
@@ -6071,7 +6080,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16">
       <c r="A14" s="8">
         <v>40467</v>
       </c>
@@ -6089,7 +6098,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16">
       <c r="A15" s="8">
         <v>40474</v>
       </c>
@@ -6107,7 +6116,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16">
       <c r="A16" s="8">
         <v>40481</v>
       </c>
@@ -6125,7 +6134,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="8">
         <v>40488</v>
       </c>
@@ -6143,7 +6152,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="8">
         <v>40495</v>
       </c>
@@ -6161,7 +6170,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="8">
         <v>40502</v>
       </c>
@@ -6179,7 +6188,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="8">
         <v>40509</v>
       </c>
@@ -6197,7 +6206,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="8">
         <v>40516</v>
       </c>
@@ -6215,7 +6224,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="8">
         <v>40523</v>
       </c>
@@ -6233,7 +6242,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="8">
         <v>40530</v>
       </c>
@@ -6251,7 +6260,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="8">
         <v>40537</v>
       </c>
@@ -6269,7 +6278,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="8">
         <v>40544</v>
       </c>
@@ -6287,7 +6296,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="8">
         <v>40551</v>
       </c>
@@ -6305,7 +6314,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="8">
         <v>40558</v>
       </c>
@@ -6323,7 +6332,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="8">
         <v>40565</v>
       </c>
@@ -6341,7 +6350,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="8">
         <v>40572</v>
       </c>
@@ -6359,7 +6368,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="8">
         <v>40579</v>
       </c>
@@ -6377,7 +6386,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="8">
         <v>40586</v>
       </c>
@@ -6395,7 +6404,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="8">
         <v>40593</v>
       </c>
@@ -6413,7 +6422,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="8">
         <v>40600</v>
       </c>
@@ -6431,7 +6440,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="8">
         <v>40607</v>
       </c>
@@ -6449,7 +6458,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="8">
         <v>40614</v>
       </c>
@@ -6467,7 +6476,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="8">
         <v>40621</v>
       </c>
@@ -6485,7 +6494,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="8">
         <v>40628</v>
       </c>
@@ -6503,7 +6512,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="8">
         <v>40635</v>
       </c>
@@ -6521,7 +6530,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="8">
         <v>40642</v>
       </c>
@@ -6539,7 +6548,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="8">
         <v>40649</v>
       </c>
@@ -6557,7 +6566,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="8">
         <v>40656</v>
       </c>
@@ -6575,7 +6584,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="8">
         <v>40663</v>
       </c>
@@ -6593,7 +6602,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="8">
         <v>40670</v>
       </c>
@@ -6611,7 +6620,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="8">
         <v>40677</v>
       </c>
@@ -6629,7 +6638,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="8">
         <v>40684</v>
       </c>
@@ -6647,7 +6656,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" s="8">
         <v>40691</v>
       </c>
@@ -6665,7 +6674,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" s="8">
         <v>40698</v>
       </c>
@@ -6683,7 +6692,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48" s="8">
         <v>40705</v>
       </c>
@@ -6701,7 +6710,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" s="8">
         <v>40712</v>
       </c>
@@ -6719,7 +6728,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" s="8">
         <v>40719</v>
       </c>
@@ -6737,7 +6746,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" s="8">
         <v>40726</v>
       </c>
@@ -6755,7 +6764,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" s="8">
         <v>40733</v>
       </c>
@@ -6773,7 +6782,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53" s="8">
         <v>40740</v>
       </c>
@@ -6791,7 +6800,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" s="8">
         <v>40747</v>
       </c>
@@ -6809,7 +6818,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55" s="8">
         <v>40754</v>
       </c>
@@ -6827,7 +6836,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56" s="8">
         <v>40761</v>
       </c>
@@ -6845,7 +6854,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57" s="8">
         <v>40768</v>
       </c>
@@ -6863,7 +6872,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58" s="8">
         <v>40775</v>
       </c>
@@ -6881,7 +6890,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59" s="8">
         <v>40782</v>
       </c>
@@ -6899,7 +6908,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" s="8">
         <v>40789</v>
       </c>
@@ -6917,7 +6926,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61" s="8">
         <v>40796</v>
       </c>
@@ -6935,7 +6944,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62" s="8">
         <v>40803</v>
       </c>
@@ -6953,7 +6962,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63" s="8">
         <v>40810</v>
       </c>
@@ -6971,7 +6980,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64" s="8">
         <v>40817</v>
       </c>
@@ -6989,7 +6998,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65" s="8">
         <v>40824</v>
       </c>
@@ -7007,7 +7016,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5">
       <c r="A66" s="8">
         <v>40831</v>
       </c>
@@ -7025,7 +7034,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67" s="8">
         <v>40838</v>
       </c>
@@ -7050,7 +7059,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68" s="8">
         <v>40845</v>
       </c>
@@ -7068,7 +7077,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5">
       <c r="A69" s="8">
         <v>40852</v>
       </c>
@@ -7086,7 +7095,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70" s="8">
         <v>40859</v>
       </c>
@@ -7104,7 +7113,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71" s="8">
         <v>40866</v>
       </c>
@@ -7122,7 +7131,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72" s="8">
         <v>40873</v>
       </c>
@@ -7140,7 +7149,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73" s="8">
         <v>40880</v>
       </c>
@@ -7158,7 +7167,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5">
       <c r="A74" s="8">
         <v>40887</v>
       </c>
@@ -7176,7 +7185,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75" s="8">
         <v>40894</v>
       </c>
@@ -7194,7 +7203,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5">
       <c r="A76" s="8">
         <v>40901</v>
       </c>
@@ -7212,7 +7221,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5">
       <c r="A77" s="8">
         <v>40908</v>
       </c>
@@ -7230,7 +7239,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5">
       <c r="A78" s="8">
         <v>40915</v>
       </c>
@@ -7248,7 +7257,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5">
       <c r="A79" s="8">
         <v>40922</v>
       </c>
@@ -7266,7 +7275,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5">
       <c r="A80" s="8">
         <v>40929</v>
       </c>
@@ -7284,7 +7293,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5">
       <c r="A81" s="8">
         <v>40936</v>
       </c>
@@ -7302,7 +7311,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5">
       <c r="A82" s="8">
         <v>40942</v>
       </c>
@@ -7320,7 +7329,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5">
       <c r="A83" s="8">
         <v>40943</v>
       </c>
@@ -7338,7 +7347,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5">
       <c r="A84" s="8">
         <v>40950</v>
       </c>
@@ -7356,7 +7365,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5">
       <c r="A85" s="8">
         <v>40957</v>
       </c>
@@ -7374,7 +7383,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5">
       <c r="A86" s="8">
         <v>40964</v>
       </c>
@@ -7392,7 +7401,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5">
       <c r="A87" s="8">
         <v>40978</v>
       </c>
@@ -7410,7 +7419,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5">
       <c r="A88" s="8">
         <v>40985</v>
       </c>
@@ -7428,7 +7437,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5">
       <c r="A89" s="8">
         <v>40992</v>
       </c>
@@ -7446,7 +7455,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5">
       <c r="A90" s="8">
         <v>40999</v>
       </c>
@@ -7464,7 +7473,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5">
       <c r="A91" s="8">
         <v>41006</v>
       </c>
@@ -7482,7 +7491,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5">
       <c r="A92" s="8">
         <v>41013</v>
       </c>
@@ -7500,7 +7509,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5">
       <c r="A93" s="8">
         <v>41020</v>
       </c>
@@ -7518,7 +7527,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5">
       <c r="A94" s="8">
         <v>41027</v>
       </c>
@@ -7536,7 +7545,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5">
       <c r="A95" s="8">
         <v>41034</v>
       </c>
@@ -7554,7 +7563,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5">
       <c r="A96" s="8">
         <v>41041</v>
       </c>
@@ -7572,7 +7581,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5">
       <c r="A97" s="8">
         <v>41048</v>
       </c>
@@ -7590,7 +7599,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98" s="8">
         <v>41055</v>
       </c>
@@ -7608,7 +7617,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5">
       <c r="A99" s="8">
         <v>41062</v>
       </c>
@@ -7626,7 +7635,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5">
       <c r="A100" s="8">
         <v>41069</v>
       </c>
@@ -7644,7 +7653,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5">
       <c r="A101" s="8">
         <v>41076</v>
       </c>
@@ -7662,7 +7671,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5">
       <c r="A102" s="8">
         <v>41083</v>
       </c>
@@ -7680,7 +7689,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5">
       <c r="A103" s="8">
         <v>41090</v>
       </c>
@@ -7698,7 +7707,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5">
       <c r="A104" s="8">
         <v>41097</v>
       </c>
@@ -7716,7 +7725,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105" s="8">
         <v>41104</v>
       </c>
@@ -7734,7 +7743,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106" s="8">
         <v>41111</v>
       </c>
@@ -7752,7 +7761,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107" s="8">
         <v>41118</v>
       </c>
@@ -7770,7 +7779,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108" s="8">
         <v>41125</v>
       </c>
@@ -7788,7 +7797,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5">
       <c r="A109" s="8">
         <v>41132</v>
       </c>
@@ -7806,7 +7815,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110" s="8">
         <v>41139</v>
       </c>
@@ -7824,7 +7833,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5">
       <c r="A111" s="8">
         <v>41146</v>
       </c>
@@ -7842,7 +7851,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5">
       <c r="A112" s="8">
         <v>41153</v>
       </c>
@@ -7860,7 +7869,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5">
       <c r="A113" s="8">
         <v>41160</v>
       </c>
@@ -7878,7 +7887,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5">
       <c r="A114" s="8">
         <v>41167</v>
       </c>
@@ -7896,7 +7905,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5">
       <c r="A115" s="8">
         <v>41174</v>
       </c>
@@ -7914,7 +7923,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5">
       <c r="A116" s="8">
         <v>41181</v>
       </c>
@@ -7932,7 +7941,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5">
       <c r="A117" s="8">
         <v>41188</v>
       </c>
@@ -7950,7 +7959,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5">
       <c r="A118" s="8">
         <v>41195</v>
       </c>
@@ -7968,7 +7977,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5">
       <c r="A119" s="8">
         <v>41202</v>
       </c>
@@ -7986,7 +7995,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5">
       <c r="A120" s="8">
         <v>41209</v>
       </c>
@@ -8004,7 +8013,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5">
       <c r="A121" s="8">
         <v>41216</v>
       </c>
@@ -8022,7 +8031,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5">
       <c r="A122" s="8">
         <v>41223</v>
       </c>
@@ -8040,7 +8049,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5">
       <c r="A123" s="8">
         <v>41230</v>
       </c>
@@ -8058,7 +8067,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5">
       <c r="A124" s="8">
         <v>41237</v>
       </c>
@@ -8076,7 +8085,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5">
       <c r="A125" s="8">
         <v>41244</v>
       </c>
@@ -8094,7 +8103,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5">
       <c r="A126" s="8">
         <v>41251</v>
       </c>
@@ -8112,7 +8121,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5">
       <c r="A127" s="8">
         <v>41258</v>
       </c>
@@ -8130,7 +8139,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5">
       <c r="A128" s="8">
         <v>41265</v>
       </c>
@@ -8148,7 +8157,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5">
       <c r="A129" s="8">
         <v>41272</v>
       </c>
@@ -8166,7 +8175,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5">
       <c r="A130" s="8">
         <v>41279</v>
       </c>
@@ -8184,7 +8193,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5">
       <c r="A131" s="8">
         <v>41286</v>
       </c>
@@ -8209,7 +8218,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5">
       <c r="A132" s="8">
         <v>41293</v>
       </c>
@@ -8227,7 +8236,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5">
       <c r="A133" s="8">
         <v>41300</v>
       </c>
@@ -8245,7 +8254,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5">
       <c r="A134" s="8">
         <v>41307</v>
       </c>
@@ -8263,7 +8272,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5">
       <c r="A135" s="8">
         <v>41314</v>
       </c>
@@ -8281,7 +8290,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5">
       <c r="A136" s="8">
         <v>41321</v>
       </c>
@@ -8299,7 +8308,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5">
       <c r="A137" s="8">
         <v>41328</v>
       </c>
@@ -8317,7 +8326,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5">
       <c r="A138" s="8">
         <v>41335</v>
       </c>
@@ -8335,7 +8344,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5">
       <c r="A139" s="8">
         <v>41342</v>
       </c>
@@ -8353,7 +8362,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5">
       <c r="A140" s="8">
         <v>41349</v>
       </c>
@@ -8371,7 +8380,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5">
       <c r="A141" s="8">
         <v>41356</v>
       </c>
@@ -8389,7 +8398,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5">
       <c r="A142" s="8">
         <v>41363</v>
       </c>
@@ -8407,7 +8416,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5">
       <c r="A143" s="8">
         <v>41370</v>
       </c>
@@ -8425,7 +8434,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5">
       <c r="A144" s="8">
         <v>41377</v>
       </c>
@@ -8443,7 +8452,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5">
       <c r="A145" s="8">
         <v>41384</v>
       </c>
@@ -8461,7 +8470,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5">
       <c r="A146" s="8">
         <v>41391</v>
       </c>
@@ -8479,7 +8488,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5">
       <c r="A147" s="8">
         <v>41398</v>
       </c>
@@ -8497,7 +8506,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5">
       <c r="A148" s="8">
         <v>41405</v>
       </c>
@@ -8515,7 +8524,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5">
       <c r="A149" s="8">
         <v>41412</v>
       </c>
@@ -8533,7 +8542,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5">
       <c r="A150" s="8">
         <v>41419</v>
       </c>
@@ -8551,7 +8560,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5">
       <c r="A151" s="8">
         <v>41426</v>
       </c>
@@ -8569,7 +8578,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5">
       <c r="A152" s="8">
         <v>41433</v>
       </c>
@@ -8587,7 +8596,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5">
       <c r="A153" s="8">
         <v>41440</v>
       </c>
@@ -8605,7 +8614,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5">
       <c r="A154" s="8">
         <v>41447</v>
       </c>
@@ -8623,7 +8632,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5">
       <c r="A155" s="8">
         <v>41454</v>
       </c>
@@ -8641,7 +8650,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5">
       <c r="A156" s="8">
         <v>41461</v>
       </c>
@@ -8659,7 +8668,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5">
       <c r="A157" s="8">
         <v>41468</v>
       </c>
@@ -8677,7 +8686,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5">
       <c r="A158" s="8">
         <v>41475</v>
       </c>
@@ -8695,7 +8704,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5">
       <c r="A159" s="8">
         <v>41482</v>
       </c>
@@ -8713,7 +8722,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5">
       <c r="A160" s="8">
         <v>41489</v>
       </c>
@@ -8731,7 +8740,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5">
       <c r="A161" s="8">
         <v>41496</v>
       </c>
@@ -8749,7 +8758,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5">
       <c r="A162" s="8">
         <v>41503</v>
       </c>
@@ -8767,7 +8776,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5">
       <c r="A163" s="8">
         <v>41510</v>
       </c>
@@ -8785,7 +8794,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5">
       <c r="A164" s="8">
         <v>41517</v>
       </c>
@@ -8803,7 +8812,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5">
       <c r="A165" s="8">
         <v>41524</v>
       </c>
@@ -8821,7 +8830,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5">
       <c r="A166" s="8">
         <v>41531</v>
       </c>
@@ -8839,7 +8848,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5">
       <c r="A167" s="8">
         <v>41538</v>
       </c>
@@ -8857,7 +8866,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5">
       <c r="A168" s="8">
         <v>41545</v>
       </c>
@@ -8875,7 +8884,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5">
       <c r="A169" s="8">
         <v>41552</v>
       </c>
@@ -8893,7 +8902,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5">
       <c r="A170" s="8">
         <v>41559</v>
       </c>
@@ -8911,7 +8920,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5">
       <c r="A171" s="8">
         <v>41566</v>
       </c>
@@ -8929,7 +8938,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5">
       <c r="A172" s="8">
         <v>41573</v>
       </c>
@@ -8947,7 +8956,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5">
       <c r="A173" s="8">
         <v>41580</v>
       </c>
@@ -8965,7 +8974,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5">
       <c r="A174" s="8">
         <v>41587</v>
       </c>
@@ -8983,7 +8992,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5">
       <c r="A175" s="8">
         <v>41594</v>
       </c>
@@ -9001,7 +9010,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5">
       <c r="A176" s="8">
         <v>41601</v>
       </c>
@@ -9019,7 +9028,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5">
       <c r="A177" s="8">
         <v>41608</v>
       </c>
@@ -9037,7 +9046,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5">
       <c r="A178" s="8">
         <v>41615</v>
       </c>
@@ -9055,7 +9064,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5">
       <c r="A179" s="8">
         <v>41622</v>
       </c>
@@ -9073,7 +9082,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5">
       <c r="A180" s="8">
         <v>41629</v>
       </c>
@@ -9091,7 +9100,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5">
       <c r="A181" s="8">
         <v>41636</v>
       </c>
@@ -9109,7 +9118,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5">
       <c r="A182" s="8">
         <v>41643</v>
       </c>
@@ -9127,7 +9136,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5">
       <c r="A183" s="8">
         <v>41650</v>
       </c>
@@ -9145,7 +9154,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5">
       <c r="A184" s="8">
         <v>41657</v>
       </c>
@@ -9163,7 +9172,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5">
       <c r="A185" s="8">
         <v>41664</v>
       </c>
@@ -9181,7 +9190,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5">
       <c r="A186" s="8">
         <v>41671</v>
       </c>
@@ -9199,7 +9208,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5">
       <c r="A187" s="8">
         <v>41678</v>
       </c>
@@ -9217,7 +9226,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5">
       <c r="A188" s="8">
         <v>41685</v>
       </c>
@@ -9235,7 +9244,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5">
       <c r="A189" s="8">
         <v>41692</v>
       </c>
@@ -9253,7 +9262,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5">
       <c r="A190" s="8">
         <v>41699</v>
       </c>
@@ -9271,7 +9280,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5">
       <c r="A191" s="8">
         <v>41706</v>
       </c>
@@ -9289,7 +9298,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5">
       <c r="A192" s="8">
         <v>41713</v>
       </c>
@@ -9307,7 +9316,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5">
       <c r="A193" s="8">
         <v>41720</v>
       </c>
@@ -9325,7 +9334,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5">
       <c r="A194" s="8">
         <v>41727</v>
       </c>
@@ -9343,7 +9352,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5">
       <c r="A195" s="8">
         <v>41734</v>
       </c>
@@ -9368,7 +9377,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5">
       <c r="A196" s="8">
         <v>41741</v>
       </c>
@@ -9386,7 +9395,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5">
       <c r="A197" s="8">
         <v>41748</v>
       </c>
@@ -9404,7 +9413,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5">
       <c r="A198" s="8">
         <v>41755</v>
       </c>
@@ -9422,7 +9431,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5">
       <c r="A199" s="8">
         <v>41762</v>
       </c>
@@ -9440,7 +9449,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5">
       <c r="A200" s="8">
         <v>41769</v>
       </c>
@@ -9458,7 +9467,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5">
       <c r="A201" s="8">
         <v>41776</v>
       </c>
@@ -9476,7 +9485,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5">
       <c r="A202" s="8">
         <v>41783</v>
       </c>
@@ -9494,7 +9503,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5">
       <c r="A203" s="8">
         <v>41790</v>
       </c>
@@ -9512,7 +9521,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5">
       <c r="A204" s="8">
         <v>41797</v>
       </c>
@@ -9530,7 +9539,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5">
       <c r="A205" s="8">
         <v>41804</v>
       </c>
@@ -9548,7 +9557,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5">
       <c r="A206" s="8">
         <v>41811</v>
       </c>
@@ -9566,7 +9575,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5">
       <c r="A207" s="8">
         <v>41818</v>
       </c>
@@ -9584,7 +9593,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5">
       <c r="A208" s="8">
         <v>41825</v>
       </c>
@@ -9602,7 +9611,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5">
       <c r="A209" s="8">
         <v>41832</v>
       </c>
@@ -9620,7 +9629,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5">
       <c r="A210" s="8">
         <v>41839</v>
       </c>
@@ -9638,7 +9647,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5">
       <c r="A211" s="8">
         <v>41846</v>
       </c>
@@ -9656,7 +9665,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5">
       <c r="A212" s="8">
         <v>41853</v>
       </c>
@@ -9674,7 +9683,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5">
       <c r="A213" s="8">
         <v>41860</v>
       </c>
@@ -9692,7 +9701,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5">
       <c r="A214" s="8">
         <v>41867</v>
       </c>
@@ -9710,7 +9719,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5">
       <c r="A215" s="8">
         <v>41874</v>
       </c>
@@ -9728,7 +9737,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5">
       <c r="A216" s="8">
         <v>41881</v>
       </c>
@@ -9746,7 +9755,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5">
       <c r="A217" s="8">
         <v>41888</v>
       </c>
@@ -9764,7 +9773,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5">
       <c r="A218" s="8">
         <v>41895</v>
       </c>
@@ -9782,7 +9791,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5">
       <c r="A219" s="8">
         <v>41902</v>
       </c>
@@ -9800,7 +9809,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5">
       <c r="A220" s="8">
         <v>41909</v>
       </c>
@@ -9818,7 +9827,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5">
       <c r="A221" s="8">
         <v>41916</v>
       </c>
@@ -9836,7 +9845,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5">
       <c r="A222" s="8">
         <v>41923</v>
       </c>
@@ -9854,7 +9863,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5">
       <c r="A223" s="8">
         <v>41930</v>
       </c>
@@ -9872,7 +9881,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5">
       <c r="A224" s="8">
         <v>41937</v>
       </c>
@@ -9890,7 +9899,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5">
       <c r="A225" s="8">
         <v>41944</v>
       </c>
@@ -9908,7 +9917,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5">
       <c r="A226" s="8">
         <v>41951</v>
       </c>
@@ -9926,7 +9935,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5">
       <c r="A227" s="8">
         <v>41958</v>
       </c>
@@ -9944,7 +9953,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5">
       <c r="A228" s="8">
         <v>41965</v>
       </c>
@@ -9962,7 +9971,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5">
       <c r="A229" s="8">
         <v>41972</v>
       </c>
@@ -9980,7 +9989,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5">
       <c r="A230" s="8">
         <v>41979</v>
       </c>
@@ -9998,7 +10007,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5">
       <c r="A231" s="8">
         <v>41986</v>
       </c>
@@ -10016,7 +10025,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5">
       <c r="A232" s="8">
         <v>41993</v>
       </c>
@@ -10034,7 +10043,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5">
       <c r="A233" s="8">
         <v>42000</v>
       </c>
@@ -10052,7 +10061,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5">
       <c r="A234" s="8">
         <v>42007</v>
       </c>
@@ -10070,7 +10079,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5">
       <c r="A235" s="8">
         <v>42014</v>
       </c>
@@ -10088,7 +10097,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5">
       <c r="A236" s="8">
         <v>42021</v>
       </c>
@@ -10106,7 +10115,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5">
       <c r="A237" s="8">
         <v>42028</v>
       </c>
@@ -10124,7 +10133,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5">
       <c r="A238" s="8">
         <v>42035</v>
       </c>
@@ -10142,7 +10151,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5">
       <c r="A239" s="8">
         <v>42042</v>
       </c>
@@ -10160,7 +10169,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5">
       <c r="A240" s="8">
         <v>42049</v>
       </c>
@@ -10178,7 +10187,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5">
       <c r="A241" s="8">
         <v>42056</v>
       </c>
@@ -10196,7 +10205,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5">
       <c r="A242" s="8">
         <v>42063</v>
       </c>
@@ -10214,7 +10223,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5">
       <c r="A243" s="8">
         <v>42070</v>
       </c>
@@ -10232,7 +10241,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5">
       <c r="A244" s="8">
         <v>42077</v>
       </c>
@@ -10250,7 +10259,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5">
       <c r="A245" s="8">
         <v>42084</v>
       </c>
@@ -10268,7 +10277,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5">
       <c r="A246" s="8">
         <v>42091</v>
       </c>
@@ -10286,7 +10295,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5">
       <c r="A247" s="8">
         <v>42098</v>
       </c>
@@ -10304,7 +10313,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5">
       <c r="A248" s="8">
         <v>42105</v>
       </c>
@@ -10322,7 +10331,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5">
       <c r="A249" s="8">
         <v>42112</v>
       </c>
@@ -10340,7 +10349,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5">
       <c r="A250" s="8">
         <v>42119</v>
       </c>
@@ -10358,7 +10367,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5">
       <c r="A251" s="8">
         <v>42126</v>
       </c>
@@ -10376,7 +10385,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5">
       <c r="A252" s="8">
         <v>42133</v>
       </c>
@@ -10394,7 +10403,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5">
       <c r="A253" s="8">
         <v>42140</v>
       </c>
@@ -10412,7 +10421,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5">
       <c r="A254" s="8">
         <v>42147</v>
       </c>
@@ -10430,7 +10439,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5">
       <c r="A255" s="8">
         <v>42154</v>
       </c>
@@ -10448,7 +10457,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5">
       <c r="A256" s="8">
         <v>42161</v>
       </c>
@@ -10466,7 +10475,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5">
       <c r="A257" s="8">
         <v>42168</v>
       </c>
@@ -10484,7 +10493,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5">
       <c r="A258" s="8">
         <v>42175</v>
       </c>
@@ -10502,7 +10511,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5">
       <c r="A259" s="8">
         <v>42182</v>
       </c>
@@ -10527,7 +10536,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5">
       <c r="A260" s="8">
         <v>42189</v>
       </c>
@@ -10545,7 +10554,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5">
       <c r="A261" s="8">
         <v>42196</v>
       </c>
@@ -10563,7 +10572,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5">
       <c r="A262" s="8">
         <v>42203</v>
       </c>
@@ -10581,7 +10590,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5">
       <c r="A263" s="8">
         <v>42210</v>
       </c>
@@ -10599,7 +10608,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5">
       <c r="A264" s="8">
         <v>42217</v>
       </c>
@@ -10617,7 +10626,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5">
       <c r="A265" s="8">
         <v>42224</v>
       </c>
@@ -10635,7 +10644,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5">
       <c r="A266" s="8">
         <v>42231</v>
       </c>
@@ -10653,7 +10662,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5">
       <c r="A267" s="8">
         <v>42238</v>
       </c>
@@ -10671,7 +10680,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5">
       <c r="A268" s="8">
         <v>42245</v>
       </c>
@@ -10689,7 +10698,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5">
       <c r="A269" s="8">
         <v>42252</v>
       </c>
@@ -10707,7 +10716,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5">
       <c r="A270" s="8">
         <v>42259</v>
       </c>
@@ -10725,7 +10734,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5">
       <c r="A271" s="8">
         <v>42266</v>
       </c>
@@ -10743,7 +10752,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5">
       <c r="A272" s="8">
         <v>42273</v>
       </c>
@@ -10761,7 +10770,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5">
       <c r="A273" s="8">
         <v>42280</v>
       </c>
@@ -10779,7 +10788,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5">
       <c r="A274" s="8">
         <v>42287</v>
       </c>
@@ -10797,7 +10806,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5">
       <c r="A275" s="8">
         <v>42294</v>
       </c>
@@ -10815,7 +10824,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5">
       <c r="A276" s="8">
         <v>42301</v>
       </c>
@@ -10833,7 +10842,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5">
       <c r="A277" s="8">
         <v>42308</v>
       </c>
@@ -10851,7 +10860,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5">
       <c r="A278" s="8">
         <v>42315</v>
       </c>
@@ -10869,7 +10878,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5">
       <c r="A279" s="8">
         <v>42322</v>
       </c>
@@ -10887,7 +10896,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5">
       <c r="A280" s="8">
         <v>42329</v>
       </c>
@@ -10905,7 +10914,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5">
       <c r="A281" s="8">
         <v>42336</v>
       </c>
@@ -10923,7 +10932,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5">
       <c r="A282" s="8">
         <v>42343</v>
       </c>
@@ -10941,7 +10950,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5">
       <c r="A283" s="8">
         <v>42350</v>
       </c>
@@ -10959,7 +10968,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5">
       <c r="A284" s="8">
         <v>42357</v>
       </c>
@@ -10977,7 +10986,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5">
       <c r="A285" s="8">
         <v>42364</v>
       </c>
@@ -10995,7 +11004,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5">
       <c r="A286" s="8">
         <v>42371</v>
       </c>
@@ -11013,7 +11022,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5">
       <c r="A287" s="8">
         <v>42378</v>
       </c>
@@ -11031,7 +11040,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5">
       <c r="A288" s="8">
         <v>42385</v>
       </c>
@@ -11049,7 +11058,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5">
       <c r="A289" s="8">
         <v>42392</v>
       </c>
@@ -11067,7 +11076,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5">
       <c r="A290" s="8">
         <v>42399</v>
       </c>
@@ -11085,7 +11094,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5">
       <c r="A291" s="8">
         <v>42406</v>
       </c>
@@ -11103,7 +11112,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5">
       <c r="A292" s="8">
         <v>42413</v>
       </c>
@@ -11121,7 +11130,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5">
       <c r="A293" s="8">
         <v>42420</v>
       </c>
@@ -11139,7 +11148,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5">
       <c r="A294" s="8">
         <v>42427</v>
       </c>
@@ -11157,7 +11166,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5">
       <c r="A295" s="8">
         <v>42434</v>
       </c>
@@ -11175,7 +11184,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5">
       <c r="A296" s="8">
         <v>42441</v>
       </c>
@@ -11193,7 +11202,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5">
       <c r="A297" s="8">
         <v>42448</v>
       </c>
@@ -11211,7 +11220,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5">
       <c r="A298" s="8">
         <v>42455</v>
       </c>
@@ -11229,7 +11238,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5">
       <c r="A299" s="8">
         <v>42462</v>
       </c>
@@ -11247,7 +11256,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5">
       <c r="A300" s="8">
         <v>42469</v>
       </c>
@@ -11265,7 +11274,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5">
       <c r="A301" s="8">
         <v>42476</v>
       </c>
@@ -11283,7 +11292,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5">
       <c r="A302" s="8">
         <v>42483</v>
       </c>
@@ -11301,7 +11310,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5">
       <c r="A303" s="8">
         <v>42490</v>
       </c>
@@ -11319,7 +11328,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5">
       <c r="A304" s="8">
         <v>42497</v>
       </c>
@@ -11337,7 +11346,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5">
       <c r="A305" s="8">
         <v>42504</v>
       </c>
@@ -11355,7 +11364,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5">
       <c r="A306" s="8">
         <v>42511</v>
       </c>
@@ -11373,7 +11382,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5">
       <c r="A307" s="8">
         <v>42518</v>
       </c>
@@ -11391,7 +11400,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5">
       <c r="A308" s="8">
         <v>42525</v>
       </c>
@@ -11409,7 +11418,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5">
       <c r="A309" s="8">
         <v>42532</v>
       </c>
@@ -11427,7 +11436,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5">
       <c r="A310" s="8">
         <v>42539</v>
       </c>
@@ -11445,7 +11454,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5">
       <c r="A311" s="8">
         <v>42546</v>
       </c>
@@ -11463,7 +11472,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5">
       <c r="A312" s="8">
         <v>42553</v>
       </c>
@@ -11481,7 +11490,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5">
       <c r="A313" s="8">
         <v>42560</v>
       </c>
@@ -11499,7 +11508,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5">
       <c r="A314" s="8">
         <v>42567</v>
       </c>
@@ -11517,7 +11526,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5">
       <c r="A315" s="8">
         <v>42574</v>
       </c>
@@ -11535,7 +11544,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5">
       <c r="A316" s="8">
         <v>42581</v>
       </c>
@@ -11553,7 +11562,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5">
       <c r="A317" s="8">
         <v>42588</v>
       </c>
@@ -11571,7 +11580,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5">
       <c r="A318" s="8">
         <v>42595</v>
       </c>
@@ -11589,7 +11598,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5">
       <c r="A319" s="8">
         <v>42602</v>
       </c>
@@ -11607,7 +11616,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5">
       <c r="A320" s="8">
         <v>42609</v>
       </c>
@@ -11625,7 +11634,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5">
       <c r="A321" s="8">
         <v>42616</v>
       </c>
@@ -11643,7 +11652,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5">
       <c r="A322" s="8">
         <v>42623</v>
       </c>
@@ -11661,7 +11670,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5">
       <c r="A323" s="8">
         <v>42630</v>
       </c>
@@ -11686,7 +11695,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5">
       <c r="A324" s="8">
         <v>42637</v>
       </c>
@@ -11704,7 +11713,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5">
       <c r="A325" s="8">
         <v>42644</v>
       </c>
@@ -11722,7 +11731,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5">
       <c r="A326" s="8">
         <v>42651</v>
       </c>
@@ -11740,7 +11749,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5">
       <c r="A327" s="8">
         <v>42658</v>
       </c>
@@ -11758,7 +11767,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5">
       <c r="A328" s="8">
         <v>42665</v>
       </c>
@@ -11776,7 +11785,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5">
       <c r="A329" s="8">
         <v>42672</v>
       </c>
@@ -11794,7 +11803,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5">
       <c r="A330" s="8">
         <v>42679</v>
       </c>
@@ -11812,7 +11821,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5">
       <c r="A331" s="8">
         <v>42686</v>
       </c>
@@ -11830,7 +11839,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5">
       <c r="A332" s="8">
         <v>42693</v>
       </c>
@@ -11848,7 +11857,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5">
       <c r="A333" s="8">
         <v>42700</v>
       </c>
@@ -11866,7 +11875,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5">
       <c r="A334" s="8">
         <v>42707</v>
       </c>
@@ -11884,7 +11893,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5">
       <c r="A335" s="8">
         <v>42714</v>
       </c>
@@ -11902,7 +11911,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5">
       <c r="A336" s="8">
         <v>42721</v>
       </c>
@@ -11920,7 +11929,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5">
       <c r="A337" s="8">
         <v>42728</v>
       </c>
@@ -11938,7 +11947,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5">
       <c r="A338" s="8">
         <v>42735</v>
       </c>
@@ -11956,7 +11965,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5">
       <c r="A339" s="8">
         <v>42742</v>
       </c>
@@ -11974,7 +11983,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5">
       <c r="A340" s="8">
         <v>42749</v>
       </c>
@@ -11992,7 +12001,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5">
       <c r="A341" s="8">
         <v>42756</v>
       </c>
@@ -12010,7 +12019,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5">
       <c r="A342" s="8">
         <v>42763</v>
       </c>
@@ -12028,7 +12037,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5">
       <c r="A343" s="8">
         <v>42770</v>
       </c>
@@ -12046,7 +12055,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5">
       <c r="A344" s="8">
         <v>42777</v>
       </c>
@@ -12064,7 +12073,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5">
       <c r="A345" s="8">
         <v>42784</v>
       </c>
@@ -12082,7 +12091,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5">
       <c r="A346" s="8">
         <v>42791</v>
       </c>
@@ -12100,7 +12109,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5">
       <c r="A347" s="8">
         <v>42798</v>
       </c>
@@ -12118,7 +12127,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5">
       <c r="A348" s="8">
         <v>42805</v>
       </c>
@@ -12136,7 +12145,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5">
       <c r="A349" s="8">
         <v>42812</v>
       </c>
@@ -12154,7 +12163,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5">
       <c r="A350" s="8">
         <v>42819</v>
       </c>
@@ -12172,7 +12181,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5">
       <c r="A351" s="8">
         <v>42826</v>
       </c>
@@ -12190,7 +12199,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5">
       <c r="A352" s="8">
         <v>42833</v>
       </c>
@@ -12208,7 +12217,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5">
       <c r="A353" s="8">
         <v>42840</v>
       </c>
@@ -12226,7 +12235,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5">
       <c r="A354" s="8">
         <v>42847</v>
       </c>
@@ -12244,7 +12253,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5">
       <c r="A355" s="8">
         <v>42854</v>
       </c>
@@ -12262,7 +12271,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5">
       <c r="A356" s="8">
         <v>42861</v>
       </c>
@@ -12280,7 +12289,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5">
       <c r="A357" s="8">
         <v>42868</v>
       </c>
@@ -12298,7 +12307,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5">
       <c r="A358" s="8">
         <v>42875</v>
       </c>
@@ -12316,7 +12325,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5">
       <c r="A359" s="8">
         <v>42882</v>
       </c>
@@ -12334,7 +12343,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5">
       <c r="A360" s="8">
         <v>42889</v>
       </c>
@@ -12352,7 +12361,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5">
       <c r="A361" s="8">
         <v>42896</v>
       </c>
@@ -12370,7 +12379,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5">
       <c r="A362" s="8">
         <v>42903</v>
       </c>
@@ -12388,7 +12397,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5">
       <c r="A363" s="8">
         <v>42910</v>
       </c>
@@ -12406,7 +12415,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5">
       <c r="A364" s="8">
         <v>42917</v>
       </c>
@@ -12424,7 +12433,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5">
       <c r="A365" s="8">
         <v>42924</v>
       </c>
@@ -12442,7 +12451,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5">
       <c r="A366" s="8">
         <v>42931</v>
       </c>
@@ -12460,7 +12469,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5">
       <c r="A367" s="8">
         <v>42938</v>
       </c>
@@ -12478,7 +12487,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5">
       <c r="A368" s="8">
         <v>42945</v>
       </c>
@@ -12496,7 +12505,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5">
       <c r="A369" s="8">
         <v>42952</v>
       </c>
@@ -12514,7 +12523,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5">
       <c r="A370" s="8">
         <v>42959</v>
       </c>
@@ -12532,7 +12541,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5">
       <c r="A371" s="8">
         <v>42966</v>
       </c>
@@ -12550,7 +12559,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5">
       <c r="A372" s="8">
         <v>42973</v>
       </c>
@@ -12568,7 +12577,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5">
       <c r="A373" s="8">
         <v>42980</v>
       </c>
@@ -12586,7 +12595,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5">
       <c r="A374" s="8">
         <v>42987</v>
       </c>
@@ -12604,7 +12613,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5">
       <c r="A375" s="8">
         <v>42994</v>
       </c>
@@ -12622,7 +12631,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5">
       <c r="A376" s="8">
         <v>43001</v>
       </c>
@@ -12640,7 +12649,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5">
       <c r="A377" s="8">
         <v>43008</v>
       </c>
@@ -12658,7 +12667,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5">
       <c r="A378" s="8">
         <v>43015</v>
       </c>
@@ -12676,7 +12685,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5">
       <c r="A379" s="8">
         <v>43022</v>
       </c>
@@ -12694,7 +12703,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5">
       <c r="A380" s="8">
         <v>43029</v>
       </c>
@@ -12712,7 +12721,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5">
       <c r="A381" s="8">
         <v>43036</v>
       </c>
@@ -12730,7 +12739,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5">
       <c r="A382" s="8">
         <v>43043</v>
       </c>
@@ -12748,7 +12757,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5">
       <c r="A383" s="8">
         <v>43050</v>
       </c>
@@ -12766,7 +12775,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5">
       <c r="A384" s="8">
         <v>43057</v>
       </c>
@@ -12784,7 +12793,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5">
       <c r="A385" s="8">
         <v>43064</v>
       </c>
@@ -12802,7 +12811,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5">
       <c r="A386" s="8">
         <v>43071</v>
       </c>
@@ -12820,7 +12829,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5">
       <c r="A387" s="8">
         <v>43078</v>
       </c>
@@ -12845,7 +12854,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5">
       <c r="A388" s="8">
         <v>43085</v>
       </c>
@@ -12863,7 +12872,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5">
       <c r="A389" s="8">
         <v>43092</v>
       </c>
@@ -12881,7 +12890,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5">
       <c r="A390" s="8">
         <v>43099</v>
       </c>
@@ -12899,7 +12908,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5">
       <c r="A391" s="8">
         <v>43106</v>
       </c>
@@ -12917,7 +12926,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5">
       <c r="A392" s="8">
         <v>43113</v>
       </c>
@@ -12935,7 +12944,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5">
       <c r="A393" s="8">
         <v>43120</v>
       </c>
@@ -12953,7 +12962,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5">
       <c r="A394" s="8">
         <v>43127</v>
       </c>
@@ -12971,7 +12980,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5">
       <c r="A395" s="8">
         <v>43134</v>
       </c>
@@ -12989,7 +12998,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5">
       <c r="A396" s="8">
         <v>43141</v>
       </c>
@@ -13007,7 +13016,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5">
       <c r="A397" s="8">
         <v>43148</v>
       </c>
@@ -13025,7 +13034,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5">
       <c r="A398" s="8">
         <v>43155</v>
       </c>
@@ -13043,7 +13052,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5">
       <c r="A399" s="8">
         <v>43162</v>
       </c>
@@ -13061,7 +13070,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5">
       <c r="A400" s="8">
         <v>43169</v>
       </c>
@@ -13079,7 +13088,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5">
       <c r="A401" s="8">
         <v>43176</v>
       </c>
@@ -13097,7 +13106,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5">
       <c r="A402" s="8">
         <v>43183</v>
       </c>
@@ -13115,7 +13124,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5">
       <c r="A403" s="8">
         <v>43190</v>
       </c>
@@ -13133,7 +13142,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5">
       <c r="A404" s="8">
         <v>43197</v>
       </c>
@@ -13151,7 +13160,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5">
       <c r="A405" s="8">
         <v>43204</v>
       </c>
@@ -13169,7 +13178,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5">
       <c r="A406" s="8">
         <v>43211</v>
       </c>
@@ -13187,7 +13196,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5">
       <c r="A407" s="8">
         <v>43218</v>
       </c>
@@ -13205,7 +13214,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5">
       <c r="A408" s="8">
         <v>43225</v>
       </c>
@@ -13223,7 +13232,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5">
       <c r="A409" s="8">
         <v>43232</v>
       </c>
@@ -13241,7 +13250,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5">
       <c r="A410" s="8">
         <v>43239</v>
       </c>
@@ -13259,7 +13268,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5">
       <c r="A411" s="8">
         <v>43245</v>
       </c>
@@ -13277,7 +13286,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5">
       <c r="A412" s="8">
         <v>43252</v>
       </c>
@@ -13295,7 +13304,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5">
       <c r="A413" s="8">
         <v>43259</v>
       </c>
@@ -13313,7 +13322,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5">
       <c r="A414" s="8">
         <v>43266</v>
       </c>
@@ -13331,7 +13340,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5">
       <c r="A415" s="8">
         <v>43273</v>
       </c>
@@ -13349,7 +13358,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5">
       <c r="A416" s="8">
         <v>43280</v>
       </c>
@@ -13367,7 +13376,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5">
       <c r="A417" s="8">
         <v>43287</v>
       </c>
@@ -13385,7 +13394,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5">
       <c r="A418" s="8">
         <v>43294</v>
       </c>
@@ -13403,7 +13412,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5">
       <c r="A419" s="8">
         <v>43301</v>
       </c>
@@ -13421,7 +13430,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5">
       <c r="A420" s="8">
         <v>43308</v>
       </c>
@@ -13439,7 +13448,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5">
       <c r="A421" s="8">
         <v>43315</v>
       </c>
@@ -13457,7 +13466,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5">
       <c r="A422" s="8">
         <v>43322</v>
       </c>
@@ -13475,7 +13484,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5">
       <c r="A423" s="8">
         <v>43329</v>
       </c>
@@ -13493,7 +13502,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5">
       <c r="A424" s="8">
         <v>43336</v>
       </c>
@@ -13511,7 +13520,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5">
       <c r="A425" s="8">
         <v>43343</v>
       </c>
@@ -13529,7 +13538,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5">
       <c r="A426" s="8">
         <v>43350</v>
       </c>
@@ -13547,7 +13556,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5">
       <c r="A427" s="8">
         <v>43357</v>
       </c>
@@ -13565,7 +13574,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5">
       <c r="A428" s="8">
         <v>43364</v>
       </c>
@@ -13583,7 +13592,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5">
       <c r="A429" s="8">
         <v>43371</v>
       </c>
@@ -13601,7 +13610,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5">
       <c r="A430" s="8">
         <v>43378</v>
       </c>
@@ -13619,7 +13628,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5">
       <c r="A431" s="8">
         <v>43385</v>
       </c>
@@ -13637,7 +13646,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5">
       <c r="A432" s="8">
         <v>43392</v>
       </c>
@@ -13655,7 +13664,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5">
       <c r="A433" s="8">
         <v>43399</v>
       </c>
@@ -13673,7 +13682,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5">
       <c r="A434" s="8">
         <v>43406</v>
       </c>
@@ -13691,7 +13700,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5">
       <c r="A435" s="8">
         <v>43413</v>
       </c>
@@ -13709,7 +13718,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5">
       <c r="A436" s="8">
         <v>43420</v>
       </c>
@@ -13727,7 +13736,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5">
       <c r="A437" s="8">
         <v>43427</v>
       </c>
@@ -13745,7 +13754,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5">
       <c r="A438" s="8">
         <v>43434</v>
       </c>
@@ -13763,7 +13772,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5">
       <c r="A439" s="8">
         <v>43441</v>
       </c>
@@ -13781,7 +13790,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5">
       <c r="A440" s="8">
         <v>43448</v>
       </c>
@@ -13799,7 +13808,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5">
       <c r="A441" s="8">
         <v>43455</v>
       </c>
@@ -13817,7 +13826,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5">
       <c r="A442" s="8">
         <v>43462</v>
       </c>
@@ -13835,7 +13844,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5">
       <c r="A443" s="8">
         <v>43469</v>
       </c>
@@ -13853,7 +13862,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5">
       <c r="A444" s="8">
         <v>43476</v>
       </c>
@@ -13871,7 +13880,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5">
       <c r="A445" s="8">
         <v>43483</v>
       </c>
@@ -13889,7 +13898,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5">
       <c r="A446" s="8">
         <v>43490</v>
       </c>
@@ -13907,7 +13916,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5">
       <c r="A447" s="8">
         <v>43497</v>
       </c>
@@ -13925,7 +13934,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5">
       <c r="A448" s="8">
         <v>43504</v>
       </c>
@@ -13943,7 +13952,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5">
       <c r="A449" s="8">
         <v>43511</v>
       </c>
@@ -13961,7 +13970,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5">
       <c r="A450" s="8">
         <v>43518</v>
       </c>
@@ -13979,7 +13988,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5">
       <c r="A451" s="8">
         <v>43525</v>
       </c>
@@ -14004,7 +14013,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5">
       <c r="A452" s="8">
         <v>43532</v>
       </c>
@@ -14022,7 +14031,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5">
       <c r="A453" s="8">
         <v>43539</v>
       </c>
@@ -14040,7 +14049,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5">
       <c r="A454" s="8">
         <v>43546</v>
       </c>
@@ -14058,7 +14067,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5">
       <c r="A455" s="8">
         <v>43553</v>
       </c>
@@ -14076,7 +14085,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5">
       <c r="A456" s="8">
         <v>43560</v>
       </c>
@@ -14094,7 +14103,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5">
       <c r="A457" s="8">
         <v>43567</v>
       </c>
@@ -14112,7 +14121,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5">
       <c r="A458" s="8">
         <v>43574</v>
       </c>
@@ -14130,7 +14139,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5">
       <c r="A459" s="8">
         <v>43581</v>
       </c>
@@ -14148,7 +14157,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5">
       <c r="A460" s="8">
         <v>43588</v>
       </c>
@@ -14166,7 +14175,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5">
       <c r="A461" s="8">
         <v>43595</v>
       </c>
@@ -14184,7 +14193,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5">
       <c r="A462" s="8">
         <v>43602</v>
       </c>
@@ -14202,7 +14211,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5">
       <c r="A463" s="8">
         <v>43609</v>
       </c>
@@ -14220,7 +14229,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5">
       <c r="A464" s="8">
         <v>43616</v>
       </c>
@@ -14238,7 +14247,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5">
       <c r="A465" s="8">
         <v>43623</v>
       </c>
@@ -14256,7 +14265,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5">
       <c r="A466" s="8">
         <v>43630</v>
       </c>
@@ -14274,7 +14283,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5">
       <c r="A467" s="8">
         <v>43637</v>
       </c>
@@ -14292,7 +14301,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5">
       <c r="A468" s="8">
         <v>43644</v>
       </c>
@@ -14310,7 +14319,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5">
       <c r="A469" s="8">
         <v>43651</v>
       </c>
@@ -14328,7 +14337,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5">
       <c r="A470" s="8">
         <v>43658</v>
       </c>
@@ -14346,7 +14355,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5">
       <c r="A471" s="8">
         <v>43665</v>
       </c>
@@ -14364,7 +14373,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5">
       <c r="A472" s="8">
         <v>43672</v>
       </c>
@@ -14382,7 +14391,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5">
       <c r="A473" s="8">
         <v>43679</v>
       </c>
@@ -14400,7 +14409,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5">
       <c r="A474" s="8">
         <v>43686</v>
       </c>
@@ -14418,7 +14427,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5">
       <c r="A475" s="8">
         <v>43693</v>
       </c>
@@ -14436,7 +14445,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5">
       <c r="A476" s="8">
         <v>43700</v>
       </c>
@@ -14454,7 +14463,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5">
       <c r="A477" s="8">
         <v>43707</v>
       </c>
@@ -14472,7 +14481,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5">
       <c r="A478" s="8">
         <v>43714</v>
       </c>
@@ -14490,7 +14499,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5">
       <c r="A479" s="8">
         <v>43721</v>
       </c>
@@ -14508,7 +14517,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5">
       <c r="A480" s="8">
         <v>43728</v>
       </c>
@@ -14526,7 +14535,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5">
       <c r="A481" s="8">
         <v>43735</v>
       </c>
@@ -14544,7 +14553,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5">
       <c r="A482" s="8">
         <v>43742</v>
       </c>
@@ -14562,7 +14571,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5">
       <c r="A483" s="8">
         <v>43749</v>
       </c>
@@ -14580,7 +14589,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5">
       <c r="A484" s="8">
         <v>43756</v>
       </c>
@@ -14598,7 +14607,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5">
       <c r="A485" s="8">
         <v>43763</v>
       </c>
@@ -14616,7 +14625,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5">
       <c r="A486" s="8">
         <v>43770</v>
       </c>
@@ -14634,7 +14643,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5">
       <c r="A487" s="8">
         <v>43777</v>
       </c>
@@ -14652,7 +14661,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5">
       <c r="A488" s="8">
         <v>43784</v>
       </c>
@@ -14670,7 +14679,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5">
       <c r="A489" s="8">
         <v>43791</v>
       </c>
@@ -14688,7 +14697,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5">
       <c r="A490" s="8">
         <v>43798</v>
       </c>
@@ -14706,7 +14715,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5">
       <c r="A491" s="8">
         <v>43805</v>
       </c>
@@ -14724,7 +14733,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5">
       <c r="A492" s="8">
         <v>43812</v>
       </c>
@@ -14742,7 +14751,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5">
       <c r="A493" s="8">
         <v>43819</v>
       </c>
@@ -14760,7 +14769,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5">
       <c r="A494" s="8">
         <v>43826</v>
       </c>
@@ -14778,7 +14787,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5">
       <c r="A495" s="8">
         <v>43833</v>
       </c>
@@ -14796,7 +14805,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5">
       <c r="A496" s="8">
         <v>43840</v>
       </c>
@@ -14814,7 +14823,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5">
       <c r="A497" s="8">
         <v>43847</v>
       </c>
@@ -14832,7 +14841,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5">
       <c r="A498" s="8">
         <v>43854</v>
       </c>
@@ -14850,7 +14859,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5">
       <c r="A499" s="8">
         <v>43861</v>
       </c>
@@ -14868,7 +14877,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5">
       <c r="A500" s="8">
         <v>43868</v>
       </c>
@@ -14886,7 +14895,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5">
       <c r="A501" s="8">
         <v>43875</v>
       </c>
@@ -14904,7 +14913,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5">
       <c r="A502" s="8">
         <v>43882</v>
       </c>
@@ -14922,7 +14931,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5">
       <c r="A503" s="8">
         <v>43889</v>
       </c>
@@ -14940,7 +14949,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5">
       <c r="A504" s="8">
         <v>43896</v>
       </c>
@@ -14958,7 +14967,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5">
       <c r="A505" s="8">
         <v>43903</v>
       </c>
@@ -14976,7 +14985,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5">
       <c r="A506" s="8">
         <v>43910</v>
       </c>
@@ -14994,7 +15003,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5">
       <c r="A507" s="8">
         <v>43917</v>
       </c>
@@ -15012,7 +15021,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5">
       <c r="A508" s="8">
         <v>43924</v>
       </c>
@@ -15030,7 +15039,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5">
       <c r="A509" s="8">
         <v>43931</v>
       </c>
@@ -15048,7 +15057,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5">
       <c r="A510" s="8">
         <v>43938</v>
       </c>
@@ -15066,7 +15075,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5">
       <c r="A511" s="8">
         <v>43945</v>
       </c>
@@ -15084,7 +15093,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5">
       <c r="A512" s="8">
         <v>43952</v>
       </c>
@@ -15102,7 +15111,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5">
       <c r="A513" s="8">
         <v>43959</v>
       </c>
@@ -15120,7 +15129,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5">
       <c r="A514" s="8">
         <v>43966</v>
       </c>
@@ -15138,7 +15147,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5">
       <c r="A515" s="8">
         <v>43973</v>
       </c>
@@ -15163,7 +15172,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5">
       <c r="A516" s="8">
         <v>43980</v>
       </c>
@@ -15181,7 +15190,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5">
       <c r="A517" s="8">
         <v>43987</v>
       </c>
@@ -15199,7 +15208,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5">
       <c r="A518" s="8">
         <v>43994</v>
       </c>
@@ -15217,7 +15226,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5">
       <c r="A519" s="8">
         <v>44001</v>
       </c>
@@ -15235,7 +15244,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5">
       <c r="A520" s="8">
         <v>44008</v>
       </c>
@@ -15253,7 +15262,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5">
       <c r="A521" s="8">
         <v>44015</v>
       </c>
@@ -15271,7 +15280,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5">
       <c r="A522" s="8">
         <v>44022</v>
       </c>
@@ -15289,7 +15298,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5">
       <c r="A523" s="8">
         <v>44029</v>
       </c>
@@ -15307,7 +15316,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5">
       <c r="A524" s="8">
         <v>44036</v>
       </c>
@@ -15325,7 +15334,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5">
       <c r="A525" s="8">
         <v>44043</v>
       </c>
@@ -15343,7 +15352,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5">
       <c r="A526" s="8">
         <v>44050</v>
       </c>
@@ -15361,7 +15370,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5">
       <c r="A527" s="8">
         <v>44057</v>
       </c>
@@ -15379,7 +15388,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5">
       <c r="A528" s="8">
         <v>44064</v>
       </c>
@@ -15397,7 +15406,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5">
       <c r="A529" s="8">
         <v>44071</v>
       </c>
@@ -15415,7 +15424,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5">
       <c r="A530" s="8">
         <v>44078</v>
       </c>
@@ -15433,7 +15442,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5">
       <c r="A531" s="8">
         <v>44085</v>
       </c>
@@ -15451,7 +15460,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5">
       <c r="A532" s="8">
         <v>44092</v>
       </c>
@@ -15469,7 +15478,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5">
       <c r="A533" s="8">
         <v>44099</v>
       </c>
@@ -15487,7 +15496,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5">
       <c r="A534" s="8">
         <v>44106</v>
       </c>
@@ -15505,7 +15514,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5">
       <c r="A535" s="8">
         <v>44113</v>
       </c>
@@ -15523,7 +15532,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5">
       <c r="A536" s="8">
         <v>44120</v>
       </c>
@@ -15541,7 +15550,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5">
       <c r="A537" s="8">
         <v>44127</v>
       </c>
@@ -15559,7 +15568,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5">
       <c r="A538" s="8">
         <v>44134</v>
       </c>
@@ -15577,7 +15586,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5">
       <c r="A539" s="8">
         <v>44141</v>
       </c>
@@ -15595,7 +15604,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5">
       <c r="A540" s="8">
         <v>44148</v>
       </c>
@@ -15613,7 +15622,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5">
       <c r="A541" s="8">
         <v>44155</v>
       </c>
@@ -15631,7 +15640,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5">
       <c r="A542" s="8">
         <v>44162</v>
       </c>
@@ -15649,7 +15658,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5">
       <c r="A543" s="8">
         <v>44169</v>
       </c>
@@ -15667,7 +15676,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5">
       <c r="A544" s="8">
         <v>44176</v>
       </c>
@@ -15685,7 +15694,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5">
       <c r="A545" s="8">
         <v>44183</v>
       </c>
@@ -15703,7 +15712,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5">
       <c r="A546" s="8">
         <v>44190</v>
       </c>
@@ -15721,7 +15730,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5">
       <c r="A547" s="8">
         <v>44197</v>
       </c>
@@ -15739,7 +15748,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5">
       <c r="A548" s="8">
         <v>44204</v>
       </c>
@@ -15757,7 +15766,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5">
       <c r="A549" s="8">
         <v>44211</v>
       </c>
@@ -15775,7 +15784,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5">
       <c r="A550" s="8">
         <v>44218</v>
       </c>
@@ -15793,7 +15802,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5">
       <c r="A551" s="8">
         <v>44225</v>
       </c>
@@ -15811,7 +15820,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5">
       <c r="A552" s="8">
         <v>44232</v>
       </c>
@@ -15829,7 +15838,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5">
       <c r="A553" s="8">
         <v>44239</v>
       </c>
@@ -15847,7 +15856,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5">
       <c r="A554" s="8">
         <v>44246</v>
       </c>
@@ -15865,7 +15874,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5">
       <c r="A555" s="8">
         <v>44253</v>
       </c>
@@ -15883,7 +15892,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5">
       <c r="A556" s="8">
         <v>44260</v>
       </c>
@@ -15901,7 +15910,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5">
       <c r="A557" s="8">
         <v>44267</v>
       </c>
@@ -15919,7 +15928,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5">
       <c r="A558" s="8">
         <v>44274</v>
       </c>
@@ -15937,7 +15946,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5">
       <c r="A559" s="8">
         <v>44281</v>
       </c>
@@ -15955,7 +15964,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5">
       <c r="A560" s="8">
         <v>44288</v>
       </c>
@@ -15973,7 +15982,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5">
       <c r="A561" s="8">
         <v>44295</v>
       </c>
@@ -15991,7 +16000,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5">
       <c r="A562" s="8">
         <v>44302</v>
       </c>
@@ -16009,7 +16018,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5">
       <c r="A563" s="8">
         <v>44309</v>
       </c>
@@ -16027,7 +16036,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5">
       <c r="A564" s="8">
         <v>44316</v>
       </c>
@@ -16045,7 +16054,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5">
       <c r="A565" s="8">
         <v>44323</v>
       </c>
@@ -16063,7 +16072,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5">
       <c r="A566" s="8">
         <v>44330</v>
       </c>
@@ -16081,7 +16090,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5">
       <c r="A567" s="8">
         <v>44337</v>
       </c>
@@ -16099,7 +16108,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5">
       <c r="A568" s="8">
         <v>44344</v>
       </c>
@@ -16117,7 +16126,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5">
       <c r="A569" s="8">
         <v>44351</v>
       </c>
@@ -16135,7 +16144,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5">
       <c r="A570" s="8">
         <v>44358</v>
       </c>
@@ -16153,7 +16162,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5">
       <c r="A571" s="8">
         <v>44365</v>
       </c>
@@ -16171,7 +16180,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5">
       <c r="A572" s="8">
         <v>44372</v>
       </c>
@@ -16189,7 +16198,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5">
       <c r="A573" s="8">
         <v>44379</v>
       </c>
@@ -16207,7 +16216,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5">
       <c r="A574" s="8">
         <v>44386</v>
       </c>
@@ -16225,7 +16234,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5">
       <c r="A575" s="8">
         <v>44393</v>
       </c>
@@ -16243,7 +16252,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5">
       <c r="A576" s="8">
         <v>44400</v>
       </c>
@@ -16261,7 +16270,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5">
       <c r="A577" s="8">
         <v>44407</v>
       </c>
@@ -16279,7 +16288,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5">
       <c r="A578" s="8">
         <v>44414</v>
       </c>
@@ -16297,7 +16306,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5">
       <c r="A579" s="8">
         <v>44421</v>
       </c>
@@ -16322,7 +16331,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5">
       <c r="A580" s="8">
         <v>44428</v>
       </c>
@@ -16340,7 +16349,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5">
       <c r="A581" s="8">
         <v>44435</v>
       </c>
@@ -16358,7 +16367,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5">
       <c r="A582" s="8">
         <v>44442</v>
       </c>
@@ -16376,7 +16385,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5">
       <c r="A583" s="8">
         <v>44449</v>
       </c>
@@ -16394,7 +16403,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5">
       <c r="A584" s="8">
         <v>44456</v>
       </c>
@@ -16412,7 +16421,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5">
       <c r="A585" s="8">
         <v>44463</v>
       </c>
@@ -16430,7 +16439,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5">
       <c r="A586" s="8">
         <v>44470</v>
       </c>
@@ -16448,7 +16457,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5">
       <c r="A587" s="8">
         <v>44477</v>
       </c>
@@ -16466,7 +16475,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5">
       <c r="A588" s="8">
         <v>44484</v>
       </c>
@@ -16484,7 +16493,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5">
       <c r="A589" s="8">
         <v>44491</v>
       </c>
@@ -16502,7 +16511,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5">
       <c r="A590" s="8">
         <v>44498</v>
       </c>
@@ -16520,7 +16529,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5">
       <c r="A591" s="8">
         <v>44505</v>
       </c>
@@ -16538,7 +16547,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5">
       <c r="A592" s="8">
         <v>44512</v>
       </c>
@@ -16556,7 +16565,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4">
       <c r="A593" s="8">
         <v>44519</v>
       </c>
@@ -16571,7 +16580,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4">
       <c r="A594" s="8">
         <v>44526</v>
       </c>
@@ -16586,7 +16595,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4">
       <c r="A595" s="8">
         <v>44533</v>
       </c>
@@ -16601,7 +16610,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4">
       <c r="A596" s="8">
         <v>44540</v>
       </c>
@@ -16616,7 +16625,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4">
       <c r="A597" s="8">
         <v>44547</v>
       </c>
@@ -16631,7 +16640,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4">
       <c r="A598" s="8">
         <v>44554</v>
       </c>
@@ -16646,7 +16655,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4">
       <c r="A599" s="8">
         <v>44561</v>
       </c>
@@ -16661,7 +16670,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4">
       <c r="A600" s="8">
         <v>44568</v>
       </c>
@@ -16676,7 +16685,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4">
       <c r="A601" s="8">
         <v>44575</v>
       </c>
@@ -16691,7 +16700,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4">
       <c r="A602" s="8">
         <v>44582</v>
       </c>
@@ -16706,7 +16715,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4">
       <c r="A603" s="8">
         <v>44589</v>
       </c>
@@ -16721,7 +16730,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4">
       <c r="A604" s="8">
         <v>44596</v>
       </c>
@@ -16736,7 +16745,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4">
       <c r="A605" s="8">
         <v>44603</v>
       </c>
@@ -16751,7 +16760,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4">
       <c r="A606" s="8">
         <v>44610</v>
       </c>
@@ -16766,7 +16775,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4">
       <c r="A607" s="8">
         <v>44617</v>
       </c>
@@ -16781,7 +16790,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4">
       <c r="A608" s="8">
         <v>44624</v>
       </c>
@@ -16796,7 +16805,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4">
       <c r="A609" s="8">
         <v>44631</v>
       </c>
@@ -16811,7 +16820,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4">
       <c r="A610" s="8">
         <v>44638</v>
       </c>
@@ -16826,7 +16835,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4">
       <c r="A611" s="8">
         <v>44645</v>
       </c>
@@ -16841,7 +16850,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4">
       <c r="A612" s="8">
         <v>44652</v>
       </c>
@@ -16856,7 +16865,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4">
       <c r="A613" s="8">
         <v>44659</v>
       </c>
@@ -16871,7 +16880,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4">
       <c r="A614" s="8">
         <v>44666</v>
       </c>
@@ -16886,7 +16895,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4">
       <c r="A615" s="8">
         <v>44673</v>
       </c>
@@ -16901,7 +16910,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4">
       <c r="A616" s="8">
         <v>44680</v>
       </c>
@@ -16916,7 +16925,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4">
       <c r="A617" s="8">
         <v>44687</v>
       </c>
@@ -16931,7 +16940,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4">
       <c r="A618" s="8">
         <v>44694</v>
       </c>
@@ -16946,7 +16955,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4">
       <c r="A619" s="8">
         <v>44701</v>
       </c>
@@ -16961,7 +16970,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4">
       <c r="A620" s="8">
         <v>44708</v>
       </c>
@@ -16976,7 +16985,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4">
       <c r="A621" s="8">
         <v>44715</v>
       </c>
@@ -16991,7 +17000,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4">
       <c r="A622" s="8">
         <v>44722</v>
       </c>
@@ -17006,7 +17015,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4">
       <c r="A623" s="8">
         <v>44729</v>
       </c>
@@ -17021,7 +17030,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4">
       <c r="A624" s="8">
         <v>44736</v>
       </c>
@@ -17036,7 +17045,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4">
       <c r="A625" s="8">
         <v>44743</v>
       </c>
@@ -17051,7 +17060,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4">
       <c r="A626" s="8">
         <v>44750</v>
       </c>
@@ -17066,7 +17075,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4">
       <c r="A627" s="8">
         <v>44757</v>
       </c>
@@ -17081,7 +17090,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4">
       <c r="A628" s="8">
         <v>44764</v>
       </c>
@@ -17096,7 +17105,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4">
       <c r="A629" s="8">
         <v>44771</v>
       </c>
@@ -17111,7 +17120,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4">
       <c r="A630" s="8">
         <v>44778</v>
       </c>
@@ -17126,7 +17135,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4">
       <c r="A631" s="8">
         <v>44785</v>
       </c>
@@ -17141,7 +17150,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4">
       <c r="A632" s="8">
         <v>44792</v>
       </c>
@@ -17156,7 +17165,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4">
       <c r="A633" s="8">
         <v>44799</v>
       </c>
@@ -17171,7 +17180,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4">
       <c r="A634" s="8">
         <v>44806</v>
       </c>
@@ -17186,7 +17195,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4">
       <c r="A635" s="8">
         <v>44813</v>
       </c>
@@ -17201,7 +17210,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4">
       <c r="A636" s="8">
         <v>44820</v>
       </c>
@@ -17216,7 +17225,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4">
       <c r="A637" s="8">
         <v>44827</v>
       </c>
@@ -17231,7 +17240,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4">
       <c r="A638" s="8">
         <v>44834</v>
       </c>
@@ -17246,7 +17255,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4">
       <c r="A639" s="8">
         <v>44841</v>
       </c>
@@ -17261,7 +17270,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4">
       <c r="A640" s="8">
         <v>44848</v>
       </c>
@@ -17276,7 +17285,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4">
       <c r="A641" s="8">
         <v>44855</v>
       </c>
@@ -17291,7 +17300,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4">
       <c r="A642" s="8">
         <v>44862</v>
       </c>
@@ -17306,7 +17315,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4">
       <c r="A643" s="8">
         <v>44869</v>
       </c>
@@ -17328,7 +17337,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4">
       <c r="A644" s="8">
         <v>44876</v>
       </c>
@@ -17343,7 +17352,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4">
       <c r="A645" s="8">
         <v>44883</v>
       </c>
@@ -17358,7 +17367,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4">
       <c r="A646" s="8">
         <v>44890</v>
       </c>
@@ -17373,7 +17382,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4">
       <c r="A647" s="8">
         <v>44897</v>
       </c>
@@ -17388,7 +17397,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4">
       <c r="A648" s="8">
         <v>44904</v>
       </c>
@@ -17403,7 +17412,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4">
       <c r="A649" s="8">
         <v>44911</v>
       </c>
@@ -17418,7 +17427,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4">
       <c r="A650" s="8">
         <v>44918</v>
       </c>
@@ -17433,7 +17442,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4">
       <c r="A651" s="8">
         <v>44925</v>
       </c>
@@ -17448,7 +17457,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4">
       <c r="A652" s="8">
         <v>44932</v>
       </c>
@@ -17463,7 +17472,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4">
       <c r="A653" s="8">
         <v>44939</v>
       </c>
@@ -17478,7 +17487,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4">
       <c r="A654" s="8">
         <v>44946</v>
       </c>
@@ -17493,7 +17502,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4">
       <c r="A655" s="8">
         <v>44953</v>
       </c>
@@ -17508,7 +17517,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4">
       <c r="A656" s="8">
         <v>44960</v>
       </c>
@@ -17523,7 +17532,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4">
       <c r="A657" s="8">
         <v>44967</v>
       </c>
@@ -17538,7 +17547,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4">
       <c r="A658" s="8">
         <v>44974</v>
       </c>
@@ -17553,7 +17562,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4">
       <c r="A659" s="8">
         <v>44981</v>
       </c>
@@ -17568,7 +17577,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4">
       <c r="A660" s="8">
         <v>44988</v>
       </c>
@@ -17583,7 +17592,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4">
       <c r="A661" s="8">
         <v>44995</v>
       </c>
@@ -17598,7 +17607,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4">
       <c r="A662" s="8">
         <v>45002</v>
       </c>
@@ -17613,7 +17622,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4">
       <c r="A663" s="8">
         <v>45009</v>
       </c>
@@ -17628,7 +17637,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4">
       <c r="A664" s="8">
         <v>45016</v>
       </c>
@@ -17643,7 +17652,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4">
       <c r="A665" s="8">
         <v>45023</v>
       </c>
@@ -17658,7 +17667,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4">
       <c r="A666" s="8">
         <v>45030</v>
       </c>
@@ -17673,7 +17682,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4">
       <c r="A667" s="8">
         <v>45037</v>
       </c>
@@ -17688,7 +17697,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4">
       <c r="A668" s="8">
         <v>45044</v>
       </c>
@@ -17703,7 +17712,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4">
       <c r="A669" s="8">
         <v>45051</v>
       </c>
@@ -17718,7 +17727,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4">
       <c r="A670" s="8">
         <v>45058</v>
       </c>
@@ -17733,7 +17742,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4">
       <c r="A671" s="8">
         <v>45065</v>
       </c>
@@ -17748,7 +17757,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4">
       <c r="A672" s="8">
         <v>45072</v>
       </c>
@@ -17763,7 +17772,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4">
       <c r="A673" s="8">
         <v>45079</v>
       </c>
@@ -17778,7 +17787,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4">
       <c r="A674" s="8">
         <v>45086</v>
       </c>
@@ -17793,7 +17802,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4">
       <c r="A675" s="8">
         <v>45093</v>
       </c>
@@ -17808,7 +17817,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4">
       <c r="A676" s="8">
         <v>45100</v>
       </c>
@@ -17823,7 +17832,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4">
       <c r="A677" s="8">
         <v>45107</v>
       </c>
@@ -17838,7 +17847,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4">
       <c r="A678" s="8">
         <v>45114</v>
       </c>
@@ -17853,7 +17862,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4">
       <c r="A679" s="8">
         <v>45121</v>
       </c>
@@ -17868,7 +17877,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4">
       <c r="A680" s="8">
         <v>45128</v>
       </c>
@@ -17883,7 +17892,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4">
       <c r="A681" s="8">
         <v>45135</v>
       </c>
@@ -17898,7 +17907,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4">
       <c r="A682" s="8">
         <v>45142</v>
       </c>
@@ -17913,7 +17922,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4">
       <c r="A683" s="8">
         <v>45149</v>
       </c>
@@ -17928,7 +17937,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4">
       <c r="A684" s="8">
         <v>45156</v>
       </c>
@@ -17943,7 +17952,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4">
       <c r="A685" s="8">
         <v>45163</v>
       </c>
@@ -17958,7 +17967,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:4">
       <c r="A686" s="8">
         <v>45170</v>
       </c>
@@ -17973,7 +17982,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:4">
       <c r="A687" s="8">
         <v>45177</v>
       </c>
@@ -17988,7 +17997,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:4">
       <c r="A688" s="8">
         <v>45184</v>
       </c>
@@ -18003,7 +18012,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:4">
       <c r="A689" s="8">
         <v>45191</v>
       </c>
@@ -18018,7 +18027,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:4">
       <c r="A690" s="8">
         <v>45198</v>
       </c>
@@ -18033,7 +18042,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:4">
       <c r="A691" s="8">
         <v>45205</v>
       </c>
@@ -18048,7 +18057,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:4">
       <c r="A692" s="8">
         <v>45212</v>
       </c>
@@ -18063,7 +18072,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:4">
       <c r="A693" s="8">
         <v>45219</v>
       </c>
@@ -18078,7 +18087,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:4">
       <c r="A694" s="8">
         <v>45226</v>
       </c>
@@ -18093,7 +18102,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:4">
       <c r="A695" s="8">
         <v>45233</v>
       </c>
@@ -18108,7 +18117,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:4">
       <c r="A696" s="8">
         <v>45240</v>
       </c>
@@ -18123,7 +18132,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:4">
       <c r="A697" s="8">
         <v>45247</v>
       </c>
@@ -18138,7 +18147,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:4">
       <c r="A698" s="8">
         <v>45254</v>
       </c>
@@ -18153,7 +18162,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4">
       <c r="A699" s="8">
         <v>45261</v>
       </c>
@@ -18168,7 +18177,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:4">
       <c r="A700" s="8">
         <v>45268</v>
       </c>
@@ -18183,7 +18192,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:4">
       <c r="A701" s="8">
         <v>45275</v>
       </c>
@@ -18198,7 +18207,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:4">
       <c r="A702" s="8">
         <v>45282</v>
       </c>
@@ -18213,7 +18222,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:4">
       <c r="A703" s="8">
         <v>45289</v>
       </c>
@@ -18228,7 +18237,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:4">
       <c r="A704" s="8">
         <v>45296</v>
       </c>
@@ -18243,7 +18252,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:4">
       <c r="A705" s="8">
         <v>45303</v>
       </c>
@@ -18258,7 +18267,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:4">
       <c r="A706" s="8">
         <v>45310</v>
       </c>
@@ -18273,7 +18282,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:4">
       <c r="A707" s="8">
         <v>45317</v>
       </c>
@@ -18295,7 +18304,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:4">
       <c r="A708" s="8">
         <v>45324</v>
       </c>
@@ -18310,7 +18319,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:4">
       <c r="A709" s="8">
         <v>45331</v>
       </c>
@@ -18325,7 +18334,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:4">
       <c r="A710" s="8">
         <v>45338</v>
       </c>
@@ -18340,7 +18349,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:4">
       <c r="A711" s="8">
         <v>45345</v>
       </c>
@@ -18355,7 +18364,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:4">
       <c r="A712" s="8">
         <v>45352</v>
       </c>
@@ -18370,7 +18379,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:4">
       <c r="A713" s="8">
         <v>45359</v>
       </c>
@@ -18385,7 +18394,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:4">
       <c r="A714" s="8">
         <v>45366</v>
       </c>
@@ -18400,7 +18409,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:4">
       <c r="A715" s="8">
         <v>45373</v>
       </c>
@@ -18415,7 +18424,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:4">
       <c r="A716" s="8">
         <v>45380</v>
       </c>
@@ -18430,7 +18439,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:4">
       <c r="A717" s="8">
         <v>45387</v>
       </c>
@@ -18445,7 +18454,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:4">
       <c r="A718" s="8">
         <v>45394</v>
       </c>
@@ -18460,7 +18469,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:4">
       <c r="A719" s="8">
         <v>45401</v>
       </c>
@@ -18475,7 +18484,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:4">
       <c r="A720" s="8">
         <v>45408</v>
       </c>
@@ -18490,7 +18499,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5">
       <c r="A721" s="8">
         <v>45415</v>
       </c>
@@ -18505,7 +18514,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5">
       <c r="A722" s="8">
         <v>45422</v>
       </c>
@@ -18520,7 +18529,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5">
       <c r="A723" s="8">
         <v>45429</v>
       </c>
@@ -18535,7 +18544,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5">
       <c r="A724" s="8">
         <v>45436</v>
       </c>
@@ -18550,7 +18559,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5">
       <c r="A725" s="8">
         <v>45443</v>
       </c>
@@ -18565,7 +18574,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5">
       <c r="A726" s="8">
         <v>45450</v>
       </c>
@@ -18580,7 +18589,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5">
       <c r="A727" s="8">
         <v>45457</v>
       </c>
@@ -18595,7 +18604,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5">
       <c r="A728" s="8">
         <v>45464</v>
       </c>
@@ -18613,7 +18622,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5">
       <c r="A729" s="8">
         <v>45471</v>
       </c>
@@ -18631,7 +18640,7 @@
         <v>1712.39</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5">
       <c r="A730" s="8">
         <v>45478</v>
       </c>
@@ -18646,7 +18655,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5">
       <c r="A731" s="8">
         <v>45485</v>
       </c>
@@ -18661,7 +18670,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5">
       <c r="A732" s="8">
         <v>45492</v>
       </c>
@@ -18676,7 +18685,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5">
       <c r="A733" s="8">
         <v>45499</v>
       </c>
@@ -18691,7 +18700,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5">
       <c r="A734" s="8">
         <v>45506</v>
       </c>
@@ -18706,7 +18715,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5">
       <c r="A735" s="8">
         <v>45513</v>
       </c>
@@ -18721,7 +18730,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5">
       <c r="A736" s="8">
         <v>45520</v>
       </c>
@@ -18736,7 +18745,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5">
       <c r="A737" s="8">
         <v>45527</v>
       </c>
@@ -18751,7 +18760,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5">
       <c r="A738" s="8">
         <v>45534</v>
       </c>
@@ -18766,7 +18775,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5">
       <c r="A739" s="8">
         <v>45541</v>
       </c>
@@ -18781,7 +18790,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5">
       <c r="A740" s="8">
         <v>45548</v>
       </c>
@@ -18796,7 +18805,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5">
       <c r="A741" s="8">
         <v>45555</v>
       </c>
@@ -18811,7 +18820,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5">
       <c r="A742" s="8">
         <v>45562</v>
       </c>
@@ -18826,7 +18835,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5">
       <c r="A743" s="8">
         <v>45569</v>
       </c>
@@ -18844,7 +18853,7 @@
         <v>1936.04</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5">
       <c r="A744" s="8">
         <v>45576</v>
       </c>
@@ -18859,7 +18868,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5">
       <c r="A745" s="8">
         <v>45583</v>
       </c>
@@ -18874,7 +18883,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5">
       <c r="A746" s="8">
         <v>45590</v>
       </c>
@@ -18889,7 +18898,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5">
       <c r="A747" s="8">
         <v>45597</v>
       </c>
@@ -18904,7 +18913,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5">
       <c r="A748" s="8">
         <v>45604</v>
       </c>
@@ -18919,7 +18928,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5">
       <c r="A749" s="8">
         <v>45611</v>
       </c>
@@ -18934,7 +18943,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5">
       <c r="A750" s="8">
         <v>45618</v>
       </c>
@@ -18949,7 +18958,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5">
       <c r="A751" s="8">
         <v>45625</v>
       </c>
@@ -18964,7 +18973,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5">
       <c r="A752" s="8">
         <v>45632</v>
       </c>
@@ -18979,7 +18988,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:4">
       <c r="A753" s="8">
         <v>45639</v>
       </c>
@@ -18994,7 +19003,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:4">
       <c r="A754" s="8">
         <v>45646</v>
       </c>
@@ -19009,7 +19018,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:4">
       <c r="A755" s="8">
         <v>45653</v>
       </c>
@@ -19024,7 +19033,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:4">
       <c r="A756" s="8">
         <v>45660</v>
       </c>
@@ -19039,7 +19048,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:4">
       <c r="A757" s="8">
         <v>45667</v>
       </c>
@@ -19054,7 +19063,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:4">
       <c r="A758" s="8">
         <v>45674</v>
       </c>
@@ -19069,7 +19078,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:4">
       <c r="A759" s="8">
         <v>45681</v>
       </c>
@@ -19084,7 +19093,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:4">
       <c r="A760" s="8">
         <v>45688</v>
       </c>
@@ -19099,7 +19108,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:4">
       <c r="A761" s="8">
         <v>45695</v>
       </c>
@@ -19114,7 +19123,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:4">
       <c r="A762" s="8">
         <v>45702</v>
       </c>
@@ -19129,7 +19138,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:4">
       <c r="A763" s="8">
         <v>45709</v>
       </c>
@@ -19144,7 +19153,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:4">
       <c r="A764" s="8">
         <v>45716</v>
       </c>
@@ -19159,7 +19168,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:4">
       <c r="A765" s="8">
         <v>45723</v>
       </c>
@@ -19174,7 +19183,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:4">
       <c r="A766" s="8">
         <v>45730</v>
       </c>
@@ -19189,7 +19198,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:4">
       <c r="A767" s="8">
         <v>45737</v>
       </c>
@@ -19204,7 +19213,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:4">
       <c r="A768" s="8">
         <v>45744</v>
       </c>
@@ -19219,7 +19228,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5">
       <c r="A769" s="8">
         <v>45751</v>
       </c>
@@ -19234,7 +19243,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5">
       <c r="A770" s="8">
         <v>45758</v>
       </c>
@@ -19249,7 +19258,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5">
       <c r="A771" s="8">
         <v>45765</v>
       </c>
@@ -19271,7 +19280,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5">
       <c r="A772" s="8">
         <v>45772</v>
       </c>
@@ -19286,7 +19295,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5">
       <c r="A773" s="8">
         <v>45779</v>
       </c>
@@ -19301,7 +19310,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5">
       <c r="A774" s="8">
         <v>45786</v>
       </c>
@@ -19316,7 +19325,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5">
       <c r="A775" s="8">
         <v>45793</v>
       </c>
@@ -19331,7 +19340,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5">
       <c r="A776" s="8">
         <v>45800</v>
       </c>
@@ -19346,7 +19355,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5">
       <c r="A777" s="8">
         <v>45807</v>
       </c>
@@ -19361,7 +19370,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5">
       <c r="A778" s="8">
         <v>45814</v>
       </c>
@@ -19376,7 +19385,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5">
       <c r="A779" s="8">
         <v>45821</v>
       </c>
@@ -19391,7 +19400,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5">
       <c r="A780" s="8">
         <v>45828</v>
       </c>
@@ -19409,7 +19418,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5">
       <c r="A781" s="8">
         <v>45835</v>
       </c>
@@ -19427,7 +19436,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5">
       <c r="A782" s="8">
         <v>45842</v>
       </c>
@@ -19445,7 +19454,7 @@
         <v>2164.15</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5">
       <c r="A783" s="8">
         <v>45849</v>
       </c>
@@ -19459,8 +19468,11 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E783" s="10">
+        <v>2164.9</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5">
       <c r="A784" s="8">
         <v>45856</v>
       </c>
@@ -19475,7 +19487,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:4">
       <c r="A785" s="8">
         <v>45863</v>
       </c>
@@ -19490,7 +19502,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:4">
       <c r="A786" s="8">
         <v>45870</v>
       </c>
@@ -19505,7 +19517,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:4">
       <c r="A787" s="8">
         <v>45877</v>
       </c>
@@ -19520,7 +19532,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:4">
       <c r="A788" s="8">
         <v>45884</v>
       </c>
@@ -19535,7 +19547,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:4">
       <c r="A789" s="8">
         <v>45891</v>
       </c>
@@ -19550,7 +19562,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:4">
       <c r="A790" s="8">
         <v>45898</v>
       </c>
@@ -19565,7 +19577,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:4">
       <c r="A791" s="8">
         <v>45905</v>
       </c>
@@ -19580,7 +19592,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:4">
       <c r="A792" s="8">
         <v>45912</v>
       </c>
@@ -19595,7 +19607,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:4">
       <c r="A793" s="8">
         <v>45919</v>
       </c>
@@ -19610,7 +19622,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:4">
       <c r="A794" s="8">
         <v>45926</v>
       </c>
@@ -19625,7 +19637,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="795" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4">
       <c r="A795" s="8">
         <v>45933</v>
       </c>
@@ -19640,7 +19652,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="796" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:4">
       <c r="A796" s="8">
         <v>45940</v>
       </c>
@@ -19655,7 +19667,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="797" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:4">
       <c r="A797" s="8">
         <v>45947</v>
       </c>
@@ -19670,7 +19682,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="798" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:4">
       <c r="A798" s="8">
         <v>45954</v>
       </c>
@@ -19685,7 +19697,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:4">
       <c r="A799" s="8">
         <v>45961</v>
       </c>
@@ -19700,7 +19712,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:4">
       <c r="A800" s="8">
         <v>45968</v>
       </c>
@@ -19715,7 +19727,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15">
       <c r="A801" s="8">
         <v>45975</v>
       </c>
@@ -19730,7 +19742,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15">
       <c r="A802" s="8">
         <v>45982</v>
       </c>
@@ -19745,7 +19757,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15">
       <c r="A803" s="8">
         <v>45989</v>
       </c>
@@ -19760,7 +19772,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15">
       <c r="A804" s="8">
         <v>45996</v>
       </c>
@@ -19775,7 +19787,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15">
       <c r="A805" s="8">
         <v>46003</v>
       </c>
@@ -19790,7 +19802,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:15">
       <c r="A806" s="8">
         <v>46010</v>
       </c>
@@ -19805,7 +19817,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:15">
       <c r="A807" s="8">
         <v>46017</v>
       </c>
@@ -19833,7 +19845,7 @@
       <c r="N807" s="15"/>
       <c r="O807" s="15"/>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:15">
       <c r="A808" s="8">
         <v>46024</v>
       </c>
@@ -19881,7 +19893,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:15">
       <c r="A809" s="8">
         <v>46031</v>
       </c>
@@ -19929,7 +19941,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:15">
       <c r="A810" s="8">
         <v>46038</v>
       </c>
@@ -19977,7 +19989,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:15">
       <c r="A811" s="8">
         <v>46045</v>
       </c>
@@ -20025,7 +20037,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:15">
       <c r="A812" s="8">
         <v>46052</v>
       </c>
@@ -20073,7 +20085,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:15">
       <c r="A813" s="8">
         <v>46059</v>
       </c>
@@ -20121,7 +20133,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:15">
       <c r="A814" s="8">
         <v>46066</v>
       </c>
@@ -20169,7 +20181,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:15">
       <c r="A815" s="8">
         <v>46073</v>
       </c>
@@ -20217,7 +20229,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:15">
       <c r="A816" s="8">
         <v>46080</v>
       </c>
@@ -20265,7 +20277,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:15">
       <c r="A817" s="8">
         <v>46087</v>
       </c>
@@ -20313,7 +20325,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:15">
       <c r="A818" s="8">
         <v>46094</v>
       </c>
@@ -20361,7 +20373,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:15">
       <c r="A819" s="8">
         <v>46101</v>
       </c>
@@ -20409,7 +20421,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:15">
       <c r="A820" s="8">
         <v>46108</v>
       </c>
@@ -20457,7 +20469,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:15">
       <c r="A821" s="8">
         <v>46115</v>
       </c>
@@ -20505,7 +20517,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:15">
       <c r="A822" s="8">
         <v>46122</v>
       </c>
@@ -20533,7 +20545,7 @@
       <c r="N822" s="15"/>
       <c r="O822" s="15"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:15">
       <c r="A823" s="8">
         <v>46129</v>
       </c>
@@ -20561,7 +20573,7 @@
       <c r="N823" s="15"/>
       <c r="O823" s="15"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:15">
       <c r="A824" s="8">
         <v>46136</v>
       </c>
@@ -20589,7 +20601,7 @@
       <c r="N824" s="15"/>
       <c r="O824" s="15"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:15">
       <c r="A825" s="8">
         <v>46143</v>
       </c>
@@ -20637,7 +20649,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:15">
       <c r="A826" s="8">
         <v>46150</v>
       </c>
@@ -20685,7 +20697,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:15">
       <c r="A827" s="8">
         <v>46157</v>
       </c>
@@ -20733,7 +20745,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:15">
       <c r="A828" s="8">
         <v>46164</v>
       </c>
@@ -20781,7 +20793,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:15">
       <c r="A829" s="8">
         <v>46171</v>
       </c>
@@ -20829,7 +20841,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:15">
       <c r="A830" s="8">
         <v>46178</v>
       </c>
@@ -20877,7 +20889,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:15">
       <c r="A831" s="8">
         <v>46185</v>
       </c>
@@ -20925,7 +20937,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:15">
       <c r="A832" s="8">
         <v>46192</v>
       </c>
@@ -20973,7 +20985,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:15">
       <c r="A833" s="8">
         <v>46199</v>
       </c>
@@ -21021,7 +21033,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:15">
       <c r="A834" s="8">
         <v>46206</v>
       </c>
@@ -21032,7 +21044,7 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="D834" s="8" t="str">
-        <f t="shared" ref="D834:D835" si="13">"UTC+"&amp;IF(
+        <f t="shared" ref="D834:D836" si="13">"UTC+"&amp;IF(
     AND(
         B834&gt;=EOMONTH(DATE(YEAR(B834),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B834),3,1),0),2),7),
         B834&lt;EOMONTH(DATE(YEAR(B834),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B834),10,1),0),2),7)
@@ -21076,7 +21088,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:15">
       <c r="A835" s="8">
         <v>46213</v>
       </c>
@@ -21121,6 +21133,54 @@
         <v>72000</v>
       </c>
       <c r="O835" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="836" spans="1:15">
+      <c r="A836" s="8">
+        <v>46220</v>
+      </c>
+      <c r="B836" s="8">
+        <v>46220</v>
+      </c>
+      <c r="C836" s="9">
+        <v>0.66666666666666796</v>
+      </c>
+      <c r="D836" s="8" t="str">
+        <f t="shared" si="13"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E836" s="10">
+        <v>2340.09</v>
+      </c>
+      <c r="F836" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G836" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H836" s="14">
+        <v>30500</v>
+      </c>
+      <c r="I836" s="14">
+        <v>34000</v>
+      </c>
+      <c r="J836" s="14">
+        <v>38000</v>
+      </c>
+      <c r="K836" s="14">
+        <v>40000</v>
+      </c>
+      <c r="L836" s="14">
+        <v>46000</v>
+      </c>
+      <c r="M836" s="14">
+        <v>57000</v>
+      </c>
+      <c r="N836" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O836" s="14">
         <v>79000</v>
       </c>
     </row>
@@ -21133,7 +21193,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21144,12 +21204,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
@@ -21157,7 +21217,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>17</v>
       </c>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEC491E-8564-6649-8B68-7491737A29B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6C3DFB-AB85-49EC-87EC-9E11753A9B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -100,12 +100,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,9 +171,9 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -181,43 +181,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -235,7 +235,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4571,6 +4571,27 @@
                 <c:pt idx="590">
                   <c:v>3852.69</c:v>
                 </c:pt>
+                <c:pt idx="699">
+                  <c:v>809.6</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>809.6</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>910.24</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>1201.73</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>1215.8900000000001</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>1230.06</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>1251.68</c:v>
+                </c:pt>
                 <c:pt idx="726">
                   <c:v>1627.4</c:v>
                 </c:pt>
@@ -4580,6 +4601,54 @@
                 <c:pt idx="741">
                   <c:v>1936.04</c:v>
                 </c:pt>
+                <c:pt idx="742">
+                  <c:v>1965.85</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>1967.35</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>1977.78</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>2052.33</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>2052.33</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>2067</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>2070</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>2070</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>2071.71</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>2074.6999999999998</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>2076</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>2082</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>2106</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>2110.48</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>2055.31</c:v>
+                </c:pt>
                 <c:pt idx="778">
                   <c:v>2158.19</c:v>
                 </c:pt>
@@ -4592,8 +4661,56 @@
                 <c:pt idx="781">
                   <c:v>2164.9</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>2165</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>2183</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>2183.54</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>2210</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>2210</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>2214.85</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>2210</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>2212</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>2203</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>2191</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>2182</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>2184</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>2184</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>2184</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>2182.0500000000002</c:v>
+                </c:pt>
                 <c:pt idx="805">
-                  <c:v>2180.56</c:v>
+                  <c:v>2182.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="806">
                   <c:v>2182.0500000000002</c:v>
@@ -5494,9 +5611,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5534,7 +5651,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5640,7 +5757,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5782,7 +5899,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5791,18 +5908,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
   <dimension ref="A1:P836"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.1640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.83203125" style="11"/>
+    <col min="5" max="5" width="11.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.77734375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1">
+    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5850,7 +5967,7 @@
       </c>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>40383</v>
       </c>
@@ -5875,7 +5992,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>40390</v>
       </c>
@@ -5900,7 +6017,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>40397</v>
       </c>
@@ -5918,7 +6035,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>40404</v>
       </c>
@@ -5936,7 +6053,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>40411</v>
       </c>
@@ -5954,7 +6071,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>40418</v>
       </c>
@@ -5972,7 +6089,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>40425</v>
       </c>
@@ -5990,7 +6107,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>40432</v>
       </c>
@@ -6008,7 +6125,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>40439</v>
       </c>
@@ -6026,7 +6143,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>40446</v>
       </c>
@@ -6044,7 +6161,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>40453</v>
       </c>
@@ -6062,7 +6179,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>40460</v>
       </c>
@@ -6080,7 +6197,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>40467</v>
       </c>
@@ -6098,7 +6215,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>40474</v>
       </c>
@@ -6116,7 +6233,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>40481</v>
       </c>
@@ -6134,7 +6251,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>40488</v>
       </c>
@@ -6152,7 +6269,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>40495</v>
       </c>
@@ -6170,7 +6287,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>40502</v>
       </c>
@@ -6188,7 +6305,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>40509</v>
       </c>
@@ -6206,7 +6323,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>40516</v>
       </c>
@@ -6224,7 +6341,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>40523</v>
       </c>
@@ -6242,7 +6359,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>40530</v>
       </c>
@@ -6260,7 +6377,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>40537</v>
       </c>
@@ -6278,7 +6395,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>40544</v>
       </c>
@@ -6296,7 +6413,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>40551</v>
       </c>
@@ -6314,7 +6431,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>40558</v>
       </c>
@@ -6332,7 +6449,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>40565</v>
       </c>
@@ -6350,7 +6467,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>40572</v>
       </c>
@@ -6368,7 +6485,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>40579</v>
       </c>
@@ -6386,7 +6503,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>40586</v>
       </c>
@@ -6404,7 +6521,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>40593</v>
       </c>
@@ -6422,7 +6539,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>40600</v>
       </c>
@@ -6440,7 +6557,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>40607</v>
       </c>
@@ -6458,7 +6575,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>40614</v>
       </c>
@@ -6476,7 +6593,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>40621</v>
       </c>
@@ -6494,7 +6611,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>40628</v>
       </c>
@@ -6512,7 +6629,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>40635</v>
       </c>
@@ -6530,7 +6647,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>40642</v>
       </c>
@@ -6548,7 +6665,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>40649</v>
       </c>
@@ -6566,7 +6683,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>40656</v>
       </c>
@@ -6584,7 +6701,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>40663</v>
       </c>
@@ -6602,7 +6719,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>40670</v>
       </c>
@@ -6620,7 +6737,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>40677</v>
       </c>
@@ -6638,7 +6755,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>40684</v>
       </c>
@@ -6656,7 +6773,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>40691</v>
       </c>
@@ -6674,7 +6791,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>40698</v>
       </c>
@@ -6692,7 +6809,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>40705</v>
       </c>
@@ -6710,7 +6827,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>40712</v>
       </c>
@@ -6728,7 +6845,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>40719</v>
       </c>
@@ -6746,7 +6863,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>40726</v>
       </c>
@@ -6764,7 +6881,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>40733</v>
       </c>
@@ -6782,7 +6899,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>40740</v>
       </c>
@@ -6800,7 +6917,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>40747</v>
       </c>
@@ -6818,7 +6935,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>40754</v>
       </c>
@@ -6836,7 +6953,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>40761</v>
       </c>
@@ -6854,7 +6971,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>40768</v>
       </c>
@@ -6872,7 +6989,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>40775</v>
       </c>
@@ -6890,7 +7007,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>40782</v>
       </c>
@@ -6908,7 +7025,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>40789</v>
       </c>
@@ -6926,7 +7043,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>40796</v>
       </c>
@@ -6944,7 +7061,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>40803</v>
       </c>
@@ -6962,7 +7079,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>40810</v>
       </c>
@@ -6980,7 +7097,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>40817</v>
       </c>
@@ -6998,7 +7115,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>40824</v>
       </c>
@@ -7016,7 +7133,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>40831</v>
       </c>
@@ -7034,7 +7151,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>40838</v>
       </c>
@@ -7059,7 +7176,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>40845</v>
       </c>
@@ -7077,7 +7194,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>40852</v>
       </c>
@@ -7095,7 +7212,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>40859</v>
       </c>
@@ -7113,7 +7230,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>40866</v>
       </c>
@@ -7131,7 +7248,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>40873</v>
       </c>
@@ -7149,7 +7266,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>40880</v>
       </c>
@@ -7167,7 +7284,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>40887</v>
       </c>
@@ -7185,7 +7302,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>40894</v>
       </c>
@@ -7203,7 +7320,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>40901</v>
       </c>
@@ -7221,7 +7338,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>40908</v>
       </c>
@@ -7239,7 +7356,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>40915</v>
       </c>
@@ -7257,7 +7374,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>40922</v>
       </c>
@@ -7275,7 +7392,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>40929</v>
       </c>
@@ -7293,7 +7410,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>40936</v>
       </c>
@@ -7311,7 +7428,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>40942</v>
       </c>
@@ -7329,7 +7446,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>40943</v>
       </c>
@@ -7347,7 +7464,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>40950</v>
       </c>
@@ -7365,7 +7482,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>40957</v>
       </c>
@@ -7383,7 +7500,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>40964</v>
       </c>
@@ -7401,7 +7518,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>40978</v>
       </c>
@@ -7419,7 +7536,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>40985</v>
       </c>
@@ -7437,7 +7554,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>40992</v>
       </c>
@@ -7455,7 +7572,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>40999</v>
       </c>
@@ -7473,7 +7590,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>41006</v>
       </c>
@@ -7491,7 +7608,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>41013</v>
       </c>
@@ -7509,7 +7626,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>41020</v>
       </c>
@@ -7527,7 +7644,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>41027</v>
       </c>
@@ -7545,7 +7662,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>41034</v>
       </c>
@@ -7563,7 +7680,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>41041</v>
       </c>
@@ -7581,7 +7698,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>41048</v>
       </c>
@@ -7599,7 +7716,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>41055</v>
       </c>
@@ -7617,7 +7734,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>41062</v>
       </c>
@@ -7635,7 +7752,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>41069</v>
       </c>
@@ -7653,7 +7770,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>41076</v>
       </c>
@@ -7671,7 +7788,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>41083</v>
       </c>
@@ -7689,7 +7806,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>41090</v>
       </c>
@@ -7707,7 +7824,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>41097</v>
       </c>
@@ -7725,7 +7842,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>41104</v>
       </c>
@@ -7743,7 +7860,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>41111</v>
       </c>
@@ -7761,7 +7878,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>41118</v>
       </c>
@@ -7779,7 +7896,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>41125</v>
       </c>
@@ -7797,7 +7914,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>41132</v>
       </c>
@@ -7815,7 +7932,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>41139</v>
       </c>
@@ -7833,7 +7950,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>41146</v>
       </c>
@@ -7851,7 +7968,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>41153</v>
       </c>
@@ -7869,7 +7986,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>41160</v>
       </c>
@@ -7887,7 +8004,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>41167</v>
       </c>
@@ -7905,7 +8022,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>41174</v>
       </c>
@@ -7923,7 +8040,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>41181</v>
       </c>
@@ -7941,7 +8058,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>41188</v>
       </c>
@@ -7959,7 +8076,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>41195</v>
       </c>
@@ -7977,7 +8094,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>41202</v>
       </c>
@@ -7995,7 +8112,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>41209</v>
       </c>
@@ -8013,7 +8130,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>41216</v>
       </c>
@@ -8031,7 +8148,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>41223</v>
       </c>
@@ -8049,7 +8166,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>41230</v>
       </c>
@@ -8067,7 +8184,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>41237</v>
       </c>
@@ -8085,7 +8202,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>41244</v>
       </c>
@@ -8103,7 +8220,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>41251</v>
       </c>
@@ -8121,7 +8238,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>41258</v>
       </c>
@@ -8139,7 +8256,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>41265</v>
       </c>
@@ -8157,7 +8274,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>41272</v>
       </c>
@@ -8175,7 +8292,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>41279</v>
       </c>
@@ -8193,7 +8310,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>41286</v>
       </c>
@@ -8218,7 +8335,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>41293</v>
       </c>
@@ -8236,7 +8353,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>41300</v>
       </c>
@@ -8254,7 +8371,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>41307</v>
       </c>
@@ -8272,7 +8389,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>41314</v>
       </c>
@@ -8290,7 +8407,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>41321</v>
       </c>
@@ -8308,7 +8425,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>41328</v>
       </c>
@@ -8326,7 +8443,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>41335</v>
       </c>
@@ -8344,7 +8461,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>41342</v>
       </c>
@@ -8362,7 +8479,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>41349</v>
       </c>
@@ -8380,7 +8497,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>41356</v>
       </c>
@@ -8398,7 +8515,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>41363</v>
       </c>
@@ -8416,7 +8533,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>41370</v>
       </c>
@@ -8434,7 +8551,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>41377</v>
       </c>
@@ -8452,7 +8569,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>41384</v>
       </c>
@@ -8470,7 +8587,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>41391</v>
       </c>
@@ -8488,7 +8605,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>41398</v>
       </c>
@@ -8506,7 +8623,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>41405</v>
       </c>
@@ -8524,7 +8641,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>41412</v>
       </c>
@@ -8542,7 +8659,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>41419</v>
       </c>
@@ -8560,7 +8677,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>41426</v>
       </c>
@@ -8578,7 +8695,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>41433</v>
       </c>
@@ -8596,7 +8713,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>41440</v>
       </c>
@@ -8614,7 +8731,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>41447</v>
       </c>
@@ -8632,7 +8749,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>41454</v>
       </c>
@@ -8650,7 +8767,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>41461</v>
       </c>
@@ -8668,7 +8785,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>41468</v>
       </c>
@@ -8686,7 +8803,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>41475</v>
       </c>
@@ -8704,7 +8821,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>41482</v>
       </c>
@@ -8722,7 +8839,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>41489</v>
       </c>
@@ -8740,7 +8857,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>41496</v>
       </c>
@@ -8758,7 +8875,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>41503</v>
       </c>
@@ -8776,7 +8893,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>41510</v>
       </c>
@@ -8794,7 +8911,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>41517</v>
       </c>
@@ -8812,7 +8929,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>41524</v>
       </c>
@@ -8830,7 +8947,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>41531</v>
       </c>
@@ -8848,7 +8965,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>41538</v>
       </c>
@@ -8866,7 +8983,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>41545</v>
       </c>
@@ -8884,7 +9001,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>41552</v>
       </c>
@@ -8902,7 +9019,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>41559</v>
       </c>
@@ -8920,7 +9037,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>41566</v>
       </c>
@@ -8938,7 +9055,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>41573</v>
       </c>
@@ -8956,7 +9073,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>41580</v>
       </c>
@@ -8974,7 +9091,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>41587</v>
       </c>
@@ -8992,7 +9109,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>41594</v>
       </c>
@@ -9010,7 +9127,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>41601</v>
       </c>
@@ -9028,7 +9145,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>41608</v>
       </c>
@@ -9046,7 +9163,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>41615</v>
       </c>
@@ -9064,7 +9181,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>41622</v>
       </c>
@@ -9082,7 +9199,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>41629</v>
       </c>
@@ -9100,7 +9217,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>41636</v>
       </c>
@@ -9118,7 +9235,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>41643</v>
       </c>
@@ -9136,7 +9253,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>41650</v>
       </c>
@@ -9154,7 +9271,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>41657</v>
       </c>
@@ -9172,7 +9289,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>41664</v>
       </c>
@@ -9190,7 +9307,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>41671</v>
       </c>
@@ -9208,7 +9325,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>41678</v>
       </c>
@@ -9226,7 +9343,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>41685</v>
       </c>
@@ -9244,7 +9361,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>41692</v>
       </c>
@@ -9262,7 +9379,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>41699</v>
       </c>
@@ -9280,7 +9397,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>41706</v>
       </c>
@@ -9298,7 +9415,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>41713</v>
       </c>
@@ -9316,7 +9433,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
         <v>41720</v>
       </c>
@@ -9334,7 +9451,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
         <v>41727</v>
       </c>
@@ -9352,7 +9469,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
         <v>41734</v>
       </c>
@@ -9377,7 +9494,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
         <v>41741</v>
       </c>
@@ -9395,7 +9512,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>41748</v>
       </c>
@@ -9413,7 +9530,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="8">
         <v>41755</v>
       </c>
@@ -9431,7 +9548,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="8">
         <v>41762</v>
       </c>
@@ -9449,7 +9566,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="8">
         <v>41769</v>
       </c>
@@ -9467,7 +9584,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="8">
         <v>41776</v>
       </c>
@@ -9485,7 +9602,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="8">
         <v>41783</v>
       </c>
@@ -9503,7 +9620,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>41790</v>
       </c>
@@ -9521,7 +9638,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="8">
         <v>41797</v>
       </c>
@@ -9539,7 +9656,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="8">
         <v>41804</v>
       </c>
@@ -9557,7 +9674,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="8">
         <v>41811</v>
       </c>
@@ -9575,7 +9692,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="8">
         <v>41818</v>
       </c>
@@ -9593,7 +9710,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="8">
         <v>41825</v>
       </c>
@@ -9611,7 +9728,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>41832</v>
       </c>
@@ -9629,7 +9746,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
         <v>41839</v>
       </c>
@@ -9647,7 +9764,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="8">
         <v>41846</v>
       </c>
@@ -9665,7 +9782,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
         <v>41853</v>
       </c>
@@ -9683,7 +9800,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>41860</v>
       </c>
@@ -9701,7 +9818,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
         <v>41867</v>
       </c>
@@ -9719,7 +9836,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="8">
         <v>41874</v>
       </c>
@@ -9737,7 +9854,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>41881</v>
       </c>
@@ -9755,7 +9872,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="8">
         <v>41888</v>
       </c>
@@ -9773,7 +9890,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="8">
         <v>41895</v>
       </c>
@@ -9791,7 +9908,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="8">
         <v>41902</v>
       </c>
@@ -9809,7 +9926,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="8">
         <v>41909</v>
       </c>
@@ -9827,7 +9944,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="8">
         <v>41916</v>
       </c>
@@ -9845,7 +9962,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="8">
         <v>41923</v>
       </c>
@@ -9863,7 +9980,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="8">
         <v>41930</v>
       </c>
@@ -9881,7 +9998,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="8">
         <v>41937</v>
       </c>
@@ -9899,7 +10016,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="8">
         <v>41944</v>
       </c>
@@ -9917,7 +10034,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="8">
         <v>41951</v>
       </c>
@@ -9935,7 +10052,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="8">
         <v>41958</v>
       </c>
@@ -9953,7 +10070,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="8">
         <v>41965</v>
       </c>
@@ -9971,7 +10088,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>41972</v>
       </c>
@@ -9989,7 +10106,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>41979</v>
       </c>
@@ -10007,7 +10124,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>41986</v>
       </c>
@@ -10025,7 +10142,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>41993</v>
       </c>
@@ -10043,7 +10160,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>42000</v>
       </c>
@@ -10061,7 +10178,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>42007</v>
       </c>
@@ -10079,7 +10196,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>42014</v>
       </c>
@@ -10097,7 +10214,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="8">
         <v>42021</v>
       </c>
@@ -10115,7 +10232,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="8">
         <v>42028</v>
       </c>
@@ -10133,7 +10250,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="8">
         <v>42035</v>
       </c>
@@ -10151,7 +10268,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="8">
         <v>42042</v>
       </c>
@@ -10169,7 +10286,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="8">
         <v>42049</v>
       </c>
@@ -10187,7 +10304,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="8">
         <v>42056</v>
       </c>
@@ -10205,7 +10322,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="8">
         <v>42063</v>
       </c>
@@ -10223,7 +10340,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>42070</v>
       </c>
@@ -10241,7 +10358,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="8">
         <v>42077</v>
       </c>
@@ -10259,7 +10376,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>42084</v>
       </c>
@@ -10277,7 +10394,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>42091</v>
       </c>
@@ -10295,7 +10412,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="8">
         <v>42098</v>
       </c>
@@ -10313,7 +10430,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>42105</v>
       </c>
@@ -10331,7 +10448,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
         <v>42112</v>
       </c>
@@ -10349,7 +10466,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="8">
         <v>42119</v>
       </c>
@@ -10367,7 +10484,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="8">
         <v>42126</v>
       </c>
@@ -10385,7 +10502,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="8">
         <v>42133</v>
       </c>
@@ -10403,7 +10520,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="8">
         <v>42140</v>
       </c>
@@ -10421,7 +10538,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="8">
         <v>42147</v>
       </c>
@@ -10439,7 +10556,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="8">
         <v>42154</v>
       </c>
@@ -10457,7 +10574,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="8">
         <v>42161</v>
       </c>
@@ -10475,7 +10592,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="8">
         <v>42168</v>
       </c>
@@ -10493,7 +10610,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="8">
         <v>42175</v>
       </c>
@@ -10511,7 +10628,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
         <v>42182</v>
       </c>
@@ -10536,7 +10653,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="8">
         <v>42189</v>
       </c>
@@ -10554,7 +10671,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="8">
         <v>42196</v>
       </c>
@@ -10572,7 +10689,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="8">
         <v>42203</v>
       </c>
@@ -10590,7 +10707,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="8">
         <v>42210</v>
       </c>
@@ -10608,7 +10725,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="8">
         <v>42217</v>
       </c>
@@ -10626,7 +10743,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="8">
         <v>42224</v>
       </c>
@@ -10644,7 +10761,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="8">
         <v>42231</v>
       </c>
@@ -10662,7 +10779,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="8">
         <v>42238</v>
       </c>
@@ -10680,7 +10797,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="8">
         <v>42245</v>
       </c>
@@ -10698,7 +10815,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>42252</v>
       </c>
@@ -10716,7 +10833,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="8">
         <v>42259</v>
       </c>
@@ -10734,7 +10851,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>42266</v>
       </c>
@@ -10752,7 +10869,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="8">
         <v>42273</v>
       </c>
@@ -10770,7 +10887,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="8">
         <v>42280</v>
       </c>
@@ -10788,7 +10905,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="8">
         <v>42287</v>
       </c>
@@ -10806,7 +10923,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="8">
         <v>42294</v>
       </c>
@@ -10824,7 +10941,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="8">
         <v>42301</v>
       </c>
@@ -10842,7 +10959,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="8">
         <v>42308</v>
       </c>
@@ -10860,7 +10977,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="8">
         <v>42315</v>
       </c>
@@ -10878,7 +10995,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="8">
         <v>42322</v>
       </c>
@@ -10896,7 +11013,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="8">
         <v>42329</v>
       </c>
@@ -10914,7 +11031,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="8">
         <v>42336</v>
       </c>
@@ -10932,7 +11049,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="8">
         <v>42343</v>
       </c>
@@ -10950,7 +11067,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="8">
         <v>42350</v>
       </c>
@@ -10968,7 +11085,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="8">
         <v>42357</v>
       </c>
@@ -10986,7 +11103,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="8">
         <v>42364</v>
       </c>
@@ -11004,7 +11121,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="8">
         <v>42371</v>
       </c>
@@ -11022,7 +11139,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="8">
         <v>42378</v>
       </c>
@@ -11040,7 +11157,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="8">
         <v>42385</v>
       </c>
@@ -11058,7 +11175,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="8">
         <v>42392</v>
       </c>
@@ -11076,7 +11193,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="8">
         <v>42399</v>
       </c>
@@ -11094,7 +11211,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="8">
         <v>42406</v>
       </c>
@@ -11112,7 +11229,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="8">
         <v>42413</v>
       </c>
@@ -11130,7 +11247,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="8">
         <v>42420</v>
       </c>
@@ -11148,7 +11265,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="8">
         <v>42427</v>
       </c>
@@ -11166,7 +11283,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="8">
         <v>42434</v>
       </c>
@@ -11184,7 +11301,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="8">
         <v>42441</v>
       </c>
@@ -11202,7 +11319,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="8">
         <v>42448</v>
       </c>
@@ -11220,7 +11337,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="8">
         <v>42455</v>
       </c>
@@ -11238,7 +11355,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="8">
         <v>42462</v>
       </c>
@@ -11256,7 +11373,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="8">
         <v>42469</v>
       </c>
@@ -11274,7 +11391,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="8">
         <v>42476</v>
       </c>
@@ -11292,7 +11409,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="8">
         <v>42483</v>
       </c>
@@ -11310,7 +11427,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="8">
         <v>42490</v>
       </c>
@@ -11328,7 +11445,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="8">
         <v>42497</v>
       </c>
@@ -11346,7 +11463,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="8">
         <v>42504</v>
       </c>
@@ -11364,7 +11481,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="8">
         <v>42511</v>
       </c>
@@ -11382,7 +11499,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="8">
         <v>42518</v>
       </c>
@@ -11400,7 +11517,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="8">
         <v>42525</v>
       </c>
@@ -11418,7 +11535,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="8">
         <v>42532</v>
       </c>
@@ -11436,7 +11553,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="8">
         <v>42539</v>
       </c>
@@ -11454,7 +11571,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="8">
         <v>42546</v>
       </c>
@@ -11472,7 +11589,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="8">
         <v>42553</v>
       </c>
@@ -11490,7 +11607,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="8">
         <v>42560</v>
       </c>
@@ -11508,7 +11625,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="8">
         <v>42567</v>
       </c>
@@ -11526,7 +11643,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="8">
         <v>42574</v>
       </c>
@@ -11544,7 +11661,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="8">
         <v>42581</v>
       </c>
@@ -11562,7 +11679,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="8">
         <v>42588</v>
       </c>
@@ -11580,7 +11697,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="8">
         <v>42595</v>
       </c>
@@ -11598,7 +11715,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="8">
         <v>42602</v>
       </c>
@@ -11616,7 +11733,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="8">
         <v>42609</v>
       </c>
@@ -11634,7 +11751,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="8">
         <v>42616</v>
       </c>
@@ -11652,7 +11769,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="8">
         <v>42623</v>
       </c>
@@ -11670,7 +11787,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="8">
         <v>42630</v>
       </c>
@@ -11695,7 +11812,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="8">
         <v>42637</v>
       </c>
@@ -11713,7 +11830,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="8">
         <v>42644</v>
       </c>
@@ -11731,7 +11848,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="8">
         <v>42651</v>
       </c>
@@ -11749,7 +11866,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="8">
         <v>42658</v>
       </c>
@@ -11767,7 +11884,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="8">
         <v>42665</v>
       </c>
@@ -11785,7 +11902,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="8">
         <v>42672</v>
       </c>
@@ -11803,7 +11920,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="8">
         <v>42679</v>
       </c>
@@ -11821,7 +11938,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="8">
         <v>42686</v>
       </c>
@@ -11839,7 +11956,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="8">
         <v>42693</v>
       </c>
@@ -11857,7 +11974,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="8">
         <v>42700</v>
       </c>
@@ -11875,7 +11992,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="8">
         <v>42707</v>
       </c>
@@ -11893,7 +12010,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="8">
         <v>42714</v>
       </c>
@@ -11911,7 +12028,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="8">
         <v>42721</v>
       </c>
@@ -11929,7 +12046,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="8">
         <v>42728</v>
       </c>
@@ -11947,7 +12064,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="8">
         <v>42735</v>
       </c>
@@ -11965,7 +12082,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="8">
         <v>42742</v>
       </c>
@@ -11983,7 +12100,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="8">
         <v>42749</v>
       </c>
@@ -12001,7 +12118,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="8">
         <v>42756</v>
       </c>
@@ -12019,7 +12136,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="8">
         <v>42763</v>
       </c>
@@ -12037,7 +12154,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="8">
         <v>42770</v>
       </c>
@@ -12055,7 +12172,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="8">
         <v>42777</v>
       </c>
@@ -12073,7 +12190,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="8">
         <v>42784</v>
       </c>
@@ -12091,7 +12208,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="8">
         <v>42791</v>
       </c>
@@ -12109,7 +12226,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="8">
         <v>42798</v>
       </c>
@@ -12127,7 +12244,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
         <v>42805</v>
       </c>
@@ -12145,7 +12262,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="8">
         <v>42812</v>
       </c>
@@ -12163,7 +12280,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="8">
         <v>42819</v>
       </c>
@@ -12181,7 +12298,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="8">
         <v>42826</v>
       </c>
@@ -12199,7 +12316,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="8">
         <v>42833</v>
       </c>
@@ -12217,7 +12334,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="8">
         <v>42840</v>
       </c>
@@ -12235,7 +12352,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="8">
         <v>42847</v>
       </c>
@@ -12253,7 +12370,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="8">
         <v>42854</v>
       </c>
@@ -12271,7 +12388,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="8">
         <v>42861</v>
       </c>
@@ -12289,7 +12406,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="8">
         <v>42868</v>
       </c>
@@ -12307,7 +12424,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="8">
         <v>42875</v>
       </c>
@@ -12325,7 +12442,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="8">
         <v>42882</v>
       </c>
@@ -12343,7 +12460,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="8">
         <v>42889</v>
       </c>
@@ -12361,7 +12478,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="8">
         <v>42896</v>
       </c>
@@ -12379,7 +12496,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="8">
         <v>42903</v>
       </c>
@@ -12397,7 +12514,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="8">
         <v>42910</v>
       </c>
@@ -12415,7 +12532,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="8">
         <v>42917</v>
       </c>
@@ -12433,7 +12550,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="8">
         <v>42924</v>
       </c>
@@ -12451,7 +12568,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="8">
         <v>42931</v>
       </c>
@@ -12469,7 +12586,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="8">
         <v>42938</v>
       </c>
@@ -12487,7 +12604,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="8">
         <v>42945</v>
       </c>
@@ -12505,7 +12622,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="8">
         <v>42952</v>
       </c>
@@ -12523,7 +12640,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="8">
         <v>42959</v>
       </c>
@@ -12541,7 +12658,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" s="8">
         <v>42966</v>
       </c>
@@ -12559,7 +12676,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="8">
         <v>42973</v>
       </c>
@@ -12577,7 +12694,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="8">
         <v>42980</v>
       </c>
@@ -12595,7 +12712,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" s="8">
         <v>42987</v>
       </c>
@@ -12613,7 +12730,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="8">
         <v>42994</v>
       </c>
@@ -12631,7 +12748,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="8">
         <v>43001</v>
       </c>
@@ -12649,7 +12766,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="8">
         <v>43008</v>
       </c>
@@ -12667,7 +12784,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="8">
         <v>43015</v>
       </c>
@@ -12685,7 +12802,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="8">
         <v>43022</v>
       </c>
@@ -12703,7 +12820,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="8">
         <v>43029</v>
       </c>
@@ -12721,7 +12838,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="8">
         <v>43036</v>
       </c>
@@ -12739,7 +12856,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="8">
         <v>43043</v>
       </c>
@@ -12757,7 +12874,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="8">
         <v>43050</v>
       </c>
@@ -12775,7 +12892,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="8">
         <v>43057</v>
       </c>
@@ -12793,7 +12910,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="8">
         <v>43064</v>
       </c>
@@ -12811,7 +12928,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="8">
         <v>43071</v>
       </c>
@@ -12829,7 +12946,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="8">
         <v>43078</v>
       </c>
@@ -12854,7 +12971,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="8">
         <v>43085</v>
       </c>
@@ -12872,7 +12989,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="8">
         <v>43092</v>
       </c>
@@ -12890,7 +13007,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="8">
         <v>43099</v>
       </c>
@@ -12908,7 +13025,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="8">
         <v>43106</v>
       </c>
@@ -12926,7 +13043,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="8">
         <v>43113</v>
       </c>
@@ -12944,7 +13061,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="8">
         <v>43120</v>
       </c>
@@ -12962,7 +13079,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="8">
         <v>43127</v>
       </c>
@@ -12980,7 +13097,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="8">
         <v>43134</v>
       </c>
@@ -12998,7 +13115,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="8">
         <v>43141</v>
       </c>
@@ -13016,7 +13133,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="8">
         <v>43148</v>
       </c>
@@ -13034,7 +13151,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="8">
         <v>43155</v>
       </c>
@@ -13052,7 +13169,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="8">
         <v>43162</v>
       </c>
@@ -13070,7 +13187,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="8">
         <v>43169</v>
       </c>
@@ -13088,7 +13205,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="8">
         <v>43176</v>
       </c>
@@ -13106,7 +13223,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="8">
         <v>43183</v>
       </c>
@@ -13124,7 +13241,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="8">
         <v>43190</v>
       </c>
@@ -13142,7 +13259,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="8">
         <v>43197</v>
       </c>
@@ -13160,7 +13277,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="8">
         <v>43204</v>
       </c>
@@ -13178,7 +13295,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="8">
         <v>43211</v>
       </c>
@@ -13196,7 +13313,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="8">
         <v>43218</v>
       </c>
@@ -13214,7 +13331,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="8">
         <v>43225</v>
       </c>
@@ -13232,7 +13349,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="8">
         <v>43232</v>
       </c>
@@ -13250,7 +13367,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="8">
         <v>43239</v>
       </c>
@@ -13268,7 +13385,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="8">
         <v>43245</v>
       </c>
@@ -13286,7 +13403,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="8">
         <v>43252</v>
       </c>
@@ -13304,7 +13421,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="8">
         <v>43259</v>
       </c>
@@ -13322,7 +13439,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="8">
         <v>43266</v>
       </c>
@@ -13340,7 +13457,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="8">
         <v>43273</v>
       </c>
@@ -13358,7 +13475,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="8">
         <v>43280</v>
       </c>
@@ -13376,7 +13493,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="8">
         <v>43287</v>
       </c>
@@ -13394,7 +13511,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="8">
         <v>43294</v>
       </c>
@@ -13412,7 +13529,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="8">
         <v>43301</v>
       </c>
@@ -13430,7 +13547,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="8">
         <v>43308</v>
       </c>
@@ -13448,7 +13565,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="8">
         <v>43315</v>
       </c>
@@ -13466,7 +13583,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="8">
         <v>43322</v>
       </c>
@@ -13484,7 +13601,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="8">
         <v>43329</v>
       </c>
@@ -13502,7 +13619,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="8">
         <v>43336</v>
       </c>
@@ -13520,7 +13637,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="8">
         <v>43343</v>
       </c>
@@ -13538,7 +13655,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="8">
         <v>43350</v>
       </c>
@@ -13556,7 +13673,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="8">
         <v>43357</v>
       </c>
@@ -13574,7 +13691,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="8">
         <v>43364</v>
       </c>
@@ -13592,7 +13709,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="8">
         <v>43371</v>
       </c>
@@ -13610,7 +13727,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="8">
         <v>43378</v>
       </c>
@@ -13628,7 +13745,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="8">
         <v>43385</v>
       </c>
@@ -13646,7 +13763,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="8">
         <v>43392</v>
       </c>
@@ -13664,7 +13781,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="8">
         <v>43399</v>
       </c>
@@ -13682,7 +13799,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="8">
         <v>43406</v>
       </c>
@@ -13700,7 +13817,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="8">
         <v>43413</v>
       </c>
@@ -13718,7 +13835,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="8">
         <v>43420</v>
       </c>
@@ -13736,7 +13853,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="8">
         <v>43427</v>
       </c>
@@ -13754,7 +13871,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="8">
         <v>43434</v>
       </c>
@@ -13772,7 +13889,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="8">
         <v>43441</v>
       </c>
@@ -13790,7 +13907,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="8">
         <v>43448</v>
       </c>
@@ -13808,7 +13925,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="8">
         <v>43455</v>
       </c>
@@ -13826,7 +13943,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="8">
         <v>43462</v>
       </c>
@@ -13844,7 +13961,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="8">
         <v>43469</v>
       </c>
@@ -13862,7 +13979,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="8">
         <v>43476</v>
       </c>
@@ -13880,7 +13997,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="8">
         <v>43483</v>
       </c>
@@ -13898,7 +14015,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="8">
         <v>43490</v>
       </c>
@@ -13916,7 +14033,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="8">
         <v>43497</v>
       </c>
@@ -13934,7 +14051,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="8">
         <v>43504</v>
       </c>
@@ -13952,7 +14069,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="8">
         <v>43511</v>
       </c>
@@ -13970,7 +14087,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="8">
         <v>43518</v>
       </c>
@@ -13988,7 +14105,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="8">
         <v>43525</v>
       </c>
@@ -14013,7 +14130,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="8">
         <v>43532</v>
       </c>
@@ -14031,7 +14148,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="8">
         <v>43539</v>
       </c>
@@ -14049,7 +14166,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="8">
         <v>43546</v>
       </c>
@@ -14067,7 +14184,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="8">
         <v>43553</v>
       </c>
@@ -14085,7 +14202,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="8">
         <v>43560</v>
       </c>
@@ -14103,7 +14220,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="8">
         <v>43567</v>
       </c>
@@ -14121,7 +14238,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="8">
         <v>43574</v>
       </c>
@@ -14139,7 +14256,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="8">
         <v>43581</v>
       </c>
@@ -14157,7 +14274,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="8">
         <v>43588</v>
       </c>
@@ -14175,7 +14292,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="8">
         <v>43595</v>
       </c>
@@ -14193,7 +14310,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="8">
         <v>43602</v>
       </c>
@@ -14211,7 +14328,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="8">
         <v>43609</v>
       </c>
@@ -14229,7 +14346,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="8">
         <v>43616</v>
       </c>
@@ -14247,7 +14364,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="8">
         <v>43623</v>
       </c>
@@ -14265,7 +14382,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="8">
         <v>43630</v>
       </c>
@@ -14283,7 +14400,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="8">
         <v>43637</v>
       </c>
@@ -14301,7 +14418,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="8">
         <v>43644</v>
       </c>
@@ -14319,7 +14436,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="8">
         <v>43651</v>
       </c>
@@ -14337,7 +14454,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="8">
         <v>43658</v>
       </c>
@@ -14355,7 +14472,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="8">
         <v>43665</v>
       </c>
@@ -14373,7 +14490,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="8">
         <v>43672</v>
       </c>
@@ -14391,7 +14508,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="8">
         <v>43679</v>
       </c>
@@ -14409,7 +14526,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="8">
         <v>43686</v>
       </c>
@@ -14427,7 +14544,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="8">
         <v>43693</v>
       </c>
@@ -14445,7 +14562,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="8">
         <v>43700</v>
       </c>
@@ -14463,7 +14580,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="8">
         <v>43707</v>
       </c>
@@ -14481,7 +14598,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="8">
         <v>43714</v>
       </c>
@@ -14499,7 +14616,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="8">
         <v>43721</v>
       </c>
@@ -14517,7 +14634,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="8">
         <v>43728</v>
       </c>
@@ -14535,7 +14652,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="8">
         <v>43735</v>
       </c>
@@ -14553,7 +14670,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="8">
         <v>43742</v>
       </c>
@@ -14571,7 +14688,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="8">
         <v>43749</v>
       </c>
@@ -14589,7 +14706,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="8">
         <v>43756</v>
       </c>
@@ -14607,7 +14724,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="8">
         <v>43763</v>
       </c>
@@ -14625,7 +14742,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="8">
         <v>43770</v>
       </c>
@@ -14643,7 +14760,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" s="8">
         <v>43777</v>
       </c>
@@ -14661,7 +14778,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" s="8">
         <v>43784</v>
       </c>
@@ -14679,7 +14796,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" s="8">
         <v>43791</v>
       </c>
@@ -14697,7 +14814,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" s="8">
         <v>43798</v>
       </c>
@@ -14715,7 +14832,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" s="8">
         <v>43805</v>
       </c>
@@ -14733,7 +14850,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" s="8">
         <v>43812</v>
       </c>
@@ -14751,7 +14868,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" s="8">
         <v>43819</v>
       </c>
@@ -14769,7 +14886,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" s="8">
         <v>43826</v>
       </c>
@@ -14787,7 +14904,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" s="8">
         <v>43833</v>
       </c>
@@ -14805,7 +14922,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" s="8">
         <v>43840</v>
       </c>
@@ -14823,7 +14940,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" s="8">
         <v>43847</v>
       </c>
@@ -14841,7 +14958,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" s="8">
         <v>43854</v>
       </c>
@@ -14859,7 +14976,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" s="8">
         <v>43861</v>
       </c>
@@ -14877,7 +14994,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="8">
         <v>43868</v>
       </c>
@@ -14895,7 +15012,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" s="8">
         <v>43875</v>
       </c>
@@ -14913,7 +15030,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" s="8">
         <v>43882</v>
       </c>
@@ -14931,7 +15048,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" s="8">
         <v>43889</v>
       </c>
@@ -14949,7 +15066,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" s="8">
         <v>43896</v>
       </c>
@@ -14967,7 +15084,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" s="8">
         <v>43903</v>
       </c>
@@ -14985,7 +15102,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" s="8">
         <v>43910</v>
       </c>
@@ -15003,7 +15120,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" s="8">
         <v>43917</v>
       </c>
@@ -15021,7 +15138,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" s="8">
         <v>43924</v>
       </c>
@@ -15039,7 +15156,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" s="8">
         <v>43931</v>
       </c>
@@ -15057,7 +15174,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" s="8">
         <v>43938</v>
       </c>
@@ -15075,7 +15192,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" s="8">
         <v>43945</v>
       </c>
@@ -15093,7 +15210,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" s="8">
         <v>43952</v>
       </c>
@@ -15111,7 +15228,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" s="8">
         <v>43959</v>
       </c>
@@ -15129,7 +15246,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" s="8">
         <v>43966</v>
       </c>
@@ -15147,7 +15264,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" s="8">
         <v>43973</v>
       </c>
@@ -15172,7 +15289,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" s="8">
         <v>43980</v>
       </c>
@@ -15190,7 +15307,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" s="8">
         <v>43987</v>
       </c>
@@ -15208,7 +15325,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" s="8">
         <v>43994</v>
       </c>
@@ -15226,7 +15343,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" s="8">
         <v>44001</v>
       </c>
@@ -15244,7 +15361,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" s="8">
         <v>44008</v>
       </c>
@@ -15262,7 +15379,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" s="8">
         <v>44015</v>
       </c>
@@ -15280,7 +15397,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" s="8">
         <v>44022</v>
       </c>
@@ -15298,7 +15415,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" s="8">
         <v>44029</v>
       </c>
@@ -15316,7 +15433,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" s="8">
         <v>44036</v>
       </c>
@@ -15334,7 +15451,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" s="8">
         <v>44043</v>
       </c>
@@ -15352,7 +15469,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" s="8">
         <v>44050</v>
       </c>
@@ -15370,7 +15487,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" s="8">
         <v>44057</v>
       </c>
@@ -15388,7 +15505,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" s="8">
         <v>44064</v>
       </c>
@@ -15406,7 +15523,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" s="8">
         <v>44071</v>
       </c>
@@ -15424,7 +15541,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" s="8">
         <v>44078</v>
       </c>
@@ -15442,7 +15559,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" s="8">
         <v>44085</v>
       </c>
@@ -15460,7 +15577,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" s="8">
         <v>44092</v>
       </c>
@@ -15478,7 +15595,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" s="8">
         <v>44099</v>
       </c>
@@ -15496,7 +15613,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" s="8">
         <v>44106</v>
       </c>
@@ -15514,7 +15631,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" s="8">
         <v>44113</v>
       </c>
@@ -15532,7 +15649,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" s="8">
         <v>44120</v>
       </c>
@@ -15550,7 +15667,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" s="8">
         <v>44127</v>
       </c>
@@ -15568,7 +15685,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" s="8">
         <v>44134</v>
       </c>
@@ -15586,7 +15703,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" s="8">
         <v>44141</v>
       </c>
@@ -15604,7 +15721,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" s="8">
         <v>44148</v>
       </c>
@@ -15622,7 +15739,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" s="8">
         <v>44155</v>
       </c>
@@ -15640,7 +15757,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" s="8">
         <v>44162</v>
       </c>
@@ -15658,7 +15775,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" s="8">
         <v>44169</v>
       </c>
@@ -15676,7 +15793,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" s="8">
         <v>44176</v>
       </c>
@@ -15694,7 +15811,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="8">
         <v>44183</v>
       </c>
@@ -15712,7 +15829,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="8">
         <v>44190</v>
       </c>
@@ -15730,7 +15847,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" s="8">
         <v>44197</v>
       </c>
@@ -15748,7 +15865,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="8">
         <v>44204</v>
       </c>
@@ -15766,7 +15883,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" s="8">
         <v>44211</v>
       </c>
@@ -15784,7 +15901,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" s="8">
         <v>44218</v>
       </c>
@@ -15802,7 +15919,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" s="8">
         <v>44225</v>
       </c>
@@ -15820,7 +15937,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" s="8">
         <v>44232</v>
       </c>
@@ -15838,7 +15955,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="8">
         <v>44239</v>
       </c>
@@ -15856,7 +15973,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" s="8">
         <v>44246</v>
       </c>
@@ -15874,7 +15991,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" s="8">
         <v>44253</v>
       </c>
@@ -15892,7 +16009,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" s="8">
         <v>44260</v>
       </c>
@@ -15910,7 +16027,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" s="8">
         <v>44267</v>
       </c>
@@ -15928,7 +16045,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" s="8">
         <v>44274</v>
       </c>
@@ -15946,7 +16063,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" s="8">
         <v>44281</v>
       </c>
@@ -15964,7 +16081,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" s="8">
         <v>44288</v>
       </c>
@@ -15982,7 +16099,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="8">
         <v>44295</v>
       </c>
@@ -16000,7 +16117,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" s="8">
         <v>44302</v>
       </c>
@@ -16018,7 +16135,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" s="8">
         <v>44309</v>
       </c>
@@ -16036,7 +16153,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" s="8">
         <v>44316</v>
       </c>
@@ -16054,7 +16171,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" s="8">
         <v>44323</v>
       </c>
@@ -16072,7 +16189,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" s="8">
         <v>44330</v>
       </c>
@@ -16090,7 +16207,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" s="8">
         <v>44337</v>
       </c>
@@ -16108,7 +16225,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="8">
         <v>44344</v>
       </c>
@@ -16126,7 +16243,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="8">
         <v>44351</v>
       </c>
@@ -16144,7 +16261,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" s="8">
         <v>44358</v>
       </c>
@@ -16162,7 +16279,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" s="8">
         <v>44365</v>
       </c>
@@ -16180,7 +16297,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" s="8">
         <v>44372</v>
       </c>
@@ -16198,7 +16315,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" s="8">
         <v>44379</v>
       </c>
@@ -16216,7 +16333,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" s="8">
         <v>44386</v>
       </c>
@@ -16234,7 +16351,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" s="8">
         <v>44393</v>
       </c>
@@ -16252,7 +16369,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" s="8">
         <v>44400</v>
       </c>
@@ -16270,7 +16387,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" s="8">
         <v>44407</v>
       </c>
@@ -16288,7 +16405,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" s="8">
         <v>44414</v>
       </c>
@@ -16306,7 +16423,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" s="8">
         <v>44421</v>
       </c>
@@ -16331,7 +16448,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" s="8">
         <v>44428</v>
       </c>
@@ -16349,7 +16466,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" s="8">
         <v>44435</v>
       </c>
@@ -16367,7 +16484,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" s="8">
         <v>44442</v>
       </c>
@@ -16385,7 +16502,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" s="8">
         <v>44449</v>
       </c>
@@ -16403,7 +16520,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" s="8">
         <v>44456</v>
       </c>
@@ -16421,7 +16538,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" s="8">
         <v>44463</v>
       </c>
@@ -16439,7 +16556,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" s="8">
         <v>44470</v>
       </c>
@@ -16457,7 +16574,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" s="8">
         <v>44477</v>
       </c>
@@ -16475,7 +16592,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" s="8">
         <v>44484</v>
       </c>
@@ -16493,7 +16610,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" s="8">
         <v>44491</v>
       </c>
@@ -16511,7 +16628,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" s="8">
         <v>44498</v>
       </c>
@@ -16529,7 +16646,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" s="8">
         <v>44505</v>
       </c>
@@ -16547,7 +16664,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" s="8">
         <v>44512</v>
       </c>
@@ -16565,7 +16682,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:4">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A593" s="8">
         <v>44519</v>
       </c>
@@ -16580,7 +16697,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="594" spans="1:4">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" s="8">
         <v>44526</v>
       </c>
@@ -16595,7 +16712,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="595" spans="1:4">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" s="8">
         <v>44533</v>
       </c>
@@ -16610,7 +16727,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="596" spans="1:4">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" s="8">
         <v>44540</v>
       </c>
@@ -16625,7 +16742,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="597" spans="1:4">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A597" s="8">
         <v>44547</v>
       </c>
@@ -16640,7 +16757,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="598" spans="1:4">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" s="8">
         <v>44554</v>
       </c>
@@ -16655,7 +16772,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="599" spans="1:4">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" s="8">
         <v>44561</v>
       </c>
@@ -16670,7 +16787,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="600" spans="1:4">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" s="8">
         <v>44568</v>
       </c>
@@ -16685,7 +16802,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="601" spans="1:4">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" s="8">
         <v>44575</v>
       </c>
@@ -16700,7 +16817,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="602" spans="1:4">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A602" s="8">
         <v>44582</v>
       </c>
@@ -16715,7 +16832,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="603" spans="1:4">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" s="8">
         <v>44589</v>
       </c>
@@ -16730,7 +16847,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="604" spans="1:4">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" s="8">
         <v>44596</v>
       </c>
@@ -16745,7 +16862,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="605" spans="1:4">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" s="8">
         <v>44603</v>
       </c>
@@ -16760,7 +16877,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="606" spans="1:4">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="8">
         <v>44610</v>
       </c>
@@ -16775,7 +16892,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="607" spans="1:4">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" s="8">
         <v>44617</v>
       </c>
@@ -16790,7 +16907,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="608" spans="1:4">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" s="8">
         <v>44624</v>
       </c>
@@ -16805,7 +16922,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="609" spans="1:4">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" s="8">
         <v>44631</v>
       </c>
@@ -16820,7 +16937,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="610" spans="1:4">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" s="8">
         <v>44638</v>
       </c>
@@ -16835,7 +16952,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="611" spans="1:4">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A611" s="8">
         <v>44645</v>
       </c>
@@ -16850,7 +16967,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="612" spans="1:4">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A612" s="8">
         <v>44652</v>
       </c>
@@ -16865,7 +16982,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="613" spans="1:4">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A613" s="8">
         <v>44659</v>
       </c>
@@ -16880,7 +16997,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="614" spans="1:4">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A614" s="8">
         <v>44666</v>
       </c>
@@ -16895,7 +17012,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="615" spans="1:4">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A615" s="8">
         <v>44673</v>
       </c>
@@ -16910,7 +17027,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="616" spans="1:4">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A616" s="8">
         <v>44680</v>
       </c>
@@ -16925,7 +17042,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="617" spans="1:4">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A617" s="8">
         <v>44687</v>
       </c>
@@ -16940,7 +17057,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="618" spans="1:4">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A618" s="8">
         <v>44694</v>
       </c>
@@ -16955,7 +17072,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="619" spans="1:4">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A619" s="8">
         <v>44701</v>
       </c>
@@ -16970,7 +17087,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="620" spans="1:4">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A620" s="8">
         <v>44708</v>
       </c>
@@ -16985,7 +17102,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="621" spans="1:4">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A621" s="8">
         <v>44715</v>
       </c>
@@ -17000,7 +17117,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="622" spans="1:4">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" s="8">
         <v>44722</v>
       </c>
@@ -17015,7 +17132,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="623" spans="1:4">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" s="8">
         <v>44729</v>
       </c>
@@ -17030,7 +17147,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="624" spans="1:4">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A624" s="8">
         <v>44736</v>
       </c>
@@ -17045,7 +17162,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="625" spans="1:4">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A625" s="8">
         <v>44743</v>
       </c>
@@ -17060,7 +17177,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="626" spans="1:4">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A626" s="8">
         <v>44750</v>
       </c>
@@ -17075,7 +17192,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="627" spans="1:4">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A627" s="8">
         <v>44757</v>
       </c>
@@ -17090,7 +17207,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="628" spans="1:4">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A628" s="8">
         <v>44764</v>
       </c>
@@ -17105,7 +17222,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="629" spans="1:4">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A629" s="8">
         <v>44771</v>
       </c>
@@ -17120,7 +17237,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="630" spans="1:4">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="8">
         <v>44778</v>
       </c>
@@ -17135,7 +17252,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="631" spans="1:4">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A631" s="8">
         <v>44785</v>
       </c>
@@ -17150,7 +17267,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="632" spans="1:4">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A632" s="8">
         <v>44792</v>
       </c>
@@ -17165,7 +17282,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="633" spans="1:4">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A633" s="8">
         <v>44799</v>
       </c>
@@ -17180,7 +17297,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="634" spans="1:4">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A634" s="8">
         <v>44806</v>
       </c>
@@ -17195,7 +17312,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="635" spans="1:4">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" s="8">
         <v>44813</v>
       </c>
@@ -17210,7 +17327,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="636" spans="1:4">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" s="8">
         <v>44820</v>
       </c>
@@ -17225,7 +17342,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="637" spans="1:4">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A637" s="8">
         <v>44827</v>
       </c>
@@ -17240,7 +17357,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="638" spans="1:4">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A638" s="8">
         <v>44834</v>
       </c>
@@ -17255,7 +17372,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="639" spans="1:4">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" s="8">
         <v>44841</v>
       </c>
@@ -17270,7 +17387,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="640" spans="1:4">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" s="8">
         <v>44848</v>
       </c>
@@ -17285,7 +17402,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="641" spans="1:4">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" s="8">
         <v>44855</v>
       </c>
@@ -17300,7 +17417,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="642" spans="1:4">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A642" s="8">
         <v>44862</v>
       </c>
@@ -17315,7 +17432,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="643" spans="1:4">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A643" s="8">
         <v>44869</v>
       </c>
@@ -17337,7 +17454,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="644" spans="1:4">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A644" s="8">
         <v>44876</v>
       </c>
@@ -17352,7 +17469,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="645" spans="1:4">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A645" s="8">
         <v>44883</v>
       </c>
@@ -17367,7 +17484,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="646" spans="1:4">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A646" s="8">
         <v>44890</v>
       </c>
@@ -17382,7 +17499,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="647" spans="1:4">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A647" s="8">
         <v>44897</v>
       </c>
@@ -17397,7 +17514,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="648" spans="1:4">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A648" s="8">
         <v>44904</v>
       </c>
@@ -17412,7 +17529,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="649" spans="1:4">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A649" s="8">
         <v>44911</v>
       </c>
@@ -17427,7 +17544,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="650" spans="1:4">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A650" s="8">
         <v>44918</v>
       </c>
@@ -17442,7 +17559,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="651" spans="1:4">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A651" s="8">
         <v>44925</v>
       </c>
@@ -17457,7 +17574,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="652" spans="1:4">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A652" s="8">
         <v>44932</v>
       </c>
@@ -17472,7 +17589,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="653" spans="1:4">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" s="8">
         <v>44939</v>
       </c>
@@ -17487,7 +17604,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="654" spans="1:4">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" s="8">
         <v>44946</v>
       </c>
@@ -17502,7 +17619,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="655" spans="1:4">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" s="8">
         <v>44953</v>
       </c>
@@ -17517,7 +17634,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="656" spans="1:4">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" s="8">
         <v>44960</v>
       </c>
@@ -17532,7 +17649,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="657" spans="1:4">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" s="8">
         <v>44967</v>
       </c>
@@ -17547,7 +17664,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="658" spans="1:4">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" s="8">
         <v>44974</v>
       </c>
@@ -17562,7 +17679,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="659" spans="1:4">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" s="8">
         <v>44981</v>
       </c>
@@ -17577,7 +17694,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="660" spans="1:4">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" s="8">
         <v>44988</v>
       </c>
@@ -17592,7 +17709,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="661" spans="1:4">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" s="8">
         <v>44995</v>
       </c>
@@ -17607,7 +17724,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="662" spans="1:4">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" s="8">
         <v>45002</v>
       </c>
@@ -17622,7 +17739,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="663" spans="1:4">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" s="8">
         <v>45009</v>
       </c>
@@ -17637,7 +17754,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="664" spans="1:4">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A664" s="8">
         <v>45016</v>
       </c>
@@ -17652,7 +17769,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="665" spans="1:4">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" s="8">
         <v>45023</v>
       </c>
@@ -17667,7 +17784,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="666" spans="1:4">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" s="8">
         <v>45030</v>
       </c>
@@ -17682,7 +17799,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="667" spans="1:4">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" s="8">
         <v>45037</v>
       </c>
@@ -17697,7 +17814,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="668" spans="1:4">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" s="8">
         <v>45044</v>
       </c>
@@ -17712,7 +17829,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="669" spans="1:4">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A669" s="8">
         <v>45051</v>
       </c>
@@ -17727,7 +17844,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="670" spans="1:4">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" s="8">
         <v>45058</v>
       </c>
@@ -17742,7 +17859,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="671" spans="1:4">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="8">
         <v>45065</v>
       </c>
@@ -17757,7 +17874,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="672" spans="1:4">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A672" s="8">
         <v>45072</v>
       </c>
@@ -17772,7 +17889,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="673" spans="1:4">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A673" s="8">
         <v>45079</v>
       </c>
@@ -17787,7 +17904,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="674" spans="1:4">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A674" s="8">
         <v>45086</v>
       </c>
@@ -17802,7 +17919,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="675" spans="1:4">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A675" s="8">
         <v>45093</v>
       </c>
@@ -17817,7 +17934,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="676" spans="1:4">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A676" s="8">
         <v>45100</v>
       </c>
@@ -17832,7 +17949,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="677" spans="1:4">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" s="8">
         <v>45107</v>
       </c>
@@ -17847,7 +17964,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="678" spans="1:4">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" s="8">
         <v>45114</v>
       </c>
@@ -17862,7 +17979,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="679" spans="1:4">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" s="8">
         <v>45121</v>
       </c>
@@ -17877,7 +17994,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="680" spans="1:4">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A680" s="8">
         <v>45128</v>
       </c>
@@ -17892,7 +18009,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="681" spans="1:4">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A681" s="8">
         <v>45135</v>
       </c>
@@ -17907,7 +18024,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="682" spans="1:4">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" s="8">
         <v>45142</v>
       </c>
@@ -17922,7 +18039,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="683" spans="1:4">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" s="8">
         <v>45149</v>
       </c>
@@ -17937,7 +18054,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="684" spans="1:4">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A684" s="8">
         <v>45156</v>
       </c>
@@ -17952,7 +18069,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="685" spans="1:4">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" s="8">
         <v>45163</v>
       </c>
@@ -17967,7 +18084,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="686" spans="1:4">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A686" s="8">
         <v>45170</v>
       </c>
@@ -17982,7 +18099,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="687" spans="1:4">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" s="8">
         <v>45177</v>
       </c>
@@ -17997,7 +18114,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="688" spans="1:4">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" s="8">
         <v>45184</v>
       </c>
@@ -18012,7 +18129,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="689" spans="1:4">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689" s="8">
         <v>45191</v>
       </c>
@@ -18027,7 +18144,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="690" spans="1:4">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" s="8">
         <v>45198</v>
       </c>
@@ -18042,7 +18159,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="691" spans="1:4">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" s="8">
         <v>45205</v>
       </c>
@@ -18057,7 +18174,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="692" spans="1:4">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692" s="8">
         <v>45212</v>
       </c>
@@ -18072,7 +18189,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="693" spans="1:4">
+    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693" s="8">
         <v>45219</v>
       </c>
@@ -18087,7 +18204,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="694" spans="1:4">
+    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694" s="8">
         <v>45226</v>
       </c>
@@ -18102,7 +18219,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="695" spans="1:4">
+    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695" s="8">
         <v>45233</v>
       </c>
@@ -18117,7 +18234,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="696" spans="1:4">
+    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A696" s="8">
         <v>45240</v>
       </c>
@@ -18132,7 +18249,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="697" spans="1:4">
+    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A697" s="8">
         <v>45247</v>
       </c>
@@ -18147,7 +18264,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="698" spans="1:4">
+    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A698" s="8">
         <v>45254</v>
       </c>
@@ -18162,7 +18279,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="699" spans="1:4">
+    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A699" s="8">
         <v>45261</v>
       </c>
@@ -18177,7 +18294,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="700" spans="1:4">
+    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A700" s="8">
         <v>45268</v>
       </c>
@@ -18192,7 +18309,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="701" spans="1:4">
+    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A701" s="8">
         <v>45275</v>
       </c>
@@ -18206,8 +18323,11 @@
         <f t="shared" si="10"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="702" spans="1:4">
+      <c r="E701" s="10">
+        <v>809.6</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A702" s="8">
         <v>45282</v>
       </c>
@@ -18221,8 +18341,11 @@
         <f t="shared" si="10"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="703" spans="1:4">
+      <c r="E702" s="10">
+        <v>809.6</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A703" s="8">
         <v>45289</v>
       </c>
@@ -18237,7 +18360,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="704" spans="1:4">
+    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A704" s="8">
         <v>45296</v>
       </c>
@@ -18252,7 +18375,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="705" spans="1:4">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A705" s="8">
         <v>45303</v>
       </c>
@@ -18266,8 +18389,11 @@
         <f t="shared" si="10"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="706" spans="1:4">
+      <c r="E705" s="10">
+        <v>910.24</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A706" s="8">
         <v>45310</v>
       </c>
@@ -18282,7 +18408,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="707" spans="1:4">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A707" s="8">
         <v>45317</v>
       </c>
@@ -18304,7 +18430,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="708" spans="1:4">
+    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A708" s="8">
         <v>45324</v>
       </c>
@@ -18319,7 +18445,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="709" spans="1:4">
+    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A709" s="8">
         <v>45331</v>
       </c>
@@ -18334,7 +18460,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="710" spans="1:4">
+    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A710" s="8">
         <v>45338</v>
       </c>
@@ -18349,7 +18475,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="711" spans="1:4">
+    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A711" s="8">
         <v>45345</v>
       </c>
@@ -18364,7 +18490,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="712" spans="1:4">
+    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A712" s="8">
         <v>45352</v>
       </c>
@@ -18379,7 +18505,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="713" spans="1:4">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A713" s="8">
         <v>45359</v>
       </c>
@@ -18393,8 +18519,11 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="714" spans="1:4">
+      <c r="E713" s="10">
+        <v>1201.73</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A714" s="8">
         <v>45366</v>
       </c>
@@ -18408,8 +18537,11 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="715" spans="1:4">
+      <c r="E714" s="10">
+        <v>1215.8900000000001</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A715" s="8">
         <v>45373</v>
       </c>
@@ -18424,7 +18556,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="716" spans="1:4">
+    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A716" s="8">
         <v>45380</v>
       </c>
@@ -18439,7 +18571,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="717" spans="1:4">
+    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A717" s="8">
         <v>45387</v>
       </c>
@@ -18454,7 +18586,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="718" spans="1:4">
+    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A718" s="8">
         <v>45394</v>
       </c>
@@ -18469,7 +18601,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="719" spans="1:4">
+    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A719" s="8">
         <v>45401</v>
       </c>
@@ -18483,8 +18615,11 @@
         <f t="shared" si="11"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="720" spans="1:4">
+      <c r="E719" s="10">
+        <v>1230.06</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A720" s="8">
         <v>45408</v>
       </c>
@@ -18498,8 +18633,11 @@
         <f t="shared" si="11"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="721" spans="1:5">
+      <c r="E720" s="10">
+        <v>1251.68</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" s="8">
         <v>45415</v>
       </c>
@@ -18514,7 +18652,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="722" spans="1:5">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" s="8">
         <v>45422</v>
       </c>
@@ -18529,7 +18667,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="723" spans="1:5">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" s="8">
         <v>45429</v>
       </c>
@@ -18544,7 +18682,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="724" spans="1:5">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" s="8">
         <v>45436</v>
       </c>
@@ -18559,7 +18697,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="725" spans="1:5">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" s="8">
         <v>45443</v>
       </c>
@@ -18574,7 +18712,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="726" spans="1:5">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" s="8">
         <v>45450</v>
       </c>
@@ -18589,7 +18727,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="727" spans="1:5">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" s="8">
         <v>45457</v>
       </c>
@@ -18604,7 +18742,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="728" spans="1:5">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" s="8">
         <v>45464</v>
       </c>
@@ -18622,7 +18760,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" s="8">
         <v>45471</v>
       </c>
@@ -18640,7 +18778,7 @@
         <v>1712.39</v>
       </c>
     </row>
-    <row r="730" spans="1:5">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A730" s="8">
         <v>45478</v>
       </c>
@@ -18655,7 +18793,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="731" spans="1:5">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A731" s="8">
         <v>45485</v>
       </c>
@@ -18670,7 +18808,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="732" spans="1:5">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A732" s="8">
         <v>45492</v>
       </c>
@@ -18685,7 +18823,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="733" spans="1:5">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A733" s="8">
         <v>45499</v>
       </c>
@@ -18700,7 +18838,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="734" spans="1:5">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A734" s="8">
         <v>45506</v>
       </c>
@@ -18715,7 +18853,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="735" spans="1:5">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A735" s="8">
         <v>45513</v>
       </c>
@@ -18730,7 +18868,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="736" spans="1:5">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A736" s="8">
         <v>45520</v>
       </c>
@@ -18745,7 +18883,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="737" spans="1:5">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A737" s="8">
         <v>45527</v>
       </c>
@@ -18760,7 +18898,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="738" spans="1:5">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A738" s="8">
         <v>45534</v>
       </c>
@@ -18775,7 +18913,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="739" spans="1:5">
+    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A739" s="8">
         <v>45541</v>
       </c>
@@ -18790,7 +18928,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="740" spans="1:5">
+    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A740" s="8">
         <v>45548</v>
       </c>
@@ -18805,7 +18943,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="741" spans="1:5">
+    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A741" s="8">
         <v>45555</v>
       </c>
@@ -18820,7 +18958,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="742" spans="1:5">
+    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A742" s="8">
         <v>45562</v>
       </c>
@@ -18835,7 +18973,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="743" spans="1:5">
+    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A743" s="8">
         <v>45569</v>
       </c>
@@ -18853,7 +18991,7 @@
         <v>1936.04</v>
       </c>
     </row>
-    <row r="744" spans="1:5">
+    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A744" s="8">
         <v>45576</v>
       </c>
@@ -18867,8 +19005,11 @@
         <f t="shared" si="11"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="745" spans="1:5">
+      <c r="E744" s="10">
+        <v>1965.85</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A745" s="8">
         <v>45583</v>
       </c>
@@ -18882,8 +19023,11 @@
         <f t="shared" si="11"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="746" spans="1:5">
+      <c r="E745" s="10">
+        <v>1967.35</v>
+      </c>
+    </row>
+    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A746" s="8">
         <v>45590</v>
       </c>
@@ -18898,7 +19042,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="747" spans="1:5">
+    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A747" s="8">
         <v>45597</v>
       </c>
@@ -18913,7 +19057,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="748" spans="1:5">
+    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A748" s="8">
         <v>45604</v>
       </c>
@@ -18928,7 +19072,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="749" spans="1:5">
+    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A749" s="8">
         <v>45611</v>
       </c>
@@ -18942,8 +19086,11 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="750" spans="1:5">
+      <c r="E749" s="10">
+        <v>1977.78</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A750" s="8">
         <v>45618</v>
       </c>
@@ -18958,7 +19105,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="751" spans="1:5">
+    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A751" s="8">
         <v>45625</v>
       </c>
@@ -18973,7 +19120,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="752" spans="1:5">
+    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A752" s="8">
         <v>45632</v>
       </c>
@@ -18988,7 +19135,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="753" spans="1:4">
+    <row r="753" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A753" s="8">
         <v>45639</v>
       </c>
@@ -19003,7 +19150,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="754" spans="1:4">
+    <row r="754" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A754" s="8">
         <v>45646</v>
       </c>
@@ -19018,7 +19165,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="755" spans="1:4">
+    <row r="755" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A755" s="8">
         <v>45653</v>
       </c>
@@ -19033,7 +19180,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="756" spans="1:4">
+    <row r="756" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A756" s="8">
         <v>45660</v>
       </c>
@@ -19047,8 +19194,11 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="757" spans="1:4">
+      <c r="E756" s="10">
+        <v>2052.33</v>
+      </c>
+    </row>
+    <row r="757" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A757" s="8">
         <v>45667</v>
       </c>
@@ -19063,7 +19213,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="758" spans="1:4">
+    <row r="758" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A758" s="8">
         <v>45674</v>
       </c>
@@ -19078,7 +19228,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="759" spans="1:4">
+    <row r="759" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A759" s="8">
         <v>45681</v>
       </c>
@@ -19093,7 +19243,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="760" spans="1:4">
+    <row r="760" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A760" s="8">
         <v>45688</v>
       </c>
@@ -19107,8 +19257,11 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="761" spans="1:4">
+      <c r="E760" s="10">
+        <v>2052.33</v>
+      </c>
+    </row>
+    <row r="761" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A761" s="8">
         <v>45695</v>
       </c>
@@ -19123,7 +19276,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="762" spans="1:4">
+    <row r="762" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A762" s="8">
         <v>45702</v>
       </c>
@@ -19138,7 +19291,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="763" spans="1:4">
+    <row r="763" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A763" s="8">
         <v>45709</v>
       </c>
@@ -19152,8 +19305,41 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="764" spans="1:4">
+      <c r="E763" s="10">
+        <v>2067</v>
+      </c>
+      <c r="F763" s="14">
+        <v>8750</v>
+      </c>
+      <c r="G763" s="14">
+        <v>15000</v>
+      </c>
+      <c r="H763" s="14">
+        <v>25000</v>
+      </c>
+      <c r="I763" s="14">
+        <v>29000</v>
+      </c>
+      <c r="J763" s="14">
+        <v>31000</v>
+      </c>
+      <c r="K763" s="14">
+        <v>33500</v>
+      </c>
+      <c r="L763" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M763" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N763" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O763" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="764" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A764" s="8">
         <v>45716</v>
       </c>
@@ -19167,8 +19353,41 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="765" spans="1:4">
+      <c r="E764" s="10">
+        <v>2070</v>
+      </c>
+      <c r="F764" s="14">
+        <v>8750</v>
+      </c>
+      <c r="G764" s="14">
+        <v>15000</v>
+      </c>
+      <c r="H764" s="14">
+        <v>25000</v>
+      </c>
+      <c r="I764" s="14">
+        <v>29000</v>
+      </c>
+      <c r="J764" s="14">
+        <v>31500</v>
+      </c>
+      <c r="K764" s="14">
+        <v>33500</v>
+      </c>
+      <c r="L764" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M764" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N764" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O764" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="765" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A765" s="8">
         <v>45723</v>
       </c>
@@ -19182,8 +19401,41 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="766" spans="1:4">
+      <c r="E765" s="10">
+        <v>2070</v>
+      </c>
+      <c r="F765" s="14">
+        <v>8750</v>
+      </c>
+      <c r="G765" s="14">
+        <v>15000</v>
+      </c>
+      <c r="H765" s="14">
+        <v>25000</v>
+      </c>
+      <c r="I765" s="14">
+        <v>29000</v>
+      </c>
+      <c r="J765" s="14">
+        <v>31500</v>
+      </c>
+      <c r="K765" s="14">
+        <v>33500</v>
+      </c>
+      <c r="L765" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M765" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N765" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O765" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="766" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A766" s="8">
         <v>45730</v>
       </c>
@@ -19197,8 +19449,41 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="767" spans="1:4">
+      <c r="E766" s="10">
+        <v>2071.71</v>
+      </c>
+      <c r="F766" s="14">
+        <v>9000</v>
+      </c>
+      <c r="G766" s="14">
+        <v>15000</v>
+      </c>
+      <c r="H766" s="14">
+        <v>25000</v>
+      </c>
+      <c r="I766" s="14">
+        <v>29000</v>
+      </c>
+      <c r="J766" s="14">
+        <v>31500</v>
+      </c>
+      <c r="K766" s="14">
+        <v>33500</v>
+      </c>
+      <c r="L766" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M766" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N766" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O766" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="767" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A767" s="8">
         <v>45737</v>
       </c>
@@ -19212,8 +19497,41 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="768" spans="1:4">
+      <c r="E767" s="10">
+        <v>2074.6999999999998</v>
+      </c>
+      <c r="F767" s="14">
+        <v>9000</v>
+      </c>
+      <c r="G767" s="14">
+        <v>15000</v>
+      </c>
+      <c r="H767" s="14">
+        <v>25500</v>
+      </c>
+      <c r="I767" s="14">
+        <v>29500</v>
+      </c>
+      <c r="J767" s="14">
+        <v>31500</v>
+      </c>
+      <c r="K767" s="14">
+        <v>33500</v>
+      </c>
+      <c r="L767" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M767" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N767" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O767" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="768" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A768" s="8">
         <v>45744</v>
       </c>
@@ -19227,8 +19545,41 @@
         <f t="shared" si="11"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="769" spans="1:5">
+      <c r="E768" s="10">
+        <v>2076</v>
+      </c>
+      <c r="F768" s="14">
+        <v>9000</v>
+      </c>
+      <c r="G768" s="14">
+        <v>15250</v>
+      </c>
+      <c r="H768" s="14">
+        <v>25500</v>
+      </c>
+      <c r="I768" s="14">
+        <v>29500</v>
+      </c>
+      <c r="J768" s="14">
+        <v>31500</v>
+      </c>
+      <c r="K768" s="14">
+        <v>33500</v>
+      </c>
+      <c r="L768" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M768" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N768" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O768" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="769" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A769" s="8">
         <v>45751</v>
       </c>
@@ -19242,8 +19593,41 @@
         <f t="shared" si="11"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="770" spans="1:5">
+      <c r="E769" s="10">
+        <v>2082</v>
+      </c>
+      <c r="F769" s="14">
+        <v>9000</v>
+      </c>
+      <c r="G769" s="14">
+        <v>15250</v>
+      </c>
+      <c r="H769" s="14">
+        <v>26000</v>
+      </c>
+      <c r="I769" s="14">
+        <v>30000</v>
+      </c>
+      <c r="J769" s="14">
+        <v>32000</v>
+      </c>
+      <c r="K769" s="14">
+        <v>33500</v>
+      </c>
+      <c r="L769" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M769" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N769" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O769" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="770" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A770" s="8">
         <v>45758</v>
       </c>
@@ -19257,8 +19641,41 @@
         <f t="shared" si="11"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="771" spans="1:5">
+      <c r="E770" s="10">
+        <v>2106</v>
+      </c>
+      <c r="F770" s="14">
+        <v>9500</v>
+      </c>
+      <c r="G770" s="14">
+        <v>15250</v>
+      </c>
+      <c r="H770" s="14">
+        <v>26000</v>
+      </c>
+      <c r="I770" s="14">
+        <v>30000</v>
+      </c>
+      <c r="J770" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K770" s="14">
+        <v>35000</v>
+      </c>
+      <c r="L770" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M770" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N770" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O770" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="771" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A771" s="8">
         <v>45765</v>
       </c>
@@ -19279,8 +19696,41 @@
 )</f>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="772" spans="1:5">
+      <c r="E771" s="10">
+        <v>2110.48</v>
+      </c>
+      <c r="F771" s="14">
+        <v>10000</v>
+      </c>
+      <c r="G771" s="14">
+        <v>15500</v>
+      </c>
+      <c r="H771" s="14">
+        <v>26000</v>
+      </c>
+      <c r="I771" s="14">
+        <v>30000</v>
+      </c>
+      <c r="J771" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K771" s="14">
+        <v>35000</v>
+      </c>
+      <c r="L771" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M771" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N771" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O771" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="772" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A772" s="8">
         <v>45772</v>
       </c>
@@ -19294,8 +19744,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="773" spans="1:5">
+      <c r="E772" s="10">
+        <v>2100</v>
+      </c>
+      <c r="F772" s="14">
+        <v>10000</v>
+      </c>
+      <c r="G772" s="14">
+        <v>15750</v>
+      </c>
+      <c r="H772" s="14">
+        <v>26000</v>
+      </c>
+      <c r="I772" s="14">
+        <v>30000</v>
+      </c>
+      <c r="J772" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K772" s="14">
+        <v>35000</v>
+      </c>
+      <c r="L772" s="14">
+        <v>41000</v>
+      </c>
+      <c r="M772" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N772" s="14">
+        <v>64000</v>
+      </c>
+      <c r="O772" s="14">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="773" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A773" s="8">
         <v>45779</v>
       </c>
@@ -19310,7 +19793,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="774" spans="1:5">
+    <row r="774" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A774" s="8">
         <v>45786</v>
       </c>
@@ -19324,8 +19807,11 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="775" spans="1:5">
+      <c r="E774" s="10">
+        <v>2055.31</v>
+      </c>
+    </row>
+    <row r="775" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A775" s="8">
         <v>45793</v>
       </c>
@@ -19340,7 +19826,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="776" spans="1:5">
+    <row r="776" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A776" s="8">
         <v>45800</v>
       </c>
@@ -19355,7 +19841,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="777" spans="1:5">
+    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A777" s="8">
         <v>45807</v>
       </c>
@@ -19370,7 +19856,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="778" spans="1:5">
+    <row r="778" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A778" s="8">
         <v>45814</v>
       </c>
@@ -19385,7 +19871,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="779" spans="1:5">
+    <row r="779" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A779" s="8">
         <v>45821</v>
       </c>
@@ -19400,7 +19886,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="780" spans="1:5">
+    <row r="780" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A780" s="8">
         <v>45828</v>
       </c>
@@ -19417,8 +19903,38 @@
       <c r="E780" s="10">
         <v>2158.19</v>
       </c>
-    </row>
-    <row r="781" spans="1:5">
+      <c r="F780" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G780" s="14">
+        <v>17000</v>
+      </c>
+      <c r="H780" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I780" s="14">
+        <v>31500</v>
+      </c>
+      <c r="J780" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K780" s="14">
+        <v>36000</v>
+      </c>
+      <c r="L780" s="14">
+        <v>43000</v>
+      </c>
+      <c r="M780" s="14">
+        <v>52000</v>
+      </c>
+      <c r="N780" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O780" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="781" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A781" s="8">
         <v>45835</v>
       </c>
@@ -19435,8 +19951,38 @@
       <c r="E781" s="10">
         <v>2158.19</v>
       </c>
-    </row>
-    <row r="782" spans="1:5">
+      <c r="F781" s="14">
+        <v>11250</v>
+      </c>
+      <c r="G781" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H781" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I781" s="14">
+        <v>31500</v>
+      </c>
+      <c r="J781" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K781" s="14">
+        <v>36000</v>
+      </c>
+      <c r="L781" s="14">
+        <v>43000</v>
+      </c>
+      <c r="M781" s="14">
+        <v>52000</v>
+      </c>
+      <c r="N781" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O781" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="782" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A782" s="8">
         <v>45842</v>
       </c>
@@ -19453,8 +19999,38 @@
       <c r="E782" s="10">
         <v>2164.15</v>
       </c>
-    </row>
-    <row r="783" spans="1:5">
+      <c r="F782" s="14">
+        <v>11250</v>
+      </c>
+      <c r="G782" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H782" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I782" s="14">
+        <v>31500</v>
+      </c>
+      <c r="J782" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K782" s="14">
+        <v>36000</v>
+      </c>
+      <c r="L782" s="14">
+        <v>43000</v>
+      </c>
+      <c r="M782" s="14">
+        <v>52000</v>
+      </c>
+      <c r="N782" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O782" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="783" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A783" s="8">
         <v>45849</v>
       </c>
@@ -19471,8 +20047,38 @@
       <c r="E783" s="10">
         <v>2164.9</v>
       </c>
-    </row>
-    <row r="784" spans="1:5">
+      <c r="F783" s="14">
+        <v>11750</v>
+      </c>
+      <c r="G783" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H783" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I783" s="14">
+        <v>31500</v>
+      </c>
+      <c r="J783" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K783" s="14">
+        <v>36000</v>
+      </c>
+      <c r="L783" s="14">
+        <v>43000</v>
+      </c>
+      <c r="M783" s="14">
+        <v>52000</v>
+      </c>
+      <c r="N783" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O783" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="784" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A784" s="8">
         <v>45856</v>
       </c>
@@ -19486,8 +20092,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="785" spans="1:4">
+      <c r="E784" s="10">
+        <v>2165</v>
+      </c>
+      <c r="F784" s="14">
+        <v>11750</v>
+      </c>
+      <c r="G784" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H784" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I784" s="14">
+        <v>31750</v>
+      </c>
+      <c r="J784" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K784" s="14">
+        <v>36000</v>
+      </c>
+      <c r="L784" s="14">
+        <v>43000</v>
+      </c>
+      <c r="M784" s="14">
+        <v>52000</v>
+      </c>
+      <c r="N784" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O784" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="785" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A785" s="8">
         <v>45863</v>
       </c>
@@ -19501,8 +20140,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="786" spans="1:4">
+      <c r="E785" s="10">
+        <v>2183</v>
+      </c>
+      <c r="F785" s="14">
+        <v>11750</v>
+      </c>
+      <c r="G785" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H785" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I785" s="14">
+        <v>31750</v>
+      </c>
+      <c r="J785" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K785" s="14">
+        <v>36000</v>
+      </c>
+      <c r="L785" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M785" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N785" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O785" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="786" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A786" s="8">
         <v>45870</v>
       </c>
@@ -19516,8 +20188,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="787" spans="1:4">
+      <c r="E786" s="10">
+        <v>2183.54</v>
+      </c>
+      <c r="F786" s="14">
+        <v>11750</v>
+      </c>
+      <c r="G786" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H786" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I786" s="14">
+        <v>32000</v>
+      </c>
+      <c r="J786" s="14">
+        <v>34000</v>
+      </c>
+      <c r="K786" s="14">
+        <v>36000</v>
+      </c>
+      <c r="L786" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M786" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N786" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O786" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="787" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A787" s="8">
         <v>45877</v>
       </c>
@@ -19532,7 +20237,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="788" spans="1:4">
+    <row r="788" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A788" s="8">
         <v>45884</v>
       </c>
@@ -19547,7 +20252,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="789" spans="1:4">
+    <row r="789" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A789" s="8">
         <v>45891</v>
       </c>
@@ -19561,8 +20266,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="790" spans="1:4">
+      <c r="E789" s="10">
+        <v>2210</v>
+      </c>
+      <c r="F789" s="14">
+        <v>11750</v>
+      </c>
+      <c r="G789" s="14">
+        <v>17500</v>
+      </c>
+      <c r="H789" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I789" s="14">
+        <v>32500</v>
+      </c>
+      <c r="J789" s="14">
+        <v>36000</v>
+      </c>
+      <c r="K789" s="14">
+        <v>38000</v>
+      </c>
+      <c r="L789" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M789" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N789" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O789" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="790" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A790" s="8">
         <v>45898</v>
       </c>
@@ -19576,8 +20314,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="791" spans="1:4">
+      <c r="E790" s="10">
+        <v>2210</v>
+      </c>
+      <c r="F790" s="14">
+        <v>11750</v>
+      </c>
+      <c r="G790" s="14">
+        <v>17500</v>
+      </c>
+      <c r="H790" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I790" s="14">
+        <v>32500</v>
+      </c>
+      <c r="J790" s="14">
+        <v>36000</v>
+      </c>
+      <c r="K790" s="14">
+        <v>38000</v>
+      </c>
+      <c r="L790" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M790" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N790" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O790" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="791" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A791" s="8">
         <v>45905</v>
       </c>
@@ -19591,8 +20362,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="792" spans="1:4">
+      <c r="E791" s="10">
+        <v>2213</v>
+      </c>
+      <c r="F791" s="14">
+        <v>11750</v>
+      </c>
+      <c r="G791" s="14">
+        <v>17500</v>
+      </c>
+      <c r="H791" s="14">
+        <v>28000</v>
+      </c>
+      <c r="I791" s="14">
+        <v>33000</v>
+      </c>
+      <c r="J791" s="14">
+        <v>36500</v>
+      </c>
+      <c r="K791" s="14">
+        <v>38500</v>
+      </c>
+      <c r="L791" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M791" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N791" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O791" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="792" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A792" s="8">
         <v>45912</v>
       </c>
@@ -19606,8 +20410,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="793" spans="1:4">
+      <c r="E792" s="10">
+        <v>2214.85</v>
+      </c>
+      <c r="F792" s="14">
+        <v>11250</v>
+      </c>
+      <c r="G792" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H792" s="14">
+        <v>28000</v>
+      </c>
+      <c r="I792" s="14">
+        <v>33000</v>
+      </c>
+      <c r="J792" s="14">
+        <v>36500</v>
+      </c>
+      <c r="K792" s="14">
+        <v>38500</v>
+      </c>
+      <c r="L792" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M792" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N792" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O792" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="793" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A793" s="8">
         <v>45919</v>
       </c>
@@ -19621,8 +20458,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="794" spans="1:4">
+      <c r="E793" s="10">
+        <v>2210</v>
+      </c>
+      <c r="F793" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G793" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H793" s="14">
+        <v>27000</v>
+      </c>
+      <c r="I793" s="14">
+        <v>33000</v>
+      </c>
+      <c r="J793" s="14">
+        <v>36500</v>
+      </c>
+      <c r="K793" s="14">
+        <v>38500</v>
+      </c>
+      <c r="L793" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M793" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N793" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O793" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="794" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A794" s="8">
         <v>45926</v>
       </c>
@@ -19636,8 +20506,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="795" spans="1:4">
+      <c r="E794" s="10">
+        <v>2212</v>
+      </c>
+      <c r="F794" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G794" s="14">
+        <v>17500</v>
+      </c>
+      <c r="H794" s="14">
+        <v>27000</v>
+      </c>
+      <c r="I794" s="14">
+        <v>33000</v>
+      </c>
+      <c r="J794" s="14">
+        <v>36500</v>
+      </c>
+      <c r="K794" s="14">
+        <v>38500</v>
+      </c>
+      <c r="L794" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M794" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N794" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O794" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="795" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A795" s="8">
         <v>45933</v>
       </c>
@@ -19651,8 +20554,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="796" spans="1:4">
+      <c r="E795" s="10">
+        <v>2203</v>
+      </c>
+      <c r="F795" s="14">
+        <v>10750</v>
+      </c>
+      <c r="G795" s="14">
+        <v>17250</v>
+      </c>
+      <c r="H795" s="14">
+        <v>27000</v>
+      </c>
+      <c r="I795" s="14">
+        <v>33000</v>
+      </c>
+      <c r="J795" s="14">
+        <v>36500</v>
+      </c>
+      <c r="K795" s="14">
+        <v>38500</v>
+      </c>
+      <c r="L795" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M795" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N795" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O795" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="796" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A796" s="8">
         <v>45940</v>
       </c>
@@ -19666,8 +20602,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="797" spans="1:4">
+      <c r="E796" s="10">
+        <v>2191</v>
+      </c>
+      <c r="F796" s="14">
+        <v>10500</v>
+      </c>
+      <c r="G796" s="14">
+        <v>17000</v>
+      </c>
+      <c r="H796" s="14">
+        <v>27000</v>
+      </c>
+      <c r="I796" s="14">
+        <v>33000</v>
+      </c>
+      <c r="J796" s="14">
+        <v>35500</v>
+      </c>
+      <c r="K796" s="14">
+        <v>38000</v>
+      </c>
+      <c r="L796" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M796" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N796" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O796" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="797" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A797" s="8">
         <v>45947</v>
       </c>
@@ -19682,7 +20651,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="798" spans="1:4">
+    <row r="798" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A798" s="8">
         <v>45954</v>
       </c>
@@ -19696,8 +20665,41 @@
         <f t="shared" si="12"/>
         <v>UTC+2</v>
       </c>
-    </row>
-    <row r="799" spans="1:4">
+      <c r="E798" s="10">
+        <v>2182</v>
+      </c>
+      <c r="F798" s="14">
+        <v>10250</v>
+      </c>
+      <c r="G798" s="14">
+        <v>17000</v>
+      </c>
+      <c r="H798" s="14">
+        <v>27000</v>
+      </c>
+      <c r="I798" s="14">
+        <v>32500</v>
+      </c>
+      <c r="J798" s="14">
+        <v>35000</v>
+      </c>
+      <c r="K798" s="14">
+        <v>37500</v>
+      </c>
+      <c r="L798" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M798" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N798" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O798" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="799" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A799" s="8">
         <v>45961</v>
       </c>
@@ -19711,8 +20713,41 @@
         <f t="shared" si="12"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="800" spans="1:4">
+      <c r="E799" s="10">
+        <v>2184</v>
+      </c>
+      <c r="F799" s="14">
+        <v>10250</v>
+      </c>
+      <c r="G799" s="14">
+        <v>17000</v>
+      </c>
+      <c r="H799" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I799" s="14">
+        <v>32500</v>
+      </c>
+      <c r="J799" s="14">
+        <v>35000</v>
+      </c>
+      <c r="K799" s="14">
+        <v>37500</v>
+      </c>
+      <c r="L799" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M799" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N799" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O799" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="800" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A800" s="8">
         <v>45968</v>
       </c>
@@ -19726,8 +20761,41 @@
         <f t="shared" si="12"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="801" spans="1:15">
+      <c r="E800" s="10">
+        <v>2184</v>
+      </c>
+      <c r="F800" s="14">
+        <v>10250</v>
+      </c>
+      <c r="G800" s="14">
+        <v>17000</v>
+      </c>
+      <c r="H800" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I800" s="14">
+        <v>32500</v>
+      </c>
+      <c r="J800" s="14">
+        <v>35000</v>
+      </c>
+      <c r="K800" s="14">
+        <v>37500</v>
+      </c>
+      <c r="L800" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M800" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N800" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O800" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A801" s="8">
         <v>45975</v>
       </c>
@@ -19741,8 +20809,41 @@
         <f t="shared" si="12"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="802" spans="1:15">
+      <c r="E801" s="10">
+        <v>2184</v>
+      </c>
+      <c r="F801" s="14">
+        <v>10250</v>
+      </c>
+      <c r="G801" s="14">
+        <v>17000</v>
+      </c>
+      <c r="H801" s="14">
+        <v>27500</v>
+      </c>
+      <c r="I801" s="14">
+        <v>32500</v>
+      </c>
+      <c r="J801" s="14">
+        <v>35000</v>
+      </c>
+      <c r="K801" s="14">
+        <v>37500</v>
+      </c>
+      <c r="L801" s="14">
+        <v>44000</v>
+      </c>
+      <c r="M801" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N801" s="14">
+        <v>66000</v>
+      </c>
+      <c r="O801" s="14">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A802" s="8">
         <v>45982</v>
       </c>
@@ -19757,7 +20858,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="803" spans="1:15">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A803" s="8">
         <v>45989</v>
       </c>
@@ -19772,7 +20873,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="804" spans="1:15">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A804" s="8">
         <v>45996</v>
       </c>
@@ -19787,7 +20888,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="805" spans="1:15">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A805" s="8">
         <v>46003</v>
       </c>
@@ -19802,7 +20903,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="806" spans="1:15">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A806" s="8">
         <v>46010</v>
       </c>
@@ -19816,8 +20917,41 @@
         <f t="shared" si="12"/>
         <v>UTC+1</v>
       </c>
-    </row>
-    <row r="807" spans="1:15">
+      <c r="E806" s="12">
+        <v>2182.0500000000002</v>
+      </c>
+      <c r="F806" s="15">
+        <v>10250</v>
+      </c>
+      <c r="G806" s="15">
+        <v>16500</v>
+      </c>
+      <c r="H806" s="15">
+        <v>27500</v>
+      </c>
+      <c r="I806" s="15">
+        <v>32000</v>
+      </c>
+      <c r="J806" s="15">
+        <v>35500</v>
+      </c>
+      <c r="K806" s="15">
+        <v>37500</v>
+      </c>
+      <c r="L806" s="15">
+        <v>44000</v>
+      </c>
+      <c r="M806" s="15">
+        <v>53000</v>
+      </c>
+      <c r="N806" s="15">
+        <v>66000</v>
+      </c>
+      <c r="O806" s="15">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A807" s="8">
         <v>46017</v>
       </c>
@@ -19832,20 +20966,40 @@
         <v>UTC+1</v>
       </c>
       <c r="E807" s="12">
-        <v>2180.56</v>
-      </c>
-      <c r="F807" s="15"/>
-      <c r="G807" s="15"/>
-      <c r="H807" s="15"/>
-      <c r="I807" s="15"/>
-      <c r="J807" s="15"/>
-      <c r="K807" s="15"/>
-      <c r="L807" s="15"/>
-      <c r="M807" s="15"/>
-      <c r="N807" s="15"/>
-      <c r="O807" s="15"/>
-    </row>
-    <row r="808" spans="1:15">
+        <v>2182.0500000000002</v>
+      </c>
+      <c r="F807" s="15">
+        <v>10250</v>
+      </c>
+      <c r="G807" s="15">
+        <v>16500</v>
+      </c>
+      <c r="H807" s="15">
+        <v>27500</v>
+      </c>
+      <c r="I807" s="15">
+        <v>32000</v>
+      </c>
+      <c r="J807" s="15">
+        <v>35500</v>
+      </c>
+      <c r="K807" s="15">
+        <v>37500</v>
+      </c>
+      <c r="L807" s="15">
+        <v>44000</v>
+      </c>
+      <c r="M807" s="15">
+        <v>53000</v>
+      </c>
+      <c r="N807" s="15">
+        <v>66000</v>
+      </c>
+      <c r="O807" s="15">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A808" s="8">
         <v>46024</v>
       </c>
@@ -19893,7 +21047,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A809" s="8">
         <v>46031</v>
       </c>
@@ -19941,7 +21095,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A810" s="8">
         <v>46038</v>
       </c>
@@ -19989,7 +21143,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A811" s="8">
         <v>46045</v>
       </c>
@@ -20037,7 +21191,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A812" s="8">
         <v>46052</v>
       </c>
@@ -20085,7 +21239,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A813" s="8">
         <v>46059</v>
       </c>
@@ -20133,7 +21287,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A814" s="8">
         <v>46066</v>
       </c>
@@ -20181,7 +21335,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A815" s="8">
         <v>46073</v>
       </c>
@@ -20229,7 +21383,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A816" s="8">
         <v>46080</v>
       </c>
@@ -20277,7 +21431,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A817" s="8">
         <v>46087</v>
       </c>
@@ -20325,7 +21479,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A818" s="8">
         <v>46094</v>
       </c>
@@ -20373,7 +21527,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A819" s="8">
         <v>46101</v>
       </c>
@@ -20421,7 +21575,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A820" s="8">
         <v>46108</v>
       </c>
@@ -20469,7 +21623,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A821" s="8">
         <v>46115</v>
       </c>
@@ -20517,7 +21671,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A822" s="8">
         <v>46122</v>
       </c>
@@ -20545,7 +21699,7 @@
       <c r="N822" s="15"/>
       <c r="O822" s="15"/>
     </row>
-    <row r="823" spans="1:15">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A823" s="8">
         <v>46129</v>
       </c>
@@ -20573,7 +21727,7 @@
       <c r="N823" s="15"/>
       <c r="O823" s="15"/>
     </row>
-    <row r="824" spans="1:15">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A824" s="8">
         <v>46136</v>
       </c>
@@ -20601,7 +21755,7 @@
       <c r="N824" s="15"/>
       <c r="O824" s="15"/>
     </row>
-    <row r="825" spans="1:15">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A825" s="8">
         <v>46143</v>
       </c>
@@ -20649,7 +21803,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A826" s="8">
         <v>46150</v>
       </c>
@@ -20697,7 +21851,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A827" s="8">
         <v>46157</v>
       </c>
@@ -20745,7 +21899,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A828" s="8">
         <v>46164</v>
       </c>
@@ -20793,7 +21947,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A829" s="8">
         <v>46171</v>
       </c>
@@ -20841,7 +21995,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A830" s="8">
         <v>46178</v>
       </c>
@@ -20889,7 +22043,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15">
+    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A831" s="8">
         <v>46185</v>
       </c>
@@ -20937,7 +22091,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15">
+    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A832" s="8">
         <v>46192</v>
       </c>
@@ -20985,7 +22139,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="833" spans="1:15">
+    <row r="833" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A833" s="8">
         <v>46199</v>
       </c>
@@ -21033,7 +22187,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="834" spans="1:15">
+    <row r="834" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A834" s="8">
         <v>46206</v>
       </c>
@@ -21088,7 +22242,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="835" spans="1:15">
+    <row r="835" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A835" s="8">
         <v>46213</v>
       </c>
@@ -21136,7 +22290,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="836" spans="1:15">
+    <row r="836" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A836" s="8">
         <v>46220</v>
       </c>
@@ -21193,7 +22347,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21204,12 +22358,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
@@ -21217,7 +22371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>17</v>
       </c>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6C3DFB-AB85-49EC-87EC-9E11753A9B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981F0383-19CC-4565-AC6D-988F5574B989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
@@ -4859,7 +4859,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -4921,7 +4921,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -4963,7 +4963,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -4998,7 +4998,9 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="aptos narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981F0383-19CC-4565-AC6D-988F5574B989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FA4F5A-654E-4DE3-A4C0-73967BEA2DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
@@ -2789,6 +2789,9 @@
                 <c:pt idx="834">
                   <c:v>46220</c:v>
                 </c:pt>
+                <c:pt idx="835">
+                  <c:v>46227</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4706,6 +4709,9 @@
                 <c:pt idx="799">
                   <c:v>2184</c:v>
                 </c:pt>
+                <c:pt idx="803">
+                  <c:v>2180.56</c:v>
+                </c:pt>
                 <c:pt idx="804">
                   <c:v>2182.0500000000002</c:v>
                 </c:pt>
@@ -4797,6 +4803,9 @@
                   <c:v>2337.11</c:v>
                 </c:pt>
                 <c:pt idx="834">
+                  <c:v>2340.09</c:v>
+                </c:pt>
+                <c:pt idx="835">
                   <c:v>2340.09</c:v>
                 </c:pt>
               </c:numCache>
@@ -5909,7 +5918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P836"/>
+  <dimension ref="A1:P837"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -20904,6 +20913,9 @@
         <f t="shared" si="12"/>
         <v>UTC+1</v>
       </c>
+      <c r="E805" s="10">
+        <v>2180.56</v>
+      </c>
     </row>
     <row r="806" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A806" s="8">
@@ -22337,6 +22349,61 @@
         <v>72000</v>
       </c>
       <c r="O836" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="837" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A837" s="8">
+        <v>46227</v>
+      </c>
+      <c r="B837" s="8">
+        <v>46227</v>
+      </c>
+      <c r="C837" s="9">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="D837" s="8" t="str">
+        <f t="shared" ref="D837" si="14">"UTC+"&amp;IF(
+    AND(
+        B837&gt;=EOMONTH(DATE(YEAR(B837),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B837),3,1),0),2),7),
+        B837&lt;EOMONTH(DATE(YEAR(B837),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B837),10,1),0),2),7)
+    ),
+    2,
+    1
+)</f>
+        <v>UTC+2</v>
+      </c>
+      <c r="E837" s="10">
+        <v>2340.09</v>
+      </c>
+      <c r="F837" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G837" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H837" s="14">
+        <v>30500</v>
+      </c>
+      <c r="I837" s="14">
+        <v>34000</v>
+      </c>
+      <c r="J837" s="14">
+        <v>38000</v>
+      </c>
+      <c r="K837" s="14">
+        <v>40000</v>
+      </c>
+      <c r="L837" s="14">
+        <v>46000</v>
+      </c>
+      <c r="M837" s="14">
+        <v>57000</v>
+      </c>
+      <c r="N837" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O837" s="14">
         <v>79000</v>
       </c>
     </row>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FA4F5A-654E-4DE3-A4C0-73967BEA2DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3710C0-28AD-2845-9FF6-869CE19BEF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="26380" yWindow="600" windowWidth="24820" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -100,12 +100,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,9 +171,9 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -181,43 +181,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -235,7 +235,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2792,6 +2792,9 @@
                 <c:pt idx="835">
                   <c:v>46227</c:v>
                 </c:pt>
+                <c:pt idx="836">
+                  <c:v>46234</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4728,13 +4731,13 @@
                   <c:v>2182.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="809">
-                  <c:v>2184</c:v>
+                  <c:v>2183.54</c:v>
                 </c:pt>
                 <c:pt idx="810">
-                  <c:v>2184</c:v>
+                  <c:v>2183.54</c:v>
                 </c:pt>
                 <c:pt idx="811">
-                  <c:v>2184</c:v>
+                  <c:v>2183.54</c:v>
                 </c:pt>
                 <c:pt idx="812">
                   <c:v>2191</c:v>
@@ -4807,6 +4810,9 @@
                 </c:pt>
                 <c:pt idx="835">
                   <c:v>2340.09</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>2343.0700000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5622,9 +5628,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5662,7 +5668,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5768,7 +5774,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5910,7 +5916,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5918,19 +5924,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P837"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P838"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.77734375" style="11"/>
+    <col min="5" max="5" width="11.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="7" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5978,7 +5984,7 @@
       </c>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16">
       <c r="A2" s="8">
         <v>40383</v>
       </c>
@@ -6003,7 +6009,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16">
       <c r="A3" s="8">
         <v>40390</v>
       </c>
@@ -6028,7 +6034,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16">
       <c r="A4" s="8">
         <v>40397</v>
       </c>
@@ -6046,7 +6052,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="A5" s="8">
         <v>40404</v>
       </c>
@@ -6064,7 +6070,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16">
       <c r="A6" s="8">
         <v>40411</v>
       </c>
@@ -6082,7 +6088,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16">
       <c r="A7" s="8">
         <v>40418</v>
       </c>
@@ -6100,7 +6106,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16">
       <c r="A8" s="8">
         <v>40425</v>
       </c>
@@ -6118,7 +6124,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16">
       <c r="A9" s="8">
         <v>40432</v>
       </c>
@@ -6136,7 +6142,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16">
       <c r="A10" s="8">
         <v>40439</v>
       </c>
@@ -6154,7 +6160,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16">
       <c r="A11" s="8">
         <v>40446</v>
       </c>
@@ -6172,7 +6178,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16">
       <c r="A12" s="8">
         <v>40453</v>
       </c>
@@ -6190,7 +6196,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16">
       <c r="A13" s="8">
         <v>40460</v>
       </c>
@@ -6208,7 +6214,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16">
       <c r="A14" s="8">
         <v>40467</v>
       </c>
@@ -6226,7 +6232,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16">
       <c r="A15" s="8">
         <v>40474</v>
       </c>
@@ -6244,7 +6250,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16">
       <c r="A16" s="8">
         <v>40481</v>
       </c>
@@ -6262,7 +6268,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="8">
         <v>40488</v>
       </c>
@@ -6280,7 +6286,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="8">
         <v>40495</v>
       </c>
@@ -6298,7 +6304,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="8">
         <v>40502</v>
       </c>
@@ -6316,7 +6322,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="8">
         <v>40509</v>
       </c>
@@ -6334,7 +6340,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="8">
         <v>40516</v>
       </c>
@@ -6352,7 +6358,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="8">
         <v>40523</v>
       </c>
@@ -6370,7 +6376,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="8">
         <v>40530</v>
       </c>
@@ -6388,7 +6394,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="8">
         <v>40537</v>
       </c>
@@ -6406,7 +6412,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="8">
         <v>40544</v>
       </c>
@@ -6424,7 +6430,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="8">
         <v>40551</v>
       </c>
@@ -6442,7 +6448,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="8">
         <v>40558</v>
       </c>
@@ -6460,7 +6466,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="8">
         <v>40565</v>
       </c>
@@ -6478,7 +6484,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="8">
         <v>40572</v>
       </c>
@@ -6496,7 +6502,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="8">
         <v>40579</v>
       </c>
@@ -6514,7 +6520,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="8">
         <v>40586</v>
       </c>
@@ -6532,7 +6538,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="8">
         <v>40593</v>
       </c>
@@ -6550,7 +6556,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="8">
         <v>40600</v>
       </c>
@@ -6568,7 +6574,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="8">
         <v>40607</v>
       </c>
@@ -6586,7 +6592,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="8">
         <v>40614</v>
       </c>
@@ -6604,7 +6610,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="8">
         <v>40621</v>
       </c>
@@ -6622,7 +6628,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="8">
         <v>40628</v>
       </c>
@@ -6640,7 +6646,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="8">
         <v>40635</v>
       </c>
@@ -6658,7 +6664,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="8">
         <v>40642</v>
       </c>
@@ -6676,7 +6682,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="8">
         <v>40649</v>
       </c>
@@ -6694,7 +6700,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="8">
         <v>40656</v>
       </c>
@@ -6712,7 +6718,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="8">
         <v>40663</v>
       </c>
@@ -6730,7 +6736,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="8">
         <v>40670</v>
       </c>
@@ -6748,7 +6754,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="8">
         <v>40677</v>
       </c>
@@ -6766,7 +6772,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="8">
         <v>40684</v>
       </c>
@@ -6784,7 +6790,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" s="8">
         <v>40691</v>
       </c>
@@ -6802,7 +6808,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" s="8">
         <v>40698</v>
       </c>
@@ -6820,7 +6826,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48" s="8">
         <v>40705</v>
       </c>
@@ -6838,7 +6844,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" s="8">
         <v>40712</v>
       </c>
@@ -6856,7 +6862,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" s="8">
         <v>40719</v>
       </c>
@@ -6874,7 +6880,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" s="8">
         <v>40726</v>
       </c>
@@ -6892,7 +6898,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" s="8">
         <v>40733</v>
       </c>
@@ -6910,7 +6916,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53" s="8">
         <v>40740</v>
       </c>
@@ -6928,7 +6934,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" s="8">
         <v>40747</v>
       </c>
@@ -6946,7 +6952,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55" s="8">
         <v>40754</v>
       </c>
@@ -6964,7 +6970,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56" s="8">
         <v>40761</v>
       </c>
@@ -6982,7 +6988,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57" s="8">
         <v>40768</v>
       </c>
@@ -7000,7 +7006,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58" s="8">
         <v>40775</v>
       </c>
@@ -7018,7 +7024,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59" s="8">
         <v>40782</v>
       </c>
@@ -7036,7 +7042,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" s="8">
         <v>40789</v>
       </c>
@@ -7054,7 +7060,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61" s="8">
         <v>40796</v>
       </c>
@@ -7072,7 +7078,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62" s="8">
         <v>40803</v>
       </c>
@@ -7090,7 +7096,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63" s="8">
         <v>40810</v>
       </c>
@@ -7108,7 +7114,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64" s="8">
         <v>40817</v>
       </c>
@@ -7126,7 +7132,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65" s="8">
         <v>40824</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5">
       <c r="A66" s="8">
         <v>40831</v>
       </c>
@@ -7162,7 +7168,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67" s="8">
         <v>40838</v>
       </c>
@@ -7187,7 +7193,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68" s="8">
         <v>40845</v>
       </c>
@@ -7205,7 +7211,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5">
       <c r="A69" s="8">
         <v>40852</v>
       </c>
@@ -7223,7 +7229,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70" s="8">
         <v>40859</v>
       </c>
@@ -7241,7 +7247,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71" s="8">
         <v>40866</v>
       </c>
@@ -7259,7 +7265,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72" s="8">
         <v>40873</v>
       </c>
@@ -7277,7 +7283,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73" s="8">
         <v>40880</v>
       </c>
@@ -7295,7 +7301,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5">
       <c r="A74" s="8">
         <v>40887</v>
       </c>
@@ -7313,7 +7319,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75" s="8">
         <v>40894</v>
       </c>
@@ -7331,7 +7337,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5">
       <c r="A76" s="8">
         <v>40901</v>
       </c>
@@ -7349,7 +7355,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5">
       <c r="A77" s="8">
         <v>40908</v>
       </c>
@@ -7367,7 +7373,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5">
       <c r="A78" s="8">
         <v>40915</v>
       </c>
@@ -7385,7 +7391,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5">
       <c r="A79" s="8">
         <v>40922</v>
       </c>
@@ -7403,7 +7409,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5">
       <c r="A80" s="8">
         <v>40929</v>
       </c>
@@ -7421,7 +7427,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5">
       <c r="A81" s="8">
         <v>40936</v>
       </c>
@@ -7439,7 +7445,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5">
       <c r="A82" s="8">
         <v>40942</v>
       </c>
@@ -7457,7 +7463,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5">
       <c r="A83" s="8">
         <v>40943</v>
       </c>
@@ -7475,7 +7481,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5">
       <c r="A84" s="8">
         <v>40950</v>
       </c>
@@ -7493,7 +7499,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5">
       <c r="A85" s="8">
         <v>40957</v>
       </c>
@@ -7511,7 +7517,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5">
       <c r="A86" s="8">
         <v>40964</v>
       </c>
@@ -7529,7 +7535,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5">
       <c r="A87" s="8">
         <v>40978</v>
       </c>
@@ -7547,7 +7553,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5">
       <c r="A88" s="8">
         <v>40985</v>
       </c>
@@ -7565,7 +7571,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5">
       <c r="A89" s="8">
         <v>40992</v>
       </c>
@@ -7583,7 +7589,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5">
       <c r="A90" s="8">
         <v>40999</v>
       </c>
@@ -7601,7 +7607,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5">
       <c r="A91" s="8">
         <v>41006</v>
       </c>
@@ -7619,7 +7625,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5">
       <c r="A92" s="8">
         <v>41013</v>
       </c>
@@ -7637,7 +7643,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5">
       <c r="A93" s="8">
         <v>41020</v>
       </c>
@@ -7655,7 +7661,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5">
       <c r="A94" s="8">
         <v>41027</v>
       </c>
@@ -7673,7 +7679,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5">
       <c r="A95" s="8">
         <v>41034</v>
       </c>
@@ -7691,7 +7697,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5">
       <c r="A96" s="8">
         <v>41041</v>
       </c>
@@ -7709,7 +7715,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5">
       <c r="A97" s="8">
         <v>41048</v>
       </c>
@@ -7727,7 +7733,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98" s="8">
         <v>41055</v>
       </c>
@@ -7745,7 +7751,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5">
       <c r="A99" s="8">
         <v>41062</v>
       </c>
@@ -7763,7 +7769,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5">
       <c r="A100" s="8">
         <v>41069</v>
       </c>
@@ -7781,7 +7787,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5">
       <c r="A101" s="8">
         <v>41076</v>
       </c>
@@ -7799,7 +7805,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5">
       <c r="A102" s="8">
         <v>41083</v>
       </c>
@@ -7817,7 +7823,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5">
       <c r="A103" s="8">
         <v>41090</v>
       </c>
@@ -7835,7 +7841,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5">
       <c r="A104" s="8">
         <v>41097</v>
       </c>
@@ -7853,7 +7859,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105" s="8">
         <v>41104</v>
       </c>
@@ -7871,7 +7877,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106" s="8">
         <v>41111</v>
       </c>
@@ -7889,7 +7895,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107" s="8">
         <v>41118</v>
       </c>
@@ -7907,7 +7913,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108" s="8">
         <v>41125</v>
       </c>
@@ -7925,7 +7931,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5">
       <c r="A109" s="8">
         <v>41132</v>
       </c>
@@ -7943,7 +7949,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110" s="8">
         <v>41139</v>
       </c>
@@ -7961,7 +7967,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5">
       <c r="A111" s="8">
         <v>41146</v>
       </c>
@@ -7979,7 +7985,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5">
       <c r="A112" s="8">
         <v>41153</v>
       </c>
@@ -7997,7 +8003,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5">
       <c r="A113" s="8">
         <v>41160</v>
       </c>
@@ -8015,7 +8021,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5">
       <c r="A114" s="8">
         <v>41167</v>
       </c>
@@ -8033,7 +8039,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5">
       <c r="A115" s="8">
         <v>41174</v>
       </c>
@@ -8051,7 +8057,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5">
       <c r="A116" s="8">
         <v>41181</v>
       </c>
@@ -8069,7 +8075,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5">
       <c r="A117" s="8">
         <v>41188</v>
       </c>
@@ -8087,7 +8093,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5">
       <c r="A118" s="8">
         <v>41195</v>
       </c>
@@ -8105,7 +8111,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5">
       <c r="A119" s="8">
         <v>41202</v>
       </c>
@@ -8123,7 +8129,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5">
       <c r="A120" s="8">
         <v>41209</v>
       </c>
@@ -8141,7 +8147,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5">
       <c r="A121" s="8">
         <v>41216</v>
       </c>
@@ -8159,7 +8165,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5">
       <c r="A122" s="8">
         <v>41223</v>
       </c>
@@ -8177,7 +8183,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5">
       <c r="A123" s="8">
         <v>41230</v>
       </c>
@@ -8195,7 +8201,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5">
       <c r="A124" s="8">
         <v>41237</v>
       </c>
@@ -8213,7 +8219,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5">
       <c r="A125" s="8">
         <v>41244</v>
       </c>
@@ -8231,7 +8237,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5">
       <c r="A126" s="8">
         <v>41251</v>
       </c>
@@ -8249,7 +8255,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5">
       <c r="A127" s="8">
         <v>41258</v>
       </c>
@@ -8267,7 +8273,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5">
       <c r="A128" s="8">
         <v>41265</v>
       </c>
@@ -8285,7 +8291,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5">
       <c r="A129" s="8">
         <v>41272</v>
       </c>
@@ -8303,7 +8309,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5">
       <c r="A130" s="8">
         <v>41279</v>
       </c>
@@ -8321,7 +8327,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5">
       <c r="A131" s="8">
         <v>41286</v>
       </c>
@@ -8346,7 +8352,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5">
       <c r="A132" s="8">
         <v>41293</v>
       </c>
@@ -8364,7 +8370,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5">
       <c r="A133" s="8">
         <v>41300</v>
       </c>
@@ -8382,7 +8388,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5">
       <c r="A134" s="8">
         <v>41307</v>
       </c>
@@ -8400,7 +8406,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5">
       <c r="A135" s="8">
         <v>41314</v>
       </c>
@@ -8418,7 +8424,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5">
       <c r="A136" s="8">
         <v>41321</v>
       </c>
@@ -8436,7 +8442,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5">
       <c r="A137" s="8">
         <v>41328</v>
       </c>
@@ -8454,7 +8460,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5">
       <c r="A138" s="8">
         <v>41335</v>
       </c>
@@ -8472,7 +8478,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5">
       <c r="A139" s="8">
         <v>41342</v>
       </c>
@@ -8490,7 +8496,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5">
       <c r="A140" s="8">
         <v>41349</v>
       </c>
@@ -8508,7 +8514,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5">
       <c r="A141" s="8">
         <v>41356</v>
       </c>
@@ -8526,7 +8532,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5">
       <c r="A142" s="8">
         <v>41363</v>
       </c>
@@ -8544,7 +8550,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5">
       <c r="A143" s="8">
         <v>41370</v>
       </c>
@@ -8562,7 +8568,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5">
       <c r="A144" s="8">
         <v>41377</v>
       </c>
@@ -8580,7 +8586,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5">
       <c r="A145" s="8">
         <v>41384</v>
       </c>
@@ -8598,7 +8604,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5">
       <c r="A146" s="8">
         <v>41391</v>
       </c>
@@ -8616,7 +8622,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5">
       <c r="A147" s="8">
         <v>41398</v>
       </c>
@@ -8634,7 +8640,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5">
       <c r="A148" s="8">
         <v>41405</v>
       </c>
@@ -8652,7 +8658,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5">
       <c r="A149" s="8">
         <v>41412</v>
       </c>
@@ -8670,7 +8676,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5">
       <c r="A150" s="8">
         <v>41419</v>
       </c>
@@ -8688,7 +8694,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5">
       <c r="A151" s="8">
         <v>41426</v>
       </c>
@@ -8706,7 +8712,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5">
       <c r="A152" s="8">
         <v>41433</v>
       </c>
@@ -8724,7 +8730,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5">
       <c r="A153" s="8">
         <v>41440</v>
       </c>
@@ -8742,7 +8748,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5">
       <c r="A154" s="8">
         <v>41447</v>
       </c>
@@ -8760,7 +8766,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5">
       <c r="A155" s="8">
         <v>41454</v>
       </c>
@@ -8778,7 +8784,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5">
       <c r="A156" s="8">
         <v>41461</v>
       </c>
@@ -8796,7 +8802,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5">
       <c r="A157" s="8">
         <v>41468</v>
       </c>
@@ -8814,7 +8820,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5">
       <c r="A158" s="8">
         <v>41475</v>
       </c>
@@ -8832,7 +8838,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5">
       <c r="A159" s="8">
         <v>41482</v>
       </c>
@@ -8850,7 +8856,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5">
       <c r="A160" s="8">
         <v>41489</v>
       </c>
@@ -8868,7 +8874,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5">
       <c r="A161" s="8">
         <v>41496</v>
       </c>
@@ -8886,7 +8892,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5">
       <c r="A162" s="8">
         <v>41503</v>
       </c>
@@ -8904,7 +8910,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5">
       <c r="A163" s="8">
         <v>41510</v>
       </c>
@@ -8922,7 +8928,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5">
       <c r="A164" s="8">
         <v>41517</v>
       </c>
@@ -8940,7 +8946,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5">
       <c r="A165" s="8">
         <v>41524</v>
       </c>
@@ -8958,7 +8964,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5">
       <c r="A166" s="8">
         <v>41531</v>
       </c>
@@ -8976,7 +8982,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5">
       <c r="A167" s="8">
         <v>41538</v>
       </c>
@@ -8994,7 +9000,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5">
       <c r="A168" s="8">
         <v>41545</v>
       </c>
@@ -9012,7 +9018,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5">
       <c r="A169" s="8">
         <v>41552</v>
       </c>
@@ -9030,7 +9036,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5">
       <c r="A170" s="8">
         <v>41559</v>
       </c>
@@ -9048,7 +9054,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5">
       <c r="A171" s="8">
         <v>41566</v>
       </c>
@@ -9066,7 +9072,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5">
       <c r="A172" s="8">
         <v>41573</v>
       </c>
@@ -9084,7 +9090,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5">
       <c r="A173" s="8">
         <v>41580</v>
       </c>
@@ -9102,7 +9108,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5">
       <c r="A174" s="8">
         <v>41587</v>
       </c>
@@ -9120,7 +9126,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5">
       <c r="A175" s="8">
         <v>41594</v>
       </c>
@@ -9138,7 +9144,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5">
       <c r="A176" s="8">
         <v>41601</v>
       </c>
@@ -9156,7 +9162,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5">
       <c r="A177" s="8">
         <v>41608</v>
       </c>
@@ -9174,7 +9180,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5">
       <c r="A178" s="8">
         <v>41615</v>
       </c>
@@ -9192,7 +9198,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5">
       <c r="A179" s="8">
         <v>41622</v>
       </c>
@@ -9210,7 +9216,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5">
       <c r="A180" s="8">
         <v>41629</v>
       </c>
@@ -9228,7 +9234,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5">
       <c r="A181" s="8">
         <v>41636</v>
       </c>
@@ -9246,7 +9252,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5">
       <c r="A182" s="8">
         <v>41643</v>
       </c>
@@ -9264,7 +9270,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5">
       <c r="A183" s="8">
         <v>41650</v>
       </c>
@@ -9282,7 +9288,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5">
       <c r="A184" s="8">
         <v>41657</v>
       </c>
@@ -9300,7 +9306,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5">
       <c r="A185" s="8">
         <v>41664</v>
       </c>
@@ -9318,7 +9324,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5">
       <c r="A186" s="8">
         <v>41671</v>
       </c>
@@ -9336,7 +9342,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5">
       <c r="A187" s="8">
         <v>41678</v>
       </c>
@@ -9354,7 +9360,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5">
       <c r="A188" s="8">
         <v>41685</v>
       </c>
@@ -9372,7 +9378,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5">
       <c r="A189" s="8">
         <v>41692</v>
       </c>
@@ -9390,7 +9396,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5">
       <c r="A190" s="8">
         <v>41699</v>
       </c>
@@ -9408,7 +9414,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5">
       <c r="A191" s="8">
         <v>41706</v>
       </c>
@@ -9426,7 +9432,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5">
       <c r="A192" s="8">
         <v>41713</v>
       </c>
@@ -9444,7 +9450,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5">
       <c r="A193" s="8">
         <v>41720</v>
       </c>
@@ -9462,7 +9468,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5">
       <c r="A194" s="8">
         <v>41727</v>
       </c>
@@ -9480,7 +9486,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5">
       <c r="A195" s="8">
         <v>41734</v>
       </c>
@@ -9505,7 +9511,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5">
       <c r="A196" s="8">
         <v>41741</v>
       </c>
@@ -9523,7 +9529,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5">
       <c r="A197" s="8">
         <v>41748</v>
       </c>
@@ -9541,7 +9547,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5">
       <c r="A198" s="8">
         <v>41755</v>
       </c>
@@ -9559,7 +9565,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5">
       <c r="A199" s="8">
         <v>41762</v>
       </c>
@@ -9577,7 +9583,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5">
       <c r="A200" s="8">
         <v>41769</v>
       </c>
@@ -9595,7 +9601,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5">
       <c r="A201" s="8">
         <v>41776</v>
       </c>
@@ -9613,7 +9619,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5">
       <c r="A202" s="8">
         <v>41783</v>
       </c>
@@ -9631,7 +9637,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5">
       <c r="A203" s="8">
         <v>41790</v>
       </c>
@@ -9649,7 +9655,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5">
       <c r="A204" s="8">
         <v>41797</v>
       </c>
@@ -9667,7 +9673,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5">
       <c r="A205" s="8">
         <v>41804</v>
       </c>
@@ -9685,7 +9691,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5">
       <c r="A206" s="8">
         <v>41811</v>
       </c>
@@ -9703,7 +9709,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5">
       <c r="A207" s="8">
         <v>41818</v>
       </c>
@@ -9721,7 +9727,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5">
       <c r="A208" s="8">
         <v>41825</v>
       </c>
@@ -9739,7 +9745,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5">
       <c r="A209" s="8">
         <v>41832</v>
       </c>
@@ -9757,7 +9763,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5">
       <c r="A210" s="8">
         <v>41839</v>
       </c>
@@ -9775,7 +9781,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5">
       <c r="A211" s="8">
         <v>41846</v>
       </c>
@@ -9793,7 +9799,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5">
       <c r="A212" s="8">
         <v>41853</v>
       </c>
@@ -9811,7 +9817,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5">
       <c r="A213" s="8">
         <v>41860</v>
       </c>
@@ -9829,7 +9835,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5">
       <c r="A214" s="8">
         <v>41867</v>
       </c>
@@ -9847,7 +9853,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5">
       <c r="A215" s="8">
         <v>41874</v>
       </c>
@@ -9865,7 +9871,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5">
       <c r="A216" s="8">
         <v>41881</v>
       </c>
@@ -9883,7 +9889,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5">
       <c r="A217" s="8">
         <v>41888</v>
       </c>
@@ -9901,7 +9907,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5">
       <c r="A218" s="8">
         <v>41895</v>
       </c>
@@ -9919,7 +9925,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5">
       <c r="A219" s="8">
         <v>41902</v>
       </c>
@@ -9937,7 +9943,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5">
       <c r="A220" s="8">
         <v>41909</v>
       </c>
@@ -9955,7 +9961,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5">
       <c r="A221" s="8">
         <v>41916</v>
       </c>
@@ -9973,7 +9979,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5">
       <c r="A222" s="8">
         <v>41923</v>
       </c>
@@ -9991,7 +9997,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5">
       <c r="A223" s="8">
         <v>41930</v>
       </c>
@@ -10009,7 +10015,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5">
       <c r="A224" s="8">
         <v>41937</v>
       </c>
@@ -10027,7 +10033,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5">
       <c r="A225" s="8">
         <v>41944</v>
       </c>
@@ -10045,7 +10051,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5">
       <c r="A226" s="8">
         <v>41951</v>
       </c>
@@ -10063,7 +10069,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5">
       <c r="A227" s="8">
         <v>41958</v>
       </c>
@@ -10081,7 +10087,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5">
       <c r="A228" s="8">
         <v>41965</v>
       </c>
@@ -10099,7 +10105,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5">
       <c r="A229" s="8">
         <v>41972</v>
       </c>
@@ -10117,7 +10123,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5">
       <c r="A230" s="8">
         <v>41979</v>
       </c>
@@ -10135,7 +10141,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5">
       <c r="A231" s="8">
         <v>41986</v>
       </c>
@@ -10153,7 +10159,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5">
       <c r="A232" s="8">
         <v>41993</v>
       </c>
@@ -10171,7 +10177,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5">
       <c r="A233" s="8">
         <v>42000</v>
       </c>
@@ -10189,7 +10195,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5">
       <c r="A234" s="8">
         <v>42007</v>
       </c>
@@ -10207,7 +10213,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5">
       <c r="A235" s="8">
         <v>42014</v>
       </c>
@@ -10225,7 +10231,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5">
       <c r="A236" s="8">
         <v>42021</v>
       </c>
@@ -10243,7 +10249,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5">
       <c r="A237" s="8">
         <v>42028</v>
       </c>
@@ -10261,7 +10267,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5">
       <c r="A238" s="8">
         <v>42035</v>
       </c>
@@ -10279,7 +10285,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5">
       <c r="A239" s="8">
         <v>42042</v>
       </c>
@@ -10297,7 +10303,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5">
       <c r="A240" s="8">
         <v>42049</v>
       </c>
@@ -10315,7 +10321,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5">
       <c r="A241" s="8">
         <v>42056</v>
       </c>
@@ -10333,7 +10339,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5">
       <c r="A242" s="8">
         <v>42063</v>
       </c>
@@ -10351,7 +10357,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5">
       <c r="A243" s="8">
         <v>42070</v>
       </c>
@@ -10369,7 +10375,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5">
       <c r="A244" s="8">
         <v>42077</v>
       </c>
@@ -10387,7 +10393,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5">
       <c r="A245" s="8">
         <v>42084</v>
       </c>
@@ -10405,7 +10411,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5">
       <c r="A246" s="8">
         <v>42091</v>
       </c>
@@ -10423,7 +10429,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5">
       <c r="A247" s="8">
         <v>42098</v>
       </c>
@@ -10441,7 +10447,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5">
       <c r="A248" s="8">
         <v>42105</v>
       </c>
@@ -10459,7 +10465,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5">
       <c r="A249" s="8">
         <v>42112</v>
       </c>
@@ -10477,7 +10483,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5">
       <c r="A250" s="8">
         <v>42119</v>
       </c>
@@ -10495,7 +10501,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5">
       <c r="A251" s="8">
         <v>42126</v>
       </c>
@@ -10513,7 +10519,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5">
       <c r="A252" s="8">
         <v>42133</v>
       </c>
@@ -10531,7 +10537,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5">
       <c r="A253" s="8">
         <v>42140</v>
       </c>
@@ -10549,7 +10555,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5">
       <c r="A254" s="8">
         <v>42147</v>
       </c>
@@ -10567,7 +10573,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5">
       <c r="A255" s="8">
         <v>42154</v>
       </c>
@@ -10585,7 +10591,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5">
       <c r="A256" s="8">
         <v>42161</v>
       </c>
@@ -10603,7 +10609,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5">
       <c r="A257" s="8">
         <v>42168</v>
       </c>
@@ -10621,7 +10627,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5">
       <c r="A258" s="8">
         <v>42175</v>
       </c>
@@ -10639,7 +10645,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5">
       <c r="A259" s="8">
         <v>42182</v>
       </c>
@@ -10664,7 +10670,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5">
       <c r="A260" s="8">
         <v>42189</v>
       </c>
@@ -10682,7 +10688,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5">
       <c r="A261" s="8">
         <v>42196</v>
       </c>
@@ -10700,7 +10706,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5">
       <c r="A262" s="8">
         <v>42203</v>
       </c>
@@ -10718,7 +10724,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5">
       <c r="A263" s="8">
         <v>42210</v>
       </c>
@@ -10736,7 +10742,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5">
       <c r="A264" s="8">
         <v>42217</v>
       </c>
@@ -10754,7 +10760,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5">
       <c r="A265" s="8">
         <v>42224</v>
       </c>
@@ -10772,7 +10778,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5">
       <c r="A266" s="8">
         <v>42231</v>
       </c>
@@ -10790,7 +10796,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5">
       <c r="A267" s="8">
         <v>42238</v>
       </c>
@@ -10808,7 +10814,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5">
       <c r="A268" s="8">
         <v>42245</v>
       </c>
@@ -10826,7 +10832,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5">
       <c r="A269" s="8">
         <v>42252</v>
       </c>
@@ -10844,7 +10850,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5">
       <c r="A270" s="8">
         <v>42259</v>
       </c>
@@ -10862,7 +10868,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5">
       <c r="A271" s="8">
         <v>42266</v>
       </c>
@@ -10880,7 +10886,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5">
       <c r="A272" s="8">
         <v>42273</v>
       </c>
@@ -10898,7 +10904,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5">
       <c r="A273" s="8">
         <v>42280</v>
       </c>
@@ -10916,7 +10922,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5">
       <c r="A274" s="8">
         <v>42287</v>
       </c>
@@ -10934,7 +10940,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5">
       <c r="A275" s="8">
         <v>42294</v>
       </c>
@@ -10952,7 +10958,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5">
       <c r="A276" s="8">
         <v>42301</v>
       </c>
@@ -10970,7 +10976,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5">
       <c r="A277" s="8">
         <v>42308</v>
       </c>
@@ -10988,7 +10994,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5">
       <c r="A278" s="8">
         <v>42315</v>
       </c>
@@ -11006,7 +11012,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5">
       <c r="A279" s="8">
         <v>42322</v>
       </c>
@@ -11024,7 +11030,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5">
       <c r="A280" s="8">
         <v>42329</v>
       </c>
@@ -11042,7 +11048,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5">
       <c r="A281" s="8">
         <v>42336</v>
       </c>
@@ -11060,7 +11066,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5">
       <c r="A282" s="8">
         <v>42343</v>
       </c>
@@ -11078,7 +11084,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5">
       <c r="A283" s="8">
         <v>42350</v>
       </c>
@@ -11096,7 +11102,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5">
       <c r="A284" s="8">
         <v>42357</v>
       </c>
@@ -11114,7 +11120,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5">
       <c r="A285" s="8">
         <v>42364</v>
       </c>
@@ -11132,7 +11138,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5">
       <c r="A286" s="8">
         <v>42371</v>
       </c>
@@ -11150,7 +11156,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5">
       <c r="A287" s="8">
         <v>42378</v>
       </c>
@@ -11168,7 +11174,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5">
       <c r="A288" s="8">
         <v>42385</v>
       </c>
@@ -11186,7 +11192,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5">
       <c r="A289" s="8">
         <v>42392</v>
       </c>
@@ -11204,7 +11210,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5">
       <c r="A290" s="8">
         <v>42399</v>
       </c>
@@ -11222,7 +11228,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5">
       <c r="A291" s="8">
         <v>42406</v>
       </c>
@@ -11240,7 +11246,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5">
       <c r="A292" s="8">
         <v>42413</v>
       </c>
@@ -11258,7 +11264,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5">
       <c r="A293" s="8">
         <v>42420</v>
       </c>
@@ -11276,7 +11282,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5">
       <c r="A294" s="8">
         <v>42427</v>
       </c>
@@ -11294,7 +11300,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5">
       <c r="A295" s="8">
         <v>42434</v>
       </c>
@@ -11312,7 +11318,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5">
       <c r="A296" s="8">
         <v>42441</v>
       </c>
@@ -11330,7 +11336,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5">
       <c r="A297" s="8">
         <v>42448</v>
       </c>
@@ -11348,7 +11354,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5">
       <c r="A298" s="8">
         <v>42455</v>
       </c>
@@ -11366,7 +11372,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5">
       <c r="A299" s="8">
         <v>42462</v>
       </c>
@@ -11384,7 +11390,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5">
       <c r="A300" s="8">
         <v>42469</v>
       </c>
@@ -11402,7 +11408,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5">
       <c r="A301" s="8">
         <v>42476</v>
       </c>
@@ -11420,7 +11426,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5">
       <c r="A302" s="8">
         <v>42483</v>
       </c>
@@ -11438,7 +11444,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5">
       <c r="A303" s="8">
         <v>42490</v>
       </c>
@@ -11456,7 +11462,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5">
       <c r="A304" s="8">
         <v>42497</v>
       </c>
@@ -11474,7 +11480,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5">
       <c r="A305" s="8">
         <v>42504</v>
       </c>
@@ -11492,7 +11498,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5">
       <c r="A306" s="8">
         <v>42511</v>
       </c>
@@ -11510,7 +11516,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5">
       <c r="A307" s="8">
         <v>42518</v>
       </c>
@@ -11528,7 +11534,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5">
       <c r="A308" s="8">
         <v>42525</v>
       </c>
@@ -11546,7 +11552,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5">
       <c r="A309" s="8">
         <v>42532</v>
       </c>
@@ -11564,7 +11570,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5">
       <c r="A310" s="8">
         <v>42539</v>
       </c>
@@ -11582,7 +11588,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5">
       <c r="A311" s="8">
         <v>42546</v>
       </c>
@@ -11600,7 +11606,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5">
       <c r="A312" s="8">
         <v>42553</v>
       </c>
@@ -11618,7 +11624,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5">
       <c r="A313" s="8">
         <v>42560</v>
       </c>
@@ -11636,7 +11642,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5">
       <c r="A314" s="8">
         <v>42567</v>
       </c>
@@ -11654,7 +11660,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5">
       <c r="A315" s="8">
         <v>42574</v>
       </c>
@@ -11672,7 +11678,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5">
       <c r="A316" s="8">
         <v>42581</v>
       </c>
@@ -11690,7 +11696,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5">
       <c r="A317" s="8">
         <v>42588</v>
       </c>
@@ -11708,7 +11714,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5">
       <c r="A318" s="8">
         <v>42595</v>
       </c>
@@ -11726,7 +11732,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5">
       <c r="A319" s="8">
         <v>42602</v>
       </c>
@@ -11744,7 +11750,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5">
       <c r="A320" s="8">
         <v>42609</v>
       </c>
@@ -11762,7 +11768,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5">
       <c r="A321" s="8">
         <v>42616</v>
       </c>
@@ -11780,7 +11786,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5">
       <c r="A322" s="8">
         <v>42623</v>
       </c>
@@ -11798,7 +11804,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5">
       <c r="A323" s="8">
         <v>42630</v>
       </c>
@@ -11823,7 +11829,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5">
       <c r="A324" s="8">
         <v>42637</v>
       </c>
@@ -11841,7 +11847,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5">
       <c r="A325" s="8">
         <v>42644</v>
       </c>
@@ -11859,7 +11865,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5">
       <c r="A326" s="8">
         <v>42651</v>
       </c>
@@ -11877,7 +11883,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5">
       <c r="A327" s="8">
         <v>42658</v>
       </c>
@@ -11895,7 +11901,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5">
       <c r="A328" s="8">
         <v>42665</v>
       </c>
@@ -11913,7 +11919,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5">
       <c r="A329" s="8">
         <v>42672</v>
       </c>
@@ -11931,7 +11937,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5">
       <c r="A330" s="8">
         <v>42679</v>
       </c>
@@ -11949,7 +11955,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5">
       <c r="A331" s="8">
         <v>42686</v>
       </c>
@@ -11967,7 +11973,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5">
       <c r="A332" s="8">
         <v>42693</v>
       </c>
@@ -11985,7 +11991,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5">
       <c r="A333" s="8">
         <v>42700</v>
       </c>
@@ -12003,7 +12009,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5">
       <c r="A334" s="8">
         <v>42707</v>
       </c>
@@ -12021,7 +12027,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5">
       <c r="A335" s="8">
         <v>42714</v>
       </c>
@@ -12039,7 +12045,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5">
       <c r="A336" s="8">
         <v>42721</v>
       </c>
@@ -12057,7 +12063,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5">
       <c r="A337" s="8">
         <v>42728</v>
       </c>
@@ -12075,7 +12081,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5">
       <c r="A338" s="8">
         <v>42735</v>
       </c>
@@ -12093,7 +12099,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5">
       <c r="A339" s="8">
         <v>42742</v>
       </c>
@@ -12111,7 +12117,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5">
       <c r="A340" s="8">
         <v>42749</v>
       </c>
@@ -12129,7 +12135,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5">
       <c r="A341" s="8">
         <v>42756</v>
       </c>
@@ -12147,7 +12153,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5">
       <c r="A342" s="8">
         <v>42763</v>
       </c>
@@ -12165,7 +12171,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5">
       <c r="A343" s="8">
         <v>42770</v>
       </c>
@@ -12183,7 +12189,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5">
       <c r="A344" s="8">
         <v>42777</v>
       </c>
@@ -12201,7 +12207,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5">
       <c r="A345" s="8">
         <v>42784</v>
       </c>
@@ -12219,7 +12225,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5">
       <c r="A346" s="8">
         <v>42791</v>
       </c>
@@ -12237,7 +12243,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5">
       <c r="A347" s="8">
         <v>42798</v>
       </c>
@@ -12255,7 +12261,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5">
       <c r="A348" s="8">
         <v>42805</v>
       </c>
@@ -12273,7 +12279,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5">
       <c r="A349" s="8">
         <v>42812</v>
       </c>
@@ -12291,7 +12297,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5">
       <c r="A350" s="8">
         <v>42819</v>
       </c>
@@ -12309,7 +12315,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5">
       <c r="A351" s="8">
         <v>42826</v>
       </c>
@@ -12327,7 +12333,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5">
       <c r="A352" s="8">
         <v>42833</v>
       </c>
@@ -12345,7 +12351,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5">
       <c r="A353" s="8">
         <v>42840</v>
       </c>
@@ -12363,7 +12369,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5">
       <c r="A354" s="8">
         <v>42847</v>
       </c>
@@ -12381,7 +12387,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5">
       <c r="A355" s="8">
         <v>42854</v>
       </c>
@@ -12399,7 +12405,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5">
       <c r="A356" s="8">
         <v>42861</v>
       </c>
@@ -12417,7 +12423,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5">
       <c r="A357" s="8">
         <v>42868</v>
       </c>
@@ -12435,7 +12441,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5">
       <c r="A358" s="8">
         <v>42875</v>
       </c>
@@ -12453,7 +12459,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5">
       <c r="A359" s="8">
         <v>42882</v>
       </c>
@@ -12471,7 +12477,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5">
       <c r="A360" s="8">
         <v>42889</v>
       </c>
@@ -12489,7 +12495,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5">
       <c r="A361" s="8">
         <v>42896</v>
       </c>
@@ -12507,7 +12513,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5">
       <c r="A362" s="8">
         <v>42903</v>
       </c>
@@ -12525,7 +12531,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5">
       <c r="A363" s="8">
         <v>42910</v>
       </c>
@@ -12543,7 +12549,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5">
       <c r="A364" s="8">
         <v>42917</v>
       </c>
@@ -12561,7 +12567,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5">
       <c r="A365" s="8">
         <v>42924</v>
       </c>
@@ -12579,7 +12585,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5">
       <c r="A366" s="8">
         <v>42931</v>
       </c>
@@ -12597,7 +12603,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5">
       <c r="A367" s="8">
         <v>42938</v>
       </c>
@@ -12615,7 +12621,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5">
       <c r="A368" s="8">
         <v>42945</v>
       </c>
@@ -12633,7 +12639,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5">
       <c r="A369" s="8">
         <v>42952</v>
       </c>
@@ -12651,7 +12657,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5">
       <c r="A370" s="8">
         <v>42959</v>
       </c>
@@ -12669,7 +12675,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5">
       <c r="A371" s="8">
         <v>42966</v>
       </c>
@@ -12687,7 +12693,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5">
       <c r="A372" s="8">
         <v>42973</v>
       </c>
@@ -12705,7 +12711,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5">
       <c r="A373" s="8">
         <v>42980</v>
       </c>
@@ -12723,7 +12729,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5">
       <c r="A374" s="8">
         <v>42987</v>
       </c>
@@ -12741,7 +12747,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5">
       <c r="A375" s="8">
         <v>42994</v>
       </c>
@@ -12759,7 +12765,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5">
       <c r="A376" s="8">
         <v>43001</v>
       </c>
@@ -12777,7 +12783,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5">
       <c r="A377" s="8">
         <v>43008</v>
       </c>
@@ -12795,7 +12801,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5">
       <c r="A378" s="8">
         <v>43015</v>
       </c>
@@ -12813,7 +12819,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5">
       <c r="A379" s="8">
         <v>43022</v>
       </c>
@@ -12831,7 +12837,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5">
       <c r="A380" s="8">
         <v>43029</v>
       </c>
@@ -12849,7 +12855,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5">
       <c r="A381" s="8">
         <v>43036</v>
       </c>
@@ -12867,7 +12873,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5">
       <c r="A382" s="8">
         <v>43043</v>
       </c>
@@ -12885,7 +12891,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5">
       <c r="A383" s="8">
         <v>43050</v>
       </c>
@@ -12903,7 +12909,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5">
       <c r="A384" s="8">
         <v>43057</v>
       </c>
@@ -12921,7 +12927,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5">
       <c r="A385" s="8">
         <v>43064</v>
       </c>
@@ -12939,7 +12945,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5">
       <c r="A386" s="8">
         <v>43071</v>
       </c>
@@ -12957,7 +12963,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5">
       <c r="A387" s="8">
         <v>43078</v>
       </c>
@@ -12982,7 +12988,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5">
       <c r="A388" s="8">
         <v>43085</v>
       </c>
@@ -13000,7 +13006,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5">
       <c r="A389" s="8">
         <v>43092</v>
       </c>
@@ -13018,7 +13024,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5">
       <c r="A390" s="8">
         <v>43099</v>
       </c>
@@ -13036,7 +13042,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5">
       <c r="A391" s="8">
         <v>43106</v>
       </c>
@@ -13054,7 +13060,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5">
       <c r="A392" s="8">
         <v>43113</v>
       </c>
@@ -13072,7 +13078,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5">
       <c r="A393" s="8">
         <v>43120</v>
       </c>
@@ -13090,7 +13096,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5">
       <c r="A394" s="8">
         <v>43127</v>
       </c>
@@ -13108,7 +13114,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5">
       <c r="A395" s="8">
         <v>43134</v>
       </c>
@@ -13126,7 +13132,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5">
       <c r="A396" s="8">
         <v>43141</v>
       </c>
@@ -13144,7 +13150,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5">
       <c r="A397" s="8">
         <v>43148</v>
       </c>
@@ -13162,7 +13168,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5">
       <c r="A398" s="8">
         <v>43155</v>
       </c>
@@ -13180,7 +13186,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5">
       <c r="A399" s="8">
         <v>43162</v>
       </c>
@@ -13198,7 +13204,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5">
       <c r="A400" s="8">
         <v>43169</v>
       </c>
@@ -13216,7 +13222,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5">
       <c r="A401" s="8">
         <v>43176</v>
       </c>
@@ -13234,7 +13240,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5">
       <c r="A402" s="8">
         <v>43183</v>
       </c>
@@ -13252,7 +13258,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5">
       <c r="A403" s="8">
         <v>43190</v>
       </c>
@@ -13270,7 +13276,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5">
       <c r="A404" s="8">
         <v>43197</v>
       </c>
@@ -13288,7 +13294,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5">
       <c r="A405" s="8">
         <v>43204</v>
       </c>
@@ -13306,7 +13312,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5">
       <c r="A406" s="8">
         <v>43211</v>
       </c>
@@ -13324,7 +13330,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5">
       <c r="A407" s="8">
         <v>43218</v>
       </c>
@@ -13342,7 +13348,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5">
       <c r="A408" s="8">
         <v>43225</v>
       </c>
@@ -13360,7 +13366,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5">
       <c r="A409" s="8">
         <v>43232</v>
       </c>
@@ -13378,7 +13384,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5">
       <c r="A410" s="8">
         <v>43239</v>
       </c>
@@ -13396,7 +13402,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5">
       <c r="A411" s="8">
         <v>43245</v>
       </c>
@@ -13414,7 +13420,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5">
       <c r="A412" s="8">
         <v>43252</v>
       </c>
@@ -13432,7 +13438,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5">
       <c r="A413" s="8">
         <v>43259</v>
       </c>
@@ -13450,7 +13456,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5">
       <c r="A414" s="8">
         <v>43266</v>
       </c>
@@ -13468,7 +13474,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5">
       <c r="A415" s="8">
         <v>43273</v>
       </c>
@@ -13486,7 +13492,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5">
       <c r="A416" s="8">
         <v>43280</v>
       </c>
@@ -13504,7 +13510,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5">
       <c r="A417" s="8">
         <v>43287</v>
       </c>
@@ -13522,7 +13528,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5">
       <c r="A418" s="8">
         <v>43294</v>
       </c>
@@ -13540,7 +13546,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5">
       <c r="A419" s="8">
         <v>43301</v>
       </c>
@@ -13558,7 +13564,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5">
       <c r="A420" s="8">
         <v>43308</v>
       </c>
@@ -13576,7 +13582,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5">
       <c r="A421" s="8">
         <v>43315</v>
       </c>
@@ -13594,7 +13600,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5">
       <c r="A422" s="8">
         <v>43322</v>
       </c>
@@ -13612,7 +13618,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5">
       <c r="A423" s="8">
         <v>43329</v>
       </c>
@@ -13630,7 +13636,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5">
       <c r="A424" s="8">
         <v>43336</v>
       </c>
@@ -13648,7 +13654,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5">
       <c r="A425" s="8">
         <v>43343</v>
       </c>
@@ -13666,7 +13672,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5">
       <c r="A426" s="8">
         <v>43350</v>
       </c>
@@ -13684,7 +13690,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5">
       <c r="A427" s="8">
         <v>43357</v>
       </c>
@@ -13702,7 +13708,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5">
       <c r="A428" s="8">
         <v>43364</v>
       </c>
@@ -13720,7 +13726,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5">
       <c r="A429" s="8">
         <v>43371</v>
       </c>
@@ -13738,7 +13744,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5">
       <c r="A430" s="8">
         <v>43378</v>
       </c>
@@ -13756,7 +13762,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5">
       <c r="A431" s="8">
         <v>43385</v>
       </c>
@@ -13774,7 +13780,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5">
       <c r="A432" s="8">
         <v>43392</v>
       </c>
@@ -13792,7 +13798,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5">
       <c r="A433" s="8">
         <v>43399</v>
       </c>
@@ -13810,7 +13816,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5">
       <c r="A434" s="8">
         <v>43406</v>
       </c>
@@ -13828,7 +13834,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5">
       <c r="A435" s="8">
         <v>43413</v>
       </c>
@@ -13846,7 +13852,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5">
       <c r="A436" s="8">
         <v>43420</v>
       </c>
@@ -13864,7 +13870,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5">
       <c r="A437" s="8">
         <v>43427</v>
       </c>
@@ -13882,7 +13888,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5">
       <c r="A438" s="8">
         <v>43434</v>
       </c>
@@ -13900,7 +13906,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5">
       <c r="A439" s="8">
         <v>43441</v>
       </c>
@@ -13918,7 +13924,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5">
       <c r="A440" s="8">
         <v>43448</v>
       </c>
@@ -13936,7 +13942,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5">
       <c r="A441" s="8">
         <v>43455</v>
       </c>
@@ -13954,7 +13960,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5">
       <c r="A442" s="8">
         <v>43462</v>
       </c>
@@ -13972,7 +13978,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5">
       <c r="A443" s="8">
         <v>43469</v>
       </c>
@@ -13990,7 +13996,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5">
       <c r="A444" s="8">
         <v>43476</v>
       </c>
@@ -14008,7 +14014,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5">
       <c r="A445" s="8">
         <v>43483</v>
       </c>
@@ -14026,7 +14032,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5">
       <c r="A446" s="8">
         <v>43490</v>
       </c>
@@ -14044,7 +14050,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5">
       <c r="A447" s="8">
         <v>43497</v>
       </c>
@@ -14062,7 +14068,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5">
       <c r="A448" s="8">
         <v>43504</v>
       </c>
@@ -14080,7 +14086,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5">
       <c r="A449" s="8">
         <v>43511</v>
       </c>
@@ -14098,7 +14104,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5">
       <c r="A450" s="8">
         <v>43518</v>
       </c>
@@ -14116,7 +14122,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5">
       <c r="A451" s="8">
         <v>43525</v>
       </c>
@@ -14141,7 +14147,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5">
       <c r="A452" s="8">
         <v>43532</v>
       </c>
@@ -14159,7 +14165,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5">
       <c r="A453" s="8">
         <v>43539</v>
       </c>
@@ -14177,7 +14183,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5">
       <c r="A454" s="8">
         <v>43546</v>
       </c>
@@ -14195,7 +14201,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5">
       <c r="A455" s="8">
         <v>43553</v>
       </c>
@@ -14213,7 +14219,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5">
       <c r="A456" s="8">
         <v>43560</v>
       </c>
@@ -14231,7 +14237,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5">
       <c r="A457" s="8">
         <v>43567</v>
       </c>
@@ -14249,7 +14255,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5">
       <c r="A458" s="8">
         <v>43574</v>
       </c>
@@ -14267,7 +14273,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5">
       <c r="A459" s="8">
         <v>43581</v>
       </c>
@@ -14285,7 +14291,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5">
       <c r="A460" s="8">
         <v>43588</v>
       </c>
@@ -14303,7 +14309,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5">
       <c r="A461" s="8">
         <v>43595</v>
       </c>
@@ -14321,7 +14327,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5">
       <c r="A462" s="8">
         <v>43602</v>
       </c>
@@ -14339,7 +14345,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5">
       <c r="A463" s="8">
         <v>43609</v>
       </c>
@@ -14357,7 +14363,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5">
       <c r="A464" s="8">
         <v>43616</v>
       </c>
@@ -14375,7 +14381,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5">
       <c r="A465" s="8">
         <v>43623</v>
       </c>
@@ -14393,7 +14399,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5">
       <c r="A466" s="8">
         <v>43630</v>
       </c>
@@ -14411,7 +14417,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5">
       <c r="A467" s="8">
         <v>43637</v>
       </c>
@@ -14429,7 +14435,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5">
       <c r="A468" s="8">
         <v>43644</v>
       </c>
@@ -14447,7 +14453,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5">
       <c r="A469" s="8">
         <v>43651</v>
       </c>
@@ -14465,7 +14471,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5">
       <c r="A470" s="8">
         <v>43658</v>
       </c>
@@ -14483,7 +14489,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5">
       <c r="A471" s="8">
         <v>43665</v>
       </c>
@@ -14501,7 +14507,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5">
       <c r="A472" s="8">
         <v>43672</v>
       </c>
@@ -14519,7 +14525,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5">
       <c r="A473" s="8">
         <v>43679</v>
       </c>
@@ -14537,7 +14543,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5">
       <c r="A474" s="8">
         <v>43686</v>
       </c>
@@ -14555,7 +14561,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5">
       <c r="A475" s="8">
         <v>43693</v>
       </c>
@@ -14573,7 +14579,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5">
       <c r="A476" s="8">
         <v>43700</v>
       </c>
@@ -14591,7 +14597,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5">
       <c r="A477" s="8">
         <v>43707</v>
       </c>
@@ -14609,7 +14615,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5">
       <c r="A478" s="8">
         <v>43714</v>
       </c>
@@ -14627,7 +14633,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5">
       <c r="A479" s="8">
         <v>43721</v>
       </c>
@@ -14645,7 +14651,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5">
       <c r="A480" s="8">
         <v>43728</v>
       </c>
@@ -14663,7 +14669,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5">
       <c r="A481" s="8">
         <v>43735</v>
       </c>
@@ -14681,7 +14687,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5">
       <c r="A482" s="8">
         <v>43742</v>
       </c>
@@ -14699,7 +14705,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5">
       <c r="A483" s="8">
         <v>43749</v>
       </c>
@@ -14717,7 +14723,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5">
       <c r="A484" s="8">
         <v>43756</v>
       </c>
@@ -14735,7 +14741,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5">
       <c r="A485" s="8">
         <v>43763</v>
       </c>
@@ -14753,7 +14759,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5">
       <c r="A486" s="8">
         <v>43770</v>
       </c>
@@ -14771,7 +14777,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5">
       <c r="A487" s="8">
         <v>43777</v>
       </c>
@@ -14789,7 +14795,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5">
       <c r="A488" s="8">
         <v>43784</v>
       </c>
@@ -14807,7 +14813,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5">
       <c r="A489" s="8">
         <v>43791</v>
       </c>
@@ -14825,7 +14831,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5">
       <c r="A490" s="8">
         <v>43798</v>
       </c>
@@ -14843,7 +14849,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5">
       <c r="A491" s="8">
         <v>43805</v>
       </c>
@@ -14861,7 +14867,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5">
       <c r="A492" s="8">
         <v>43812</v>
       </c>
@@ -14879,7 +14885,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5">
       <c r="A493" s="8">
         <v>43819</v>
       </c>
@@ -14897,7 +14903,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5">
       <c r="A494" s="8">
         <v>43826</v>
       </c>
@@ -14915,7 +14921,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5">
       <c r="A495" s="8">
         <v>43833</v>
       </c>
@@ -14933,7 +14939,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5">
       <c r="A496" s="8">
         <v>43840</v>
       </c>
@@ -14951,7 +14957,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5">
       <c r="A497" s="8">
         <v>43847</v>
       </c>
@@ -14969,7 +14975,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5">
       <c r="A498" s="8">
         <v>43854</v>
       </c>
@@ -14987,7 +14993,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5">
       <c r="A499" s="8">
         <v>43861</v>
       </c>
@@ -15005,7 +15011,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5">
       <c r="A500" s="8">
         <v>43868</v>
       </c>
@@ -15023,7 +15029,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5">
       <c r="A501" s="8">
         <v>43875</v>
       </c>
@@ -15041,7 +15047,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5">
       <c r="A502" s="8">
         <v>43882</v>
       </c>
@@ -15059,7 +15065,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5">
       <c r="A503" s="8">
         <v>43889</v>
       </c>
@@ -15077,7 +15083,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5">
       <c r="A504" s="8">
         <v>43896</v>
       </c>
@@ -15095,7 +15101,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5">
       <c r="A505" s="8">
         <v>43903</v>
       </c>
@@ -15113,7 +15119,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5">
       <c r="A506" s="8">
         <v>43910</v>
       </c>
@@ -15131,7 +15137,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5">
       <c r="A507" s="8">
         <v>43917</v>
       </c>
@@ -15149,7 +15155,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5">
       <c r="A508" s="8">
         <v>43924</v>
       </c>
@@ -15167,7 +15173,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5">
       <c r="A509" s="8">
         <v>43931</v>
       </c>
@@ -15185,7 +15191,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5">
       <c r="A510" s="8">
         <v>43938</v>
       </c>
@@ -15203,7 +15209,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5">
       <c r="A511" s="8">
         <v>43945</v>
       </c>
@@ -15221,7 +15227,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5">
       <c r="A512" s="8">
         <v>43952</v>
       </c>
@@ -15239,7 +15245,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5">
       <c r="A513" s="8">
         <v>43959</v>
       </c>
@@ -15257,7 +15263,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5">
       <c r="A514" s="8">
         <v>43966</v>
       </c>
@@ -15275,7 +15281,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5">
       <c r="A515" s="8">
         <v>43973</v>
       </c>
@@ -15300,7 +15306,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5">
       <c r="A516" s="8">
         <v>43980</v>
       </c>
@@ -15318,7 +15324,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5">
       <c r="A517" s="8">
         <v>43987</v>
       </c>
@@ -15336,7 +15342,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5">
       <c r="A518" s="8">
         <v>43994</v>
       </c>
@@ -15354,7 +15360,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5">
       <c r="A519" s="8">
         <v>44001</v>
       </c>
@@ -15372,7 +15378,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5">
       <c r="A520" s="8">
         <v>44008</v>
       </c>
@@ -15390,7 +15396,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5">
       <c r="A521" s="8">
         <v>44015</v>
       </c>
@@ -15408,7 +15414,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5">
       <c r="A522" s="8">
         <v>44022</v>
       </c>
@@ -15426,7 +15432,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5">
       <c r="A523" s="8">
         <v>44029</v>
       </c>
@@ -15444,7 +15450,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5">
       <c r="A524" s="8">
         <v>44036</v>
       </c>
@@ -15462,7 +15468,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5">
       <c r="A525" s="8">
         <v>44043</v>
       </c>
@@ -15480,7 +15486,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5">
       <c r="A526" s="8">
         <v>44050</v>
       </c>
@@ -15498,7 +15504,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5">
       <c r="A527" s="8">
         <v>44057</v>
       </c>
@@ -15516,7 +15522,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5">
       <c r="A528" s="8">
         <v>44064</v>
       </c>
@@ -15534,7 +15540,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5">
       <c r="A529" s="8">
         <v>44071</v>
       </c>
@@ -15552,7 +15558,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5">
       <c r="A530" s="8">
         <v>44078</v>
       </c>
@@ -15570,7 +15576,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5">
       <c r="A531" s="8">
         <v>44085</v>
       </c>
@@ -15588,7 +15594,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5">
       <c r="A532" s="8">
         <v>44092</v>
       </c>
@@ -15606,7 +15612,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5">
       <c r="A533" s="8">
         <v>44099</v>
       </c>
@@ -15624,7 +15630,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5">
       <c r="A534" s="8">
         <v>44106</v>
       </c>
@@ -15642,7 +15648,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5">
       <c r="A535" s="8">
         <v>44113</v>
       </c>
@@ -15660,7 +15666,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5">
       <c r="A536" s="8">
         <v>44120</v>
       </c>
@@ -15678,7 +15684,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5">
       <c r="A537" s="8">
         <v>44127</v>
       </c>
@@ -15696,7 +15702,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5">
       <c r="A538" s="8">
         <v>44134</v>
       </c>
@@ -15714,7 +15720,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5">
       <c r="A539" s="8">
         <v>44141</v>
       </c>
@@ -15732,7 +15738,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5">
       <c r="A540" s="8">
         <v>44148</v>
       </c>
@@ -15750,7 +15756,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5">
       <c r="A541" s="8">
         <v>44155</v>
       </c>
@@ -15768,7 +15774,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5">
       <c r="A542" s="8">
         <v>44162</v>
       </c>
@@ -15786,7 +15792,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5">
       <c r="A543" s="8">
         <v>44169</v>
       </c>
@@ -15804,7 +15810,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5">
       <c r="A544" s="8">
         <v>44176</v>
       </c>
@@ -15822,7 +15828,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5">
       <c r="A545" s="8">
         <v>44183</v>
       </c>
@@ -15840,7 +15846,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5">
       <c r="A546" s="8">
         <v>44190</v>
       </c>
@@ -15858,7 +15864,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5">
       <c r="A547" s="8">
         <v>44197</v>
       </c>
@@ -15876,7 +15882,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5">
       <c r="A548" s="8">
         <v>44204</v>
       </c>
@@ -15894,7 +15900,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5">
       <c r="A549" s="8">
         <v>44211</v>
       </c>
@@ -15912,7 +15918,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5">
       <c r="A550" s="8">
         <v>44218</v>
       </c>
@@ -15930,7 +15936,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5">
       <c r="A551" s="8">
         <v>44225</v>
       </c>
@@ -15948,7 +15954,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5">
       <c r="A552" s="8">
         <v>44232</v>
       </c>
@@ -15966,7 +15972,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5">
       <c r="A553" s="8">
         <v>44239</v>
       </c>
@@ -15984,7 +15990,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5">
       <c r="A554" s="8">
         <v>44246</v>
       </c>
@@ -16002,7 +16008,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5">
       <c r="A555" s="8">
         <v>44253</v>
       </c>
@@ -16020,7 +16026,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5">
       <c r="A556" s="8">
         <v>44260</v>
       </c>
@@ -16038,7 +16044,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5">
       <c r="A557" s="8">
         <v>44267</v>
       </c>
@@ -16056,7 +16062,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5">
       <c r="A558" s="8">
         <v>44274</v>
       </c>
@@ -16074,7 +16080,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5">
       <c r="A559" s="8">
         <v>44281</v>
       </c>
@@ -16092,7 +16098,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5">
       <c r="A560" s="8">
         <v>44288</v>
       </c>
@@ -16110,7 +16116,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5">
       <c r="A561" s="8">
         <v>44295</v>
       </c>
@@ -16128,7 +16134,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5">
       <c r="A562" s="8">
         <v>44302</v>
       </c>
@@ -16146,7 +16152,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5">
       <c r="A563" s="8">
         <v>44309</v>
       </c>
@@ -16164,7 +16170,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5">
       <c r="A564" s="8">
         <v>44316</v>
       </c>
@@ -16182,7 +16188,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5">
       <c r="A565" s="8">
         <v>44323</v>
       </c>
@@ -16200,7 +16206,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5">
       <c r="A566" s="8">
         <v>44330</v>
       </c>
@@ -16218,7 +16224,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5">
       <c r="A567" s="8">
         <v>44337</v>
       </c>
@@ -16236,7 +16242,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5">
       <c r="A568" s="8">
         <v>44344</v>
       </c>
@@ -16254,7 +16260,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5">
       <c r="A569" s="8">
         <v>44351</v>
       </c>
@@ -16272,7 +16278,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5">
       <c r="A570" s="8">
         <v>44358</v>
       </c>
@@ -16290,7 +16296,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5">
       <c r="A571" s="8">
         <v>44365</v>
       </c>
@@ -16308,7 +16314,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5">
       <c r="A572" s="8">
         <v>44372</v>
       </c>
@@ -16326,7 +16332,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5">
       <c r="A573" s="8">
         <v>44379</v>
       </c>
@@ -16344,7 +16350,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5">
       <c r="A574" s="8">
         <v>44386</v>
       </c>
@@ -16362,7 +16368,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5">
       <c r="A575" s="8">
         <v>44393</v>
       </c>
@@ -16380,7 +16386,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5">
       <c r="A576" s="8">
         <v>44400</v>
       </c>
@@ -16398,7 +16404,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5">
       <c r="A577" s="8">
         <v>44407</v>
       </c>
@@ -16416,7 +16422,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5">
       <c r="A578" s="8">
         <v>44414</v>
       </c>
@@ -16434,7 +16440,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5">
       <c r="A579" s="8">
         <v>44421</v>
       </c>
@@ -16459,7 +16465,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5">
       <c r="A580" s="8">
         <v>44428</v>
       </c>
@@ -16477,7 +16483,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5">
       <c r="A581" s="8">
         <v>44435</v>
       </c>
@@ -16495,7 +16501,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5">
       <c r="A582" s="8">
         <v>44442</v>
       </c>
@@ -16513,7 +16519,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5">
       <c r="A583" s="8">
         <v>44449</v>
       </c>
@@ -16531,7 +16537,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5">
       <c r="A584" s="8">
         <v>44456</v>
       </c>
@@ -16549,7 +16555,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5">
       <c r="A585" s="8">
         <v>44463</v>
       </c>
@@ -16567,7 +16573,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5">
       <c r="A586" s="8">
         <v>44470</v>
       </c>
@@ -16585,7 +16591,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5">
       <c r="A587" s="8">
         <v>44477</v>
       </c>
@@ -16603,7 +16609,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5">
       <c r="A588" s="8">
         <v>44484</v>
       </c>
@@ -16621,7 +16627,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5">
       <c r="A589" s="8">
         <v>44491</v>
       </c>
@@ -16639,7 +16645,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5">
       <c r="A590" s="8">
         <v>44498</v>
       </c>
@@ -16657,7 +16663,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5">
       <c r="A591" s="8">
         <v>44505</v>
       </c>
@@ -16675,7 +16681,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5">
       <c r="A592" s="8">
         <v>44512</v>
       </c>
@@ -16693,7 +16699,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4">
       <c r="A593" s="8">
         <v>44519</v>
       </c>
@@ -16708,7 +16714,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4">
       <c r="A594" s="8">
         <v>44526</v>
       </c>
@@ -16723,7 +16729,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4">
       <c r="A595" s="8">
         <v>44533</v>
       </c>
@@ -16738,7 +16744,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4">
       <c r="A596" s="8">
         <v>44540</v>
       </c>
@@ -16753,7 +16759,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4">
       <c r="A597" s="8">
         <v>44547</v>
       </c>
@@ -16768,7 +16774,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4">
       <c r="A598" s="8">
         <v>44554</v>
       </c>
@@ -16783,7 +16789,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4">
       <c r="A599" s="8">
         <v>44561</v>
       </c>
@@ -16798,7 +16804,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4">
       <c r="A600" s="8">
         <v>44568</v>
       </c>
@@ -16813,7 +16819,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4">
       <c r="A601" s="8">
         <v>44575</v>
       </c>
@@ -16828,7 +16834,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4">
       <c r="A602" s="8">
         <v>44582</v>
       </c>
@@ -16843,7 +16849,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4">
       <c r="A603" s="8">
         <v>44589</v>
       </c>
@@ -16858,7 +16864,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4">
       <c r="A604" s="8">
         <v>44596</v>
       </c>
@@ -16873,7 +16879,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4">
       <c r="A605" s="8">
         <v>44603</v>
       </c>
@@ -16888,7 +16894,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4">
       <c r="A606" s="8">
         <v>44610</v>
       </c>
@@ -16903,7 +16909,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4">
       <c r="A607" s="8">
         <v>44617</v>
       </c>
@@ -16918,7 +16924,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4">
       <c r="A608" s="8">
         <v>44624</v>
       </c>
@@ -16933,7 +16939,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4">
       <c r="A609" s="8">
         <v>44631</v>
       </c>
@@ -16948,7 +16954,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4">
       <c r="A610" s="8">
         <v>44638</v>
       </c>
@@ -16963,7 +16969,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4">
       <c r="A611" s="8">
         <v>44645</v>
       </c>
@@ -16978,7 +16984,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4">
       <c r="A612" s="8">
         <v>44652</v>
       </c>
@@ -16993,7 +16999,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4">
       <c r="A613" s="8">
         <v>44659</v>
       </c>
@@ -17008,7 +17014,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4">
       <c r="A614" s="8">
         <v>44666</v>
       </c>
@@ -17023,7 +17029,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4">
       <c r="A615" s="8">
         <v>44673</v>
       </c>
@@ -17038,7 +17044,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4">
       <c r="A616" s="8">
         <v>44680</v>
       </c>
@@ -17053,7 +17059,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4">
       <c r="A617" s="8">
         <v>44687</v>
       </c>
@@ -17068,7 +17074,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4">
       <c r="A618" s="8">
         <v>44694</v>
       </c>
@@ -17083,7 +17089,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4">
       <c r="A619" s="8">
         <v>44701</v>
       </c>
@@ -17098,7 +17104,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4">
       <c r="A620" s="8">
         <v>44708</v>
       </c>
@@ -17113,7 +17119,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4">
       <c r="A621" s="8">
         <v>44715</v>
       </c>
@@ -17128,7 +17134,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4">
       <c r="A622" s="8">
         <v>44722</v>
       </c>
@@ -17143,7 +17149,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4">
       <c r="A623" s="8">
         <v>44729</v>
       </c>
@@ -17158,7 +17164,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4">
       <c r="A624" s="8">
         <v>44736</v>
       </c>
@@ -17173,7 +17179,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4">
       <c r="A625" s="8">
         <v>44743</v>
       </c>
@@ -17188,7 +17194,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4">
       <c r="A626" s="8">
         <v>44750</v>
       </c>
@@ -17203,7 +17209,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4">
       <c r="A627" s="8">
         <v>44757</v>
       </c>
@@ -17218,7 +17224,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4">
       <c r="A628" s="8">
         <v>44764</v>
       </c>
@@ -17233,7 +17239,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4">
       <c r="A629" s="8">
         <v>44771</v>
       </c>
@@ -17248,7 +17254,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4">
       <c r="A630" s="8">
         <v>44778</v>
       </c>
@@ -17263,7 +17269,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4">
       <c r="A631" s="8">
         <v>44785</v>
       </c>
@@ -17278,7 +17284,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4">
       <c r="A632" s="8">
         <v>44792</v>
       </c>
@@ -17293,7 +17299,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4">
       <c r="A633" s="8">
         <v>44799</v>
       </c>
@@ -17308,7 +17314,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4">
       <c r="A634" s="8">
         <v>44806</v>
       </c>
@@ -17323,7 +17329,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4">
       <c r="A635" s="8">
         <v>44813</v>
       </c>
@@ -17338,7 +17344,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4">
       <c r="A636" s="8">
         <v>44820</v>
       </c>
@@ -17353,7 +17359,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4">
       <c r="A637" s="8">
         <v>44827</v>
       </c>
@@ -17368,7 +17374,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4">
       <c r="A638" s="8">
         <v>44834</v>
       </c>
@@ -17383,7 +17389,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4">
       <c r="A639" s="8">
         <v>44841</v>
       </c>
@@ -17398,7 +17404,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4">
       <c r="A640" s="8">
         <v>44848</v>
       </c>
@@ -17413,7 +17419,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4">
       <c r="A641" s="8">
         <v>44855</v>
       </c>
@@ -17428,7 +17434,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4">
       <c r="A642" s="8">
         <v>44862</v>
       </c>
@@ -17443,7 +17449,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4">
       <c r="A643" s="8">
         <v>44869</v>
       </c>
@@ -17465,7 +17471,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4">
       <c r="A644" s="8">
         <v>44876</v>
       </c>
@@ -17480,7 +17486,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4">
       <c r="A645" s="8">
         <v>44883</v>
       </c>
@@ -17495,7 +17501,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4">
       <c r="A646" s="8">
         <v>44890</v>
       </c>
@@ -17510,7 +17516,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4">
       <c r="A647" s="8">
         <v>44897</v>
       </c>
@@ -17525,7 +17531,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4">
       <c r="A648" s="8">
         <v>44904</v>
       </c>
@@ -17540,7 +17546,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4">
       <c r="A649" s="8">
         <v>44911</v>
       </c>
@@ -17555,7 +17561,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4">
       <c r="A650" s="8">
         <v>44918</v>
       </c>
@@ -17570,7 +17576,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4">
       <c r="A651" s="8">
         <v>44925</v>
       </c>
@@ -17585,7 +17591,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4">
       <c r="A652" s="8">
         <v>44932</v>
       </c>
@@ -17600,7 +17606,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4">
       <c r="A653" s="8">
         <v>44939</v>
       </c>
@@ -17615,7 +17621,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4">
       <c r="A654" s="8">
         <v>44946</v>
       </c>
@@ -17630,7 +17636,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4">
       <c r="A655" s="8">
         <v>44953</v>
       </c>
@@ -17645,7 +17651,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4">
       <c r="A656" s="8">
         <v>44960</v>
       </c>
@@ -17660,7 +17666,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4">
       <c r="A657" s="8">
         <v>44967</v>
       </c>
@@ -17675,7 +17681,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4">
       <c r="A658" s="8">
         <v>44974</v>
       </c>
@@ -17690,7 +17696,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4">
       <c r="A659" s="8">
         <v>44981</v>
       </c>
@@ -17705,7 +17711,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4">
       <c r="A660" s="8">
         <v>44988</v>
       </c>
@@ -17720,7 +17726,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4">
       <c r="A661" s="8">
         <v>44995</v>
       </c>
@@ -17735,7 +17741,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4">
       <c r="A662" s="8">
         <v>45002</v>
       </c>
@@ -17750,7 +17756,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4">
       <c r="A663" s="8">
         <v>45009</v>
       </c>
@@ -17765,7 +17771,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4">
       <c r="A664" s="8">
         <v>45016</v>
       </c>
@@ -17780,7 +17786,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4">
       <c r="A665" s="8">
         <v>45023</v>
       </c>
@@ -17795,7 +17801,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4">
       <c r="A666" s="8">
         <v>45030</v>
       </c>
@@ -17810,7 +17816,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4">
       <c r="A667" s="8">
         <v>45037</v>
       </c>
@@ -17825,7 +17831,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4">
       <c r="A668" s="8">
         <v>45044</v>
       </c>
@@ -17840,7 +17846,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4">
       <c r="A669" s="8">
         <v>45051</v>
       </c>
@@ -17855,7 +17861,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4">
       <c r="A670" s="8">
         <v>45058</v>
       </c>
@@ -17870,7 +17876,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4">
       <c r="A671" s="8">
         <v>45065</v>
       </c>
@@ -17885,7 +17891,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4">
       <c r="A672" s="8">
         <v>45072</v>
       </c>
@@ -17900,7 +17906,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4">
       <c r="A673" s="8">
         <v>45079</v>
       </c>
@@ -17915,7 +17921,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4">
       <c r="A674" s="8">
         <v>45086</v>
       </c>
@@ -17930,7 +17936,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4">
       <c r="A675" s="8">
         <v>45093</v>
       </c>
@@ -17945,7 +17951,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4">
       <c r="A676" s="8">
         <v>45100</v>
       </c>
@@ -17960,7 +17966,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4">
       <c r="A677" s="8">
         <v>45107</v>
       </c>
@@ -17975,7 +17981,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4">
       <c r="A678" s="8">
         <v>45114</v>
       </c>
@@ -17990,7 +17996,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4">
       <c r="A679" s="8">
         <v>45121</v>
       </c>
@@ -18005,7 +18011,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4">
       <c r="A680" s="8">
         <v>45128</v>
       </c>
@@ -18020,7 +18026,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4">
       <c r="A681" s="8">
         <v>45135</v>
       </c>
@@ -18035,7 +18041,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4">
       <c r="A682" s="8">
         <v>45142</v>
       </c>
@@ -18050,7 +18056,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4">
       <c r="A683" s="8">
         <v>45149</v>
       </c>
@@ -18065,7 +18071,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4">
       <c r="A684" s="8">
         <v>45156</v>
       </c>
@@ -18080,7 +18086,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4">
       <c r="A685" s="8">
         <v>45163</v>
       </c>
@@ -18095,7 +18101,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:4">
       <c r="A686" s="8">
         <v>45170</v>
       </c>
@@ -18110,7 +18116,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:4">
       <c r="A687" s="8">
         <v>45177</v>
       </c>
@@ -18125,7 +18131,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:4">
       <c r="A688" s="8">
         <v>45184</v>
       </c>
@@ -18140,7 +18146,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5">
       <c r="A689" s="8">
         <v>45191</v>
       </c>
@@ -18155,7 +18161,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5">
       <c r="A690" s="8">
         <v>45198</v>
       </c>
@@ -18170,7 +18176,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5">
       <c r="A691" s="8">
         <v>45205</v>
       </c>
@@ -18185,7 +18191,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5">
       <c r="A692" s="8">
         <v>45212</v>
       </c>
@@ -18200,7 +18206,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5">
       <c r="A693" s="8">
         <v>45219</v>
       </c>
@@ -18215,7 +18221,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5">
       <c r="A694" s="8">
         <v>45226</v>
       </c>
@@ -18230,7 +18236,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5">
       <c r="A695" s="8">
         <v>45233</v>
       </c>
@@ -18245,7 +18251,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5">
       <c r="A696" s="8">
         <v>45240</v>
       </c>
@@ -18260,7 +18266,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5">
       <c r="A697" s="8">
         <v>45247</v>
       </c>
@@ -18275,7 +18281,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5">
       <c r="A698" s="8">
         <v>45254</v>
       </c>
@@ -18290,7 +18296,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5">
       <c r="A699" s="8">
         <v>45261</v>
       </c>
@@ -18305,7 +18311,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5">
       <c r="A700" s="8">
         <v>45268</v>
       </c>
@@ -18320,7 +18326,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5">
       <c r="A701" s="8">
         <v>45275</v>
       </c>
@@ -18338,7 +18344,7 @@
         <v>809.6</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5">
       <c r="A702" s="8">
         <v>45282</v>
       </c>
@@ -18356,7 +18362,7 @@
         <v>809.6</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5">
       <c r="A703" s="8">
         <v>45289</v>
       </c>
@@ -18371,7 +18377,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5">
       <c r="A704" s="8">
         <v>45296</v>
       </c>
@@ -18386,7 +18392,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5">
       <c r="A705" s="8">
         <v>45303</v>
       </c>
@@ -18404,7 +18410,7 @@
         <v>910.24</v>
       </c>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5">
       <c r="A706" s="8">
         <v>45310</v>
       </c>
@@ -18419,7 +18425,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5">
       <c r="A707" s="8">
         <v>45317</v>
       </c>
@@ -18441,7 +18447,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5">
       <c r="A708" s="8">
         <v>45324</v>
       </c>
@@ -18456,7 +18462,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5">
       <c r="A709" s="8">
         <v>45331</v>
       </c>
@@ -18471,7 +18477,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5">
       <c r="A710" s="8">
         <v>45338</v>
       </c>
@@ -18486,7 +18492,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5">
       <c r="A711" s="8">
         <v>45345</v>
       </c>
@@ -18501,7 +18507,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5">
       <c r="A712" s="8">
         <v>45352</v>
       </c>
@@ -18516,7 +18522,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5">
       <c r="A713" s="8">
         <v>45359</v>
       </c>
@@ -18534,7 +18540,7 @@
         <v>1201.73</v>
       </c>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5">
       <c r="A714" s="8">
         <v>45366</v>
       </c>
@@ -18552,7 +18558,7 @@
         <v>1215.8900000000001</v>
       </c>
     </row>
-    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5">
       <c r="A715" s="8">
         <v>45373</v>
       </c>
@@ -18567,7 +18573,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5">
       <c r="A716" s="8">
         <v>45380</v>
       </c>
@@ -18582,7 +18588,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5">
       <c r="A717" s="8">
         <v>45387</v>
       </c>
@@ -18597,7 +18603,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5">
       <c r="A718" s="8">
         <v>45394</v>
       </c>
@@ -18612,7 +18618,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5">
       <c r="A719" s="8">
         <v>45401</v>
       </c>
@@ -18630,7 +18636,7 @@
         <v>1230.06</v>
       </c>
     </row>
-    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5">
       <c r="A720" s="8">
         <v>45408</v>
       </c>
@@ -18648,7 +18654,7 @@
         <v>1251.68</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5">
       <c r="A721" s="8">
         <v>45415</v>
       </c>
@@ -18663,7 +18669,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5">
       <c r="A722" s="8">
         <v>45422</v>
       </c>
@@ -18678,7 +18684,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5">
       <c r="A723" s="8">
         <v>45429</v>
       </c>
@@ -18693,7 +18699,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5">
       <c r="A724" s="8">
         <v>45436</v>
       </c>
@@ -18708,7 +18714,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5">
       <c r="A725" s="8">
         <v>45443</v>
       </c>
@@ -18723,7 +18729,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5">
       <c r="A726" s="8">
         <v>45450</v>
       </c>
@@ -18738,7 +18744,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5">
       <c r="A727" s="8">
         <v>45457</v>
       </c>
@@ -18753,7 +18759,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5">
       <c r="A728" s="8">
         <v>45464</v>
       </c>
@@ -18771,7 +18777,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5">
       <c r="A729" s="8">
         <v>45471</v>
       </c>
@@ -18789,7 +18795,7 @@
         <v>1712.39</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5">
       <c r="A730" s="8">
         <v>45478</v>
       </c>
@@ -18804,7 +18810,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5">
       <c r="A731" s="8">
         <v>45485</v>
       </c>
@@ -18819,7 +18825,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5">
       <c r="A732" s="8">
         <v>45492</v>
       </c>
@@ -18834,7 +18840,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5">
       <c r="A733" s="8">
         <v>45499</v>
       </c>
@@ -18849,7 +18855,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5">
       <c r="A734" s="8">
         <v>45506</v>
       </c>
@@ -18864,7 +18870,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5">
       <c r="A735" s="8">
         <v>45513</v>
       </c>
@@ -18879,7 +18885,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5">
       <c r="A736" s="8">
         <v>45520</v>
       </c>
@@ -18894,7 +18900,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5">
       <c r="A737" s="8">
         <v>45527</v>
       </c>
@@ -18909,7 +18915,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5">
       <c r="A738" s="8">
         <v>45534</v>
       </c>
@@ -18924,7 +18930,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5">
       <c r="A739" s="8">
         <v>45541</v>
       </c>
@@ -18939,7 +18945,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5">
       <c r="A740" s="8">
         <v>45548</v>
       </c>
@@ -18954,7 +18960,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5">
       <c r="A741" s="8">
         <v>45555</v>
       </c>
@@ -18969,7 +18975,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5">
       <c r="A742" s="8">
         <v>45562</v>
       </c>
@@ -18984,7 +18990,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5">
       <c r="A743" s="8">
         <v>45569</v>
       </c>
@@ -19002,7 +19008,7 @@
         <v>1936.04</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5">
       <c r="A744" s="8">
         <v>45576</v>
       </c>
@@ -19020,7 +19026,7 @@
         <v>1965.85</v>
       </c>
     </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5">
       <c r="A745" s="8">
         <v>45583</v>
       </c>
@@ -19038,7 +19044,7 @@
         <v>1967.35</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5">
       <c r="A746" s="8">
         <v>45590</v>
       </c>
@@ -19053,7 +19059,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5">
       <c r="A747" s="8">
         <v>45597</v>
       </c>
@@ -19068,7 +19074,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5">
       <c r="A748" s="8">
         <v>45604</v>
       </c>
@@ -19083,7 +19089,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5">
       <c r="A749" s="8">
         <v>45611</v>
       </c>
@@ -19101,7 +19107,7 @@
         <v>1977.78</v>
       </c>
     </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5">
       <c r="A750" s="8">
         <v>45618</v>
       </c>
@@ -19116,7 +19122,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5">
       <c r="A751" s="8">
         <v>45625</v>
       </c>
@@ -19131,7 +19137,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5">
       <c r="A752" s="8">
         <v>45632</v>
       </c>
@@ -19146,7 +19152,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:15">
       <c r="A753" s="8">
         <v>45639</v>
       </c>
@@ -19161,7 +19167,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:15">
       <c r="A754" s="8">
         <v>45646</v>
       </c>
@@ -19176,7 +19182,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:15">
       <c r="A755" s="8">
         <v>45653</v>
       </c>
@@ -19191,7 +19197,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:15">
       <c r="A756" s="8">
         <v>45660</v>
       </c>
@@ -19209,7 +19215,7 @@
         <v>2052.33</v>
       </c>
     </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:15">
       <c r="A757" s="8">
         <v>45667</v>
       </c>
@@ -19224,7 +19230,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:15">
       <c r="A758" s="8">
         <v>45674</v>
       </c>
@@ -19239,7 +19245,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:15">
       <c r="A759" s="8">
         <v>45681</v>
       </c>
@@ -19254,7 +19260,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:15">
       <c r="A760" s="8">
         <v>45688</v>
       </c>
@@ -19272,7 +19278,7 @@
         <v>2052.33</v>
       </c>
     </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:15">
       <c r="A761" s="8">
         <v>45695</v>
       </c>
@@ -19287,7 +19293,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:15">
       <c r="A762" s="8">
         <v>45702</v>
       </c>
@@ -19302,7 +19308,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:15">
       <c r="A763" s="8">
         <v>45709</v>
       </c>
@@ -19350,7 +19356,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:15">
       <c r="A764" s="8">
         <v>45716</v>
       </c>
@@ -19398,7 +19404,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:15">
       <c r="A765" s="8">
         <v>45723</v>
       </c>
@@ -19446,7 +19452,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:15">
       <c r="A766" s="8">
         <v>45730</v>
       </c>
@@ -19494,7 +19500,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:15">
       <c r="A767" s="8">
         <v>45737</v>
       </c>
@@ -19542,7 +19548,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:15">
       <c r="A768" s="8">
         <v>45744</v>
       </c>
@@ -19590,7 +19596,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:15">
       <c r="A769" s="8">
         <v>45751</v>
       </c>
@@ -19638,7 +19644,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:15">
       <c r="A770" s="8">
         <v>45758</v>
       </c>
@@ -19686,7 +19692,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:15">
       <c r="A771" s="8">
         <v>45765</v>
       </c>
@@ -19741,7 +19747,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:15">
       <c r="A772" s="8">
         <v>45772</v>
       </c>
@@ -19789,7 +19795,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:15">
       <c r="A773" s="8">
         <v>45779</v>
       </c>
@@ -19804,7 +19810,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:15">
       <c r="A774" s="8">
         <v>45786</v>
       </c>
@@ -19822,7 +19828,7 @@
         <v>2055.31</v>
       </c>
     </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:15">
       <c r="A775" s="8">
         <v>45793</v>
       </c>
@@ -19837,7 +19843,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:15">
       <c r="A776" s="8">
         <v>45800</v>
       </c>
@@ -19852,7 +19858,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:15">
       <c r="A777" s="8">
         <v>45807</v>
       </c>
@@ -19867,7 +19873,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:15">
       <c r="A778" s="8">
         <v>45814</v>
       </c>
@@ -19882,7 +19888,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:15">
       <c r="A779" s="8">
         <v>45821</v>
       </c>
@@ -19897,7 +19903,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:15">
       <c r="A780" s="8">
         <v>45828</v>
       </c>
@@ -19945,7 +19951,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:15">
       <c r="A781" s="8">
         <v>45835</v>
       </c>
@@ -19993,7 +19999,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:15">
       <c r="A782" s="8">
         <v>45842</v>
       </c>
@@ -20041,7 +20047,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:15">
       <c r="A783" s="8">
         <v>45849</v>
       </c>
@@ -20089,7 +20095,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:15">
       <c r="A784" s="8">
         <v>45856</v>
       </c>
@@ -20137,7 +20143,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:15">
       <c r="A785" s="8">
         <v>45863</v>
       </c>
@@ -20185,7 +20191,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:15">
       <c r="A786" s="8">
         <v>45870</v>
       </c>
@@ -20233,7 +20239,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:15">
       <c r="A787" s="8">
         <v>45877</v>
       </c>
@@ -20248,7 +20254,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="788" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:15">
       <c r="A788" s="8">
         <v>45884</v>
       </c>
@@ -20263,7 +20269,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="789" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:15">
       <c r="A789" s="8">
         <v>45891</v>
       </c>
@@ -20311,7 +20317,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:15">
       <c r="A790" s="8">
         <v>45898</v>
       </c>
@@ -20359,7 +20365,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="791" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:15">
       <c r="A791" s="8">
         <v>45905</v>
       </c>
@@ -20407,7 +20413,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="792" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:15">
       <c r="A792" s="8">
         <v>45912</v>
       </c>
@@ -20455,7 +20461,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="793" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:15">
       <c r="A793" s="8">
         <v>45919</v>
       </c>
@@ -20503,7 +20509,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="794" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:15">
       <c r="A794" s="8">
         <v>45926</v>
       </c>
@@ -20551,7 +20557,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="795" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:15">
       <c r="A795" s="8">
         <v>45933</v>
       </c>
@@ -20599,7 +20605,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="796" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:15">
       <c r="A796" s="8">
         <v>45940</v>
       </c>
@@ -20647,7 +20653,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="797" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:15">
       <c r="A797" s="8">
         <v>45947</v>
       </c>
@@ -20662,7 +20668,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="798" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:15">
       <c r="A798" s="8">
         <v>45954</v>
       </c>
@@ -20710,7 +20716,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="799" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:15">
       <c r="A799" s="8">
         <v>45961</v>
       </c>
@@ -20758,7 +20764,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="800" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:15">
       <c r="A800" s="8">
         <v>45968</v>
       </c>
@@ -20806,7 +20812,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15">
       <c r="A801" s="8">
         <v>45975</v>
       </c>
@@ -20854,7 +20860,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15">
       <c r="A802" s="8">
         <v>45982</v>
       </c>
@@ -20869,7 +20875,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15">
       <c r="A803" s="8">
         <v>45989</v>
       </c>
@@ -20884,7 +20890,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15">
       <c r="A804" s="8">
         <v>45996</v>
       </c>
@@ -20899,7 +20905,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15">
       <c r="A805" s="8">
         <v>46003</v>
       </c>
@@ -20917,7 +20923,7 @@
         <v>2180.56</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:15">
       <c r="A806" s="8">
         <v>46010</v>
       </c>
@@ -20965,7 +20971,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:15">
       <c r="A807" s="8">
         <v>46017</v>
       </c>
@@ -21013,7 +21019,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:15">
       <c r="A808" s="8">
         <v>46024</v>
       </c>
@@ -21061,7 +21067,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:15">
       <c r="A809" s="8">
         <v>46031</v>
       </c>
@@ -21109,7 +21115,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:15">
       <c r="A810" s="8">
         <v>46038</v>
       </c>
@@ -21157,7 +21163,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:15">
       <c r="A811" s="8">
         <v>46045</v>
       </c>
@@ -21172,7 +21178,7 @@
         <v>UTC+1</v>
       </c>
       <c r="E811" s="12">
-        <v>2184</v>
+        <v>2183.54</v>
       </c>
       <c r="F811" s="15">
         <v>10250</v>
@@ -21205,7 +21211,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:15">
       <c r="A812" s="8">
         <v>46052</v>
       </c>
@@ -21220,7 +21226,7 @@
         <v>UTC+1</v>
       </c>
       <c r="E812" s="12">
-        <v>2184</v>
+        <v>2183.54</v>
       </c>
       <c r="F812" s="15">
         <v>10250</v>
@@ -21253,7 +21259,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:15">
       <c r="A813" s="8">
         <v>46059</v>
       </c>
@@ -21268,7 +21274,7 @@
         <v>UTC+1</v>
       </c>
       <c r="E813" s="12">
-        <v>2184</v>
+        <v>2183.54</v>
       </c>
       <c r="F813" s="15">
         <v>10250</v>
@@ -21301,7 +21307,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:15">
       <c r="A814" s="8">
         <v>46066</v>
       </c>
@@ -21349,7 +21355,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:15">
       <c r="A815" s="8">
         <v>46073</v>
       </c>
@@ -21397,7 +21403,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:15">
       <c r="A816" s="8">
         <v>46080</v>
       </c>
@@ -21445,7 +21451,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:15">
       <c r="A817" s="8">
         <v>46087</v>
       </c>
@@ -21493,7 +21499,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:15">
       <c r="A818" s="8">
         <v>46094</v>
       </c>
@@ -21541,7 +21547,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:15">
       <c r="A819" s="8">
         <v>46101</v>
       </c>
@@ -21589,7 +21595,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:15">
       <c r="A820" s="8">
         <v>46108</v>
       </c>
@@ -21637,7 +21643,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:15">
       <c r="A821" s="8">
         <v>46115</v>
       </c>
@@ -21685,7 +21691,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:15">
       <c r="A822" s="8">
         <v>46122</v>
       </c>
@@ -21713,7 +21719,7 @@
       <c r="N822" s="15"/>
       <c r="O822" s="15"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:15">
       <c r="A823" s="8">
         <v>46129</v>
       </c>
@@ -21741,7 +21747,7 @@
       <c r="N823" s="15"/>
       <c r="O823" s="15"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:15">
       <c r="A824" s="8">
         <v>46136</v>
       </c>
@@ -21769,7 +21775,7 @@
       <c r="N824" s="15"/>
       <c r="O824" s="15"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:15">
       <c r="A825" s="8">
         <v>46143</v>
       </c>
@@ -21817,7 +21823,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:15">
       <c r="A826" s="8">
         <v>46150</v>
       </c>
@@ -21865,7 +21871,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:15">
       <c r="A827" s="8">
         <v>46157</v>
       </c>
@@ -21913,7 +21919,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:15">
       <c r="A828" s="8">
         <v>46164</v>
       </c>
@@ -21961,7 +21967,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:15">
       <c r="A829" s="8">
         <v>46171</v>
       </c>
@@ -22009,7 +22015,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:15">
       <c r="A830" s="8">
         <v>46178</v>
       </c>
@@ -22057,7 +22063,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:15">
       <c r="A831" s="8">
         <v>46185</v>
       </c>
@@ -22105,7 +22111,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:15">
       <c r="A832" s="8">
         <v>46192</v>
       </c>
@@ -22153,7 +22159,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:15">
       <c r="A833" s="8">
         <v>46199</v>
       </c>
@@ -22201,7 +22207,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:15">
       <c r="A834" s="8">
         <v>46206</v>
       </c>
@@ -22256,7 +22262,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:15">
       <c r="A835" s="8">
         <v>46213</v>
       </c>
@@ -22304,7 +22310,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:15">
       <c r="A836" s="8">
         <v>46220</v>
       </c>
@@ -22352,7 +22358,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="837" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:15">
       <c r="A837" s="8">
         <v>46227</v>
       </c>
@@ -22363,7 +22369,7 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="D837" s="8" t="str">
-        <f t="shared" ref="D837" si="14">"UTC+"&amp;IF(
+        <f t="shared" ref="D837:D838" si="14">"UTC+"&amp;IF(
     AND(
         B837&gt;=EOMONTH(DATE(YEAR(B837),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B837),3,1),0),2),7),
         B837&lt;EOMONTH(DATE(YEAR(B837),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B837),10,1),0),2),7)
@@ -22404,6 +22410,54 @@
         <v>72000</v>
       </c>
       <c r="O837" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="838" spans="1:15">
+      <c r="A838" s="8">
+        <v>46234</v>
+      </c>
+      <c r="B838" s="8">
+        <v>46234</v>
+      </c>
+      <c r="C838" s="9">
+        <v>0.66666666666666996</v>
+      </c>
+      <c r="D838" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E838" s="10">
+        <v>2343.0700000000002</v>
+      </c>
+      <c r="F838" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G838" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H838" s="14">
+        <v>31000</v>
+      </c>
+      <c r="I838" s="14">
+        <v>34500</v>
+      </c>
+      <c r="J838" s="14">
+        <v>38000</v>
+      </c>
+      <c r="K838" s="14">
+        <v>40000</v>
+      </c>
+      <c r="L838" s="14">
+        <v>46000</v>
+      </c>
+      <c r="M838" s="14">
+        <v>57000</v>
+      </c>
+      <c r="N838" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O838" s="14">
         <v>79000</v>
       </c>
     </row>
@@ -22416,7 +22470,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22427,12 +22481,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
@@ -22440,7 +22494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>17</v>
       </c>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3710C0-28AD-2845-9FF6-869CE19BEF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D186BAC-371B-4267-9A9A-D81BAABF00F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26380" yWindow="600" windowWidth="24820" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -53,36 +53,6 @@
     <t>HARPEX</t>
   </si>
   <si>
-    <t>Vessel Size in TEU:700</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:1100</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:1700</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:1800</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:2500</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:2700</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:3500</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:4250</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:6500</t>
-  </si>
-  <si>
-    <t>Vessel Size in TEU:8500</t>
-  </si>
-  <si>
     <t>source</t>
   </si>
   <si>
@@ -94,18 +64,58 @@
   <si>
     <t>weekly</t>
   </si>
+  <si>
+    <t>HARPEX0700</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX1100</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX1700</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX1800</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX2500</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX2700</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX3500</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX4250</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX6500</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARPEX8500</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,9 +181,9 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -181,43 +191,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -235,7 +245,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5628,9 +5638,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5668,7 +5678,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5774,7 +5784,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5916,7 +5926,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5925,18 +5935,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
   <dimension ref="A1:P838"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.1640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.83203125" style="11"/>
+    <col min="5" max="5" width="9.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="14" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.77734375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1">
+    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5953,38 +5963,38 @@
         <v>4</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>40383</v>
       </c>
@@ -6009,7 +6019,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>40390</v>
       </c>
@@ -6034,7 +6044,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>40397</v>
       </c>
@@ -6052,7 +6062,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>40404</v>
       </c>
@@ -6070,7 +6080,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>40411</v>
       </c>
@@ -6088,7 +6098,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>40418</v>
       </c>
@@ -6106,7 +6116,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>40425</v>
       </c>
@@ -6124,7 +6134,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>40432</v>
       </c>
@@ -6142,7 +6152,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>40439</v>
       </c>
@@ -6160,7 +6170,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>40446</v>
       </c>
@@ -6178,7 +6188,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>40453</v>
       </c>
@@ -6196,7 +6206,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>40460</v>
       </c>
@@ -6214,7 +6224,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>40467</v>
       </c>
@@ -6232,7 +6242,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>40474</v>
       </c>
@@ -6250,7 +6260,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>40481</v>
       </c>
@@ -6268,7 +6278,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>40488</v>
       </c>
@@ -6286,7 +6296,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>40495</v>
       </c>
@@ -6304,7 +6314,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>40502</v>
       </c>
@@ -6322,7 +6332,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>40509</v>
       </c>
@@ -6340,7 +6350,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>40516</v>
       </c>
@@ -6358,7 +6368,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>40523</v>
       </c>
@@ -6376,7 +6386,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>40530</v>
       </c>
@@ -6394,7 +6404,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>40537</v>
       </c>
@@ -6412,7 +6422,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>40544</v>
       </c>
@@ -6430,7 +6440,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>40551</v>
       </c>
@@ -6448,7 +6458,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>40558</v>
       </c>
@@ -6466,7 +6476,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>40565</v>
       </c>
@@ -6484,7 +6494,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>40572</v>
       </c>
@@ -6502,7 +6512,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>40579</v>
       </c>
@@ -6520,7 +6530,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>40586</v>
       </c>
@@ -6538,7 +6548,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>40593</v>
       </c>
@@ -6556,7 +6566,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>40600</v>
       </c>
@@ -6574,7 +6584,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>40607</v>
       </c>
@@ -6592,7 +6602,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>40614</v>
       </c>
@@ -6610,7 +6620,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>40621</v>
       </c>
@@ -6628,7 +6638,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>40628</v>
       </c>
@@ -6646,7 +6656,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>40635</v>
       </c>
@@ -6664,7 +6674,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>40642</v>
       </c>
@@ -6682,7 +6692,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>40649</v>
       </c>
@@ -6700,7 +6710,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>40656</v>
       </c>
@@ -6718,7 +6728,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>40663</v>
       </c>
@@ -6736,7 +6746,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>40670</v>
       </c>
@@ -6754,7 +6764,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>40677</v>
       </c>
@@ -6772,7 +6782,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>40684</v>
       </c>
@@ -6790,7 +6800,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>40691</v>
       </c>
@@ -6808,7 +6818,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>40698</v>
       </c>
@@ -6826,7 +6836,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>40705</v>
       </c>
@@ -6844,7 +6854,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>40712</v>
       </c>
@@ -6862,7 +6872,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>40719</v>
       </c>
@@ -6880,7 +6890,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>40726</v>
       </c>
@@ -6898,7 +6908,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>40733</v>
       </c>
@@ -6916,7 +6926,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>40740</v>
       </c>
@@ -6934,7 +6944,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>40747</v>
       </c>
@@ -6952,7 +6962,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>40754</v>
       </c>
@@ -6970,7 +6980,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>40761</v>
       </c>
@@ -6988,7 +6998,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>40768</v>
       </c>
@@ -7006,7 +7016,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>40775</v>
       </c>
@@ -7024,7 +7034,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>40782</v>
       </c>
@@ -7042,7 +7052,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>40789</v>
       </c>
@@ -7060,7 +7070,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>40796</v>
       </c>
@@ -7078,7 +7088,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>40803</v>
       </c>
@@ -7096,7 +7106,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>40810</v>
       </c>
@@ -7114,7 +7124,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>40817</v>
       </c>
@@ -7132,7 +7142,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>40824</v>
       </c>
@@ -7150,7 +7160,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>40831</v>
       </c>
@@ -7168,7 +7178,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>40838</v>
       </c>
@@ -7193,7 +7203,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>40845</v>
       </c>
@@ -7211,7 +7221,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>40852</v>
       </c>
@@ -7229,7 +7239,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>40859</v>
       </c>
@@ -7247,7 +7257,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>40866</v>
       </c>
@@ -7265,7 +7275,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>40873</v>
       </c>
@@ -7283,7 +7293,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>40880</v>
       </c>
@@ -7301,7 +7311,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>40887</v>
       </c>
@@ -7319,7 +7329,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>40894</v>
       </c>
@@ -7337,7 +7347,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>40901</v>
       </c>
@@ -7355,7 +7365,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>40908</v>
       </c>
@@ -7373,7 +7383,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>40915</v>
       </c>
@@ -7391,7 +7401,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>40922</v>
       </c>
@@ -7409,7 +7419,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>40929</v>
       </c>
@@ -7427,7 +7437,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>40936</v>
       </c>
@@ -7445,7 +7455,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>40942</v>
       </c>
@@ -7463,7 +7473,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>40943</v>
       </c>
@@ -7481,7 +7491,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>40950</v>
       </c>
@@ -7499,7 +7509,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>40957</v>
       </c>
@@ -7517,7 +7527,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>40964</v>
       </c>
@@ -7535,7 +7545,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>40978</v>
       </c>
@@ -7553,7 +7563,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>40985</v>
       </c>
@@ -7571,7 +7581,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>40992</v>
       </c>
@@ -7589,7 +7599,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>40999</v>
       </c>
@@ -7607,7 +7617,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>41006</v>
       </c>
@@ -7625,7 +7635,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>41013</v>
       </c>
@@ -7643,7 +7653,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>41020</v>
       </c>
@@ -7661,7 +7671,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>41027</v>
       </c>
@@ -7679,7 +7689,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>41034</v>
       </c>
@@ -7697,7 +7707,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>41041</v>
       </c>
@@ -7715,7 +7725,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>41048</v>
       </c>
@@ -7733,7 +7743,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>41055</v>
       </c>
@@ -7751,7 +7761,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>41062</v>
       </c>
@@ -7769,7 +7779,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>41069</v>
       </c>
@@ -7787,7 +7797,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>41076</v>
       </c>
@@ -7805,7 +7815,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>41083</v>
       </c>
@@ -7823,7 +7833,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>41090</v>
       </c>
@@ -7841,7 +7851,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>41097</v>
       </c>
@@ -7859,7 +7869,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>41104</v>
       </c>
@@ -7877,7 +7887,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>41111</v>
       </c>
@@ -7895,7 +7905,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>41118</v>
       </c>
@@ -7913,7 +7923,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>41125</v>
       </c>
@@ -7931,7 +7941,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>41132</v>
       </c>
@@ -7949,7 +7959,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>41139</v>
       </c>
@@ -7967,7 +7977,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>41146</v>
       </c>
@@ -7985,7 +7995,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>41153</v>
       </c>
@@ -8003,7 +8013,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>41160</v>
       </c>
@@ -8021,7 +8031,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>41167</v>
       </c>
@@ -8039,7 +8049,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>41174</v>
       </c>
@@ -8057,7 +8067,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>41181</v>
       </c>
@@ -8075,7 +8085,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>41188</v>
       </c>
@@ -8093,7 +8103,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>41195</v>
       </c>
@@ -8111,7 +8121,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>41202</v>
       </c>
@@ -8129,7 +8139,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>41209</v>
       </c>
@@ -8147,7 +8157,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>41216</v>
       </c>
@@ -8165,7 +8175,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>41223</v>
       </c>
@@ -8183,7 +8193,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>41230</v>
       </c>
@@ -8201,7 +8211,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>41237</v>
       </c>
@@ -8219,7 +8229,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>41244</v>
       </c>
@@ -8237,7 +8247,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>41251</v>
       </c>
@@ -8255,7 +8265,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>41258</v>
       </c>
@@ -8273,7 +8283,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>41265</v>
       </c>
@@ -8291,7 +8301,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>41272</v>
       </c>
@@ -8309,7 +8319,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>41279</v>
       </c>
@@ -8327,7 +8337,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>41286</v>
       </c>
@@ -8352,7 +8362,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>41293</v>
       </c>
@@ -8370,7 +8380,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>41300</v>
       </c>
@@ -8388,7 +8398,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>41307</v>
       </c>
@@ -8406,7 +8416,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>41314</v>
       </c>
@@ -8424,7 +8434,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>41321</v>
       </c>
@@ -8442,7 +8452,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>41328</v>
       </c>
@@ -8460,7 +8470,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>41335</v>
       </c>
@@ -8478,7 +8488,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>41342</v>
       </c>
@@ -8496,7 +8506,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>41349</v>
       </c>
@@ -8514,7 +8524,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>41356</v>
       </c>
@@ -8532,7 +8542,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>41363</v>
       </c>
@@ -8550,7 +8560,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>41370</v>
       </c>
@@ -8568,7 +8578,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>41377</v>
       </c>
@@ -8586,7 +8596,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>41384</v>
       </c>
@@ -8604,7 +8614,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>41391</v>
       </c>
@@ -8622,7 +8632,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>41398</v>
       </c>
@@ -8640,7 +8650,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>41405</v>
       </c>
@@ -8658,7 +8668,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>41412</v>
       </c>
@@ -8676,7 +8686,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>41419</v>
       </c>
@@ -8694,7 +8704,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>41426</v>
       </c>
@@ -8712,7 +8722,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>41433</v>
       </c>
@@ -8730,7 +8740,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>41440</v>
       </c>
@@ -8748,7 +8758,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>41447</v>
       </c>
@@ -8766,7 +8776,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>41454</v>
       </c>
@@ -8784,7 +8794,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>41461</v>
       </c>
@@ -8802,7 +8812,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>41468</v>
       </c>
@@ -8820,7 +8830,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>41475</v>
       </c>
@@ -8838,7 +8848,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>41482</v>
       </c>
@@ -8856,7 +8866,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>41489</v>
       </c>
@@ -8874,7 +8884,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>41496</v>
       </c>
@@ -8892,7 +8902,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>41503</v>
       </c>
@@ -8910,7 +8920,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>41510</v>
       </c>
@@ -8928,7 +8938,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>41517</v>
       </c>
@@ -8946,7 +8956,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>41524</v>
       </c>
@@ -8964,7 +8974,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>41531</v>
       </c>
@@ -8982,7 +8992,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>41538</v>
       </c>
@@ -9000,7 +9010,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>41545</v>
       </c>
@@ -9018,7 +9028,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>41552</v>
       </c>
@@ -9036,7 +9046,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>41559</v>
       </c>
@@ -9054,7 +9064,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>41566</v>
       </c>
@@ -9072,7 +9082,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>41573</v>
       </c>
@@ -9090,7 +9100,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>41580</v>
       </c>
@@ -9108,7 +9118,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>41587</v>
       </c>
@@ -9126,7 +9136,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>41594</v>
       </c>
@@ -9144,7 +9154,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>41601</v>
       </c>
@@ -9162,7 +9172,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>41608</v>
       </c>
@@ -9180,7 +9190,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>41615</v>
       </c>
@@ -9198,7 +9208,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>41622</v>
       </c>
@@ -9216,7 +9226,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>41629</v>
       </c>
@@ -9234,7 +9244,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>41636</v>
       </c>
@@ -9252,7 +9262,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>41643</v>
       </c>
@@ -9270,7 +9280,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>41650</v>
       </c>
@@ -9288,7 +9298,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>41657</v>
       </c>
@@ -9306,7 +9316,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>41664</v>
       </c>
@@ -9324,7 +9334,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>41671</v>
       </c>
@@ -9342,7 +9352,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>41678</v>
       </c>
@@ -9360,7 +9370,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>41685</v>
       </c>
@@ -9378,7 +9388,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>41692</v>
       </c>
@@ -9396,7 +9406,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>41699</v>
       </c>
@@ -9414,7 +9424,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>41706</v>
       </c>
@@ -9432,7 +9442,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>41713</v>
       </c>
@@ -9450,7 +9460,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
         <v>41720</v>
       </c>
@@ -9468,7 +9478,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
         <v>41727</v>
       </c>
@@ -9486,7 +9496,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
         <v>41734</v>
       </c>
@@ -9511,7 +9521,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
         <v>41741</v>
       </c>
@@ -9529,7 +9539,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>41748</v>
       </c>
@@ -9547,7 +9557,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="8">
         <v>41755</v>
       </c>
@@ -9565,7 +9575,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="8">
         <v>41762</v>
       </c>
@@ -9583,7 +9593,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="8">
         <v>41769</v>
       </c>
@@ -9601,7 +9611,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="8">
         <v>41776</v>
       </c>
@@ -9619,7 +9629,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="8">
         <v>41783</v>
       </c>
@@ -9637,7 +9647,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>41790</v>
       </c>
@@ -9655,7 +9665,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="8">
         <v>41797</v>
       </c>
@@ -9673,7 +9683,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="8">
         <v>41804</v>
       </c>
@@ -9691,7 +9701,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="8">
         <v>41811</v>
       </c>
@@ -9709,7 +9719,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="8">
         <v>41818</v>
       </c>
@@ -9727,7 +9737,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="8">
         <v>41825</v>
       </c>
@@ -9745,7 +9755,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>41832</v>
       </c>
@@ -9763,7 +9773,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
         <v>41839</v>
       </c>
@@ -9781,7 +9791,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="8">
         <v>41846</v>
       </c>
@@ -9799,7 +9809,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
         <v>41853</v>
       </c>
@@ -9817,7 +9827,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>41860</v>
       </c>
@@ -9835,7 +9845,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
         <v>41867</v>
       </c>
@@ -9853,7 +9863,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="8">
         <v>41874</v>
       </c>
@@ -9871,7 +9881,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>41881</v>
       </c>
@@ -9889,7 +9899,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="8">
         <v>41888</v>
       </c>
@@ -9907,7 +9917,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="8">
         <v>41895</v>
       </c>
@@ -9925,7 +9935,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="8">
         <v>41902</v>
       </c>
@@ -9943,7 +9953,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="8">
         <v>41909</v>
       </c>
@@ -9961,7 +9971,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="8">
         <v>41916</v>
       </c>
@@ -9979,7 +9989,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="8">
         <v>41923</v>
       </c>
@@ -9997,7 +10007,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="8">
         <v>41930</v>
       </c>
@@ -10015,7 +10025,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="8">
         <v>41937</v>
       </c>
@@ -10033,7 +10043,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="8">
         <v>41944</v>
       </c>
@@ -10051,7 +10061,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="8">
         <v>41951</v>
       </c>
@@ -10069,7 +10079,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="8">
         <v>41958</v>
       </c>
@@ -10087,7 +10097,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="8">
         <v>41965</v>
       </c>
@@ -10105,7 +10115,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>41972</v>
       </c>
@@ -10123,7 +10133,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>41979</v>
       </c>
@@ -10141,7 +10151,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>41986</v>
       </c>
@@ -10159,7 +10169,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>41993</v>
       </c>
@@ -10177,7 +10187,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>42000</v>
       </c>
@@ -10195,7 +10205,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>42007</v>
       </c>
@@ -10213,7 +10223,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>42014</v>
       </c>
@@ -10231,7 +10241,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="8">
         <v>42021</v>
       </c>
@@ -10249,7 +10259,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="8">
         <v>42028</v>
       </c>
@@ -10267,7 +10277,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="8">
         <v>42035</v>
       </c>
@@ -10285,7 +10295,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="8">
         <v>42042</v>
       </c>
@@ -10303,7 +10313,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="8">
         <v>42049</v>
       </c>
@@ -10321,7 +10331,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="8">
         <v>42056</v>
       </c>
@@ -10339,7 +10349,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="8">
         <v>42063</v>
       </c>
@@ -10357,7 +10367,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>42070</v>
       </c>
@@ -10375,7 +10385,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="8">
         <v>42077</v>
       </c>
@@ -10393,7 +10403,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>42084</v>
       </c>
@@ -10411,7 +10421,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>42091</v>
       </c>
@@ -10429,7 +10439,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="8">
         <v>42098</v>
       </c>
@@ -10447,7 +10457,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>42105</v>
       </c>
@@ -10465,7 +10475,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
         <v>42112</v>
       </c>
@@ -10483,7 +10493,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="8">
         <v>42119</v>
       </c>
@@ -10501,7 +10511,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="8">
         <v>42126</v>
       </c>
@@ -10519,7 +10529,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="8">
         <v>42133</v>
       </c>
@@ -10537,7 +10547,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="8">
         <v>42140</v>
       </c>
@@ -10555,7 +10565,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="8">
         <v>42147</v>
       </c>
@@ -10573,7 +10583,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="8">
         <v>42154</v>
       </c>
@@ -10591,7 +10601,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="8">
         <v>42161</v>
       </c>
@@ -10609,7 +10619,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="8">
         <v>42168</v>
       </c>
@@ -10627,7 +10637,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="8">
         <v>42175</v>
       </c>
@@ -10645,7 +10655,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
         <v>42182</v>
       </c>
@@ -10670,7 +10680,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="8">
         <v>42189</v>
       </c>
@@ -10688,7 +10698,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="8">
         <v>42196</v>
       </c>
@@ -10706,7 +10716,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="8">
         <v>42203</v>
       </c>
@@ -10724,7 +10734,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="8">
         <v>42210</v>
       </c>
@@ -10742,7 +10752,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="8">
         <v>42217</v>
       </c>
@@ -10760,7 +10770,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="8">
         <v>42224</v>
       </c>
@@ -10778,7 +10788,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="8">
         <v>42231</v>
       </c>
@@ -10796,7 +10806,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="8">
         <v>42238</v>
       </c>
@@ -10814,7 +10824,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="8">
         <v>42245</v>
       </c>
@@ -10832,7 +10842,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>42252</v>
       </c>
@@ -10850,7 +10860,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="8">
         <v>42259</v>
       </c>
@@ -10868,7 +10878,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>42266</v>
       </c>
@@ -10886,7 +10896,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="8">
         <v>42273</v>
       </c>
@@ -10904,7 +10914,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="8">
         <v>42280</v>
       </c>
@@ -10922,7 +10932,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="8">
         <v>42287</v>
       </c>
@@ -10940,7 +10950,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="8">
         <v>42294</v>
       </c>
@@ -10958,7 +10968,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="8">
         <v>42301</v>
       </c>
@@ -10976,7 +10986,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="8">
         <v>42308</v>
       </c>
@@ -10994,7 +11004,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="8">
         <v>42315</v>
       </c>
@@ -11012,7 +11022,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="8">
         <v>42322</v>
       </c>
@@ -11030,7 +11040,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="8">
         <v>42329</v>
       </c>
@@ -11048,7 +11058,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="8">
         <v>42336</v>
       </c>
@@ -11066,7 +11076,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="8">
         <v>42343</v>
       </c>
@@ -11084,7 +11094,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="8">
         <v>42350</v>
       </c>
@@ -11102,7 +11112,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="8">
         <v>42357</v>
       </c>
@@ -11120,7 +11130,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="8">
         <v>42364</v>
       </c>
@@ -11138,7 +11148,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="8">
         <v>42371</v>
       </c>
@@ -11156,7 +11166,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="8">
         <v>42378</v>
       </c>
@@ -11174,7 +11184,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="8">
         <v>42385</v>
       </c>
@@ -11192,7 +11202,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="8">
         <v>42392</v>
       </c>
@@ -11210,7 +11220,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="8">
         <v>42399</v>
       </c>
@@ -11228,7 +11238,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="8">
         <v>42406</v>
       </c>
@@ -11246,7 +11256,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="8">
         <v>42413</v>
       </c>
@@ -11264,7 +11274,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="8">
         <v>42420</v>
       </c>
@@ -11282,7 +11292,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="8">
         <v>42427</v>
       </c>
@@ -11300,7 +11310,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="8">
         <v>42434</v>
       </c>
@@ -11318,7 +11328,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="8">
         <v>42441</v>
       </c>
@@ -11336,7 +11346,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="8">
         <v>42448</v>
       </c>
@@ -11354,7 +11364,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="8">
         <v>42455</v>
       </c>
@@ -11372,7 +11382,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="8">
         <v>42462</v>
       </c>
@@ -11390,7 +11400,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="8">
         <v>42469</v>
       </c>
@@ -11408,7 +11418,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="8">
         <v>42476</v>
       </c>
@@ -11426,7 +11436,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="8">
         <v>42483</v>
       </c>
@@ -11444,7 +11454,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="8">
         <v>42490</v>
       </c>
@@ -11462,7 +11472,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="8">
         <v>42497</v>
       </c>
@@ -11480,7 +11490,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="8">
         <v>42504</v>
       </c>
@@ -11498,7 +11508,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="8">
         <v>42511</v>
       </c>
@@ -11516,7 +11526,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="8">
         <v>42518</v>
       </c>
@@ -11534,7 +11544,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="8">
         <v>42525</v>
       </c>
@@ -11552,7 +11562,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="8">
         <v>42532</v>
       </c>
@@ -11570,7 +11580,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="8">
         <v>42539</v>
       </c>
@@ -11588,7 +11598,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="8">
         <v>42546</v>
       </c>
@@ -11606,7 +11616,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="8">
         <v>42553</v>
       </c>
@@ -11624,7 +11634,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="8">
         <v>42560</v>
       </c>
@@ -11642,7 +11652,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="8">
         <v>42567</v>
       </c>
@@ -11660,7 +11670,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="8">
         <v>42574</v>
       </c>
@@ -11678,7 +11688,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="8">
         <v>42581</v>
       </c>
@@ -11696,7 +11706,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="8">
         <v>42588</v>
       </c>
@@ -11714,7 +11724,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="8">
         <v>42595</v>
       </c>
@@ -11732,7 +11742,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="8">
         <v>42602</v>
       </c>
@@ -11750,7 +11760,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="8">
         <v>42609</v>
       </c>
@@ -11768,7 +11778,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="8">
         <v>42616</v>
       </c>
@@ -11786,7 +11796,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="8">
         <v>42623</v>
       </c>
@@ -11804,7 +11814,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="8">
         <v>42630</v>
       </c>
@@ -11829,7 +11839,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="8">
         <v>42637</v>
       </c>
@@ -11847,7 +11857,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="8">
         <v>42644</v>
       </c>
@@ -11865,7 +11875,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="8">
         <v>42651</v>
       </c>
@@ -11883,7 +11893,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="8">
         <v>42658</v>
       </c>
@@ -11901,7 +11911,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="8">
         <v>42665</v>
       </c>
@@ -11919,7 +11929,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="8">
         <v>42672</v>
       </c>
@@ -11937,7 +11947,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="8">
         <v>42679</v>
       </c>
@@ -11955,7 +11965,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="8">
         <v>42686</v>
       </c>
@@ -11973,7 +11983,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="8">
         <v>42693</v>
       </c>
@@ -11991,7 +12001,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="8">
         <v>42700</v>
       </c>
@@ -12009,7 +12019,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="8">
         <v>42707</v>
       </c>
@@ -12027,7 +12037,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="8">
         <v>42714</v>
       </c>
@@ -12045,7 +12055,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="8">
         <v>42721</v>
       </c>
@@ -12063,7 +12073,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="8">
         <v>42728</v>
       </c>
@@ -12081,7 +12091,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="8">
         <v>42735</v>
       </c>
@@ -12099,7 +12109,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="8">
         <v>42742</v>
       </c>
@@ -12117,7 +12127,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="8">
         <v>42749</v>
       </c>
@@ -12135,7 +12145,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="8">
         <v>42756</v>
       </c>
@@ -12153,7 +12163,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="8">
         <v>42763</v>
       </c>
@@ -12171,7 +12181,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="8">
         <v>42770</v>
       </c>
@@ -12189,7 +12199,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="8">
         <v>42777</v>
       </c>
@@ -12207,7 +12217,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="8">
         <v>42784</v>
       </c>
@@ -12225,7 +12235,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="8">
         <v>42791</v>
       </c>
@@ -12243,7 +12253,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="8">
         <v>42798</v>
       </c>
@@ -12261,7 +12271,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
         <v>42805</v>
       </c>
@@ -12279,7 +12289,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="8">
         <v>42812</v>
       </c>
@@ -12297,7 +12307,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="8">
         <v>42819</v>
       </c>
@@ -12315,7 +12325,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="8">
         <v>42826</v>
       </c>
@@ -12333,7 +12343,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="8">
         <v>42833</v>
       </c>
@@ -12351,7 +12361,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="8">
         <v>42840</v>
       </c>
@@ -12369,7 +12379,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="8">
         <v>42847</v>
       </c>
@@ -12387,7 +12397,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="8">
         <v>42854</v>
       </c>
@@ -12405,7 +12415,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="8">
         <v>42861</v>
       </c>
@@ -12423,7 +12433,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="8">
         <v>42868</v>
       </c>
@@ -12441,7 +12451,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="8">
         <v>42875</v>
       </c>
@@ -12459,7 +12469,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="8">
         <v>42882</v>
       </c>
@@ -12477,7 +12487,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="8">
         <v>42889</v>
       </c>
@@ -12495,7 +12505,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="8">
         <v>42896</v>
       </c>
@@ -12513,7 +12523,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="8">
         <v>42903</v>
       </c>
@@ -12531,7 +12541,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="8">
         <v>42910</v>
       </c>
@@ -12549,7 +12559,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="8">
         <v>42917</v>
       </c>
@@ -12567,7 +12577,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="8">
         <v>42924</v>
       </c>
@@ -12585,7 +12595,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="8">
         <v>42931</v>
       </c>
@@ -12603,7 +12613,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="8">
         <v>42938</v>
       </c>
@@ -12621,7 +12631,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="8">
         <v>42945</v>
       </c>
@@ -12639,7 +12649,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="8">
         <v>42952</v>
       </c>
@@ -12657,7 +12667,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="8">
         <v>42959</v>
       </c>
@@ -12675,7 +12685,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" s="8">
         <v>42966</v>
       </c>
@@ -12693,7 +12703,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="8">
         <v>42973</v>
       </c>
@@ -12711,7 +12721,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="8">
         <v>42980</v>
       </c>
@@ -12729,7 +12739,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" s="8">
         <v>42987</v>
       </c>
@@ -12747,7 +12757,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="8">
         <v>42994</v>
       </c>
@@ -12765,7 +12775,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="8">
         <v>43001</v>
       </c>
@@ -12783,7 +12793,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="8">
         <v>43008</v>
       </c>
@@ -12801,7 +12811,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="8">
         <v>43015</v>
       </c>
@@ -12819,7 +12829,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="8">
         <v>43022</v>
       </c>
@@ -12837,7 +12847,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="8">
         <v>43029</v>
       </c>
@@ -12855,7 +12865,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="8">
         <v>43036</v>
       </c>
@@ -12873,7 +12883,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="8">
         <v>43043</v>
       </c>
@@ -12891,7 +12901,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="8">
         <v>43050</v>
       </c>
@@ -12909,7 +12919,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="8">
         <v>43057</v>
       </c>
@@ -12927,7 +12937,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="8">
         <v>43064</v>
       </c>
@@ -12945,7 +12955,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="8">
         <v>43071</v>
       </c>
@@ -12963,7 +12973,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="8">
         <v>43078</v>
       </c>
@@ -12988,7 +12998,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="8">
         <v>43085</v>
       </c>
@@ -13006,7 +13016,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="8">
         <v>43092</v>
       </c>
@@ -13024,7 +13034,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="8">
         <v>43099</v>
       </c>
@@ -13042,7 +13052,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="8">
         <v>43106</v>
       </c>
@@ -13060,7 +13070,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="8">
         <v>43113</v>
       </c>
@@ -13078,7 +13088,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="8">
         <v>43120</v>
       </c>
@@ -13096,7 +13106,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="8">
         <v>43127</v>
       </c>
@@ -13114,7 +13124,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="8">
         <v>43134</v>
       </c>
@@ -13132,7 +13142,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="8">
         <v>43141</v>
       </c>
@@ -13150,7 +13160,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="8">
         <v>43148</v>
       </c>
@@ -13168,7 +13178,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="8">
         <v>43155</v>
       </c>
@@ -13186,7 +13196,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="8">
         <v>43162</v>
       </c>
@@ -13204,7 +13214,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="8">
         <v>43169</v>
       </c>
@@ -13222,7 +13232,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="8">
         <v>43176</v>
       </c>
@@ -13240,7 +13250,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="8">
         <v>43183</v>
       </c>
@@ -13258,7 +13268,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="8">
         <v>43190</v>
       </c>
@@ -13276,7 +13286,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="8">
         <v>43197</v>
       </c>
@@ -13294,7 +13304,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="8">
         <v>43204</v>
       </c>
@@ -13312,7 +13322,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="8">
         <v>43211</v>
       </c>
@@ -13330,7 +13340,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="8">
         <v>43218</v>
       </c>
@@ -13348,7 +13358,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="8">
         <v>43225</v>
       </c>
@@ -13366,7 +13376,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="8">
         <v>43232</v>
       </c>
@@ -13384,7 +13394,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="8">
         <v>43239</v>
       </c>
@@ -13402,7 +13412,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="8">
         <v>43245</v>
       </c>
@@ -13420,7 +13430,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="8">
         <v>43252</v>
       </c>
@@ -13438,7 +13448,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="8">
         <v>43259</v>
       </c>
@@ -13456,7 +13466,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="8">
         <v>43266</v>
       </c>
@@ -13474,7 +13484,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="8">
         <v>43273</v>
       </c>
@@ -13492,7 +13502,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="8">
         <v>43280</v>
       </c>
@@ -13510,7 +13520,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="8">
         <v>43287</v>
       </c>
@@ -13528,7 +13538,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="8">
         <v>43294</v>
       </c>
@@ -13546,7 +13556,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="8">
         <v>43301</v>
       </c>
@@ -13564,7 +13574,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="8">
         <v>43308</v>
       </c>
@@ -13582,7 +13592,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="8">
         <v>43315</v>
       </c>
@@ -13600,7 +13610,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="8">
         <v>43322</v>
       </c>
@@ -13618,7 +13628,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="8">
         <v>43329</v>
       </c>
@@ -13636,7 +13646,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="8">
         <v>43336</v>
       </c>
@@ -13654,7 +13664,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="8">
         <v>43343</v>
       </c>
@@ -13672,7 +13682,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="8">
         <v>43350</v>
       </c>
@@ -13690,7 +13700,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="8">
         <v>43357</v>
       </c>
@@ -13708,7 +13718,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="8">
         <v>43364</v>
       </c>
@@ -13726,7 +13736,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="8">
         <v>43371</v>
       </c>
@@ -13744,7 +13754,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="8">
         <v>43378</v>
       </c>
@@ -13762,7 +13772,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="8">
         <v>43385</v>
       </c>
@@ -13780,7 +13790,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="8">
         <v>43392</v>
       </c>
@@ -13798,7 +13808,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="8">
         <v>43399</v>
       </c>
@@ -13816,7 +13826,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="8">
         <v>43406</v>
       </c>
@@ -13834,7 +13844,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="8">
         <v>43413</v>
       </c>
@@ -13852,7 +13862,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="8">
         <v>43420</v>
       </c>
@@ -13870,7 +13880,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="8">
         <v>43427</v>
       </c>
@@ -13888,7 +13898,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="8">
         <v>43434</v>
       </c>
@@ -13906,7 +13916,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="8">
         <v>43441</v>
       </c>
@@ -13924,7 +13934,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="8">
         <v>43448</v>
       </c>
@@ -13942,7 +13952,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="8">
         <v>43455</v>
       </c>
@@ -13960,7 +13970,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="8">
         <v>43462</v>
       </c>
@@ -13978,7 +13988,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="8">
         <v>43469</v>
       </c>
@@ -13996,7 +14006,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="8">
         <v>43476</v>
       </c>
@@ -14014,7 +14024,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="8">
         <v>43483</v>
       </c>
@@ -14032,7 +14042,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="8">
         <v>43490</v>
       </c>
@@ -14050,7 +14060,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="8">
         <v>43497</v>
       </c>
@@ -14068,7 +14078,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="8">
         <v>43504</v>
       </c>
@@ -14086,7 +14096,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="8">
         <v>43511</v>
       </c>
@@ -14104,7 +14114,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="8">
         <v>43518</v>
       </c>
@@ -14122,7 +14132,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="8">
         <v>43525</v>
       </c>
@@ -14147,7 +14157,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="8">
         <v>43532</v>
       </c>
@@ -14165,7 +14175,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="8">
         <v>43539</v>
       </c>
@@ -14183,7 +14193,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="8">
         <v>43546</v>
       </c>
@@ -14201,7 +14211,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="8">
         <v>43553</v>
       </c>
@@ -14219,7 +14229,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="8">
         <v>43560</v>
       </c>
@@ -14237,7 +14247,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="8">
         <v>43567</v>
       </c>
@@ -14255,7 +14265,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="8">
         <v>43574</v>
       </c>
@@ -14273,7 +14283,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="8">
         <v>43581</v>
       </c>
@@ -14291,7 +14301,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="8">
         <v>43588</v>
       </c>
@@ -14309,7 +14319,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="8">
         <v>43595</v>
       </c>
@@ -14327,7 +14337,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="8">
         <v>43602</v>
       </c>
@@ -14345,7 +14355,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="8">
         <v>43609</v>
       </c>
@@ -14363,7 +14373,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="8">
         <v>43616</v>
       </c>
@@ -14381,7 +14391,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="8">
         <v>43623</v>
       </c>
@@ -14399,7 +14409,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="8">
         <v>43630</v>
       </c>
@@ -14417,7 +14427,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="8">
         <v>43637</v>
       </c>
@@ -14435,7 +14445,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="8">
         <v>43644</v>
       </c>
@@ -14453,7 +14463,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="8">
         <v>43651</v>
       </c>
@@ -14471,7 +14481,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="8">
         <v>43658</v>
       </c>
@@ -14489,7 +14499,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="8">
         <v>43665</v>
       </c>
@@ -14507,7 +14517,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="8">
         <v>43672</v>
       </c>
@@ -14525,7 +14535,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="8">
         <v>43679</v>
       </c>
@@ -14543,7 +14553,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="8">
         <v>43686</v>
       </c>
@@ -14561,7 +14571,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="8">
         <v>43693</v>
       </c>
@@ -14579,7 +14589,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="8">
         <v>43700</v>
       </c>
@@ -14597,7 +14607,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="8">
         <v>43707</v>
       </c>
@@ -14615,7 +14625,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="8">
         <v>43714</v>
       </c>
@@ -14633,7 +14643,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="8">
         <v>43721</v>
       </c>
@@ -14651,7 +14661,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="8">
         <v>43728</v>
       </c>
@@ -14669,7 +14679,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="8">
         <v>43735</v>
       </c>
@@ -14687,7 +14697,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="8">
         <v>43742</v>
       </c>
@@ -14705,7 +14715,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="8">
         <v>43749</v>
       </c>
@@ -14723,7 +14733,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="8">
         <v>43756</v>
       </c>
@@ -14741,7 +14751,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="8">
         <v>43763</v>
       </c>
@@ -14759,7 +14769,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="8">
         <v>43770</v>
       </c>
@@ -14777,7 +14787,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" s="8">
         <v>43777</v>
       </c>
@@ -14795,7 +14805,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" s="8">
         <v>43784</v>
       </c>
@@ -14813,7 +14823,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" s="8">
         <v>43791</v>
       </c>
@@ -14831,7 +14841,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" s="8">
         <v>43798</v>
       </c>
@@ -14849,7 +14859,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" s="8">
         <v>43805</v>
       </c>
@@ -14867,7 +14877,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" s="8">
         <v>43812</v>
       </c>
@@ -14885,7 +14895,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" s="8">
         <v>43819</v>
       </c>
@@ -14903,7 +14913,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" s="8">
         <v>43826</v>
       </c>
@@ -14921,7 +14931,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" s="8">
         <v>43833</v>
       </c>
@@ -14939,7 +14949,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" s="8">
         <v>43840</v>
       </c>
@@ -14957,7 +14967,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" s="8">
         <v>43847</v>
       </c>
@@ -14975,7 +14985,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" s="8">
         <v>43854</v>
       </c>
@@ -14993,7 +15003,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" s="8">
         <v>43861</v>
       </c>
@@ -15011,7 +15021,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="8">
         <v>43868</v>
       </c>
@@ -15029,7 +15039,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" s="8">
         <v>43875</v>
       </c>
@@ -15047,7 +15057,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" s="8">
         <v>43882</v>
       </c>
@@ -15065,7 +15075,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" s="8">
         <v>43889</v>
       </c>
@@ -15083,7 +15093,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" s="8">
         <v>43896</v>
       </c>
@@ -15101,7 +15111,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" s="8">
         <v>43903</v>
       </c>
@@ -15119,7 +15129,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" s="8">
         <v>43910</v>
       </c>
@@ -15137,7 +15147,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" s="8">
         <v>43917</v>
       </c>
@@ -15155,7 +15165,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" s="8">
         <v>43924</v>
       </c>
@@ -15173,7 +15183,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" s="8">
         <v>43931</v>
       </c>
@@ -15191,7 +15201,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" s="8">
         <v>43938</v>
       </c>
@@ -15209,7 +15219,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" s="8">
         <v>43945</v>
       </c>
@@ -15227,7 +15237,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" s="8">
         <v>43952</v>
       </c>
@@ -15245,7 +15255,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" s="8">
         <v>43959</v>
       </c>
@@ -15263,7 +15273,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" s="8">
         <v>43966</v>
       </c>
@@ -15281,7 +15291,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" s="8">
         <v>43973</v>
       </c>
@@ -15306,7 +15316,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" s="8">
         <v>43980</v>
       </c>
@@ -15324,7 +15334,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" s="8">
         <v>43987</v>
       </c>
@@ -15342,7 +15352,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" s="8">
         <v>43994</v>
       </c>
@@ -15360,7 +15370,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" s="8">
         <v>44001</v>
       </c>
@@ -15378,7 +15388,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" s="8">
         <v>44008</v>
       </c>
@@ -15396,7 +15406,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" s="8">
         <v>44015</v>
       </c>
@@ -15414,7 +15424,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" s="8">
         <v>44022</v>
       </c>
@@ -15432,7 +15442,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" s="8">
         <v>44029</v>
       </c>
@@ -15450,7 +15460,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" s="8">
         <v>44036</v>
       </c>
@@ -15468,7 +15478,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" s="8">
         <v>44043</v>
       </c>
@@ -15486,7 +15496,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" s="8">
         <v>44050</v>
       </c>
@@ -15504,7 +15514,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" s="8">
         <v>44057</v>
       </c>
@@ -15522,7 +15532,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" s="8">
         <v>44064</v>
       </c>
@@ -15540,7 +15550,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" s="8">
         <v>44071</v>
       </c>
@@ -15558,7 +15568,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" s="8">
         <v>44078</v>
       </c>
@@ -15576,7 +15586,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" s="8">
         <v>44085</v>
       </c>
@@ -15594,7 +15604,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" s="8">
         <v>44092</v>
       </c>
@@ -15612,7 +15622,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" s="8">
         <v>44099</v>
       </c>
@@ -15630,7 +15640,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" s="8">
         <v>44106</v>
       </c>
@@ -15648,7 +15658,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" s="8">
         <v>44113</v>
       </c>
@@ -15666,7 +15676,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" s="8">
         <v>44120</v>
       </c>
@@ -15684,7 +15694,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" s="8">
         <v>44127</v>
       </c>
@@ -15702,7 +15712,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" s="8">
         <v>44134</v>
       </c>
@@ -15720,7 +15730,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" s="8">
         <v>44141</v>
       </c>
@@ -15738,7 +15748,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" s="8">
         <v>44148</v>
       </c>
@@ -15756,7 +15766,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" s="8">
         <v>44155</v>
       </c>
@@ -15774,7 +15784,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" s="8">
         <v>44162</v>
       </c>
@@ -15792,7 +15802,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" s="8">
         <v>44169</v>
       </c>
@@ -15810,7 +15820,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" s="8">
         <v>44176</v>
       </c>
@@ -15828,7 +15838,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="8">
         <v>44183</v>
       </c>
@@ -15846,7 +15856,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="8">
         <v>44190</v>
       </c>
@@ -15864,7 +15874,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" s="8">
         <v>44197</v>
       </c>
@@ -15882,7 +15892,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="8">
         <v>44204</v>
       </c>
@@ -15900,7 +15910,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" s="8">
         <v>44211</v>
       </c>
@@ -15918,7 +15928,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" s="8">
         <v>44218</v>
       </c>
@@ -15936,7 +15946,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" s="8">
         <v>44225</v>
       </c>
@@ -15954,7 +15964,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" s="8">
         <v>44232</v>
       </c>
@@ -15972,7 +15982,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="8">
         <v>44239</v>
       </c>
@@ -15990,7 +16000,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" s="8">
         <v>44246</v>
       </c>
@@ -16008,7 +16018,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" s="8">
         <v>44253</v>
       </c>
@@ -16026,7 +16036,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" s="8">
         <v>44260</v>
       </c>
@@ -16044,7 +16054,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" s="8">
         <v>44267</v>
       </c>
@@ -16062,7 +16072,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" s="8">
         <v>44274</v>
       </c>
@@ -16080,7 +16090,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" s="8">
         <v>44281</v>
       </c>
@@ -16098,7 +16108,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" s="8">
         <v>44288</v>
       </c>
@@ -16116,7 +16126,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="8">
         <v>44295</v>
       </c>
@@ -16134,7 +16144,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" s="8">
         <v>44302</v>
       </c>
@@ -16152,7 +16162,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" s="8">
         <v>44309</v>
       </c>
@@ -16170,7 +16180,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" s="8">
         <v>44316</v>
       </c>
@@ -16188,7 +16198,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" s="8">
         <v>44323</v>
       </c>
@@ -16206,7 +16216,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" s="8">
         <v>44330</v>
       </c>
@@ -16224,7 +16234,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" s="8">
         <v>44337</v>
       </c>
@@ -16242,7 +16252,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="8">
         <v>44344</v>
       </c>
@@ -16260,7 +16270,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="8">
         <v>44351</v>
       </c>
@@ -16278,7 +16288,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" s="8">
         <v>44358</v>
       </c>
@@ -16296,7 +16306,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" s="8">
         <v>44365</v>
       </c>
@@ -16314,7 +16324,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" s="8">
         <v>44372</v>
       </c>
@@ -16332,7 +16342,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" s="8">
         <v>44379</v>
       </c>
@@ -16350,7 +16360,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" s="8">
         <v>44386</v>
       </c>
@@ -16368,7 +16378,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" s="8">
         <v>44393</v>
       </c>
@@ -16386,7 +16396,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" s="8">
         <v>44400</v>
       </c>
@@ -16404,7 +16414,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" s="8">
         <v>44407</v>
       </c>
@@ -16422,7 +16432,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" s="8">
         <v>44414</v>
       </c>
@@ -16440,7 +16450,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" s="8">
         <v>44421</v>
       </c>
@@ -16465,7 +16475,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" s="8">
         <v>44428</v>
       </c>
@@ -16483,7 +16493,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" s="8">
         <v>44435</v>
       </c>
@@ -16501,7 +16511,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" s="8">
         <v>44442</v>
       </c>
@@ -16519,7 +16529,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" s="8">
         <v>44449</v>
       </c>
@@ -16537,7 +16547,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" s="8">
         <v>44456</v>
       </c>
@@ -16555,7 +16565,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" s="8">
         <v>44463</v>
       </c>
@@ -16573,7 +16583,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" s="8">
         <v>44470</v>
       </c>
@@ -16591,7 +16601,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" s="8">
         <v>44477</v>
       </c>
@@ -16609,7 +16619,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" s="8">
         <v>44484</v>
       </c>
@@ -16627,7 +16637,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" s="8">
         <v>44491</v>
       </c>
@@ -16645,7 +16655,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" s="8">
         <v>44498</v>
       </c>
@@ -16663,7 +16673,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" s="8">
         <v>44505</v>
       </c>
@@ -16681,7 +16691,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" s="8">
         <v>44512</v>
       </c>
@@ -16699,7 +16709,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:4">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A593" s="8">
         <v>44519</v>
       </c>
@@ -16714,7 +16724,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="594" spans="1:4">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" s="8">
         <v>44526</v>
       </c>
@@ -16729,7 +16739,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="595" spans="1:4">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" s="8">
         <v>44533</v>
       </c>
@@ -16744,7 +16754,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="596" spans="1:4">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" s="8">
         <v>44540</v>
       </c>
@@ -16759,7 +16769,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="597" spans="1:4">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A597" s="8">
         <v>44547</v>
       </c>
@@ -16774,7 +16784,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="598" spans="1:4">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" s="8">
         <v>44554</v>
       </c>
@@ -16789,7 +16799,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="599" spans="1:4">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" s="8">
         <v>44561</v>
       </c>
@@ -16804,7 +16814,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="600" spans="1:4">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" s="8">
         <v>44568</v>
       </c>
@@ -16819,7 +16829,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="601" spans="1:4">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" s="8">
         <v>44575</v>
       </c>
@@ -16834,7 +16844,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="602" spans="1:4">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A602" s="8">
         <v>44582</v>
       </c>
@@ -16849,7 +16859,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="603" spans="1:4">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" s="8">
         <v>44589</v>
       </c>
@@ -16864,7 +16874,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="604" spans="1:4">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" s="8">
         <v>44596</v>
       </c>
@@ -16879,7 +16889,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="605" spans="1:4">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" s="8">
         <v>44603</v>
       </c>
@@ -16894,7 +16904,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="606" spans="1:4">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="8">
         <v>44610</v>
       </c>
@@ -16909,7 +16919,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="607" spans="1:4">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" s="8">
         <v>44617</v>
       </c>
@@ -16924,7 +16934,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="608" spans="1:4">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" s="8">
         <v>44624</v>
       </c>
@@ -16939,7 +16949,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="609" spans="1:4">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" s="8">
         <v>44631</v>
       </c>
@@ -16954,7 +16964,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="610" spans="1:4">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" s="8">
         <v>44638</v>
       </c>
@@ -16969,7 +16979,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="611" spans="1:4">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A611" s="8">
         <v>44645</v>
       </c>
@@ -16984,7 +16994,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="612" spans="1:4">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A612" s="8">
         <v>44652</v>
       </c>
@@ -16999,7 +17009,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="613" spans="1:4">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A613" s="8">
         <v>44659</v>
       </c>
@@ -17014,7 +17024,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="614" spans="1:4">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A614" s="8">
         <v>44666</v>
       </c>
@@ -17029,7 +17039,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="615" spans="1:4">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A615" s="8">
         <v>44673</v>
       </c>
@@ -17044,7 +17054,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="616" spans="1:4">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A616" s="8">
         <v>44680</v>
       </c>
@@ -17059,7 +17069,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="617" spans="1:4">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A617" s="8">
         <v>44687</v>
       </c>
@@ -17074,7 +17084,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="618" spans="1:4">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A618" s="8">
         <v>44694</v>
       </c>
@@ -17089,7 +17099,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="619" spans="1:4">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A619" s="8">
         <v>44701</v>
       </c>
@@ -17104,7 +17114,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="620" spans="1:4">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A620" s="8">
         <v>44708</v>
       </c>
@@ -17119,7 +17129,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="621" spans="1:4">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A621" s="8">
         <v>44715</v>
       </c>
@@ -17134,7 +17144,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="622" spans="1:4">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" s="8">
         <v>44722</v>
       </c>
@@ -17149,7 +17159,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="623" spans="1:4">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" s="8">
         <v>44729</v>
       </c>
@@ -17164,7 +17174,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="624" spans="1:4">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A624" s="8">
         <v>44736</v>
       </c>
@@ -17179,7 +17189,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="625" spans="1:4">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A625" s="8">
         <v>44743</v>
       </c>
@@ -17194,7 +17204,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="626" spans="1:4">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A626" s="8">
         <v>44750</v>
       </c>
@@ -17209,7 +17219,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="627" spans="1:4">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A627" s="8">
         <v>44757</v>
       </c>
@@ -17224,7 +17234,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="628" spans="1:4">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A628" s="8">
         <v>44764</v>
       </c>
@@ -17239,7 +17249,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="629" spans="1:4">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A629" s="8">
         <v>44771</v>
       </c>
@@ -17254,7 +17264,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="630" spans="1:4">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="8">
         <v>44778</v>
       </c>
@@ -17269,7 +17279,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="631" spans="1:4">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A631" s="8">
         <v>44785</v>
       </c>
@@ -17284,7 +17294,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="632" spans="1:4">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A632" s="8">
         <v>44792</v>
       </c>
@@ -17299,7 +17309,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="633" spans="1:4">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A633" s="8">
         <v>44799</v>
       </c>
@@ -17314,7 +17324,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="634" spans="1:4">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A634" s="8">
         <v>44806</v>
       </c>
@@ -17329,7 +17339,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="635" spans="1:4">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" s="8">
         <v>44813</v>
       </c>
@@ -17344,7 +17354,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="636" spans="1:4">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" s="8">
         <v>44820</v>
       </c>
@@ -17359,7 +17369,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="637" spans="1:4">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A637" s="8">
         <v>44827</v>
       </c>
@@ -17374,7 +17384,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="638" spans="1:4">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A638" s="8">
         <v>44834</v>
       </c>
@@ -17389,7 +17399,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="639" spans="1:4">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" s="8">
         <v>44841</v>
       </c>
@@ -17404,7 +17414,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="640" spans="1:4">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" s="8">
         <v>44848</v>
       </c>
@@ -17419,7 +17429,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="641" spans="1:4">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" s="8">
         <v>44855</v>
       </c>
@@ -17434,7 +17444,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="642" spans="1:4">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A642" s="8">
         <v>44862</v>
       </c>
@@ -17449,7 +17459,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="643" spans="1:4">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A643" s="8">
         <v>44869</v>
       </c>
@@ -17471,7 +17481,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="644" spans="1:4">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A644" s="8">
         <v>44876</v>
       </c>
@@ -17486,7 +17496,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="645" spans="1:4">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A645" s="8">
         <v>44883</v>
       </c>
@@ -17501,7 +17511,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="646" spans="1:4">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A646" s="8">
         <v>44890</v>
       </c>
@@ -17516,7 +17526,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="647" spans="1:4">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A647" s="8">
         <v>44897</v>
       </c>
@@ -17531,7 +17541,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="648" spans="1:4">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A648" s="8">
         <v>44904</v>
       </c>
@@ -17546,7 +17556,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="649" spans="1:4">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A649" s="8">
         <v>44911</v>
       </c>
@@ -17561,7 +17571,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="650" spans="1:4">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A650" s="8">
         <v>44918</v>
       </c>
@@ -17576,7 +17586,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="651" spans="1:4">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A651" s="8">
         <v>44925</v>
       </c>
@@ -17591,7 +17601,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="652" spans="1:4">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A652" s="8">
         <v>44932</v>
       </c>
@@ -17606,7 +17616,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="653" spans="1:4">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" s="8">
         <v>44939</v>
       </c>
@@ -17621,7 +17631,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="654" spans="1:4">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" s="8">
         <v>44946</v>
       </c>
@@ -17636,7 +17646,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="655" spans="1:4">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" s="8">
         <v>44953</v>
       </c>
@@ -17651,7 +17661,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="656" spans="1:4">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" s="8">
         <v>44960</v>
       </c>
@@ -17666,7 +17676,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="657" spans="1:4">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" s="8">
         <v>44967</v>
       </c>
@@ -17681,7 +17691,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="658" spans="1:4">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" s="8">
         <v>44974</v>
       </c>
@@ -17696,7 +17706,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="659" spans="1:4">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" s="8">
         <v>44981</v>
       </c>
@@ -17711,7 +17721,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="660" spans="1:4">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" s="8">
         <v>44988</v>
       </c>
@@ -17726,7 +17736,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="661" spans="1:4">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" s="8">
         <v>44995</v>
       </c>
@@ -17741,7 +17751,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="662" spans="1:4">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" s="8">
         <v>45002</v>
       </c>
@@ -17756,7 +17766,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="663" spans="1:4">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" s="8">
         <v>45009</v>
       </c>
@@ -17771,7 +17781,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="664" spans="1:4">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A664" s="8">
         <v>45016</v>
       </c>
@@ -17786,7 +17796,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="665" spans="1:4">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" s="8">
         <v>45023</v>
       </c>
@@ -17801,7 +17811,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="666" spans="1:4">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" s="8">
         <v>45030</v>
       </c>
@@ -17816,7 +17826,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="667" spans="1:4">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" s="8">
         <v>45037</v>
       </c>
@@ -17831,7 +17841,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="668" spans="1:4">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" s="8">
         <v>45044</v>
       </c>
@@ -17846,7 +17856,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="669" spans="1:4">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A669" s="8">
         <v>45051</v>
       </c>
@@ -17861,7 +17871,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="670" spans="1:4">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" s="8">
         <v>45058</v>
       </c>
@@ -17876,7 +17886,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="671" spans="1:4">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="8">
         <v>45065</v>
       </c>
@@ -17891,7 +17901,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="672" spans="1:4">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A672" s="8">
         <v>45072</v>
       </c>
@@ -17906,7 +17916,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="673" spans="1:4">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A673" s="8">
         <v>45079</v>
       </c>
@@ -17921,7 +17931,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="674" spans="1:4">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A674" s="8">
         <v>45086</v>
       </c>
@@ -17936,7 +17946,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="675" spans="1:4">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A675" s="8">
         <v>45093</v>
       </c>
@@ -17951,7 +17961,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="676" spans="1:4">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A676" s="8">
         <v>45100</v>
       </c>
@@ -17966,7 +17976,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="677" spans="1:4">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" s="8">
         <v>45107</v>
       </c>
@@ -17981,7 +17991,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="678" spans="1:4">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" s="8">
         <v>45114</v>
       </c>
@@ -17996,7 +18006,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="679" spans="1:4">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" s="8">
         <v>45121</v>
       </c>
@@ -18011,7 +18021,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="680" spans="1:4">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A680" s="8">
         <v>45128</v>
       </c>
@@ -18026,7 +18036,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="681" spans="1:4">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A681" s="8">
         <v>45135</v>
       </c>
@@ -18041,7 +18051,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="682" spans="1:4">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" s="8">
         <v>45142</v>
       </c>
@@ -18056,7 +18066,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="683" spans="1:4">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" s="8">
         <v>45149</v>
       </c>
@@ -18071,7 +18081,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="684" spans="1:4">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A684" s="8">
         <v>45156</v>
       </c>
@@ -18086,7 +18096,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="685" spans="1:4">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" s="8">
         <v>45163</v>
       </c>
@@ -18101,7 +18111,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="686" spans="1:4">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A686" s="8">
         <v>45170</v>
       </c>
@@ -18116,7 +18126,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="687" spans="1:4">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" s="8">
         <v>45177</v>
       </c>
@@ -18131,7 +18141,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="688" spans="1:4">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" s="8">
         <v>45184</v>
       </c>
@@ -18146,7 +18156,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="689" spans="1:5">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689" s="8">
         <v>45191</v>
       </c>
@@ -18161,7 +18171,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="690" spans="1:5">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" s="8">
         <v>45198</v>
       </c>
@@ -18176,7 +18186,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="691" spans="1:5">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" s="8">
         <v>45205</v>
       </c>
@@ -18191,7 +18201,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="692" spans="1:5">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692" s="8">
         <v>45212</v>
       </c>
@@ -18206,7 +18216,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="693" spans="1:5">
+    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693" s="8">
         <v>45219</v>
       </c>
@@ -18221,7 +18231,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="694" spans="1:5">
+    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694" s="8">
         <v>45226</v>
       </c>
@@ -18236,7 +18246,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="695" spans="1:5">
+    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695" s="8">
         <v>45233</v>
       </c>
@@ -18251,7 +18261,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="696" spans="1:5">
+    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A696" s="8">
         <v>45240</v>
       </c>
@@ -18266,7 +18276,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="697" spans="1:5">
+    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A697" s="8">
         <v>45247</v>
       </c>
@@ -18281,7 +18291,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="698" spans="1:5">
+    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A698" s="8">
         <v>45254</v>
       </c>
@@ -18296,7 +18306,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="699" spans="1:5">
+    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A699" s="8">
         <v>45261</v>
       </c>
@@ -18311,7 +18321,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="700" spans="1:5">
+    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A700" s="8">
         <v>45268</v>
       </c>
@@ -18326,7 +18336,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="701" spans="1:5">
+    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A701" s="8">
         <v>45275</v>
       </c>
@@ -18344,7 +18354,7 @@
         <v>809.6</v>
       </c>
     </row>
-    <row r="702" spans="1:5">
+    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A702" s="8">
         <v>45282</v>
       </c>
@@ -18362,7 +18372,7 @@
         <v>809.6</v>
       </c>
     </row>
-    <row r="703" spans="1:5">
+    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A703" s="8">
         <v>45289</v>
       </c>
@@ -18377,7 +18387,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="704" spans="1:5">
+    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A704" s="8">
         <v>45296</v>
       </c>
@@ -18392,7 +18402,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="705" spans="1:5">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A705" s="8">
         <v>45303</v>
       </c>
@@ -18410,7 +18420,7 @@
         <v>910.24</v>
       </c>
     </row>
-    <row r="706" spans="1:5">
+    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A706" s="8">
         <v>45310</v>
       </c>
@@ -18425,7 +18435,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="707" spans="1:5">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A707" s="8">
         <v>45317</v>
       </c>
@@ -18447,7 +18457,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="708" spans="1:5">
+    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A708" s="8">
         <v>45324</v>
       </c>
@@ -18462,7 +18472,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="709" spans="1:5">
+    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A709" s="8">
         <v>45331</v>
       </c>
@@ -18477,7 +18487,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="710" spans="1:5">
+    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A710" s="8">
         <v>45338</v>
       </c>
@@ -18492,7 +18502,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="711" spans="1:5">
+    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A711" s="8">
         <v>45345</v>
       </c>
@@ -18507,7 +18517,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="712" spans="1:5">
+    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A712" s="8">
         <v>45352</v>
       </c>
@@ -18522,7 +18532,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="713" spans="1:5">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A713" s="8">
         <v>45359</v>
       </c>
@@ -18540,7 +18550,7 @@
         <v>1201.73</v>
       </c>
     </row>
-    <row r="714" spans="1:5">
+    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A714" s="8">
         <v>45366</v>
       </c>
@@ -18558,7 +18568,7 @@
         <v>1215.8900000000001</v>
       </c>
     </row>
-    <row r="715" spans="1:5">
+    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A715" s="8">
         <v>45373</v>
       </c>
@@ -18573,7 +18583,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="716" spans="1:5">
+    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A716" s="8">
         <v>45380</v>
       </c>
@@ -18588,7 +18598,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="717" spans="1:5">
+    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A717" s="8">
         <v>45387</v>
       </c>
@@ -18603,7 +18613,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="718" spans="1:5">
+    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A718" s="8">
         <v>45394</v>
       </c>
@@ -18618,7 +18628,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="719" spans="1:5">
+    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A719" s="8">
         <v>45401</v>
       </c>
@@ -18636,7 +18646,7 @@
         <v>1230.06</v>
       </c>
     </row>
-    <row r="720" spans="1:5">
+    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A720" s="8">
         <v>45408</v>
       </c>
@@ -18654,7 +18664,7 @@
         <v>1251.68</v>
       </c>
     </row>
-    <row r="721" spans="1:5">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" s="8">
         <v>45415</v>
       </c>
@@ -18669,7 +18679,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="722" spans="1:5">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" s="8">
         <v>45422</v>
       </c>
@@ -18684,7 +18694,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="723" spans="1:5">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" s="8">
         <v>45429</v>
       </c>
@@ -18699,7 +18709,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="724" spans="1:5">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" s="8">
         <v>45436</v>
       </c>
@@ -18714,7 +18724,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="725" spans="1:5">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" s="8">
         <v>45443</v>
       </c>
@@ -18729,7 +18739,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="726" spans="1:5">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" s="8">
         <v>45450</v>
       </c>
@@ -18744,7 +18754,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="727" spans="1:5">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" s="8">
         <v>45457</v>
       </c>
@@ -18759,7 +18769,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="728" spans="1:5">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" s="8">
         <v>45464</v>
       </c>
@@ -18777,7 +18787,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" s="8">
         <v>45471</v>
       </c>
@@ -18795,7 +18805,7 @@
         <v>1712.39</v>
       </c>
     </row>
-    <row r="730" spans="1:5">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A730" s="8">
         <v>45478</v>
       </c>
@@ -18810,7 +18820,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="731" spans="1:5">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A731" s="8">
         <v>45485</v>
       </c>
@@ -18825,7 +18835,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="732" spans="1:5">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A732" s="8">
         <v>45492</v>
       </c>
@@ -18840,7 +18850,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="733" spans="1:5">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A733" s="8">
         <v>45499</v>
       </c>
@@ -18855,7 +18865,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="734" spans="1:5">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A734" s="8">
         <v>45506</v>
       </c>
@@ -18870,7 +18880,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="735" spans="1:5">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A735" s="8">
         <v>45513</v>
       </c>
@@ -18885,7 +18895,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="736" spans="1:5">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A736" s="8">
         <v>45520</v>
       </c>
@@ -18900,7 +18910,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="737" spans="1:5">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A737" s="8">
         <v>45527</v>
       </c>
@@ -18915,7 +18925,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="738" spans="1:5">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A738" s="8">
         <v>45534</v>
       </c>
@@ -18930,7 +18940,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="739" spans="1:5">
+    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A739" s="8">
         <v>45541</v>
       </c>
@@ -18945,7 +18955,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="740" spans="1:5">
+    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A740" s="8">
         <v>45548</v>
       </c>
@@ -18960,7 +18970,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="741" spans="1:5">
+    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A741" s="8">
         <v>45555</v>
       </c>
@@ -18975,7 +18985,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="742" spans="1:5">
+    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A742" s="8">
         <v>45562</v>
       </c>
@@ -18990,7 +19000,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="743" spans="1:5">
+    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A743" s="8">
         <v>45569</v>
       </c>
@@ -19008,7 +19018,7 @@
         <v>1936.04</v>
       </c>
     </row>
-    <row r="744" spans="1:5">
+    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A744" s="8">
         <v>45576</v>
       </c>
@@ -19026,7 +19036,7 @@
         <v>1965.85</v>
       </c>
     </row>
-    <row r="745" spans="1:5">
+    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A745" s="8">
         <v>45583</v>
       </c>
@@ -19044,7 +19054,7 @@
         <v>1967.35</v>
       </c>
     </row>
-    <row r="746" spans="1:5">
+    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A746" s="8">
         <v>45590</v>
       </c>
@@ -19059,7 +19069,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="747" spans="1:5">
+    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A747" s="8">
         <v>45597</v>
       </c>
@@ -19074,7 +19084,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="748" spans="1:5">
+    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A748" s="8">
         <v>45604</v>
       </c>
@@ -19089,7 +19099,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="749" spans="1:5">
+    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A749" s="8">
         <v>45611</v>
       </c>
@@ -19107,7 +19117,7 @@
         <v>1977.78</v>
       </c>
     </row>
-    <row r="750" spans="1:5">
+    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A750" s="8">
         <v>45618</v>
       </c>
@@ -19122,7 +19132,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="751" spans="1:5">
+    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A751" s="8">
         <v>45625</v>
       </c>
@@ -19137,7 +19147,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="752" spans="1:5">
+    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A752" s="8">
         <v>45632</v>
       </c>
@@ -19152,7 +19162,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="753" spans="1:15">
+    <row r="753" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A753" s="8">
         <v>45639</v>
       </c>
@@ -19167,7 +19177,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="754" spans="1:15">
+    <row r="754" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A754" s="8">
         <v>45646</v>
       </c>
@@ -19182,7 +19192,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="755" spans="1:15">
+    <row r="755" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A755" s="8">
         <v>45653</v>
       </c>
@@ -19197,7 +19207,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="756" spans="1:15">
+    <row r="756" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A756" s="8">
         <v>45660</v>
       </c>
@@ -19215,7 +19225,7 @@
         <v>2052.33</v>
       </c>
     </row>
-    <row r="757" spans="1:15">
+    <row r="757" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A757" s="8">
         <v>45667</v>
       </c>
@@ -19230,7 +19240,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="758" spans="1:15">
+    <row r="758" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A758" s="8">
         <v>45674</v>
       </c>
@@ -19245,7 +19255,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="759" spans="1:15">
+    <row r="759" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A759" s="8">
         <v>45681</v>
       </c>
@@ -19260,7 +19270,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="760" spans="1:15">
+    <row r="760" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A760" s="8">
         <v>45688</v>
       </c>
@@ -19278,7 +19288,7 @@
         <v>2052.33</v>
       </c>
     </row>
-    <row r="761" spans="1:15">
+    <row r="761" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A761" s="8">
         <v>45695</v>
       </c>
@@ -19293,7 +19303,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="762" spans="1:15">
+    <row r="762" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A762" s="8">
         <v>45702</v>
       </c>
@@ -19308,7 +19318,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="763" spans="1:15">
+    <row r="763" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A763" s="8">
         <v>45709</v>
       </c>
@@ -19356,7 +19366,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="764" spans="1:15">
+    <row r="764" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A764" s="8">
         <v>45716</v>
       </c>
@@ -19404,7 +19414,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="765" spans="1:15">
+    <row r="765" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A765" s="8">
         <v>45723</v>
       </c>
@@ -19452,7 +19462,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="766" spans="1:15">
+    <row r="766" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A766" s="8">
         <v>45730</v>
       </c>
@@ -19500,7 +19510,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="767" spans="1:15">
+    <row r="767" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A767" s="8">
         <v>45737</v>
       </c>
@@ -19548,7 +19558,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="768" spans="1:15">
+    <row r="768" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A768" s="8">
         <v>45744</v>
       </c>
@@ -19596,7 +19606,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="769" spans="1:15">
+    <row r="769" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A769" s="8">
         <v>45751</v>
       </c>
@@ -19644,7 +19654,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="770" spans="1:15">
+    <row r="770" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A770" s="8">
         <v>45758</v>
       </c>
@@ -19692,7 +19702,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="771" spans="1:15">
+    <row r="771" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A771" s="8">
         <v>45765</v>
       </c>
@@ -19747,7 +19757,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="772" spans="1:15">
+    <row r="772" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A772" s="8">
         <v>45772</v>
       </c>
@@ -19795,7 +19805,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="773" spans="1:15">
+    <row r="773" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A773" s="8">
         <v>45779</v>
       </c>
@@ -19810,7 +19820,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="774" spans="1:15">
+    <row r="774" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A774" s="8">
         <v>45786</v>
       </c>
@@ -19828,7 +19838,7 @@
         <v>2055.31</v>
       </c>
     </row>
-    <row r="775" spans="1:15">
+    <row r="775" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A775" s="8">
         <v>45793</v>
       </c>
@@ -19843,7 +19853,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="776" spans="1:15">
+    <row r="776" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A776" s="8">
         <v>45800</v>
       </c>
@@ -19858,7 +19868,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="777" spans="1:15">
+    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A777" s="8">
         <v>45807</v>
       </c>
@@ -19873,7 +19883,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="778" spans="1:15">
+    <row r="778" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A778" s="8">
         <v>45814</v>
       </c>
@@ -19888,7 +19898,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="779" spans="1:15">
+    <row r="779" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A779" s="8">
         <v>45821</v>
       </c>
@@ -19903,7 +19913,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="780" spans="1:15">
+    <row r="780" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A780" s="8">
         <v>45828</v>
       </c>
@@ -19951,7 +19961,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="781" spans="1:15">
+    <row r="781" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A781" s="8">
         <v>45835</v>
       </c>
@@ -19999,7 +20009,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="782" spans="1:15">
+    <row r="782" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A782" s="8">
         <v>45842</v>
       </c>
@@ -20047,7 +20057,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="783" spans="1:15">
+    <row r="783" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A783" s="8">
         <v>45849</v>
       </c>
@@ -20095,7 +20105,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="784" spans="1:15">
+    <row r="784" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A784" s="8">
         <v>45856</v>
       </c>
@@ -20143,7 +20153,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="785" spans="1:15">
+    <row r="785" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A785" s="8">
         <v>45863</v>
       </c>
@@ -20191,7 +20201,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="786" spans="1:15">
+    <row r="786" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A786" s="8">
         <v>45870</v>
       </c>
@@ -20239,7 +20249,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="787" spans="1:15">
+    <row r="787" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A787" s="8">
         <v>45877</v>
       </c>
@@ -20254,7 +20264,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="788" spans="1:15">
+    <row r="788" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A788" s="8">
         <v>45884</v>
       </c>
@@ -20269,7 +20279,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="789" spans="1:15">
+    <row r="789" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A789" s="8">
         <v>45891</v>
       </c>
@@ -20317,7 +20327,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="790" spans="1:15">
+    <row r="790" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A790" s="8">
         <v>45898</v>
       </c>
@@ -20365,7 +20375,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="791" spans="1:15">
+    <row r="791" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A791" s="8">
         <v>45905</v>
       </c>
@@ -20413,7 +20423,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="792" spans="1:15">
+    <row r="792" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A792" s="8">
         <v>45912</v>
       </c>
@@ -20461,7 +20471,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="793" spans="1:15">
+    <row r="793" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A793" s="8">
         <v>45919</v>
       </c>
@@ -20509,7 +20519,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="794" spans="1:15">
+    <row r="794" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A794" s="8">
         <v>45926</v>
       </c>
@@ -20557,7 +20567,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="795" spans="1:15">
+    <row r="795" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A795" s="8">
         <v>45933</v>
       </c>
@@ -20605,7 +20615,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="796" spans="1:15">
+    <row r="796" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A796" s="8">
         <v>45940</v>
       </c>
@@ -20653,7 +20663,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="797" spans="1:15">
+    <row r="797" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A797" s="8">
         <v>45947</v>
       </c>
@@ -20668,7 +20678,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="798" spans="1:15">
+    <row r="798" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A798" s="8">
         <v>45954</v>
       </c>
@@ -20716,7 +20726,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="799" spans="1:15">
+    <row r="799" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A799" s="8">
         <v>45961</v>
       </c>
@@ -20764,7 +20774,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="800" spans="1:15">
+    <row r="800" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A800" s="8">
         <v>45968</v>
       </c>
@@ -20812,7 +20822,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="801" spans="1:15">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A801" s="8">
         <v>45975</v>
       </c>
@@ -20860,7 +20870,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="802" spans="1:15">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A802" s="8">
         <v>45982</v>
       </c>
@@ -20875,7 +20885,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="803" spans="1:15">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A803" s="8">
         <v>45989</v>
       </c>
@@ -20890,7 +20900,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="804" spans="1:15">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A804" s="8">
         <v>45996</v>
       </c>
@@ -20905,7 +20915,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="805" spans="1:15">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A805" s="8">
         <v>46003</v>
       </c>
@@ -20923,7 +20933,7 @@
         <v>2180.56</v>
       </c>
     </row>
-    <row r="806" spans="1:15">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A806" s="8">
         <v>46010</v>
       </c>
@@ -20971,7 +20981,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="807" spans="1:15">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A807" s="8">
         <v>46017</v>
       </c>
@@ -21019,7 +21029,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="808" spans="1:15">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A808" s="8">
         <v>46024</v>
       </c>
@@ -21067,7 +21077,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A809" s="8">
         <v>46031</v>
       </c>
@@ -21115,7 +21125,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A810" s="8">
         <v>46038</v>
       </c>
@@ -21163,7 +21173,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A811" s="8">
         <v>46045</v>
       </c>
@@ -21211,7 +21221,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A812" s="8">
         <v>46052</v>
       </c>
@@ -21259,7 +21269,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A813" s="8">
         <v>46059</v>
       </c>
@@ -21307,7 +21317,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A814" s="8">
         <v>46066</v>
       </c>
@@ -21355,7 +21365,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A815" s="8">
         <v>46073</v>
       </c>
@@ -21403,7 +21413,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A816" s="8">
         <v>46080</v>
       </c>
@@ -21451,7 +21461,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A817" s="8">
         <v>46087</v>
       </c>
@@ -21499,7 +21509,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A818" s="8">
         <v>46094</v>
       </c>
@@ -21547,7 +21557,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A819" s="8">
         <v>46101</v>
       </c>
@@ -21595,7 +21605,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A820" s="8">
         <v>46108</v>
       </c>
@@ -21643,7 +21653,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A821" s="8">
         <v>46115</v>
       </c>
@@ -21691,7 +21701,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A822" s="8">
         <v>46122</v>
       </c>
@@ -21719,7 +21729,7 @@
       <c r="N822" s="15"/>
       <c r="O822" s="15"/>
     </row>
-    <row r="823" spans="1:15">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A823" s="8">
         <v>46129</v>
       </c>
@@ -21747,7 +21757,7 @@
       <c r="N823" s="15"/>
       <c r="O823" s="15"/>
     </row>
-    <row r="824" spans="1:15">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A824" s="8">
         <v>46136</v>
       </c>
@@ -21775,7 +21785,7 @@
       <c r="N824" s="15"/>
       <c r="O824" s="15"/>
     </row>
-    <row r="825" spans="1:15">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A825" s="8">
         <v>46143</v>
       </c>
@@ -21823,7 +21833,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A826" s="8">
         <v>46150</v>
       </c>
@@ -21871,7 +21881,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A827" s="8">
         <v>46157</v>
       </c>
@@ -21919,7 +21929,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A828" s="8">
         <v>46164</v>
       </c>
@@ -21967,7 +21977,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A829" s="8">
         <v>46171</v>
       </c>
@@ -22015,7 +22025,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A830" s="8">
         <v>46178</v>
       </c>
@@ -22063,7 +22073,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15">
+    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A831" s="8">
         <v>46185</v>
       </c>
@@ -22111,7 +22121,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15">
+    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A832" s="8">
         <v>46192</v>
       </c>
@@ -22159,7 +22169,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="833" spans="1:15">
+    <row r="833" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A833" s="8">
         <v>46199</v>
       </c>
@@ -22207,7 +22217,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="834" spans="1:15">
+    <row r="834" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A834" s="8">
         <v>46206</v>
       </c>
@@ -22262,7 +22272,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="835" spans="1:15">
+    <row r="835" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A835" s="8">
         <v>46213</v>
       </c>
@@ -22310,7 +22320,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="836" spans="1:15">
+    <row r="836" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A836" s="8">
         <v>46220</v>
       </c>
@@ -22358,7 +22368,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="837" spans="1:15">
+    <row r="837" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A837" s="8">
         <v>46227</v>
       </c>
@@ -22413,7 +22423,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="838" spans="1:15">
+    <row r="838" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A838" s="8">
         <v>46234</v>
       </c>
@@ -22470,7 +22480,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22481,25 +22491,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D186BAC-371B-4267-9A9A-D81BAABF00F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A147BC77-CF50-4D93-A22F-0E514CB4E047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -2805,6 +2805,9 @@
                 <c:pt idx="836">
                   <c:v>46234</c:v>
                 </c:pt>
+                <c:pt idx="837">
+                  <c:v>46241</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4823,6 +4826,9 @@
                 </c:pt>
                 <c:pt idx="836">
                   <c:v>2343.0700000000002</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>2346.0500000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5934,7 +5940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P838"/>
+  <dimension ref="A1:P839"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -22379,7 +22385,7 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="D837" s="8" t="str">
-        <f t="shared" ref="D837:D838" si="14">"UTC+"&amp;IF(
+        <f t="shared" ref="D837:D839" si="14">"UTC+"&amp;IF(
     AND(
         B837&gt;=EOMONTH(DATE(YEAR(B837),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B837),3,1),0),2),7),
         B837&lt;EOMONTH(DATE(YEAR(B837),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B837),10,1),0),2),7)
@@ -22468,6 +22474,54 @@
         <v>72000</v>
       </c>
       <c r="O838" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="839" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A839" s="8">
+        <v>46241</v>
+      </c>
+      <c r="B839" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C839" s="9">
+        <v>0.66666666666666496</v>
+      </c>
+      <c r="D839" s="8" t="str">
+        <f t="shared" si="14"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E839" s="10">
+        <v>2346.0500000000002</v>
+      </c>
+      <c r="F839" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G839" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H839" s="14">
+        <v>31500</v>
+      </c>
+      <c r="I839" s="14">
+        <v>35000</v>
+      </c>
+      <c r="J839" s="14">
+        <v>38000</v>
+      </c>
+      <c r="K839" s="14">
+        <v>40000</v>
+      </c>
+      <c r="L839" s="14">
+        <v>46000</v>
+      </c>
+      <c r="M839" s="14">
+        <v>57000</v>
+      </c>
+      <c r="N839" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O839" s="14">
         <v>79000</v>
       </c>
     </row>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A147BC77-CF50-4D93-A22F-0E514CB4E047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A31BD09-2809-4FCE-B8CC-286981D6771B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
@@ -2807,6 +2807,9 @@
                 </c:pt>
                 <c:pt idx="837">
                   <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>46248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5940,7 +5943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P839"/>
+  <dimension ref="A1:P840"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
@@ -22523,6 +22526,28 @@
       </c>
       <c r="O839" s="14">
         <v>79000</v>
+      </c>
+    </row>
+    <row r="840" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A840" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B840" s="8">
+        <v>46248</v>
+      </c>
+      <c r="C840" s="9">
+        <v>0.66666666666667596</v>
+      </c>
+      <c r="D840" s="8" t="str">
+        <f t="shared" ref="D840" si="15">"UTC+"&amp;IF(
+    AND(
+        B840&gt;=EOMONTH(DATE(YEAR(B840),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B840),3,1),0),2),7),
+        B840&lt;EOMONTH(DATE(YEAR(B840),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B840),10,1),0),2),7)
+    ),
+    2,
+    1
+)</f>
+        <v>UTC+2</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A31BD09-2809-4FCE-B8CC-286981D6771B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2EDF21-9692-B94B-9178-FB6CB825DE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -110,12 +110,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,9 +181,9 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -191,43 +191,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -245,7 +245,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4756,7 +4756,7 @@
                   <c:v>2183.54</c:v>
                 </c:pt>
                 <c:pt idx="812">
-                  <c:v>2191</c:v>
+                  <c:v>2190.9899999999998</c:v>
                 </c:pt>
                 <c:pt idx="813">
                   <c:v>2206</c:v>
@@ -4831,6 +4831,9 @@
                   <c:v>2343.0700000000002</c:v>
                 </c:pt>
                 <c:pt idx="837">
+                  <c:v>2346.0500000000002</c:v>
+                </c:pt>
+                <c:pt idx="838">
                   <c:v>2346.0500000000002</c:v>
                 </c:pt>
               </c:numCache>
@@ -5647,9 +5650,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5687,7 +5690,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5793,7 +5796,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5935,7 +5938,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5944,18 +5947,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
   <dimension ref="A1:P840"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="15" width="14" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.77734375" style="11"/>
+    <col min="16" max="16384" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="7" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6003,7 +6006,7 @@
       </c>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16">
       <c r="A2" s="8">
         <v>40383</v>
       </c>
@@ -6028,7 +6031,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16">
       <c r="A3" s="8">
         <v>40390</v>
       </c>
@@ -6053,7 +6056,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16">
       <c r="A4" s="8">
         <v>40397</v>
       </c>
@@ -6071,7 +6074,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="A5" s="8">
         <v>40404</v>
       </c>
@@ -6089,7 +6092,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16">
       <c r="A6" s="8">
         <v>40411</v>
       </c>
@@ -6107,7 +6110,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16">
       <c r="A7" s="8">
         <v>40418</v>
       </c>
@@ -6125,7 +6128,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16">
       <c r="A8" s="8">
         <v>40425</v>
       </c>
@@ -6143,7 +6146,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16">
       <c r="A9" s="8">
         <v>40432</v>
       </c>
@@ -6161,7 +6164,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16">
       <c r="A10" s="8">
         <v>40439</v>
       </c>
@@ -6179,7 +6182,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16">
       <c r="A11" s="8">
         <v>40446</v>
       </c>
@@ -6197,7 +6200,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16">
       <c r="A12" s="8">
         <v>40453</v>
       </c>
@@ -6215,7 +6218,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16">
       <c r="A13" s="8">
         <v>40460</v>
       </c>
@@ -6233,7 +6236,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16">
       <c r="A14" s="8">
         <v>40467</v>
       </c>
@@ -6251,7 +6254,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16">
       <c r="A15" s="8">
         <v>40474</v>
       </c>
@@ -6269,7 +6272,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16">
       <c r="A16" s="8">
         <v>40481</v>
       </c>
@@ -6287,7 +6290,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="8">
         <v>40488</v>
       </c>
@@ -6305,7 +6308,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="8">
         <v>40495</v>
       </c>
@@ -6323,7 +6326,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="8">
         <v>40502</v>
       </c>
@@ -6341,7 +6344,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="8">
         <v>40509</v>
       </c>
@@ -6359,7 +6362,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="8">
         <v>40516</v>
       </c>
@@ -6377,7 +6380,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="8">
         <v>40523</v>
       </c>
@@ -6395,7 +6398,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="8">
         <v>40530</v>
       </c>
@@ -6413,7 +6416,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="8">
         <v>40537</v>
       </c>
@@ -6431,7 +6434,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="8">
         <v>40544</v>
       </c>
@@ -6449,7 +6452,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="8">
         <v>40551</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="8">
         <v>40558</v>
       </c>
@@ -6485,7 +6488,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="8">
         <v>40565</v>
       </c>
@@ -6503,7 +6506,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="8">
         <v>40572</v>
       </c>
@@ -6521,7 +6524,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="8">
         <v>40579</v>
       </c>
@@ -6539,7 +6542,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="8">
         <v>40586</v>
       </c>
@@ -6557,7 +6560,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="8">
         <v>40593</v>
       </c>
@@ -6575,7 +6578,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="8">
         <v>40600</v>
       </c>
@@ -6593,7 +6596,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="8">
         <v>40607</v>
       </c>
@@ -6611,7 +6614,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="8">
         <v>40614</v>
       </c>
@@ -6629,7 +6632,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="8">
         <v>40621</v>
       </c>
@@ -6647,7 +6650,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="8">
         <v>40628</v>
       </c>
@@ -6665,7 +6668,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="8">
         <v>40635</v>
       </c>
@@ -6683,7 +6686,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="8">
         <v>40642</v>
       </c>
@@ -6701,7 +6704,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="8">
         <v>40649</v>
       </c>
@@ -6719,7 +6722,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="8">
         <v>40656</v>
       </c>
@@ -6737,7 +6740,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="8">
         <v>40663</v>
       </c>
@@ -6755,7 +6758,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="8">
         <v>40670</v>
       </c>
@@ -6773,7 +6776,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="8">
         <v>40677</v>
       </c>
@@ -6791,7 +6794,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="8">
         <v>40684</v>
       </c>
@@ -6809,7 +6812,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" s="8">
         <v>40691</v>
       </c>
@@ -6827,7 +6830,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" s="8">
         <v>40698</v>
       </c>
@@ -6845,7 +6848,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48" s="8">
         <v>40705</v>
       </c>
@@ -6863,7 +6866,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" s="8">
         <v>40712</v>
       </c>
@@ -6881,7 +6884,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" s="8">
         <v>40719</v>
       </c>
@@ -6899,7 +6902,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" s="8">
         <v>40726</v>
       </c>
@@ -6917,7 +6920,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" s="8">
         <v>40733</v>
       </c>
@@ -6935,7 +6938,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53" s="8">
         <v>40740</v>
       </c>
@@ -6953,7 +6956,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" s="8">
         <v>40747</v>
       </c>
@@ -6971,7 +6974,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55" s="8">
         <v>40754</v>
       </c>
@@ -6989,7 +6992,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56" s="8">
         <v>40761</v>
       </c>
@@ -7007,7 +7010,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57" s="8">
         <v>40768</v>
       </c>
@@ -7025,7 +7028,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58" s="8">
         <v>40775</v>
       </c>
@@ -7043,7 +7046,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59" s="8">
         <v>40782</v>
       </c>
@@ -7061,7 +7064,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" s="8">
         <v>40789</v>
       </c>
@@ -7079,7 +7082,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61" s="8">
         <v>40796</v>
       </c>
@@ -7097,7 +7100,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62" s="8">
         <v>40803</v>
       </c>
@@ -7115,7 +7118,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63" s="8">
         <v>40810</v>
       </c>
@@ -7133,7 +7136,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64" s="8">
         <v>40817</v>
       </c>
@@ -7151,7 +7154,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65" s="8">
         <v>40824</v>
       </c>
@@ -7169,7 +7172,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5">
       <c r="A66" s="8">
         <v>40831</v>
       </c>
@@ -7187,7 +7190,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67" s="8">
         <v>40838</v>
       </c>
@@ -7212,7 +7215,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68" s="8">
         <v>40845</v>
       </c>
@@ -7230,7 +7233,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5">
       <c r="A69" s="8">
         <v>40852</v>
       </c>
@@ -7248,7 +7251,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70" s="8">
         <v>40859</v>
       </c>
@@ -7266,7 +7269,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71" s="8">
         <v>40866</v>
       </c>
@@ -7284,7 +7287,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72" s="8">
         <v>40873</v>
       </c>
@@ -7302,7 +7305,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73" s="8">
         <v>40880</v>
       </c>
@@ -7320,7 +7323,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5">
       <c r="A74" s="8">
         <v>40887</v>
       </c>
@@ -7338,7 +7341,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75" s="8">
         <v>40894</v>
       </c>
@@ -7356,7 +7359,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5">
       <c r="A76" s="8">
         <v>40901</v>
       </c>
@@ -7374,7 +7377,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5">
       <c r="A77" s="8">
         <v>40908</v>
       </c>
@@ -7392,7 +7395,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5">
       <c r="A78" s="8">
         <v>40915</v>
       </c>
@@ -7410,7 +7413,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5">
       <c r="A79" s="8">
         <v>40922</v>
       </c>
@@ -7428,7 +7431,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5">
       <c r="A80" s="8">
         <v>40929</v>
       </c>
@@ -7446,7 +7449,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5">
       <c r="A81" s="8">
         <v>40936</v>
       </c>
@@ -7464,7 +7467,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5">
       <c r="A82" s="8">
         <v>40942</v>
       </c>
@@ -7482,7 +7485,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5">
       <c r="A83" s="8">
         <v>40943</v>
       </c>
@@ -7500,7 +7503,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5">
       <c r="A84" s="8">
         <v>40950</v>
       </c>
@@ -7518,7 +7521,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5">
       <c r="A85" s="8">
         <v>40957</v>
       </c>
@@ -7536,7 +7539,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5">
       <c r="A86" s="8">
         <v>40964</v>
       </c>
@@ -7554,7 +7557,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5">
       <c r="A87" s="8">
         <v>40978</v>
       </c>
@@ -7572,7 +7575,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5">
       <c r="A88" s="8">
         <v>40985</v>
       </c>
@@ -7590,7 +7593,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5">
       <c r="A89" s="8">
         <v>40992</v>
       </c>
@@ -7608,7 +7611,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5">
       <c r="A90" s="8">
         <v>40999</v>
       </c>
@@ -7626,7 +7629,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5">
       <c r="A91" s="8">
         <v>41006</v>
       </c>
@@ -7644,7 +7647,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5">
       <c r="A92" s="8">
         <v>41013</v>
       </c>
@@ -7662,7 +7665,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5">
       <c r="A93" s="8">
         <v>41020</v>
       </c>
@@ -7680,7 +7683,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5">
       <c r="A94" s="8">
         <v>41027</v>
       </c>
@@ -7698,7 +7701,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5">
       <c r="A95" s="8">
         <v>41034</v>
       </c>
@@ -7716,7 +7719,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5">
       <c r="A96" s="8">
         <v>41041</v>
       </c>
@@ -7734,7 +7737,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5">
       <c r="A97" s="8">
         <v>41048</v>
       </c>
@@ -7752,7 +7755,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98" s="8">
         <v>41055</v>
       </c>
@@ -7770,7 +7773,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5">
       <c r="A99" s="8">
         <v>41062</v>
       </c>
@@ -7788,7 +7791,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5">
       <c r="A100" s="8">
         <v>41069</v>
       </c>
@@ -7806,7 +7809,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5">
       <c r="A101" s="8">
         <v>41076</v>
       </c>
@@ -7824,7 +7827,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5">
       <c r="A102" s="8">
         <v>41083</v>
       </c>
@@ -7842,7 +7845,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5">
       <c r="A103" s="8">
         <v>41090</v>
       </c>
@@ -7860,7 +7863,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5">
       <c r="A104" s="8">
         <v>41097</v>
       </c>
@@ -7878,7 +7881,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105" s="8">
         <v>41104</v>
       </c>
@@ -7896,7 +7899,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106" s="8">
         <v>41111</v>
       </c>
@@ -7914,7 +7917,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107" s="8">
         <v>41118</v>
       </c>
@@ -7932,7 +7935,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108" s="8">
         <v>41125</v>
       </c>
@@ -7950,7 +7953,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5">
       <c r="A109" s="8">
         <v>41132</v>
       </c>
@@ -7968,7 +7971,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110" s="8">
         <v>41139</v>
       </c>
@@ -7986,7 +7989,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5">
       <c r="A111" s="8">
         <v>41146</v>
       </c>
@@ -8004,7 +8007,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5">
       <c r="A112" s="8">
         <v>41153</v>
       </c>
@@ -8022,7 +8025,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5">
       <c r="A113" s="8">
         <v>41160</v>
       </c>
@@ -8040,7 +8043,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5">
       <c r="A114" s="8">
         <v>41167</v>
       </c>
@@ -8058,7 +8061,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5">
       <c r="A115" s="8">
         <v>41174</v>
       </c>
@@ -8076,7 +8079,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5">
       <c r="A116" s="8">
         <v>41181</v>
       </c>
@@ -8094,7 +8097,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5">
       <c r="A117" s="8">
         <v>41188</v>
       </c>
@@ -8112,7 +8115,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5">
       <c r="A118" s="8">
         <v>41195</v>
       </c>
@@ -8130,7 +8133,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5">
       <c r="A119" s="8">
         <v>41202</v>
       </c>
@@ -8148,7 +8151,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5">
       <c r="A120" s="8">
         <v>41209</v>
       </c>
@@ -8166,7 +8169,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5">
       <c r="A121" s="8">
         <v>41216</v>
       </c>
@@ -8184,7 +8187,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5">
       <c r="A122" s="8">
         <v>41223</v>
       </c>
@@ -8202,7 +8205,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5">
       <c r="A123" s="8">
         <v>41230</v>
       </c>
@@ -8220,7 +8223,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5">
       <c r="A124" s="8">
         <v>41237</v>
       </c>
@@ -8238,7 +8241,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5">
       <c r="A125" s="8">
         <v>41244</v>
       </c>
@@ -8256,7 +8259,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5">
       <c r="A126" s="8">
         <v>41251</v>
       </c>
@@ -8274,7 +8277,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5">
       <c r="A127" s="8">
         <v>41258</v>
       </c>
@@ -8292,7 +8295,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5">
       <c r="A128" s="8">
         <v>41265</v>
       </c>
@@ -8310,7 +8313,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5">
       <c r="A129" s="8">
         <v>41272</v>
       </c>
@@ -8328,7 +8331,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5">
       <c r="A130" s="8">
         <v>41279</v>
       </c>
@@ -8346,7 +8349,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5">
       <c r="A131" s="8">
         <v>41286</v>
       </c>
@@ -8371,7 +8374,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5">
       <c r="A132" s="8">
         <v>41293</v>
       </c>
@@ -8389,7 +8392,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5">
       <c r="A133" s="8">
         <v>41300</v>
       </c>
@@ -8407,7 +8410,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5">
       <c r="A134" s="8">
         <v>41307</v>
       </c>
@@ -8425,7 +8428,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5">
       <c r="A135" s="8">
         <v>41314</v>
       </c>
@@ -8443,7 +8446,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5">
       <c r="A136" s="8">
         <v>41321</v>
       </c>
@@ -8461,7 +8464,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5">
       <c r="A137" s="8">
         <v>41328</v>
       </c>
@@ -8479,7 +8482,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5">
       <c r="A138" s="8">
         <v>41335</v>
       </c>
@@ -8497,7 +8500,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5">
       <c r="A139" s="8">
         <v>41342</v>
       </c>
@@ -8515,7 +8518,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5">
       <c r="A140" s="8">
         <v>41349</v>
       </c>
@@ -8533,7 +8536,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5">
       <c r="A141" s="8">
         <v>41356</v>
       </c>
@@ -8551,7 +8554,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5">
       <c r="A142" s="8">
         <v>41363</v>
       </c>
@@ -8569,7 +8572,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5">
       <c r="A143" s="8">
         <v>41370</v>
       </c>
@@ -8587,7 +8590,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5">
       <c r="A144" s="8">
         <v>41377</v>
       </c>
@@ -8605,7 +8608,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5">
       <c r="A145" s="8">
         <v>41384</v>
       </c>
@@ -8623,7 +8626,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5">
       <c r="A146" s="8">
         <v>41391</v>
       </c>
@@ -8641,7 +8644,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5">
       <c r="A147" s="8">
         <v>41398</v>
       </c>
@@ -8659,7 +8662,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5">
       <c r="A148" s="8">
         <v>41405</v>
       </c>
@@ -8677,7 +8680,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5">
       <c r="A149" s="8">
         <v>41412</v>
       </c>
@@ -8695,7 +8698,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5">
       <c r="A150" s="8">
         <v>41419</v>
       </c>
@@ -8713,7 +8716,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5">
       <c r="A151" s="8">
         <v>41426</v>
       </c>
@@ -8731,7 +8734,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5">
       <c r="A152" s="8">
         <v>41433</v>
       </c>
@@ -8749,7 +8752,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5">
       <c r="A153" s="8">
         <v>41440</v>
       </c>
@@ -8767,7 +8770,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5">
       <c r="A154" s="8">
         <v>41447</v>
       </c>
@@ -8785,7 +8788,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5">
       <c r="A155" s="8">
         <v>41454</v>
       </c>
@@ -8803,7 +8806,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5">
       <c r="A156" s="8">
         <v>41461</v>
       </c>
@@ -8821,7 +8824,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5">
       <c r="A157" s="8">
         <v>41468</v>
       </c>
@@ -8839,7 +8842,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5">
       <c r="A158" s="8">
         <v>41475</v>
       </c>
@@ -8857,7 +8860,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5">
       <c r="A159" s="8">
         <v>41482</v>
       </c>
@@ -8875,7 +8878,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5">
       <c r="A160" s="8">
         <v>41489</v>
       </c>
@@ -8893,7 +8896,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5">
       <c r="A161" s="8">
         <v>41496</v>
       </c>
@@ -8911,7 +8914,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5">
       <c r="A162" s="8">
         <v>41503</v>
       </c>
@@ -8929,7 +8932,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5">
       <c r="A163" s="8">
         <v>41510</v>
       </c>
@@ -8947,7 +8950,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5">
       <c r="A164" s="8">
         <v>41517</v>
       </c>
@@ -8965,7 +8968,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5">
       <c r="A165" s="8">
         <v>41524</v>
       </c>
@@ -8983,7 +8986,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5">
       <c r="A166" s="8">
         <v>41531</v>
       </c>
@@ -9001,7 +9004,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5">
       <c r="A167" s="8">
         <v>41538</v>
       </c>
@@ -9019,7 +9022,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5">
       <c r="A168" s="8">
         <v>41545</v>
       </c>
@@ -9037,7 +9040,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5">
       <c r="A169" s="8">
         <v>41552</v>
       </c>
@@ -9055,7 +9058,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5">
       <c r="A170" s="8">
         <v>41559</v>
       </c>
@@ -9073,7 +9076,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5">
       <c r="A171" s="8">
         <v>41566</v>
       </c>
@@ -9091,7 +9094,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5">
       <c r="A172" s="8">
         <v>41573</v>
       </c>
@@ -9109,7 +9112,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5">
       <c r="A173" s="8">
         <v>41580</v>
       </c>
@@ -9127,7 +9130,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5">
       <c r="A174" s="8">
         <v>41587</v>
       </c>
@@ -9145,7 +9148,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5">
       <c r="A175" s="8">
         <v>41594</v>
       </c>
@@ -9163,7 +9166,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5">
       <c r="A176" s="8">
         <v>41601</v>
       </c>
@@ -9181,7 +9184,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5">
       <c r="A177" s="8">
         <v>41608</v>
       </c>
@@ -9199,7 +9202,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5">
       <c r="A178" s="8">
         <v>41615</v>
       </c>
@@ -9217,7 +9220,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5">
       <c r="A179" s="8">
         <v>41622</v>
       </c>
@@ -9235,7 +9238,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5">
       <c r="A180" s="8">
         <v>41629</v>
       </c>
@@ -9253,7 +9256,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5">
       <c r="A181" s="8">
         <v>41636</v>
       </c>
@@ -9271,7 +9274,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5">
       <c r="A182" s="8">
         <v>41643</v>
       </c>
@@ -9289,7 +9292,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5">
       <c r="A183" s="8">
         <v>41650</v>
       </c>
@@ -9307,7 +9310,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5">
       <c r="A184" s="8">
         <v>41657</v>
       </c>
@@ -9325,7 +9328,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5">
       <c r="A185" s="8">
         <v>41664</v>
       </c>
@@ -9343,7 +9346,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5">
       <c r="A186" s="8">
         <v>41671</v>
       </c>
@@ -9361,7 +9364,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5">
       <c r="A187" s="8">
         <v>41678</v>
       </c>
@@ -9379,7 +9382,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5">
       <c r="A188" s="8">
         <v>41685</v>
       </c>
@@ -9397,7 +9400,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5">
       <c r="A189" s="8">
         <v>41692</v>
       </c>
@@ -9415,7 +9418,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5">
       <c r="A190" s="8">
         <v>41699</v>
       </c>
@@ -9433,7 +9436,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5">
       <c r="A191" s="8">
         <v>41706</v>
       </c>
@@ -9451,7 +9454,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5">
       <c r="A192" s="8">
         <v>41713</v>
       </c>
@@ -9469,7 +9472,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5">
       <c r="A193" s="8">
         <v>41720</v>
       </c>
@@ -9487,7 +9490,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5">
       <c r="A194" s="8">
         <v>41727</v>
       </c>
@@ -9505,7 +9508,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5">
       <c r="A195" s="8">
         <v>41734</v>
       </c>
@@ -9530,7 +9533,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5">
       <c r="A196" s="8">
         <v>41741</v>
       </c>
@@ -9548,7 +9551,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5">
       <c r="A197" s="8">
         <v>41748</v>
       </c>
@@ -9566,7 +9569,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5">
       <c r="A198" s="8">
         <v>41755</v>
       </c>
@@ -9584,7 +9587,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5">
       <c r="A199" s="8">
         <v>41762</v>
       </c>
@@ -9602,7 +9605,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5">
       <c r="A200" s="8">
         <v>41769</v>
       </c>
@@ -9620,7 +9623,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5">
       <c r="A201" s="8">
         <v>41776</v>
       </c>
@@ -9638,7 +9641,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5">
       <c r="A202" s="8">
         <v>41783</v>
       </c>
@@ -9656,7 +9659,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5">
       <c r="A203" s="8">
         <v>41790</v>
       </c>
@@ -9674,7 +9677,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5">
       <c r="A204" s="8">
         <v>41797</v>
       </c>
@@ -9692,7 +9695,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5">
       <c r="A205" s="8">
         <v>41804</v>
       </c>
@@ -9710,7 +9713,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5">
       <c r="A206" s="8">
         <v>41811</v>
       </c>
@@ -9728,7 +9731,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5">
       <c r="A207" s="8">
         <v>41818</v>
       </c>
@@ -9746,7 +9749,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5">
       <c r="A208" s="8">
         <v>41825</v>
       </c>
@@ -9764,7 +9767,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5">
       <c r="A209" s="8">
         <v>41832</v>
       </c>
@@ -9782,7 +9785,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5">
       <c r="A210" s="8">
         <v>41839</v>
       </c>
@@ -9800,7 +9803,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5">
       <c r="A211" s="8">
         <v>41846</v>
       </c>
@@ -9818,7 +9821,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5">
       <c r="A212" s="8">
         <v>41853</v>
       </c>
@@ -9836,7 +9839,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5">
       <c r="A213" s="8">
         <v>41860</v>
       </c>
@@ -9854,7 +9857,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5">
       <c r="A214" s="8">
         <v>41867</v>
       </c>
@@ -9872,7 +9875,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5">
       <c r="A215" s="8">
         <v>41874</v>
       </c>
@@ -9890,7 +9893,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5">
       <c r="A216" s="8">
         <v>41881</v>
       </c>
@@ -9908,7 +9911,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5">
       <c r="A217" s="8">
         <v>41888</v>
       </c>
@@ -9926,7 +9929,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5">
       <c r="A218" s="8">
         <v>41895</v>
       </c>
@@ -9944,7 +9947,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5">
       <c r="A219" s="8">
         <v>41902</v>
       </c>
@@ -9962,7 +9965,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5">
       <c r="A220" s="8">
         <v>41909</v>
       </c>
@@ -9980,7 +9983,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5">
       <c r="A221" s="8">
         <v>41916</v>
       </c>
@@ -9998,7 +10001,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5">
       <c r="A222" s="8">
         <v>41923</v>
       </c>
@@ -10016,7 +10019,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5">
       <c r="A223" s="8">
         <v>41930</v>
       </c>
@@ -10034,7 +10037,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5">
       <c r="A224" s="8">
         <v>41937</v>
       </c>
@@ -10052,7 +10055,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5">
       <c r="A225" s="8">
         <v>41944</v>
       </c>
@@ -10070,7 +10073,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5">
       <c r="A226" s="8">
         <v>41951</v>
       </c>
@@ -10088,7 +10091,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5">
       <c r="A227" s="8">
         <v>41958</v>
       </c>
@@ -10106,7 +10109,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5">
       <c r="A228" s="8">
         <v>41965</v>
       </c>
@@ -10124,7 +10127,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5">
       <c r="A229" s="8">
         <v>41972</v>
       </c>
@@ -10142,7 +10145,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5">
       <c r="A230" s="8">
         <v>41979</v>
       </c>
@@ -10160,7 +10163,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5">
       <c r="A231" s="8">
         <v>41986</v>
       </c>
@@ -10178,7 +10181,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5">
       <c r="A232" s="8">
         <v>41993</v>
       </c>
@@ -10196,7 +10199,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5">
       <c r="A233" s="8">
         <v>42000</v>
       </c>
@@ -10214,7 +10217,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5">
       <c r="A234" s="8">
         <v>42007</v>
       </c>
@@ -10232,7 +10235,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5">
       <c r="A235" s="8">
         <v>42014</v>
       </c>
@@ -10250,7 +10253,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5">
       <c r="A236" s="8">
         <v>42021</v>
       </c>
@@ -10268,7 +10271,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5">
       <c r="A237" s="8">
         <v>42028</v>
       </c>
@@ -10286,7 +10289,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5">
       <c r="A238" s="8">
         <v>42035</v>
       </c>
@@ -10304,7 +10307,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5">
       <c r="A239" s="8">
         <v>42042</v>
       </c>
@@ -10322,7 +10325,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5">
       <c r="A240" s="8">
         <v>42049</v>
       </c>
@@ -10340,7 +10343,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5">
       <c r="A241" s="8">
         <v>42056</v>
       </c>
@@ -10358,7 +10361,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5">
       <c r="A242" s="8">
         <v>42063</v>
       </c>
@@ -10376,7 +10379,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5">
       <c r="A243" s="8">
         <v>42070</v>
       </c>
@@ -10394,7 +10397,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5">
       <c r="A244" s="8">
         <v>42077</v>
       </c>
@@ -10412,7 +10415,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5">
       <c r="A245" s="8">
         <v>42084</v>
       </c>
@@ -10430,7 +10433,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5">
       <c r="A246" s="8">
         <v>42091</v>
       </c>
@@ -10448,7 +10451,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5">
       <c r="A247" s="8">
         <v>42098</v>
       </c>
@@ -10466,7 +10469,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5">
       <c r="A248" s="8">
         <v>42105</v>
       </c>
@@ -10484,7 +10487,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5">
       <c r="A249" s="8">
         <v>42112</v>
       </c>
@@ -10502,7 +10505,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5">
       <c r="A250" s="8">
         <v>42119</v>
       </c>
@@ -10520,7 +10523,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5">
       <c r="A251" s="8">
         <v>42126</v>
       </c>
@@ -10538,7 +10541,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5">
       <c r="A252" s="8">
         <v>42133</v>
       </c>
@@ -10556,7 +10559,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5">
       <c r="A253" s="8">
         <v>42140</v>
       </c>
@@ -10574,7 +10577,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5">
       <c r="A254" s="8">
         <v>42147</v>
       </c>
@@ -10592,7 +10595,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5">
       <c r="A255" s="8">
         <v>42154</v>
       </c>
@@ -10610,7 +10613,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5">
       <c r="A256" s="8">
         <v>42161</v>
       </c>
@@ -10628,7 +10631,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5">
       <c r="A257" s="8">
         <v>42168</v>
       </c>
@@ -10646,7 +10649,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5">
       <c r="A258" s="8">
         <v>42175</v>
       </c>
@@ -10664,7 +10667,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5">
       <c r="A259" s="8">
         <v>42182</v>
       </c>
@@ -10689,7 +10692,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5">
       <c r="A260" s="8">
         <v>42189</v>
       </c>
@@ -10707,7 +10710,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5">
       <c r="A261" s="8">
         <v>42196</v>
       </c>
@@ -10725,7 +10728,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5">
       <c r="A262" s="8">
         <v>42203</v>
       </c>
@@ -10743,7 +10746,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5">
       <c r="A263" s="8">
         <v>42210</v>
       </c>
@@ -10761,7 +10764,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5">
       <c r="A264" s="8">
         <v>42217</v>
       </c>
@@ -10779,7 +10782,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5">
       <c r="A265" s="8">
         <v>42224</v>
       </c>
@@ -10797,7 +10800,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5">
       <c r="A266" s="8">
         <v>42231</v>
       </c>
@@ -10815,7 +10818,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5">
       <c r="A267" s="8">
         <v>42238</v>
       </c>
@@ -10833,7 +10836,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5">
       <c r="A268" s="8">
         <v>42245</v>
       </c>
@@ -10851,7 +10854,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5">
       <c r="A269" s="8">
         <v>42252</v>
       </c>
@@ -10869,7 +10872,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5">
       <c r="A270" s="8">
         <v>42259</v>
       </c>
@@ -10887,7 +10890,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5">
       <c r="A271" s="8">
         <v>42266</v>
       </c>
@@ -10905,7 +10908,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5">
       <c r="A272" s="8">
         <v>42273</v>
       </c>
@@ -10923,7 +10926,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5">
       <c r="A273" s="8">
         <v>42280</v>
       </c>
@@ -10941,7 +10944,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5">
       <c r="A274" s="8">
         <v>42287</v>
       </c>
@@ -10959,7 +10962,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5">
       <c r="A275" s="8">
         <v>42294</v>
       </c>
@@ -10977,7 +10980,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5">
       <c r="A276" s="8">
         <v>42301</v>
       </c>
@@ -10995,7 +10998,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5">
       <c r="A277" s="8">
         <v>42308</v>
       </c>
@@ -11013,7 +11016,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5">
       <c r="A278" s="8">
         <v>42315</v>
       </c>
@@ -11031,7 +11034,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5">
       <c r="A279" s="8">
         <v>42322</v>
       </c>
@@ -11049,7 +11052,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5">
       <c r="A280" s="8">
         <v>42329</v>
       </c>
@@ -11067,7 +11070,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5">
       <c r="A281" s="8">
         <v>42336</v>
       </c>
@@ -11085,7 +11088,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5">
       <c r="A282" s="8">
         <v>42343</v>
       </c>
@@ -11103,7 +11106,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5">
       <c r="A283" s="8">
         <v>42350</v>
       </c>
@@ -11121,7 +11124,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5">
       <c r="A284" s="8">
         <v>42357</v>
       </c>
@@ -11139,7 +11142,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5">
       <c r="A285" s="8">
         <v>42364</v>
       </c>
@@ -11157,7 +11160,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5">
       <c r="A286" s="8">
         <v>42371</v>
       </c>
@@ -11175,7 +11178,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5">
       <c r="A287" s="8">
         <v>42378</v>
       </c>
@@ -11193,7 +11196,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5">
       <c r="A288" s="8">
         <v>42385</v>
       </c>
@@ -11211,7 +11214,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5">
       <c r="A289" s="8">
         <v>42392</v>
       </c>
@@ -11229,7 +11232,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5">
       <c r="A290" s="8">
         <v>42399</v>
       </c>
@@ -11247,7 +11250,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5">
       <c r="A291" s="8">
         <v>42406</v>
       </c>
@@ -11265,7 +11268,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5">
       <c r="A292" s="8">
         <v>42413</v>
       </c>
@@ -11283,7 +11286,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5">
       <c r="A293" s="8">
         <v>42420</v>
       </c>
@@ -11301,7 +11304,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5">
       <c r="A294" s="8">
         <v>42427</v>
       </c>
@@ -11319,7 +11322,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5">
       <c r="A295" s="8">
         <v>42434</v>
       </c>
@@ -11337,7 +11340,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5">
       <c r="A296" s="8">
         <v>42441</v>
       </c>
@@ -11355,7 +11358,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5">
       <c r="A297" s="8">
         <v>42448</v>
       </c>
@@ -11373,7 +11376,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5">
       <c r="A298" s="8">
         <v>42455</v>
       </c>
@@ -11391,7 +11394,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5">
       <c r="A299" s="8">
         <v>42462</v>
       </c>
@@ -11409,7 +11412,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5">
       <c r="A300" s="8">
         <v>42469</v>
       </c>
@@ -11427,7 +11430,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5">
       <c r="A301" s="8">
         <v>42476</v>
       </c>
@@ -11445,7 +11448,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5">
       <c r="A302" s="8">
         <v>42483</v>
       </c>
@@ -11463,7 +11466,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5">
       <c r="A303" s="8">
         <v>42490</v>
       </c>
@@ -11481,7 +11484,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5">
       <c r="A304" s="8">
         <v>42497</v>
       </c>
@@ -11499,7 +11502,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5">
       <c r="A305" s="8">
         <v>42504</v>
       </c>
@@ -11517,7 +11520,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5">
       <c r="A306" s="8">
         <v>42511</v>
       </c>
@@ -11535,7 +11538,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5">
       <c r="A307" s="8">
         <v>42518</v>
       </c>
@@ -11553,7 +11556,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5">
       <c r="A308" s="8">
         <v>42525</v>
       </c>
@@ -11571,7 +11574,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5">
       <c r="A309" s="8">
         <v>42532</v>
       </c>
@@ -11589,7 +11592,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5">
       <c r="A310" s="8">
         <v>42539</v>
       </c>
@@ -11607,7 +11610,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5">
       <c r="A311" s="8">
         <v>42546</v>
       </c>
@@ -11625,7 +11628,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5">
       <c r="A312" s="8">
         <v>42553</v>
       </c>
@@ -11643,7 +11646,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5">
       <c r="A313" s="8">
         <v>42560</v>
       </c>
@@ -11661,7 +11664,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5">
       <c r="A314" s="8">
         <v>42567</v>
       </c>
@@ -11679,7 +11682,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5">
       <c r="A315" s="8">
         <v>42574</v>
       </c>
@@ -11697,7 +11700,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5">
       <c r="A316" s="8">
         <v>42581</v>
       </c>
@@ -11715,7 +11718,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5">
       <c r="A317" s="8">
         <v>42588</v>
       </c>
@@ -11733,7 +11736,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5">
       <c r="A318" s="8">
         <v>42595</v>
       </c>
@@ -11751,7 +11754,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5">
       <c r="A319" s="8">
         <v>42602</v>
       </c>
@@ -11769,7 +11772,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5">
       <c r="A320" s="8">
         <v>42609</v>
       </c>
@@ -11787,7 +11790,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5">
       <c r="A321" s="8">
         <v>42616</v>
       </c>
@@ -11805,7 +11808,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5">
       <c r="A322" s="8">
         <v>42623</v>
       </c>
@@ -11823,7 +11826,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5">
       <c r="A323" s="8">
         <v>42630</v>
       </c>
@@ -11848,7 +11851,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5">
       <c r="A324" s="8">
         <v>42637</v>
       </c>
@@ -11866,7 +11869,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5">
       <c r="A325" s="8">
         <v>42644</v>
       </c>
@@ -11884,7 +11887,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5">
       <c r="A326" s="8">
         <v>42651</v>
       </c>
@@ -11902,7 +11905,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5">
       <c r="A327" s="8">
         <v>42658</v>
       </c>
@@ -11920,7 +11923,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5">
       <c r="A328" s="8">
         <v>42665</v>
       </c>
@@ -11938,7 +11941,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5">
       <c r="A329" s="8">
         <v>42672</v>
       </c>
@@ -11956,7 +11959,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5">
       <c r="A330" s="8">
         <v>42679</v>
       </c>
@@ -11974,7 +11977,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5">
       <c r="A331" s="8">
         <v>42686</v>
       </c>
@@ -11992,7 +11995,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5">
       <c r="A332" s="8">
         <v>42693</v>
       </c>
@@ -12010,7 +12013,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5">
       <c r="A333" s="8">
         <v>42700</v>
       </c>
@@ -12028,7 +12031,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5">
       <c r="A334" s="8">
         <v>42707</v>
       </c>
@@ -12046,7 +12049,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5">
       <c r="A335" s="8">
         <v>42714</v>
       </c>
@@ -12064,7 +12067,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5">
       <c r="A336" s="8">
         <v>42721</v>
       </c>
@@ -12082,7 +12085,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5">
       <c r="A337" s="8">
         <v>42728</v>
       </c>
@@ -12100,7 +12103,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5">
       <c r="A338" s="8">
         <v>42735</v>
       </c>
@@ -12118,7 +12121,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5">
       <c r="A339" s="8">
         <v>42742</v>
       </c>
@@ -12136,7 +12139,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5">
       <c r="A340" s="8">
         <v>42749</v>
       </c>
@@ -12154,7 +12157,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5">
       <c r="A341" s="8">
         <v>42756</v>
       </c>
@@ -12172,7 +12175,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5">
       <c r="A342" s="8">
         <v>42763</v>
       </c>
@@ -12190,7 +12193,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5">
       <c r="A343" s="8">
         <v>42770</v>
       </c>
@@ -12208,7 +12211,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5">
       <c r="A344" s="8">
         <v>42777</v>
       </c>
@@ -12226,7 +12229,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5">
       <c r="A345" s="8">
         <v>42784</v>
       </c>
@@ -12244,7 +12247,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5">
       <c r="A346" s="8">
         <v>42791</v>
       </c>
@@ -12262,7 +12265,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5">
       <c r="A347" s="8">
         <v>42798</v>
       </c>
@@ -12280,7 +12283,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5">
       <c r="A348" s="8">
         <v>42805</v>
       </c>
@@ -12298,7 +12301,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5">
       <c r="A349" s="8">
         <v>42812</v>
       </c>
@@ -12316,7 +12319,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5">
       <c r="A350" s="8">
         <v>42819</v>
       </c>
@@ -12334,7 +12337,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5">
       <c r="A351" s="8">
         <v>42826</v>
       </c>
@@ -12352,7 +12355,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5">
       <c r="A352" s="8">
         <v>42833</v>
       </c>
@@ -12370,7 +12373,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5">
       <c r="A353" s="8">
         <v>42840</v>
       </c>
@@ -12388,7 +12391,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5">
       <c r="A354" s="8">
         <v>42847</v>
       </c>
@@ -12406,7 +12409,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5">
       <c r="A355" s="8">
         <v>42854</v>
       </c>
@@ -12424,7 +12427,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5">
       <c r="A356" s="8">
         <v>42861</v>
       </c>
@@ -12442,7 +12445,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5">
       <c r="A357" s="8">
         <v>42868</v>
       </c>
@@ -12460,7 +12463,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5">
       <c r="A358" s="8">
         <v>42875</v>
       </c>
@@ -12478,7 +12481,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5">
       <c r="A359" s="8">
         <v>42882</v>
       </c>
@@ -12496,7 +12499,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5">
       <c r="A360" s="8">
         <v>42889</v>
       </c>
@@ -12514,7 +12517,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5">
       <c r="A361" s="8">
         <v>42896</v>
       </c>
@@ -12532,7 +12535,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5">
       <c r="A362" s="8">
         <v>42903</v>
       </c>
@@ -12550,7 +12553,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5">
       <c r="A363" s="8">
         <v>42910</v>
       </c>
@@ -12568,7 +12571,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5">
       <c r="A364" s="8">
         <v>42917</v>
       </c>
@@ -12586,7 +12589,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5">
       <c r="A365" s="8">
         <v>42924</v>
       </c>
@@ -12604,7 +12607,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5">
       <c r="A366" s="8">
         <v>42931</v>
       </c>
@@ -12622,7 +12625,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5">
       <c r="A367" s="8">
         <v>42938</v>
       </c>
@@ -12640,7 +12643,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5">
       <c r="A368" s="8">
         <v>42945</v>
       </c>
@@ -12658,7 +12661,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5">
       <c r="A369" s="8">
         <v>42952</v>
       </c>
@@ -12676,7 +12679,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5">
       <c r="A370" s="8">
         <v>42959</v>
       </c>
@@ -12694,7 +12697,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5">
       <c r="A371" s="8">
         <v>42966</v>
       </c>
@@ -12712,7 +12715,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5">
       <c r="A372" s="8">
         <v>42973</v>
       </c>
@@ -12730,7 +12733,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5">
       <c r="A373" s="8">
         <v>42980</v>
       </c>
@@ -12748,7 +12751,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5">
       <c r="A374" s="8">
         <v>42987</v>
       </c>
@@ -12766,7 +12769,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5">
       <c r="A375" s="8">
         <v>42994</v>
       </c>
@@ -12784,7 +12787,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5">
       <c r="A376" s="8">
         <v>43001</v>
       </c>
@@ -12802,7 +12805,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5">
       <c r="A377" s="8">
         <v>43008</v>
       </c>
@@ -12820,7 +12823,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5">
       <c r="A378" s="8">
         <v>43015</v>
       </c>
@@ -12838,7 +12841,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5">
       <c r="A379" s="8">
         <v>43022</v>
       </c>
@@ -12856,7 +12859,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5">
       <c r="A380" s="8">
         <v>43029</v>
       </c>
@@ -12874,7 +12877,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5">
       <c r="A381" s="8">
         <v>43036</v>
       </c>
@@ -12892,7 +12895,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5">
       <c r="A382" s="8">
         <v>43043</v>
       </c>
@@ -12910,7 +12913,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5">
       <c r="A383" s="8">
         <v>43050</v>
       </c>
@@ -12928,7 +12931,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5">
       <c r="A384" s="8">
         <v>43057</v>
       </c>
@@ -12946,7 +12949,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5">
       <c r="A385" s="8">
         <v>43064</v>
       </c>
@@ -12964,7 +12967,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5">
       <c r="A386" s="8">
         <v>43071</v>
       </c>
@@ -12982,7 +12985,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5">
       <c r="A387" s="8">
         <v>43078</v>
       </c>
@@ -13007,7 +13010,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5">
       <c r="A388" s="8">
         <v>43085</v>
       </c>
@@ -13025,7 +13028,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5">
       <c r="A389" s="8">
         <v>43092</v>
       </c>
@@ -13043,7 +13046,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5">
       <c r="A390" s="8">
         <v>43099</v>
       </c>
@@ -13061,7 +13064,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5">
       <c r="A391" s="8">
         <v>43106</v>
       </c>
@@ -13079,7 +13082,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5">
       <c r="A392" s="8">
         <v>43113</v>
       </c>
@@ -13097,7 +13100,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5">
       <c r="A393" s="8">
         <v>43120</v>
       </c>
@@ -13115,7 +13118,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5">
       <c r="A394" s="8">
         <v>43127</v>
       </c>
@@ -13133,7 +13136,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5">
       <c r="A395" s="8">
         <v>43134</v>
       </c>
@@ -13151,7 +13154,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5">
       <c r="A396" s="8">
         <v>43141</v>
       </c>
@@ -13169,7 +13172,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5">
       <c r="A397" s="8">
         <v>43148</v>
       </c>
@@ -13187,7 +13190,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5">
       <c r="A398" s="8">
         <v>43155</v>
       </c>
@@ -13205,7 +13208,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5">
       <c r="A399" s="8">
         <v>43162</v>
       </c>
@@ -13223,7 +13226,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5">
       <c r="A400" s="8">
         <v>43169</v>
       </c>
@@ -13241,7 +13244,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5">
       <c r="A401" s="8">
         <v>43176</v>
       </c>
@@ -13259,7 +13262,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5">
       <c r="A402" s="8">
         <v>43183</v>
       </c>
@@ -13277,7 +13280,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5">
       <c r="A403" s="8">
         <v>43190</v>
       </c>
@@ -13295,7 +13298,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5">
       <c r="A404" s="8">
         <v>43197</v>
       </c>
@@ -13313,7 +13316,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5">
       <c r="A405" s="8">
         <v>43204</v>
       </c>
@@ -13331,7 +13334,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5">
       <c r="A406" s="8">
         <v>43211</v>
       </c>
@@ -13349,7 +13352,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5">
       <c r="A407" s="8">
         <v>43218</v>
       </c>
@@ -13367,7 +13370,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5">
       <c r="A408" s="8">
         <v>43225</v>
       </c>
@@ -13385,7 +13388,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5">
       <c r="A409" s="8">
         <v>43232</v>
       </c>
@@ -13403,7 +13406,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5">
       <c r="A410" s="8">
         <v>43239</v>
       </c>
@@ -13421,7 +13424,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5">
       <c r="A411" s="8">
         <v>43245</v>
       </c>
@@ -13439,7 +13442,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5">
       <c r="A412" s="8">
         <v>43252</v>
       </c>
@@ -13457,7 +13460,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5">
       <c r="A413" s="8">
         <v>43259</v>
       </c>
@@ -13475,7 +13478,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5">
       <c r="A414" s="8">
         <v>43266</v>
       </c>
@@ -13493,7 +13496,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5">
       <c r="A415" s="8">
         <v>43273</v>
       </c>
@@ -13511,7 +13514,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5">
       <c r="A416" s="8">
         <v>43280</v>
       </c>
@@ -13529,7 +13532,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5">
       <c r="A417" s="8">
         <v>43287</v>
       </c>
@@ -13547,7 +13550,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5">
       <c r="A418" s="8">
         <v>43294</v>
       </c>
@@ -13565,7 +13568,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5">
       <c r="A419" s="8">
         <v>43301</v>
       </c>
@@ -13583,7 +13586,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5">
       <c r="A420" s="8">
         <v>43308</v>
       </c>
@@ -13601,7 +13604,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5">
       <c r="A421" s="8">
         <v>43315</v>
       </c>
@@ -13619,7 +13622,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5">
       <c r="A422" s="8">
         <v>43322</v>
       </c>
@@ -13637,7 +13640,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5">
       <c r="A423" s="8">
         <v>43329</v>
       </c>
@@ -13655,7 +13658,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5">
       <c r="A424" s="8">
         <v>43336</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5">
       <c r="A425" s="8">
         <v>43343</v>
       </c>
@@ -13691,7 +13694,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5">
       <c r="A426" s="8">
         <v>43350</v>
       </c>
@@ -13709,7 +13712,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5">
       <c r="A427" s="8">
         <v>43357</v>
       </c>
@@ -13727,7 +13730,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5">
       <c r="A428" s="8">
         <v>43364</v>
       </c>
@@ -13745,7 +13748,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5">
       <c r="A429" s="8">
         <v>43371</v>
       </c>
@@ -13763,7 +13766,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5">
       <c r="A430" s="8">
         <v>43378</v>
       </c>
@@ -13781,7 +13784,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5">
       <c r="A431" s="8">
         <v>43385</v>
       </c>
@@ -13799,7 +13802,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5">
       <c r="A432" s="8">
         <v>43392</v>
       </c>
@@ -13817,7 +13820,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5">
       <c r="A433" s="8">
         <v>43399</v>
       </c>
@@ -13835,7 +13838,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5">
       <c r="A434" s="8">
         <v>43406</v>
       </c>
@@ -13853,7 +13856,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5">
       <c r="A435" s="8">
         <v>43413</v>
       </c>
@@ -13871,7 +13874,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5">
       <c r="A436" s="8">
         <v>43420</v>
       </c>
@@ -13889,7 +13892,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5">
       <c r="A437" s="8">
         <v>43427</v>
       </c>
@@ -13907,7 +13910,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5">
       <c r="A438" s="8">
         <v>43434</v>
       </c>
@@ -13925,7 +13928,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5">
       <c r="A439" s="8">
         <v>43441</v>
       </c>
@@ -13943,7 +13946,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5">
       <c r="A440" s="8">
         <v>43448</v>
       </c>
@@ -13961,7 +13964,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5">
       <c r="A441" s="8">
         <v>43455</v>
       </c>
@@ -13979,7 +13982,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5">
       <c r="A442" s="8">
         <v>43462</v>
       </c>
@@ -13997,7 +14000,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5">
       <c r="A443" s="8">
         <v>43469</v>
       </c>
@@ -14015,7 +14018,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5">
       <c r="A444" s="8">
         <v>43476</v>
       </c>
@@ -14033,7 +14036,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5">
       <c r="A445" s="8">
         <v>43483</v>
       </c>
@@ -14051,7 +14054,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5">
       <c r="A446" s="8">
         <v>43490</v>
       </c>
@@ -14069,7 +14072,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5">
       <c r="A447" s="8">
         <v>43497</v>
       </c>
@@ -14087,7 +14090,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5">
       <c r="A448" s="8">
         <v>43504</v>
       </c>
@@ -14105,7 +14108,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5">
       <c r="A449" s="8">
         <v>43511</v>
       </c>
@@ -14123,7 +14126,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5">
       <c r="A450" s="8">
         <v>43518</v>
       </c>
@@ -14141,7 +14144,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5">
       <c r="A451" s="8">
         <v>43525</v>
       </c>
@@ -14166,7 +14169,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5">
       <c r="A452" s="8">
         <v>43532</v>
       </c>
@@ -14184,7 +14187,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5">
       <c r="A453" s="8">
         <v>43539</v>
       </c>
@@ -14202,7 +14205,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5">
       <c r="A454" s="8">
         <v>43546</v>
       </c>
@@ -14220,7 +14223,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5">
       <c r="A455" s="8">
         <v>43553</v>
       </c>
@@ -14238,7 +14241,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5">
       <c r="A456" s="8">
         <v>43560</v>
       </c>
@@ -14256,7 +14259,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5">
       <c r="A457" s="8">
         <v>43567</v>
       </c>
@@ -14274,7 +14277,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5">
       <c r="A458" s="8">
         <v>43574</v>
       </c>
@@ -14292,7 +14295,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5">
       <c r="A459" s="8">
         <v>43581</v>
       </c>
@@ -14310,7 +14313,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5">
       <c r="A460" s="8">
         <v>43588</v>
       </c>
@@ -14328,7 +14331,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5">
       <c r="A461" s="8">
         <v>43595</v>
       </c>
@@ -14346,7 +14349,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5">
       <c r="A462" s="8">
         <v>43602</v>
       </c>
@@ -14364,7 +14367,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5">
       <c r="A463" s="8">
         <v>43609</v>
       </c>
@@ -14382,7 +14385,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5">
       <c r="A464" s="8">
         <v>43616</v>
       </c>
@@ -14400,7 +14403,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5">
       <c r="A465" s="8">
         <v>43623</v>
       </c>
@@ -14418,7 +14421,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5">
       <c r="A466" s="8">
         <v>43630</v>
       </c>
@@ -14436,7 +14439,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5">
       <c r="A467" s="8">
         <v>43637</v>
       </c>
@@ -14454,7 +14457,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5">
       <c r="A468" s="8">
         <v>43644</v>
       </c>
@@ -14472,7 +14475,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5">
       <c r="A469" s="8">
         <v>43651</v>
       </c>
@@ -14490,7 +14493,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5">
       <c r="A470" s="8">
         <v>43658</v>
       </c>
@@ -14508,7 +14511,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5">
       <c r="A471" s="8">
         <v>43665</v>
       </c>
@@ -14526,7 +14529,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5">
       <c r="A472" s="8">
         <v>43672</v>
       </c>
@@ -14544,7 +14547,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5">
       <c r="A473" s="8">
         <v>43679</v>
       </c>
@@ -14562,7 +14565,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5">
       <c r="A474" s="8">
         <v>43686</v>
       </c>
@@ -14580,7 +14583,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5">
       <c r="A475" s="8">
         <v>43693</v>
       </c>
@@ -14598,7 +14601,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5">
       <c r="A476" s="8">
         <v>43700</v>
       </c>
@@ -14616,7 +14619,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5">
       <c r="A477" s="8">
         <v>43707</v>
       </c>
@@ -14634,7 +14637,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5">
       <c r="A478" s="8">
         <v>43714</v>
       </c>
@@ -14652,7 +14655,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5">
       <c r="A479" s="8">
         <v>43721</v>
       </c>
@@ -14670,7 +14673,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5">
       <c r="A480" s="8">
         <v>43728</v>
       </c>
@@ -14688,7 +14691,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5">
       <c r="A481" s="8">
         <v>43735</v>
       </c>
@@ -14706,7 +14709,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5">
       <c r="A482" s="8">
         <v>43742</v>
       </c>
@@ -14724,7 +14727,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5">
       <c r="A483" s="8">
         <v>43749</v>
       </c>
@@ -14742,7 +14745,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5">
       <c r="A484" s="8">
         <v>43756</v>
       </c>
@@ -14760,7 +14763,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5">
       <c r="A485" s="8">
         <v>43763</v>
       </c>
@@ -14778,7 +14781,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5">
       <c r="A486" s="8">
         <v>43770</v>
       </c>
@@ -14796,7 +14799,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5">
       <c r="A487" s="8">
         <v>43777</v>
       </c>
@@ -14814,7 +14817,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5">
       <c r="A488" s="8">
         <v>43784</v>
       </c>
@@ -14832,7 +14835,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5">
       <c r="A489" s="8">
         <v>43791</v>
       </c>
@@ -14850,7 +14853,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5">
       <c r="A490" s="8">
         <v>43798</v>
       </c>
@@ -14868,7 +14871,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5">
       <c r="A491" s="8">
         <v>43805</v>
       </c>
@@ -14886,7 +14889,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5">
       <c r="A492" s="8">
         <v>43812</v>
       </c>
@@ -14904,7 +14907,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5">
       <c r="A493" s="8">
         <v>43819</v>
       </c>
@@ -14922,7 +14925,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5">
       <c r="A494" s="8">
         <v>43826</v>
       </c>
@@ -14940,7 +14943,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5">
       <c r="A495" s="8">
         <v>43833</v>
       </c>
@@ -14958,7 +14961,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5">
       <c r="A496" s="8">
         <v>43840</v>
       </c>
@@ -14976,7 +14979,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5">
       <c r="A497" s="8">
         <v>43847</v>
       </c>
@@ -14994,7 +14997,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5">
       <c r="A498" s="8">
         <v>43854</v>
       </c>
@@ -15012,7 +15015,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5">
       <c r="A499" s="8">
         <v>43861</v>
       </c>
@@ -15030,7 +15033,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5">
       <c r="A500" s="8">
         <v>43868</v>
       </c>
@@ -15048,7 +15051,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5">
       <c r="A501" s="8">
         <v>43875</v>
       </c>
@@ -15066,7 +15069,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5">
       <c r="A502" s="8">
         <v>43882</v>
       </c>
@@ -15084,7 +15087,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5">
       <c r="A503" s="8">
         <v>43889</v>
       </c>
@@ -15102,7 +15105,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5">
       <c r="A504" s="8">
         <v>43896</v>
       </c>
@@ -15120,7 +15123,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5">
       <c r="A505" s="8">
         <v>43903</v>
       </c>
@@ -15138,7 +15141,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5">
       <c r="A506" s="8">
         <v>43910</v>
       </c>
@@ -15156,7 +15159,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5">
       <c r="A507" s="8">
         <v>43917</v>
       </c>
@@ -15174,7 +15177,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5">
       <c r="A508" s="8">
         <v>43924</v>
       </c>
@@ -15192,7 +15195,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5">
       <c r="A509" s="8">
         <v>43931</v>
       </c>
@@ -15210,7 +15213,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5">
       <c r="A510" s="8">
         <v>43938</v>
       </c>
@@ -15228,7 +15231,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5">
       <c r="A511" s="8">
         <v>43945</v>
       </c>
@@ -15246,7 +15249,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5">
       <c r="A512" s="8">
         <v>43952</v>
       </c>
@@ -15264,7 +15267,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5">
       <c r="A513" s="8">
         <v>43959</v>
       </c>
@@ -15282,7 +15285,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5">
       <c r="A514" s="8">
         <v>43966</v>
       </c>
@@ -15300,7 +15303,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5">
       <c r="A515" s="8">
         <v>43973</v>
       </c>
@@ -15325,7 +15328,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5">
       <c r="A516" s="8">
         <v>43980</v>
       </c>
@@ -15343,7 +15346,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5">
       <c r="A517" s="8">
         <v>43987</v>
       </c>
@@ -15361,7 +15364,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5">
       <c r="A518" s="8">
         <v>43994</v>
       </c>
@@ -15379,7 +15382,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5">
       <c r="A519" s="8">
         <v>44001</v>
       </c>
@@ -15397,7 +15400,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5">
       <c r="A520" s="8">
         <v>44008</v>
       </c>
@@ -15415,7 +15418,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5">
       <c r="A521" s="8">
         <v>44015</v>
       </c>
@@ -15433,7 +15436,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5">
       <c r="A522" s="8">
         <v>44022</v>
       </c>
@@ -15451,7 +15454,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5">
       <c r="A523" s="8">
         <v>44029</v>
       </c>
@@ -15469,7 +15472,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5">
       <c r="A524" s="8">
         <v>44036</v>
       </c>
@@ -15487,7 +15490,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5">
       <c r="A525" s="8">
         <v>44043</v>
       </c>
@@ -15505,7 +15508,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5">
       <c r="A526" s="8">
         <v>44050</v>
       </c>
@@ -15523,7 +15526,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5">
       <c r="A527" s="8">
         <v>44057</v>
       </c>
@@ -15541,7 +15544,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5">
       <c r="A528" s="8">
         <v>44064</v>
       </c>
@@ -15559,7 +15562,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5">
       <c r="A529" s="8">
         <v>44071</v>
       </c>
@@ -15577,7 +15580,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5">
       <c r="A530" s="8">
         <v>44078</v>
       </c>
@@ -15595,7 +15598,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5">
       <c r="A531" s="8">
         <v>44085</v>
       </c>
@@ -15613,7 +15616,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5">
       <c r="A532" s="8">
         <v>44092</v>
       </c>
@@ -15631,7 +15634,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5">
       <c r="A533" s="8">
         <v>44099</v>
       </c>
@@ -15649,7 +15652,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5">
       <c r="A534" s="8">
         <v>44106</v>
       </c>
@@ -15667,7 +15670,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5">
       <c r="A535" s="8">
         <v>44113</v>
       </c>
@@ -15685,7 +15688,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5">
       <c r="A536" s="8">
         <v>44120</v>
       </c>
@@ -15703,7 +15706,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5">
       <c r="A537" s="8">
         <v>44127</v>
       </c>
@@ -15721,7 +15724,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5">
       <c r="A538" s="8">
         <v>44134</v>
       </c>
@@ -15739,7 +15742,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5">
       <c r="A539" s="8">
         <v>44141</v>
       </c>
@@ -15757,7 +15760,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5">
       <c r="A540" s="8">
         <v>44148</v>
       </c>
@@ -15775,7 +15778,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5">
       <c r="A541" s="8">
         <v>44155</v>
       </c>
@@ -15793,7 +15796,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5">
       <c r="A542" s="8">
         <v>44162</v>
       </c>
@@ -15811,7 +15814,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5">
       <c r="A543" s="8">
         <v>44169</v>
       </c>
@@ -15829,7 +15832,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5">
       <c r="A544" s="8">
         <v>44176</v>
       </c>
@@ -15847,7 +15850,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5">
       <c r="A545" s="8">
         <v>44183</v>
       </c>
@@ -15865,7 +15868,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5">
       <c r="A546" s="8">
         <v>44190</v>
       </c>
@@ -15883,7 +15886,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5">
       <c r="A547" s="8">
         <v>44197</v>
       </c>
@@ -15901,7 +15904,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5">
       <c r="A548" s="8">
         <v>44204</v>
       </c>
@@ -15919,7 +15922,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5">
       <c r="A549" s="8">
         <v>44211</v>
       </c>
@@ -15937,7 +15940,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5">
       <c r="A550" s="8">
         <v>44218</v>
       </c>
@@ -15955,7 +15958,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5">
       <c r="A551" s="8">
         <v>44225</v>
       </c>
@@ -15973,7 +15976,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5">
       <c r="A552" s="8">
         <v>44232</v>
       </c>
@@ -15991,7 +15994,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5">
       <c r="A553" s="8">
         <v>44239</v>
       </c>
@@ -16009,7 +16012,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5">
       <c r="A554" s="8">
         <v>44246</v>
       </c>
@@ -16027,7 +16030,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5">
       <c r="A555" s="8">
         <v>44253</v>
       </c>
@@ -16045,7 +16048,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5">
       <c r="A556" s="8">
         <v>44260</v>
       </c>
@@ -16063,7 +16066,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5">
       <c r="A557" s="8">
         <v>44267</v>
       </c>
@@ -16081,7 +16084,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5">
       <c r="A558" s="8">
         <v>44274</v>
       </c>
@@ -16099,7 +16102,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5">
       <c r="A559" s="8">
         <v>44281</v>
       </c>
@@ -16117,7 +16120,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5">
       <c r="A560" s="8">
         <v>44288</v>
       </c>
@@ -16135,7 +16138,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5">
       <c r="A561" s="8">
         <v>44295</v>
       </c>
@@ -16153,7 +16156,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5">
       <c r="A562" s="8">
         <v>44302</v>
       </c>
@@ -16171,7 +16174,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5">
       <c r="A563" s="8">
         <v>44309</v>
       </c>
@@ -16189,7 +16192,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5">
       <c r="A564" s="8">
         <v>44316</v>
       </c>
@@ -16207,7 +16210,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5">
       <c r="A565" s="8">
         <v>44323</v>
       </c>
@@ -16225,7 +16228,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5">
       <c r="A566" s="8">
         <v>44330</v>
       </c>
@@ -16243,7 +16246,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5">
       <c r="A567" s="8">
         <v>44337</v>
       </c>
@@ -16261,7 +16264,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5">
       <c r="A568" s="8">
         <v>44344</v>
       </c>
@@ -16279,7 +16282,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5">
       <c r="A569" s="8">
         <v>44351</v>
       </c>
@@ -16297,7 +16300,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5">
       <c r="A570" s="8">
         <v>44358</v>
       </c>
@@ -16315,7 +16318,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5">
       <c r="A571" s="8">
         <v>44365</v>
       </c>
@@ -16333,7 +16336,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5">
       <c r="A572" s="8">
         <v>44372</v>
       </c>
@@ -16351,7 +16354,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5">
       <c r="A573" s="8">
         <v>44379</v>
       </c>
@@ -16369,7 +16372,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5">
       <c r="A574" s="8">
         <v>44386</v>
       </c>
@@ -16387,7 +16390,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5">
       <c r="A575" s="8">
         <v>44393</v>
       </c>
@@ -16405,7 +16408,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5">
       <c r="A576" s="8">
         <v>44400</v>
       </c>
@@ -16423,7 +16426,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5">
       <c r="A577" s="8">
         <v>44407</v>
       </c>
@@ -16441,7 +16444,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5">
       <c r="A578" s="8">
         <v>44414</v>
       </c>
@@ -16459,7 +16462,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5">
       <c r="A579" s="8">
         <v>44421</v>
       </c>
@@ -16484,7 +16487,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5">
       <c r="A580" s="8">
         <v>44428</v>
       </c>
@@ -16502,7 +16505,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5">
       <c r="A581" s="8">
         <v>44435</v>
       </c>
@@ -16520,7 +16523,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5">
       <c r="A582" s="8">
         <v>44442</v>
       </c>
@@ -16538,7 +16541,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5">
       <c r="A583" s="8">
         <v>44449</v>
       </c>
@@ -16556,7 +16559,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5">
       <c r="A584" s="8">
         <v>44456</v>
       </c>
@@ -16574,7 +16577,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5">
       <c r="A585" s="8">
         <v>44463</v>
       </c>
@@ -16592,7 +16595,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5">
       <c r="A586" s="8">
         <v>44470</v>
       </c>
@@ -16610,7 +16613,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5">
       <c r="A587" s="8">
         <v>44477</v>
       </c>
@@ -16628,7 +16631,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5">
       <c r="A588" s="8">
         <v>44484</v>
       </c>
@@ -16646,7 +16649,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5">
       <c r="A589" s="8">
         <v>44491</v>
       </c>
@@ -16664,7 +16667,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5">
       <c r="A590" s="8">
         <v>44498</v>
       </c>
@@ -16682,7 +16685,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5">
       <c r="A591" s="8">
         <v>44505</v>
       </c>
@@ -16700,7 +16703,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5">
       <c r="A592" s="8">
         <v>44512</v>
       </c>
@@ -16718,7 +16721,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4">
       <c r="A593" s="8">
         <v>44519</v>
       </c>
@@ -16733,7 +16736,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4">
       <c r="A594" s="8">
         <v>44526</v>
       </c>
@@ -16748,7 +16751,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4">
       <c r="A595" s="8">
         <v>44533</v>
       </c>
@@ -16763,7 +16766,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4">
       <c r="A596" s="8">
         <v>44540</v>
       </c>
@@ -16778,7 +16781,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4">
       <c r="A597" s="8">
         <v>44547</v>
       </c>
@@ -16793,7 +16796,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4">
       <c r="A598" s="8">
         <v>44554</v>
       </c>
@@ -16808,7 +16811,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4">
       <c r="A599" s="8">
         <v>44561</v>
       </c>
@@ -16823,7 +16826,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4">
       <c r="A600" s="8">
         <v>44568</v>
       </c>
@@ -16838,7 +16841,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4">
       <c r="A601" s="8">
         <v>44575</v>
       </c>
@@ -16853,7 +16856,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4">
       <c r="A602" s="8">
         <v>44582</v>
       </c>
@@ -16868,7 +16871,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4">
       <c r="A603" s="8">
         <v>44589</v>
       </c>
@@ -16883,7 +16886,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4">
       <c r="A604" s="8">
         <v>44596</v>
       </c>
@@ -16898,7 +16901,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4">
       <c r="A605" s="8">
         <v>44603</v>
       </c>
@@ -16913,7 +16916,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4">
       <c r="A606" s="8">
         <v>44610</v>
       </c>
@@ -16928,7 +16931,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4">
       <c r="A607" s="8">
         <v>44617</v>
       </c>
@@ -16943,7 +16946,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4">
       <c r="A608" s="8">
         <v>44624</v>
       </c>
@@ -16958,7 +16961,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4">
       <c r="A609" s="8">
         <v>44631</v>
       </c>
@@ -16973,7 +16976,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4">
       <c r="A610" s="8">
         <v>44638</v>
       </c>
@@ -16988,7 +16991,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4">
       <c r="A611" s="8">
         <v>44645</v>
       </c>
@@ -17003,7 +17006,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4">
       <c r="A612" s="8">
         <v>44652</v>
       </c>
@@ -17018,7 +17021,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4">
       <c r="A613" s="8">
         <v>44659</v>
       </c>
@@ -17033,7 +17036,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4">
       <c r="A614" s="8">
         <v>44666</v>
       </c>
@@ -17048,7 +17051,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4">
       <c r="A615" s="8">
         <v>44673</v>
       </c>
@@ -17063,7 +17066,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4">
       <c r="A616" s="8">
         <v>44680</v>
       </c>
@@ -17078,7 +17081,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4">
       <c r="A617" s="8">
         <v>44687</v>
       </c>
@@ -17093,7 +17096,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4">
       <c r="A618" s="8">
         <v>44694</v>
       </c>
@@ -17108,7 +17111,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4">
       <c r="A619" s="8">
         <v>44701</v>
       </c>
@@ -17123,7 +17126,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4">
       <c r="A620" s="8">
         <v>44708</v>
       </c>
@@ -17138,7 +17141,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4">
       <c r="A621" s="8">
         <v>44715</v>
       </c>
@@ -17153,7 +17156,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4">
       <c r="A622" s="8">
         <v>44722</v>
       </c>
@@ -17168,7 +17171,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4">
       <c r="A623" s="8">
         <v>44729</v>
       </c>
@@ -17183,7 +17186,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4">
       <c r="A624" s="8">
         <v>44736</v>
       </c>
@@ -17198,7 +17201,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4">
       <c r="A625" s="8">
         <v>44743</v>
       </c>
@@ -17213,7 +17216,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4">
       <c r="A626" s="8">
         <v>44750</v>
       </c>
@@ -17228,7 +17231,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4">
       <c r="A627" s="8">
         <v>44757</v>
       </c>
@@ -17243,7 +17246,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4">
       <c r="A628" s="8">
         <v>44764</v>
       </c>
@@ -17258,7 +17261,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4">
       <c r="A629" s="8">
         <v>44771</v>
       </c>
@@ -17273,7 +17276,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4">
       <c r="A630" s="8">
         <v>44778</v>
       </c>
@@ -17288,7 +17291,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4">
       <c r="A631" s="8">
         <v>44785</v>
       </c>
@@ -17303,7 +17306,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4">
       <c r="A632" s="8">
         <v>44792</v>
       </c>
@@ -17318,7 +17321,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4">
       <c r="A633" s="8">
         <v>44799</v>
       </c>
@@ -17333,7 +17336,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4">
       <c r="A634" s="8">
         <v>44806</v>
       </c>
@@ -17348,7 +17351,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4">
       <c r="A635" s="8">
         <v>44813</v>
       </c>
@@ -17363,7 +17366,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4">
       <c r="A636" s="8">
         <v>44820</v>
       </c>
@@ -17378,7 +17381,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4">
       <c r="A637" s="8">
         <v>44827</v>
       </c>
@@ -17393,7 +17396,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4">
       <c r="A638" s="8">
         <v>44834</v>
       </c>
@@ -17408,7 +17411,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4">
       <c r="A639" s="8">
         <v>44841</v>
       </c>
@@ -17423,7 +17426,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4">
       <c r="A640" s="8">
         <v>44848</v>
       </c>
@@ -17438,7 +17441,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4">
       <c r="A641" s="8">
         <v>44855</v>
       </c>
@@ -17453,7 +17456,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4">
       <c r="A642" s="8">
         <v>44862</v>
       </c>
@@ -17468,7 +17471,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4">
       <c r="A643" s="8">
         <v>44869</v>
       </c>
@@ -17490,7 +17493,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4">
       <c r="A644" s="8">
         <v>44876</v>
       </c>
@@ -17505,7 +17508,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4">
       <c r="A645" s="8">
         <v>44883</v>
       </c>
@@ -17520,7 +17523,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4">
       <c r="A646" s="8">
         <v>44890</v>
       </c>
@@ -17535,7 +17538,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4">
       <c r="A647" s="8">
         <v>44897</v>
       </c>
@@ -17550,7 +17553,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4">
       <c r="A648" s="8">
         <v>44904</v>
       </c>
@@ -17565,7 +17568,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4">
       <c r="A649" s="8">
         <v>44911</v>
       </c>
@@ -17580,7 +17583,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4">
       <c r="A650" s="8">
         <v>44918</v>
       </c>
@@ -17595,7 +17598,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4">
       <c r="A651" s="8">
         <v>44925</v>
       </c>
@@ -17610,7 +17613,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4">
       <c r="A652" s="8">
         <v>44932</v>
       </c>
@@ -17625,7 +17628,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4">
       <c r="A653" s="8">
         <v>44939</v>
       </c>
@@ -17640,7 +17643,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4">
       <c r="A654" s="8">
         <v>44946</v>
       </c>
@@ -17655,7 +17658,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4">
       <c r="A655" s="8">
         <v>44953</v>
       </c>
@@ -17670,7 +17673,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4">
       <c r="A656" s="8">
         <v>44960</v>
       </c>
@@ -17685,7 +17688,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4">
       <c r="A657" s="8">
         <v>44967</v>
       </c>
@@ -17700,7 +17703,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4">
       <c r="A658" s="8">
         <v>44974</v>
       </c>
@@ -17715,7 +17718,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4">
       <c r="A659" s="8">
         <v>44981</v>
       </c>
@@ -17730,7 +17733,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4">
       <c r="A660" s="8">
         <v>44988</v>
       </c>
@@ -17745,7 +17748,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4">
       <c r="A661" s="8">
         <v>44995</v>
       </c>
@@ -17760,7 +17763,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4">
       <c r="A662" s="8">
         <v>45002</v>
       </c>
@@ -17775,7 +17778,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4">
       <c r="A663" s="8">
         <v>45009</v>
       </c>
@@ -17790,7 +17793,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4">
       <c r="A664" s="8">
         <v>45016</v>
       </c>
@@ -17805,7 +17808,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4">
       <c r="A665" s="8">
         <v>45023</v>
       </c>
@@ -17820,7 +17823,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4">
       <c r="A666" s="8">
         <v>45030</v>
       </c>
@@ -17835,7 +17838,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4">
       <c r="A667" s="8">
         <v>45037</v>
       </c>
@@ -17850,7 +17853,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4">
       <c r="A668" s="8">
         <v>45044</v>
       </c>
@@ -17865,7 +17868,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4">
       <c r="A669" s="8">
         <v>45051</v>
       </c>
@@ -17880,7 +17883,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4">
       <c r="A670" s="8">
         <v>45058</v>
       </c>
@@ -17895,7 +17898,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4">
       <c r="A671" s="8">
         <v>45065</v>
       </c>
@@ -17910,7 +17913,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4">
       <c r="A672" s="8">
         <v>45072</v>
       </c>
@@ -17925,7 +17928,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4">
       <c r="A673" s="8">
         <v>45079</v>
       </c>
@@ -17940,7 +17943,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4">
       <c r="A674" s="8">
         <v>45086</v>
       </c>
@@ -17955,7 +17958,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4">
       <c r="A675" s="8">
         <v>45093</v>
       </c>
@@ -17970,7 +17973,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4">
       <c r="A676" s="8">
         <v>45100</v>
       </c>
@@ -17985,7 +17988,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4">
       <c r="A677" s="8">
         <v>45107</v>
       </c>
@@ -18000,7 +18003,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4">
       <c r="A678" s="8">
         <v>45114</v>
       </c>
@@ -18015,7 +18018,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4">
       <c r="A679" s="8">
         <v>45121</v>
       </c>
@@ -18030,7 +18033,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4">
       <c r="A680" s="8">
         <v>45128</v>
       </c>
@@ -18045,7 +18048,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4">
       <c r="A681" s="8">
         <v>45135</v>
       </c>
@@ -18060,7 +18063,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4">
       <c r="A682" s="8">
         <v>45142</v>
       </c>
@@ -18075,7 +18078,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4">
       <c r="A683" s="8">
         <v>45149</v>
       </c>
@@ -18090,7 +18093,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4">
       <c r="A684" s="8">
         <v>45156</v>
       </c>
@@ -18105,7 +18108,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4">
       <c r="A685" s="8">
         <v>45163</v>
       </c>
@@ -18120,7 +18123,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:4">
       <c r="A686" s="8">
         <v>45170</v>
       </c>
@@ -18135,7 +18138,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:4">
       <c r="A687" s="8">
         <v>45177</v>
       </c>
@@ -18150,7 +18153,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:4">
       <c r="A688" s="8">
         <v>45184</v>
       </c>
@@ -18165,7 +18168,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5">
       <c r="A689" s="8">
         <v>45191</v>
       </c>
@@ -18180,7 +18183,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5">
       <c r="A690" s="8">
         <v>45198</v>
       </c>
@@ -18195,7 +18198,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5">
       <c r="A691" s="8">
         <v>45205</v>
       </c>
@@ -18210,7 +18213,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5">
       <c r="A692" s="8">
         <v>45212</v>
       </c>
@@ -18225,7 +18228,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5">
       <c r="A693" s="8">
         <v>45219</v>
       </c>
@@ -18240,7 +18243,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5">
       <c r="A694" s="8">
         <v>45226</v>
       </c>
@@ -18255,7 +18258,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5">
       <c r="A695" s="8">
         <v>45233</v>
       </c>
@@ -18270,7 +18273,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5">
       <c r="A696" s="8">
         <v>45240</v>
       </c>
@@ -18285,7 +18288,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5">
       <c r="A697" s="8">
         <v>45247</v>
       </c>
@@ -18300,7 +18303,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5">
       <c r="A698" s="8">
         <v>45254</v>
       </c>
@@ -18315,7 +18318,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5">
       <c r="A699" s="8">
         <v>45261</v>
       </c>
@@ -18330,7 +18333,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5">
       <c r="A700" s="8">
         <v>45268</v>
       </c>
@@ -18345,7 +18348,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5">
       <c r="A701" s="8">
         <v>45275</v>
       </c>
@@ -18363,7 +18366,7 @@
         <v>809.6</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5">
       <c r="A702" s="8">
         <v>45282</v>
       </c>
@@ -18381,7 +18384,7 @@
         <v>809.6</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5">
       <c r="A703" s="8">
         <v>45289</v>
       </c>
@@ -18396,7 +18399,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5">
       <c r="A704" s="8">
         <v>45296</v>
       </c>
@@ -18411,7 +18414,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5">
       <c r="A705" s="8">
         <v>45303</v>
       </c>
@@ -18429,7 +18432,7 @@
         <v>910.24</v>
       </c>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5">
       <c r="A706" s="8">
         <v>45310</v>
       </c>
@@ -18444,7 +18447,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5">
       <c r="A707" s="8">
         <v>45317</v>
       </c>
@@ -18466,7 +18469,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5">
       <c r="A708" s="8">
         <v>45324</v>
       </c>
@@ -18481,7 +18484,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5">
       <c r="A709" s="8">
         <v>45331</v>
       </c>
@@ -18496,7 +18499,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5">
       <c r="A710" s="8">
         <v>45338</v>
       </c>
@@ -18511,7 +18514,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5">
       <c r="A711" s="8">
         <v>45345</v>
       </c>
@@ -18526,7 +18529,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5">
       <c r="A712" s="8">
         <v>45352</v>
       </c>
@@ -18541,7 +18544,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5">
       <c r="A713" s="8">
         <v>45359</v>
       </c>
@@ -18559,7 +18562,7 @@
         <v>1201.73</v>
       </c>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5">
       <c r="A714" s="8">
         <v>45366</v>
       </c>
@@ -18577,7 +18580,7 @@
         <v>1215.8900000000001</v>
       </c>
     </row>
-    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5">
       <c r="A715" s="8">
         <v>45373</v>
       </c>
@@ -18592,7 +18595,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5">
       <c r="A716" s="8">
         <v>45380</v>
       </c>
@@ -18607,7 +18610,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5">
       <c r="A717" s="8">
         <v>45387</v>
       </c>
@@ -18622,7 +18625,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5">
       <c r="A718" s="8">
         <v>45394</v>
       </c>
@@ -18637,7 +18640,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5">
       <c r="A719" s="8">
         <v>45401</v>
       </c>
@@ -18655,7 +18658,7 @@
         <v>1230.06</v>
       </c>
     </row>
-    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5">
       <c r="A720" s="8">
         <v>45408</v>
       </c>
@@ -18673,7 +18676,7 @@
         <v>1251.68</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5">
       <c r="A721" s="8">
         <v>45415</v>
       </c>
@@ -18688,7 +18691,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5">
       <c r="A722" s="8">
         <v>45422</v>
       </c>
@@ -18703,7 +18706,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5">
       <c r="A723" s="8">
         <v>45429</v>
       </c>
@@ -18718,7 +18721,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5">
       <c r="A724" s="8">
         <v>45436</v>
       </c>
@@ -18733,7 +18736,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5">
       <c r="A725" s="8">
         <v>45443</v>
       </c>
@@ -18748,7 +18751,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5">
       <c r="A726" s="8">
         <v>45450</v>
       </c>
@@ -18763,7 +18766,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5">
       <c r="A727" s="8">
         <v>45457</v>
       </c>
@@ -18778,7 +18781,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5">
       <c r="A728" s="8">
         <v>45464</v>
       </c>
@@ -18796,7 +18799,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5">
       <c r="A729" s="8">
         <v>45471</v>
       </c>
@@ -18814,7 +18817,7 @@
         <v>1712.39</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5">
       <c r="A730" s="8">
         <v>45478</v>
       </c>
@@ -18829,7 +18832,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5">
       <c r="A731" s="8">
         <v>45485</v>
       </c>
@@ -18844,7 +18847,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5">
       <c r="A732" s="8">
         <v>45492</v>
       </c>
@@ -18859,7 +18862,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5">
       <c r="A733" s="8">
         <v>45499</v>
       </c>
@@ -18874,7 +18877,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5">
       <c r="A734" s="8">
         <v>45506</v>
       </c>
@@ -18889,7 +18892,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5">
       <c r="A735" s="8">
         <v>45513</v>
       </c>
@@ -18904,7 +18907,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5">
       <c r="A736" s="8">
         <v>45520</v>
       </c>
@@ -18919,7 +18922,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5">
       <c r="A737" s="8">
         <v>45527</v>
       </c>
@@ -18934,7 +18937,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5">
       <c r="A738" s="8">
         <v>45534</v>
       </c>
@@ -18949,7 +18952,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5">
       <c r="A739" s="8">
         <v>45541</v>
       </c>
@@ -18964,7 +18967,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5">
       <c r="A740" s="8">
         <v>45548</v>
       </c>
@@ -18979,7 +18982,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5">
       <c r="A741" s="8">
         <v>45555</v>
       </c>
@@ -18994,7 +18997,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5">
       <c r="A742" s="8">
         <v>45562</v>
       </c>
@@ -19009,7 +19012,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5">
       <c r="A743" s="8">
         <v>45569</v>
       </c>
@@ -19027,7 +19030,7 @@
         <v>1936.04</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5">
       <c r="A744" s="8">
         <v>45576</v>
       </c>
@@ -19045,7 +19048,7 @@
         <v>1965.85</v>
       </c>
     </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5">
       <c r="A745" s="8">
         <v>45583</v>
       </c>
@@ -19063,7 +19066,7 @@
         <v>1967.35</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5">
       <c r="A746" s="8">
         <v>45590</v>
       </c>
@@ -19078,7 +19081,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5">
       <c r="A747" s="8">
         <v>45597</v>
       </c>
@@ -19093,7 +19096,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5">
       <c r="A748" s="8">
         <v>45604</v>
       </c>
@@ -19108,7 +19111,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5">
       <c r="A749" s="8">
         <v>45611</v>
       </c>
@@ -19126,7 +19129,7 @@
         <v>1977.78</v>
       </c>
     </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5">
       <c r="A750" s="8">
         <v>45618</v>
       </c>
@@ -19141,7 +19144,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5">
       <c r="A751" s="8">
         <v>45625</v>
       </c>
@@ -19156,7 +19159,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5">
       <c r="A752" s="8">
         <v>45632</v>
       </c>
@@ -19171,7 +19174,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:15">
       <c r="A753" s="8">
         <v>45639</v>
       </c>
@@ -19186,7 +19189,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:15">
       <c r="A754" s="8">
         <v>45646</v>
       </c>
@@ -19201,7 +19204,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:15">
       <c r="A755" s="8">
         <v>45653</v>
       </c>
@@ -19216,7 +19219,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:15">
       <c r="A756" s="8">
         <v>45660</v>
       </c>
@@ -19234,7 +19237,7 @@
         <v>2052.33</v>
       </c>
     </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:15">
       <c r="A757" s="8">
         <v>45667</v>
       </c>
@@ -19249,7 +19252,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:15">
       <c r="A758" s="8">
         <v>45674</v>
       </c>
@@ -19264,7 +19267,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:15">
       <c r="A759" s="8">
         <v>45681</v>
       </c>
@@ -19279,7 +19282,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:15">
       <c r="A760" s="8">
         <v>45688</v>
       </c>
@@ -19297,7 +19300,7 @@
         <v>2052.33</v>
       </c>
     </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:15">
       <c r="A761" s="8">
         <v>45695</v>
       </c>
@@ -19312,7 +19315,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:15">
       <c r="A762" s="8">
         <v>45702</v>
       </c>
@@ -19327,7 +19330,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:15">
       <c r="A763" s="8">
         <v>45709</v>
       </c>
@@ -19375,7 +19378,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:15">
       <c r="A764" s="8">
         <v>45716</v>
       </c>
@@ -19423,7 +19426,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:15">
       <c r="A765" s="8">
         <v>45723</v>
       </c>
@@ -19471,7 +19474,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:15">
       <c r="A766" s="8">
         <v>45730</v>
       </c>
@@ -19519,7 +19522,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:15">
       <c r="A767" s="8">
         <v>45737</v>
       </c>
@@ -19567,7 +19570,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:15">
       <c r="A768" s="8">
         <v>45744</v>
       </c>
@@ -19615,7 +19618,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:15">
       <c r="A769" s="8">
         <v>45751</v>
       </c>
@@ -19663,7 +19666,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:15">
       <c r="A770" s="8">
         <v>45758</v>
       </c>
@@ -19711,7 +19714,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:15">
       <c r="A771" s="8">
         <v>45765</v>
       </c>
@@ -19766,7 +19769,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:15">
       <c r="A772" s="8">
         <v>45772</v>
       </c>
@@ -19814,7 +19817,7 @@
         <v>72000</v>
       </c>
     </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:15">
       <c r="A773" s="8">
         <v>45779</v>
       </c>
@@ -19829,7 +19832,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:15">
       <c r="A774" s="8">
         <v>45786</v>
       </c>
@@ -19847,7 +19850,7 @@
         <v>2055.31</v>
       </c>
     </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:15">
       <c r="A775" s="8">
         <v>45793</v>
       </c>
@@ -19862,7 +19865,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:15">
       <c r="A776" s="8">
         <v>45800</v>
       </c>
@@ -19877,7 +19880,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:15">
       <c r="A777" s="8">
         <v>45807</v>
       </c>
@@ -19892,7 +19895,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:15">
       <c r="A778" s="8">
         <v>45814</v>
       </c>
@@ -19907,7 +19910,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:15">
       <c r="A779" s="8">
         <v>45821</v>
       </c>
@@ -19922,7 +19925,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:15">
       <c r="A780" s="8">
         <v>45828</v>
       </c>
@@ -19970,7 +19973,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:15">
       <c r="A781" s="8">
         <v>45835</v>
       </c>
@@ -20018,7 +20021,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:15">
       <c r="A782" s="8">
         <v>45842</v>
       </c>
@@ -20066,7 +20069,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:15">
       <c r="A783" s="8">
         <v>45849</v>
       </c>
@@ -20114,7 +20117,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:15">
       <c r="A784" s="8">
         <v>45856</v>
       </c>
@@ -20162,7 +20165,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:15">
       <c r="A785" s="8">
         <v>45863</v>
       </c>
@@ -20210,7 +20213,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:15">
       <c r="A786" s="8">
         <v>45870</v>
       </c>
@@ -20258,7 +20261,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:15">
       <c r="A787" s="8">
         <v>45877</v>
       </c>
@@ -20273,7 +20276,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="788" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:15">
       <c r="A788" s="8">
         <v>45884</v>
       </c>
@@ -20288,7 +20291,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="789" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:15">
       <c r="A789" s="8">
         <v>45891</v>
       </c>
@@ -20336,7 +20339,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:15">
       <c r="A790" s="8">
         <v>45898</v>
       </c>
@@ -20384,7 +20387,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="791" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:15">
       <c r="A791" s="8">
         <v>45905</v>
       </c>
@@ -20432,7 +20435,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="792" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:15">
       <c r="A792" s="8">
         <v>45912</v>
       </c>
@@ -20480,7 +20483,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="793" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:15">
       <c r="A793" s="8">
         <v>45919</v>
       </c>
@@ -20528,7 +20531,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="794" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:15">
       <c r="A794" s="8">
         <v>45926</v>
       </c>
@@ -20576,7 +20579,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="795" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:15">
       <c r="A795" s="8">
         <v>45933</v>
       </c>
@@ -20624,7 +20627,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="796" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:15">
       <c r="A796" s="8">
         <v>45940</v>
       </c>
@@ -20672,7 +20675,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="797" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:15">
       <c r="A797" s="8">
         <v>45947</v>
       </c>
@@ -20687,7 +20690,7 @@
         <v>UTC+2</v>
       </c>
     </row>
-    <row r="798" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:15">
       <c r="A798" s="8">
         <v>45954</v>
       </c>
@@ -20735,7 +20738,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="799" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:15">
       <c r="A799" s="8">
         <v>45961</v>
       </c>
@@ -20783,7 +20786,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="800" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:15">
       <c r="A800" s="8">
         <v>45968</v>
       </c>
@@ -20831,7 +20834,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15">
       <c r="A801" s="8">
         <v>45975</v>
       </c>
@@ -20879,7 +20882,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15">
       <c r="A802" s="8">
         <v>45982</v>
       </c>
@@ -20894,7 +20897,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15">
       <c r="A803" s="8">
         <v>45989</v>
       </c>
@@ -20909,7 +20912,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15">
       <c r="A804" s="8">
         <v>45996</v>
       </c>
@@ -20924,7 +20927,7 @@
         <v>UTC+1</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15">
       <c r="A805" s="8">
         <v>46003</v>
       </c>
@@ -20942,7 +20945,7 @@
         <v>2180.56</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:15">
       <c r="A806" s="8">
         <v>46010</v>
       </c>
@@ -20990,7 +20993,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:15">
       <c r="A807" s="8">
         <v>46017</v>
       </c>
@@ -21038,7 +21041,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:15">
       <c r="A808" s="8">
         <v>46024</v>
       </c>
@@ -21086,7 +21089,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:15">
       <c r="A809" s="8">
         <v>46031</v>
       </c>
@@ -21134,7 +21137,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:15">
       <c r="A810" s="8">
         <v>46038</v>
       </c>
@@ -21182,7 +21185,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:15">
       <c r="A811" s="8">
         <v>46045</v>
       </c>
@@ -21230,7 +21233,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:15">
       <c r="A812" s="8">
         <v>46052</v>
       </c>
@@ -21278,7 +21281,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:15">
       <c r="A813" s="8">
         <v>46059</v>
       </c>
@@ -21326,7 +21329,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:15">
       <c r="A814" s="8">
         <v>46066</v>
       </c>
@@ -21341,7 +21344,7 @@
         <v>UTC+1</v>
       </c>
       <c r="E814" s="12">
-        <v>2191</v>
+        <v>2190.9899999999998</v>
       </c>
       <c r="F814" s="15">
         <v>10250</v>
@@ -21374,7 +21377,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:15">
       <c r="A815" s="8">
         <v>46073</v>
       </c>
@@ -21422,7 +21425,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:15">
       <c r="A816" s="8">
         <v>46080</v>
       </c>
@@ -21470,7 +21473,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:15">
       <c r="A817" s="8">
         <v>46087</v>
       </c>
@@ -21518,7 +21521,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:15">
       <c r="A818" s="8">
         <v>46094</v>
       </c>
@@ -21566,7 +21569,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:15">
       <c r="A819" s="8">
         <v>46101</v>
       </c>
@@ -21614,7 +21617,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:15">
       <c r="A820" s="8">
         <v>46108</v>
       </c>
@@ -21662,7 +21665,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:15">
       <c r="A821" s="8">
         <v>46115</v>
       </c>
@@ -21710,7 +21713,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:15">
       <c r="A822" s="8">
         <v>46122</v>
       </c>
@@ -21738,7 +21741,7 @@
       <c r="N822" s="15"/>
       <c r="O822" s="15"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:15">
       <c r="A823" s="8">
         <v>46129</v>
       </c>
@@ -21766,7 +21769,7 @@
       <c r="N823" s="15"/>
       <c r="O823" s="15"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:15">
       <c r="A824" s="8">
         <v>46136</v>
       </c>
@@ -21794,7 +21797,7 @@
       <c r="N824" s="15"/>
       <c r="O824" s="15"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:15">
       <c r="A825" s="8">
         <v>46143</v>
       </c>
@@ -21842,7 +21845,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:15">
       <c r="A826" s="8">
         <v>46150</v>
       </c>
@@ -21890,7 +21893,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:15">
       <c r="A827" s="8">
         <v>46157</v>
       </c>
@@ -21938,7 +21941,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:15">
       <c r="A828" s="8">
         <v>46164</v>
       </c>
@@ -21986,7 +21989,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:15">
       <c r="A829" s="8">
         <v>46171</v>
       </c>
@@ -22034,7 +22037,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:15">
       <c r="A830" s="8">
         <v>46178</v>
       </c>
@@ -22082,7 +22085,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:15">
       <c r="A831" s="8">
         <v>46185</v>
       </c>
@@ -22130,7 +22133,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:15">
       <c r="A832" s="8">
         <v>46192</v>
       </c>
@@ -22178,7 +22181,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:15">
       <c r="A833" s="8">
         <v>46199</v>
       </c>
@@ -22226,7 +22229,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:15">
       <c r="A834" s="8">
         <v>46206</v>
       </c>
@@ -22281,7 +22284,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:15">
       <c r="A835" s="8">
         <v>46213</v>
       </c>
@@ -22329,7 +22332,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:15">
       <c r="A836" s="8">
         <v>46220</v>
       </c>
@@ -22377,7 +22380,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="837" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:15">
       <c r="A837" s="8">
         <v>46227</v>
       </c>
@@ -22432,7 +22435,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="838" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:15">
       <c r="A838" s="8">
         <v>46234</v>
       </c>
@@ -22480,7 +22483,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="839" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:15">
       <c r="A839" s="8">
         <v>46241</v>
       </c>
@@ -22528,7 +22531,7 @@
         <v>79000</v>
       </c>
     </row>
-    <row r="840" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:15">
       <c r="A840" s="8">
         <v>46248</v>
       </c>
@@ -22549,6 +22552,39 @@
 )</f>
         <v>UTC+2</v>
       </c>
+      <c r="E840" s="10">
+        <v>2346.0500000000002</v>
+      </c>
+      <c r="F840" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G840" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H840" s="14">
+        <v>31500</v>
+      </c>
+      <c r="I840" s="14">
+        <v>35000</v>
+      </c>
+      <c r="J840" s="14">
+        <v>38000</v>
+      </c>
+      <c r="K840" s="14">
+        <v>40000</v>
+      </c>
+      <c r="L840" s="14">
+        <v>46000</v>
+      </c>
+      <c r="M840" s="14">
+        <v>57000</v>
+      </c>
+      <c r="N840" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O840" s="14">
+        <v>79000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -22559,7 +22595,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22570,12 +22606,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -22583,7 +22619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2EDF21-9692-B94B-9178-FB6CB825DE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BC0B5E-01DC-E242-8C16-1E71DC094E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20680" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
     <sheet name="fig" sheetId="3" r:id="rId2"/>
     <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2811,6 +2811,9 @@
                 <c:pt idx="838">
                   <c:v>46248</c:v>
                 </c:pt>
+                <c:pt idx="839">
+                  <c:v>46255</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4759,7 +4762,7 @@
                   <c:v>2190.9899999999998</c:v>
                 </c:pt>
                 <c:pt idx="813">
-                  <c:v>2206</c:v>
+                  <c:v>2205.9</c:v>
                 </c:pt>
                 <c:pt idx="814">
                   <c:v>2213</c:v>
@@ -4835,6 +4838,9 @@
                 </c:pt>
                 <c:pt idx="838">
                   <c:v>2346.0500000000002</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>2380.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5650,9 +5656,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5690,7 +5696,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5796,7 +5802,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5938,7 +5944,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5946,7 +5952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P840"/>
+  <dimension ref="A1:P841"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -21392,7 +21398,7 @@
         <v>UTC+1</v>
       </c>
       <c r="E815" s="12">
-        <v>2206</v>
+        <v>2205.9</v>
       </c>
       <c r="F815" s="15">
         <v>10750</v>
@@ -22542,7 +22548,7 @@
         <v>0.66666666666667596</v>
       </c>
       <c r="D840" s="8" t="str">
-        <f t="shared" ref="D840" si="15">"UTC+"&amp;IF(
+        <f t="shared" ref="D840:D841" si="15">"UTC+"&amp;IF(
     AND(
         B840&gt;=EOMONTH(DATE(YEAR(B840),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B840),3,1),0),2),7),
         B840&lt;EOMONTH(DATE(YEAR(B840),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B840),10,1),0),2),7)
@@ -22583,6 +22589,54 @@
         <v>72000</v>
       </c>
       <c r="O840" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="841" spans="1:15">
+      <c r="A841" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B841" s="8">
+        <v>46255</v>
+      </c>
+      <c r="C841" s="9">
+        <v>0.66666666666665497</v>
+      </c>
+      <c r="D841" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E841" s="10">
+        <v>2380.35</v>
+      </c>
+      <c r="F841" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G841" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H841" s="14">
+        <v>32500</v>
+      </c>
+      <c r="I841" s="14">
+        <v>35500</v>
+      </c>
+      <c r="J841" s="14">
+        <v>40000</v>
+      </c>
+      <c r="K841" s="14">
+        <v>42000</v>
+      </c>
+      <c r="L841" s="14">
+        <v>47000</v>
+      </c>
+      <c r="M841" s="14">
+        <v>57000</v>
+      </c>
+      <c r="N841" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O841" s="14">
         <v>79000</v>
       </c>
     </row>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BC0B5E-01DC-E242-8C16-1E71DC094E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CFF203-5F7E-5149-8500-29C72E86C811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20680" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="fig" sheetId="3" r:id="rId2"/>
     <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -2814,6 +2816,9 @@
                 <c:pt idx="839">
                   <c:v>46255</c:v>
                 </c:pt>
+                <c:pt idx="840">
+                  <c:v>46262</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4841,6 +4846,9 @@
                 </c:pt>
                 <c:pt idx="839">
                   <c:v>2380.35</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>2413.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5656,9 +5664,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5696,7 +5704,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5802,7 +5810,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5944,7 +5952,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5952,7 +5960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P841"/>
+  <dimension ref="A1:P842"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -22548,7 +22556,7 @@
         <v>0.66666666666667596</v>
       </c>
       <c r="D840" s="8" t="str">
-        <f t="shared" ref="D840:D841" si="15">"UTC+"&amp;IF(
+        <f t="shared" ref="D840:D842" si="15">"UTC+"&amp;IF(
     AND(
         B840&gt;=EOMONTH(DATE(YEAR(B840),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B840),3,1),0),2),7),
         B840&lt;EOMONTH(DATE(YEAR(B840),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B840),10,1),0),2),7)
@@ -22637,6 +22645,54 @@
         <v>72000</v>
       </c>
       <c r="O841" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="842" spans="1:15">
+      <c r="A842" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B842" s="8">
+        <v>46262</v>
+      </c>
+      <c r="C842" s="9">
+        <v>0.66666666666669805</v>
+      </c>
+      <c r="D842" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E842" s="10">
+        <v>2413.15</v>
+      </c>
+      <c r="F842" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G842" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H842" s="14">
+        <v>33000</v>
+      </c>
+      <c r="I842" s="14">
+        <v>36000</v>
+      </c>
+      <c r="J842" s="14">
+        <v>42000</v>
+      </c>
+      <c r="K842" s="14">
+        <v>44000</v>
+      </c>
+      <c r="L842" s="14">
+        <v>48000</v>
+      </c>
+      <c r="M842" s="14">
+        <v>57000</v>
+      </c>
+      <c r="N842" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O842" s="14">
         <v>79000</v>
       </c>
     </row>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CFF203-5F7E-5149-8500-29C72E86C811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C11894F-27BC-2748-B7E4-9348EE0E24DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20680" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
@@ -2819,6 +2819,9 @@
                 <c:pt idx="840">
                   <c:v>46262</c:v>
                 </c:pt>
+                <c:pt idx="841">
+                  <c:v>46269</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4849,6 +4852,9 @@
                 </c:pt>
                 <c:pt idx="840">
                   <c:v>2413.15</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>2442.9699999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5960,7 +5966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P842"/>
+  <dimension ref="A1:P843"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -22693,6 +22699,61 @@
         <v>72000</v>
       </c>
       <c r="O842" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="843" spans="1:15">
+      <c r="A843" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B843" s="8">
+        <v>46269</v>
+      </c>
+      <c r="C843" s="9">
+        <v>0.66666666666661301</v>
+      </c>
+      <c r="D843" s="8" t="str">
+        <f t="shared" ref="D843" si="16">"UTC+"&amp;IF(
+    AND(
+        B843&gt;=EOMONTH(DATE(YEAR(B843),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B843),3,1),0),2),7),
+        B843&lt;EOMONTH(DATE(YEAR(B843),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B843),10,1),0),2),7)
+    ),
+    2,
+    1
+)</f>
+        <v>UTC+2</v>
+      </c>
+      <c r="E843" s="10">
+        <v>2442.9699999999998</v>
+      </c>
+      <c r="F843" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G843" s="14">
+        <v>17750</v>
+      </c>
+      <c r="H843" s="14">
+        <v>34000</v>
+      </c>
+      <c r="I843" s="14">
+        <v>37000</v>
+      </c>
+      <c r="J843" s="14">
+        <v>43000</v>
+      </c>
+      <c r="K843" s="14">
+        <v>45000</v>
+      </c>
+      <c r="L843" s="14">
+        <v>49000</v>
+      </c>
+      <c r="M843" s="14">
+        <v>58000</v>
+      </c>
+      <c r="N843" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O843" s="14">
         <v>79000</v>
       </c>
     </row>
